--- a/2026/EL MIRADOR/Agosto/Agosto - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Agosto/Agosto - EL MIRADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E358DAA-EB69-4418-AB5B-3FD69562ADB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C477E8-B334-483B-BB06-7E08B931DCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -24,11 +24,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$127</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1961,7 +1956,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="383">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2297,9 +2292,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2332,6 +2324,24 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2444,53 +2454,14 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2509,6 +2480,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2579,6 +2559,21 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="23" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2607,9 +2602,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2732,9 +2724,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2772,9 +2764,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2807,26 +2799,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2859,26 +2834,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3053,24 +3011,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N142"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="68"/>
       <c r="B1" s="76"/>
       <c r="C1" s="81" t="s">
@@ -3084,7 +3042,7 @@
       <c r="I1" s="66"/>
       <c r="J1" s="67"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="69"/>
       <c r="B2" s="77"/>
       <c r="C2" s="77" t="s">
@@ -3098,7 +3056,7 @@
       <c r="I2" s="78"/>
       <c r="J2" s="65"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="69"/>
       <c r="B3" s="77"/>
       <c r="C3" s="77" t="s">
@@ -3114,7 +3072,7 @@
       <c r="I3" s="78"/>
       <c r="J3" s="65"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="69"/>
       <c r="B4" s="77"/>
       <c r="C4" s="77" t="s">
@@ -3128,7 +3086,7 @@
       <c r="I4" s="78"/>
       <c r="J4" s="65"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="72"/>
       <c r="B5" s="77"/>
       <c r="C5" s="77" t="s">
@@ -3144,7 +3102,7 @@
       <c r="I5" s="77"/>
       <c r="J5" s="73"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="72"/>
       <c r="B6" s="77"/>
       <c r="C6" s="77" t="s">
@@ -3158,7 +3116,7 @@
       <c r="I6" s="77"/>
       <c r="J6" s="73"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="74"/>
       <c r="B7" s="75"/>
       <c r="C7" s="75"/>
@@ -3170,115 +3128,115 @@
       <c r="I7" s="75"/>
       <c r="J7" s="79"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="314" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="276" t="s">
         <v>243</v>
       </c>
-      <c r="B14" s="314"/>
-      <c r="C14" s="314"/>
-      <c r="D14" s="314"/>
-      <c r="E14" s="314"/>
-      <c r="F14" s="314"/>
-      <c r="G14" s="314"/>
-      <c r="H14" s="314"/>
-      <c r="I14" s="314"/>
-      <c r="J14" s="314"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="314"/>
-      <c r="B15" s="314"/>
-      <c r="C15" s="314"/>
-      <c r="D15" s="314"/>
-      <c r="E15" s="314"/>
-      <c r="F15" s="314"/>
-      <c r="G15" s="314"/>
-      <c r="H15" s="314"/>
-      <c r="I15" s="314"/>
-      <c r="J15" s="314"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="314"/>
-      <c r="B16" s="314"/>
-      <c r="C16" s="314"/>
-      <c r="D16" s="314"/>
-      <c r="E16" s="314"/>
-      <c r="F16" s="314"/>
-      <c r="G16" s="314"/>
-      <c r="H16" s="314"/>
-      <c r="I16" s="314"/>
-      <c r="J16" s="314"/>
-    </row>
-    <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="314"/>
-      <c r="B17" s="314"/>
-      <c r="C17" s="314"/>
-      <c r="D17" s="314"/>
-      <c r="E17" s="314"/>
-      <c r="F17" s="314"/>
-      <c r="G17" s="314"/>
-      <c r="H17" s="314"/>
-      <c r="I17" s="314"/>
-      <c r="J17" s="314"/>
-    </row>
-    <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="314"/>
-      <c r="B18" s="314"/>
-      <c r="C18" s="314"/>
-      <c r="D18" s="314"/>
-      <c r="E18" s="314"/>
-      <c r="F18" s="314"/>
-      <c r="G18" s="314"/>
-      <c r="H18" s="314"/>
-      <c r="I18" s="314"/>
-      <c r="J18" s="314"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="276"/>
+      <c r="C14" s="276"/>
+      <c r="D14" s="276"/>
+      <c r="E14" s="276"/>
+      <c r="F14" s="276"/>
+      <c r="G14" s="276"/>
+      <c r="H14" s="276"/>
+      <c r="I14" s="276"/>
+      <c r="J14" s="276"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="276"/>
+      <c r="B15" s="276"/>
+      <c r="C15" s="276"/>
+      <c r="D15" s="276"/>
+      <c r="E15" s="276"/>
+      <c r="F15" s="276"/>
+      <c r="G15" s="276"/>
+      <c r="H15" s="276"/>
+      <c r="I15" s="276"/>
+      <c r="J15" s="276"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="276"/>
+      <c r="B16" s="276"/>
+      <c r="C16" s="276"/>
+      <c r="D16" s="276"/>
+      <c r="E16" s="276"/>
+      <c r="F16" s="276"/>
+      <c r="G16" s="276"/>
+      <c r="H16" s="276"/>
+      <c r="I16" s="276"/>
+      <c r="J16" s="276"/>
+    </row>
+    <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="276"/>
+      <c r="B17" s="276"/>
+      <c r="C17" s="276"/>
+      <c r="D17" s="276"/>
+      <c r="E17" s="276"/>
+      <c r="F17" s="276"/>
+      <c r="G17" s="276"/>
+      <c r="H17" s="276"/>
+      <c r="I17" s="276"/>
+      <c r="J17" s="276"/>
+    </row>
+    <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="276"/>
+      <c r="B18" s="276"/>
+      <c r="C18" s="276"/>
+      <c r="D18" s="276"/>
+      <c r="E18" s="276"/>
+      <c r="F18" s="276"/>
+      <c r="G18" s="276"/>
+      <c r="H18" s="276"/>
+      <c r="I18" s="276"/>
+      <c r="J18" s="276"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="H19" s="60"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="315" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="277" t="s">
         <v>381</v>
       </c>
-      <c r="B20" s="315"/>
-      <c r="C20" s="315"/>
-      <c r="D20" s="315"/>
-      <c r="E20" s="315"/>
-      <c r="F20" s="315"/>
-      <c r="G20" s="315"/>
-      <c r="H20" s="315"/>
-      <c r="I20" s="315"/>
-      <c r="J20" s="315"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="315"/>
-      <c r="B21" s="315"/>
-      <c r="C21" s="315"/>
-      <c r="D21" s="315"/>
-      <c r="E21" s="315"/>
-      <c r="F21" s="315"/>
-      <c r="G21" s="315"/>
-      <c r="H21" s="315"/>
-      <c r="I21" s="315"/>
-      <c r="J21" s="315"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="315"/>
-      <c r="B22" s="315"/>
-      <c r="C22" s="315"/>
-      <c r="D22" s="315"/>
-      <c r="E22" s="315"/>
-      <c r="F22" s="315"/>
-      <c r="G22" s="315"/>
-      <c r="H22" s="315"/>
-      <c r="I22" s="315"/>
-      <c r="J22" s="315"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="277"/>
+      <c r="C20" s="277"/>
+      <c r="D20" s="277"/>
+      <c r="E20" s="277"/>
+      <c r="F20" s="277"/>
+      <c r="G20" s="277"/>
+      <c r="H20" s="277"/>
+      <c r="I20" s="277"/>
+      <c r="J20" s="277"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="277"/>
+      <c r="B21" s="277"/>
+      <c r="C21" s="277"/>
+      <c r="D21" s="277"/>
+      <c r="E21" s="277"/>
+      <c r="F21" s="277"/>
+      <c r="G21" s="277"/>
+      <c r="H21" s="277"/>
+      <c r="I21" s="277"/>
+      <c r="J21" s="277"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="277"/>
+      <c r="B22" s="277"/>
+      <c r="C22" s="277"/>
+      <c r="D22" s="277"/>
+      <c r="E22" s="277"/>
+      <c r="F22" s="277"/>
+      <c r="G22" s="277"/>
+      <c r="H22" s="277"/>
+      <c r="I22" s="277"/>
+      <c r="J22" s="277"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="56"/>
       <c r="B23" s="56"/>
       <c r="C23" s="56"/>
@@ -3286,11 +3244,11 @@
       <c r="E23" s="56"/>
       <c r="F23" s="56"/>
       <c r="G23" s="56"/>
-      <c r="H23" s="265"/>
+      <c r="H23" s="264"/>
       <c r="I23" s="56"/>
       <c r="J23" s="56"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="180" t="s">
         <v>18</v>
       </c>
@@ -3312,11 +3270,11 @@
       <c r="I24" s="184" t="s">
         <v>168</v>
       </c>
-      <c r="J24" s="266" t="s">
+      <c r="J24" s="265" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="185" t="s">
         <v>335</v>
       </c>
@@ -3331,7 +3289,7 @@
       <c r="J25" s="186"/>
       <c r="L25" s="43"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="187" t="s">
         <v>359</v>
       </c>
@@ -3352,7 +3310,7 @@
       <c r="J26" s="157"/>
       <c r="L26" s="43"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="188" t="s">
         <v>35</v>
       </c>
@@ -3395,7 +3353,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="187" t="s">
         <v>232</v>
       </c>
@@ -3410,7 +3368,7 @@
       <c r="J28" s="186"/>
       <c r="L28" s="43"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="187"/>
       <c r="B29" s="157"/>
       <c r="C29" s="157"/>
@@ -3423,7 +3381,7 @@
       <c r="J29" s="186"/>
       <c r="L29" s="43"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="188" t="s">
         <v>16</v>
       </c>
@@ -3441,7 +3399,7 @@
       <c r="G30" s="30"/>
       <c r="H30" s="30"/>
       <c r="I30" s="30"/>
-      <c r="J30" s="267"/>
+      <c r="J30" s="266"/>
       <c r="K30" s="31">
         <f>E30+J30+F30+G30+H30+I30</f>
         <v>0</v>
@@ -3451,7 +3409,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="187" t="s">
         <v>228</v>
       </c>
@@ -3466,7 +3424,7 @@
       <c r="J31" s="190"/>
       <c r="L31" s="43"/>
     </row>
-    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="119" t="s">
         <v>351</v>
       </c>
@@ -3487,7 +3445,7 @@
       <c r="J32" s="190"/>
       <c r="L32" s="43"/>
     </row>
-    <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="119" t="s">
         <v>231</v>
       </c>
@@ -3508,7 +3466,7 @@
       <c r="J33" s="190"/>
       <c r="L33" s="43"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="119"/>
       <c r="B34" s="119"/>
       <c r="C34" s="119"/>
@@ -3521,7 +3479,7 @@
       <c r="J34" s="190"/>
       <c r="L34" s="43"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="188" t="s">
         <v>230</v>
       </c>
@@ -3564,7 +3522,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="187" t="s">
         <v>1</v>
       </c>
@@ -3579,7 +3537,7 @@
       <c r="J36" s="157"/>
       <c r="L36" s="43"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="157"/>
       <c r="B37" s="157"/>
       <c r="C37" s="157"/>
@@ -3592,7 +3550,7 @@
       <c r="J37" s="157"/>
       <c r="L37" s="43"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="157"/>
       <c r="B38" s="157"/>
       <c r="C38" s="157"/>
@@ -3605,7 +3563,7 @@
       <c r="J38" s="157"/>
       <c r="L38" s="43"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="157"/>
       <c r="B39" s="157"/>
       <c r="C39" s="193"/>
@@ -3618,7 +3576,7 @@
       <c r="J39" s="157"/>
       <c r="L39" s="43"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="188" t="s">
         <v>229</v>
       </c>
@@ -3661,7 +3619,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="187" t="s">
         <v>221</v>
       </c>
@@ -3673,10 +3631,10 @@
       <c r="G41" s="195"/>
       <c r="H41" s="195"/>
       <c r="I41" s="195"/>
-      <c r="J41" s="268"/>
+      <c r="J41" s="267"/>
       <c r="L41" s="43"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="157" t="s">
         <v>225</v>
       </c>
@@ -3717,9 +3675,9 @@
       </c>
       <c r="L42" s="43"/>
     </row>
-    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="316"/>
-      <c r="B43" s="317"/>
+    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="278"/>
+      <c r="B43" s="279"/>
       <c r="C43" s="157"/>
       <c r="D43" s="32"/>
       <c r="E43" s="186"/>
@@ -3731,7 +3689,7 @@
       <c r="K43" s="31"/>
       <c r="L43" s="43"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="188" t="s">
         <v>2</v>
       </c>
@@ -3774,7 +3732,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="187" t="s">
         <v>3</v>
       </c>
@@ -3789,7 +3747,7 @@
       <c r="J45" s="157"/>
       <c r="L45" s="43"/>
     </row>
-    <row r="46" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="197" t="s">
         <v>371</v>
       </c>
@@ -3797,7 +3755,7 @@
       <c r="C46" s="240" t="s">
         <v>390</v>
       </c>
-      <c r="D46" s="269">
+      <c r="D46" s="268">
         <v>209128.04</v>
       </c>
       <c r="E46" s="198">
@@ -3835,7 +3793,7 @@
       <c r="M46" s="55"/>
       <c r="N46" s="55"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="157" t="s">
         <v>226</v>
       </c>
@@ -3843,7 +3801,7 @@
       <c r="C47" s="240" t="s">
         <v>397</v>
       </c>
-      <c r="D47" s="269">
+      <c r="D47" s="268">
         <v>6120722.7199999997</v>
       </c>
       <c r="E47" s="198">
@@ -3881,7 +3839,7 @@
       <c r="M47" s="55"/>
       <c r="N47" s="55"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="157" t="s">
         <v>227</v>
       </c>
@@ -3918,7 +3876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="197" t="s">
         <v>385</v>
       </c>
@@ -3949,11 +3907,11 @@
       <c r="M49" s="55"/>
       <c r="N49" s="55"/>
     </row>
-    <row r="50" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="275" t="s">
+    <row r="50" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="274" t="s">
         <v>386</v>
       </c>
-      <c r="B50" s="276"/>
+      <c r="B50" s="275"/>
       <c r="C50" s="240" t="s">
         <v>398</v>
       </c>
@@ -3986,11 +3944,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="119" t="s">
         <v>257</v>
       </c>
-      <c r="B51" s="253"/>
+      <c r="B51" s="220"/>
       <c r="C51" s="240" t="s">
         <v>401</v>
       </c>
@@ -4017,7 +3975,7 @@
       <c r="M51" s="55"/>
       <c r="N51" s="55"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="119" t="s">
         <v>258</v>
       </c>
@@ -4069,7 +4027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="199" t="s">
         <v>256</v>
       </c>
@@ -4102,7 +4060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="188" t="s">
         <v>4</v>
       </c>
@@ -4149,7 +4107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="157"/>
       <c r="B55" s="157"/>
       <c r="C55" s="157"/>
@@ -4162,7 +4120,7 @@
       <c r="J55" s="157"/>
       <c r="L55" s="43"/>
     </row>
-    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="157"/>
       <c r="B56" s="157"/>
       <c r="C56" s="157"/>
@@ -4175,7 +4133,7 @@
       <c r="J56" s="157"/>
       <c r="L56" s="43"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="187" t="s">
         <v>222</v>
       </c>
@@ -4190,7 +4148,7 @@
       <c r="J57" s="157"/>
       <c r="L57" s="43"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="191" t="s">
         <v>334</v>
       </c>
@@ -4219,11 +4177,11 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="318" t="s">
+    <row r="59" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="280" t="s">
         <v>396</v>
       </c>
-      <c r="B59" s="319"/>
+      <c r="B59" s="281"/>
       <c r="C59" s="119" t="s">
         <v>395</v>
       </c>
@@ -4263,11 +4221,11 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="318" t="s">
+    <row r="60" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="280" t="s">
         <v>394</v>
       </c>
-      <c r="B60" s="319"/>
+      <c r="B60" s="281"/>
       <c r="C60" s="119" t="s">
         <v>395</v>
       </c>
@@ -4307,11 +4265,11 @@
         <v>95700</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="275" t="s">
+    <row r="61" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="274" t="s">
         <v>403</v>
       </c>
-      <c r="B61" s="276"/>
+      <c r="B61" s="275"/>
       <c r="C61" s="119" t="s">
         <v>397</v>
       </c>
@@ -4351,11 +4309,11 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="239" t="s">
         <v>404</v>
       </c>
-      <c r="B62" s="253"/>
+      <c r="B62" s="220"/>
       <c r="C62" s="119" t="s">
         <v>397</v>
       </c>
@@ -4395,11 +4353,11 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="275" t="s">
+    <row r="63" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="274" t="s">
         <v>405</v>
       </c>
-      <c r="B63" s="276"/>
+      <c r="B63" s="275"/>
       <c r="C63" s="240" t="s">
         <v>390</v>
       </c>
@@ -4424,11 +4382,11 @@
         <v>550000</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="275" t="s">
+    <row r="64" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="274" t="s">
         <v>391</v>
       </c>
-      <c r="B64" s="276"/>
+      <c r="B64" s="275"/>
       <c r="C64" s="240" t="s">
         <v>390</v>
       </c>
@@ -4468,11 +4426,11 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="275" t="s">
+    <row r="65" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="274" t="s">
         <v>400</v>
       </c>
-      <c r="B65" s="276"/>
+      <c r="B65" s="275"/>
       <c r="C65" s="240" t="s">
         <v>399</v>
       </c>
@@ -4512,11 +4470,11 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="254" t="s">
+    <row r="66" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="253" t="s">
         <v>370</v>
       </c>
-      <c r="B66" s="255"/>
+      <c r="B66" s="254"/>
       <c r="C66" s="240" t="s">
         <v>390</v>
       </c>
@@ -4556,7 +4514,7 @@
         <v>392015.8</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="188" t="s">
         <v>223</v>
       </c>
@@ -4601,7 +4559,7 @@
       <c r="M67" s="31"/>
       <c r="N67" s="31"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="187" t="s">
         <v>5</v>
       </c>
@@ -4616,7 +4574,7 @@
       <c r="J68" s="157"/>
       <c r="L68" s="43"/>
     </row>
-    <row r="69" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="202" t="s">
         <v>6</v>
       </c>
@@ -4658,12 +4616,12 @@
         <v>372</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="277" t="s">
+    <row r="70" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="282" t="s">
         <v>406</v>
       </c>
-      <c r="B70" s="278"/>
-      <c r="C70" s="279"/>
+      <c r="B70" s="283"/>
+      <c r="C70" s="284"/>
       <c r="D70" s="32">
         <v>0</v>
       </c>
@@ -4694,7 +4652,7 @@
       <c r="L70" s="43"/>
       <c r="N70" s="32"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="157"/>
       <c r="B71" s="157"/>
       <c r="C71" s="157"/>
@@ -4708,7 +4666,7 @@
       <c r="L71" s="43"/>
       <c r="N71" s="31"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="188" t="s">
         <v>7</v>
       </c>
@@ -4752,7 +4710,7 @@
       </c>
       <c r="N72" s="31"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="157" t="s">
         <v>26</v>
       </c>
@@ -4787,7 +4745,7 @@
       </c>
       <c r="L73" s="43"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="157" t="s">
         <v>27</v>
       </c>
@@ -4822,7 +4780,7 @@
       </c>
       <c r="L74" s="43"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="188" t="s">
         <v>224</v>
       </c>
@@ -4865,7 +4823,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="61"/>
       <c r="B76" s="61"/>
       <c r="C76" s="61"/>
@@ -4878,12 +4836,12 @@
       <c r="J76" s="61"/>
       <c r="L76" s="43"/>
     </row>
-    <row r="77" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="311" t="s">
+    <row r="77" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="316" t="s">
         <v>412</v>
       </c>
-      <c r="B77" s="312"/>
-      <c r="C77" s="313"/>
+      <c r="B77" s="317"/>
+      <c r="C77" s="318"/>
       <c r="D77" s="62">
         <f>24275955.4-15214817.97+1950000</f>
         <v>11011137.429999998</v>
@@ -4908,7 +4866,7 @@
         <f>$D77*1.49%</f>
         <v>164065.94770699996</v>
       </c>
-      <c r="J77" s="270">
+      <c r="J77" s="269">
         <f>D77*1.74%</f>
         <v>191593.79128199996</v>
       </c>
@@ -4921,7 +4879,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="207"/>
       <c r="B78" s="208"/>
       <c r="C78" s="208"/>
@@ -4931,11 +4889,11 @@
       <c r="G78" s="63"/>
       <c r="H78" s="63"/>
       <c r="I78" s="63"/>
-      <c r="J78" s="271"/>
+      <c r="J78" s="270"/>
       <c r="K78" s="31"/>
       <c r="L78" s="43"/>
     </row>
-    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="209" t="s">
         <v>28</v>
       </c>
@@ -4982,7 +4940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="56"/>
       <c r="B80" s="56"/>
       <c r="C80" s="56"/>
@@ -4994,7 +4952,7 @@
       <c r="I80" s="212"/>
       <c r="J80" s="56"/>
     </row>
-    <row r="81" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="213" t="s">
         <v>36</v>
       </c>
@@ -5008,12 +4966,12 @@
       <c r="I81" s="212"/>
       <c r="J81" s="56"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="215" t="s">
         <v>392</v>
       </c>
       <c r="B82" s="56"/>
-      <c r="C82" s="272">
+      <c r="C82" s="271">
         <v>300000</v>
       </c>
       <c r="D82" s="56"/>
@@ -5024,12 +4982,12 @@
       <c r="I82" s="212"/>
       <c r="J82" s="56"/>
     </row>
-    <row r="83" spans="1:13" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="215" t="s">
         <v>393</v>
       </c>
       <c r="B83" s="56"/>
-      <c r="C83" s="272">
+      <c r="C83" s="271">
         <v>106464</v>
       </c>
       <c r="D83" s="212"/>
@@ -5040,7 +4998,7 @@
       <c r="I83" s="212"/>
       <c r="J83" s="56"/>
     </row>
-    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="216" t="s">
         <v>16</v>
       </c>
@@ -5057,7 +5015,7 @@
       <c r="I84" s="212"/>
       <c r="J84" s="56"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="56"/>
       <c r="B85" s="56"/>
       <c r="C85" s="56"/>
@@ -5068,7 +5026,7 @@
       <c r="H85" s="31"/>
       <c r="I85" s="31"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="56"/>
       <c r="B86" s="56"/>
       <c r="C86" s="56"/>
@@ -5079,13 +5037,13 @@
       <c r="H86" s="40"/>
       <c r="I86" s="40"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="298" t="s">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="303" t="s">
         <v>32</v>
       </c>
-      <c r="B87" s="299"/>
-      <c r="C87" s="299"/>
-      <c r="D87" s="299"/>
+      <c r="B87" s="304"/>
+      <c r="C87" s="304"/>
+      <c r="D87" s="304"/>
       <c r="E87" s="51" t="s">
         <v>10</v>
       </c>
@@ -5105,9 +5063,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="275"/>
-      <c r="B88" s="280"/>
+    <row r="88" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="274"/>
+      <c r="B88" s="285"/>
       <c r="C88" s="220"/>
       <c r="D88" s="32"/>
       <c r="E88" s="198">
@@ -5120,9 +5078,9 @@
       <c r="I88" s="42"/>
       <c r="J88" s="38"/>
     </row>
-    <row r="89" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="300"/>
-      <c r="B89" s="301"/>
+    <row r="89" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="305"/>
+      <c r="B89" s="306"/>
       <c r="C89" s="53"/>
       <c r="D89" s="32"/>
       <c r="E89" s="42"/>
@@ -5132,12 +5090,12 @@
       <c r="I89" s="42"/>
       <c r="J89" s="38"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="295" t="s">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="300" t="s">
         <v>16</v>
       </c>
-      <c r="B90" s="296"/>
-      <c r="C90" s="297"/>
+      <c r="B90" s="301"/>
+      <c r="C90" s="302"/>
       <c r="D90" s="50">
         <f>SUM(D88:D89)</f>
         <v>0</v>
@@ -5163,14 +5121,14 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E92" s="31"/>
       <c r="F92" s="31"/>
       <c r="G92" s="31"/>
       <c r="H92" s="31"/>
       <c r="I92" s="31"/>
     </row>
-    <row r="93" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="26" t="s">
         <v>29</v>
       </c>
@@ -5179,7 +5137,7 @@
         <v>26225955.399999999</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="28" t="s">
         <v>31</v>
       </c>
@@ -5187,45 +5145,45 @@
         <f>D79-D77</f>
         <v>15214817.970000001</v>
       </c>
-      <c r="D94" s="281" t="s">
+      <c r="D94" s="286" t="s">
         <v>373</v>
       </c>
-      <c r="E94" s="281"/>
-      <c r="F94" s="281"/>
-      <c r="G94" s="281"/>
-      <c r="H94" s="281"/>
-      <c r="I94" s="281"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D95" s="281"/>
-      <c r="E95" s="281"/>
-      <c r="F95" s="281"/>
-      <c r="G95" s="281"/>
-      <c r="H95" s="281"/>
-      <c r="I95" s="281"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D96" s="281"/>
-      <c r="E96" s="281"/>
-      <c r="F96" s="281"/>
-      <c r="G96" s="281"/>
-      <c r="H96" s="281"/>
-      <c r="I96" s="281"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E94" s="286"/>
+      <c r="F94" s="286"/>
+      <c r="G94" s="286"/>
+      <c r="H94" s="286"/>
+      <c r="I94" s="286"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D95" s="286"/>
+      <c r="E95" s="286"/>
+      <c r="F95" s="286"/>
+      <c r="G95" s="286"/>
+      <c r="H95" s="286"/>
+      <c r="I95" s="286"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D96" s="286"/>
+      <c r="E96" s="286"/>
+      <c r="F96" s="286"/>
+      <c r="G96" s="286"/>
+      <c r="H96" s="286"/>
+      <c r="I96" s="286"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
         <v>409</v>
       </c>
       <c r="B97" s="8"/>
       <c r="C97" s="9"/>
-      <c r="D97" s="281"/>
-      <c r="E97" s="281"/>
-      <c r="F97" s="281"/>
-      <c r="G97" s="281"/>
-      <c r="H97" s="281"/>
-      <c r="I97" s="281"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D97" s="286"/>
+      <c r="E97" s="286"/>
+      <c r="F97" s="286"/>
+      <c r="G97" s="286"/>
+      <c r="H97" s="286"/>
+      <c r="I97" s="286"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>20</v>
       </c>
@@ -5233,14 +5191,14 @@
         <v>1682660.59</v>
       </c>
       <c r="C98" s="11"/>
-      <c r="D98" s="281"/>
-      <c r="E98" s="281"/>
-      <c r="F98" s="281"/>
-      <c r="G98" s="281"/>
-      <c r="H98" s="281"/>
-      <c r="I98" s="281"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D98" s="286"/>
+      <c r="E98" s="286"/>
+      <c r="F98" s="286"/>
+      <c r="G98" s="286"/>
+      <c r="H98" s="286"/>
+      <c r="I98" s="286"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
         <v>21</v>
       </c>
@@ -5251,14 +5209,14 @@
       <c r="C99" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D99" s="281"/>
-      <c r="E99" s="281"/>
-      <c r="F99" s="281"/>
-      <c r="G99" s="281"/>
-      <c r="H99" s="281"/>
-      <c r="I99" s="281"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D99" s="286"/>
+      <c r="E99" s="286"/>
+      <c r="F99" s="286"/>
+      <c r="G99" s="286"/>
+      <c r="H99" s="286"/>
+      <c r="I99" s="286"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
         <v>338</v>
       </c>
@@ -5267,14 +5225,14 @@
         <v>0</v>
       </c>
       <c r="C100" s="11"/>
-      <c r="D100" s="281"/>
-      <c r="E100" s="281"/>
-      <c r="F100" s="281"/>
-      <c r="G100" s="281"/>
-      <c r="H100" s="281"/>
-      <c r="I100" s="281"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D100" s="286"/>
+      <c r="E100" s="286"/>
+      <c r="F100" s="286"/>
+      <c r="G100" s="286"/>
+      <c r="H100" s="286"/>
+      <c r="I100" s="286"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
         <v>34</v>
       </c>
@@ -5283,15 +5241,15 @@
         <v>-15214817.970000001</v>
       </c>
       <c r="C101" s="9"/>
-      <c r="D101" s="281"/>
-      <c r="E101" s="281"/>
-      <c r="F101" s="281"/>
-      <c r="G101" s="281"/>
-      <c r="H101" s="281"/>
-      <c r="I101" s="281"/>
+      <c r="D101" s="286"/>
+      <c r="E101" s="286"/>
+      <c r="F101" s="286"/>
+      <c r="G101" s="286"/>
+      <c r="H101" s="286"/>
+      <c r="I101" s="286"/>
       <c r="K101" s="32"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="12" t="s">
         <v>33</v>
       </c>
@@ -5300,15 +5258,15 @@
         <v>0</v>
       </c>
       <c r="C102" s="9"/>
-      <c r="D102" s="281"/>
-      <c r="E102" s="281"/>
-      <c r="F102" s="281"/>
-      <c r="G102" s="281"/>
-      <c r="H102" s="281"/>
-      <c r="I102" s="281"/>
+      <c r="D102" s="286"/>
+      <c r="E102" s="286"/>
+      <c r="F102" s="286"/>
+      <c r="G102" s="286"/>
+      <c r="H102" s="286"/>
+      <c r="I102" s="286"/>
       <c r="K102" s="33"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="12" t="s">
         <v>272</v>
       </c>
@@ -5317,15 +5275,15 @@
         <v>0</v>
       </c>
       <c r="C103" s="9"/>
-      <c r="D103" s="281"/>
-      <c r="E103" s="281"/>
-      <c r="F103" s="281"/>
-      <c r="G103" s="281"/>
-      <c r="H103" s="281"/>
-      <c r="I103" s="281"/>
+      <c r="D103" s="286"/>
+      <c r="E103" s="286"/>
+      <c r="F103" s="286"/>
+      <c r="G103" s="286"/>
+      <c r="H103" s="286"/>
+      <c r="I103" s="286"/>
       <c r="K103" s="33"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="12" t="s">
         <v>410</v>
       </c>
@@ -5333,15 +5291,15 @@
         <v>-141000</v>
       </c>
       <c r="C104" s="9"/>
-      <c r="D104" s="281"/>
-      <c r="E104" s="281"/>
-      <c r="F104" s="281"/>
-      <c r="G104" s="281"/>
-      <c r="H104" s="281"/>
-      <c r="I104" s="281"/>
+      <c r="D104" s="286"/>
+      <c r="E104" s="286"/>
+      <c r="F104" s="286"/>
+      <c r="G104" s="286"/>
+      <c r="H104" s="286"/>
+      <c r="I104" s="286"/>
       <c r="K104" s="33"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="12" t="s">
         <v>30</v>
       </c>
@@ -5350,14 +5308,14 @@
         <v>-20000</v>
       </c>
       <c r="C105" s="13"/>
-      <c r="D105" s="281"/>
-      <c r="E105" s="281"/>
-      <c r="F105" s="281"/>
-      <c r="G105" s="281"/>
-      <c r="H105" s="281"/>
-      <c r="I105" s="281"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D105" s="286"/>
+      <c r="E105" s="286"/>
+      <c r="F105" s="286"/>
+      <c r="G105" s="286"/>
+      <c r="H105" s="286"/>
+      <c r="I105" s="286"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="12" t="s">
         <v>36</v>
       </c>
@@ -5366,14 +5324,14 @@
         <v>-406464</v>
       </c>
       <c r="C106" s="13"/>
-      <c r="D106" s="281"/>
-      <c r="E106" s="281"/>
-      <c r="F106" s="281"/>
-      <c r="G106" s="281"/>
-      <c r="H106" s="281"/>
-      <c r="I106" s="281"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D106" s="286"/>
+      <c r="E106" s="286"/>
+      <c r="F106" s="286"/>
+      <c r="G106" s="286"/>
+      <c r="H106" s="286"/>
+      <c r="I106" s="286"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
         <v>23</v>
       </c>
@@ -5382,37 +5340,37 @@
         <v>2575051.7590119969</v>
       </c>
       <c r="C107" s="44"/>
-      <c r="D107" s="281"/>
-      <c r="E107" s="281"/>
-      <c r="F107" s="281"/>
-      <c r="G107" s="281"/>
-      <c r="H107" s="281"/>
-      <c r="I107" s="281"/>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D107" s="286"/>
+      <c r="E107" s="286"/>
+      <c r="F107" s="286"/>
+      <c r="G107" s="286"/>
+      <c r="H107" s="286"/>
+      <c r="I107" s="286"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="13"/>
       <c r="C108" s="9"/>
-      <c r="D108" s="281"/>
-      <c r="E108" s="281"/>
-      <c r="F108" s="281"/>
-      <c r="G108" s="281"/>
-      <c r="H108" s="281"/>
-      <c r="I108" s="281"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D108" s="286"/>
+      <c r="E108" s="286"/>
+      <c r="F108" s="286"/>
+      <c r="G108" s="286"/>
+      <c r="H108" s="286"/>
+      <c r="I108" s="286"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
         <v>271</v>
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="9"/>
-      <c r="D109" s="281"/>
-      <c r="E109" s="281"/>
-      <c r="F109" s="281"/>
-      <c r="G109" s="281"/>
-      <c r="H109" s="281"/>
-      <c r="I109" s="281"/>
-    </row>
-    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D109" s="286"/>
+      <c r="E109" s="286"/>
+      <c r="F109" s="286"/>
+      <c r="G109" s="286"/>
+      <c r="H109" s="286"/>
+      <c r="I109" s="286"/>
+    </row>
+    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="177"/>
       <c r="B110" s="21">
         <v>0</v>
@@ -5421,7 +5379,7 @@
       <c r="D110" s="16"/>
       <c r="E110" s="16"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="24" t="s">
         <v>16</v>
       </c>
@@ -5432,17 +5390,17 @@
       <c r="C111" s="9"/>
       <c r="E111" s="16"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="13"/>
       <c r="C112" s="9"/>
       <c r="D112" s="16"/>
     </row>
-    <row r="113" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="13"/>
       <c r="C113" s="9"/>
       <c r="D113" s="16"/>
     </row>
-    <row r="114" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="s">
         <v>19</v>
       </c>
@@ -5450,46 +5408,46 @@
         <v>-25817.72</v>
       </c>
       <c r="C114" s="9"/>
-      <c r="D114" s="302" t="s">
+      <c r="D114" s="307" t="s">
         <v>411</v>
       </c>
-      <c r="E114" s="303"/>
-      <c r="F114" s="303"/>
-      <c r="G114" s="303"/>
-      <c r="H114" s="303"/>
-      <c r="I114" s="304"/>
-    </row>
-    <row r="115" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E114" s="308"/>
+      <c r="F114" s="308"/>
+      <c r="G114" s="308"/>
+      <c r="H114" s="308"/>
+      <c r="I114" s="309"/>
+    </row>
+    <row r="115" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="179" t="s">
         <v>407</v>
       </c>
-      <c r="B115" s="256">
+      <c r="B115" s="255">
         <v>-24000</v>
       </c>
       <c r="C115" s="9"/>
-      <c r="D115" s="305"/>
-      <c r="E115" s="306"/>
-      <c r="F115" s="306"/>
-      <c r="G115" s="306"/>
-      <c r="H115" s="306"/>
-      <c r="I115" s="307"/>
-    </row>
-    <row r="116" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D115" s="310"/>
+      <c r="E115" s="311"/>
+      <c r="F115" s="311"/>
+      <c r="G115" s="311"/>
+      <c r="H115" s="311"/>
+      <c r="I115" s="312"/>
+    </row>
+    <row r="116" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="179" t="s">
         <v>408</v>
       </c>
-      <c r="B116" s="256">
+      <c r="B116" s="255">
         <v>-24000</v>
       </c>
       <c r="C116" s="9"/>
-      <c r="D116" s="305"/>
-      <c r="E116" s="306"/>
-      <c r="F116" s="306"/>
-      <c r="G116" s="306"/>
-      <c r="H116" s="306"/>
-      <c r="I116" s="307"/>
-    </row>
-    <row r="117" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D116" s="310"/>
+      <c r="E116" s="311"/>
+      <c r="F116" s="311"/>
+      <c r="G116" s="311"/>
+      <c r="H116" s="311"/>
+      <c r="I116" s="312"/>
+    </row>
+    <row r="117" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="24" t="s">
         <v>16</v>
       </c>
@@ -5498,31 +5456,31 @@
         <v>-73817.72</v>
       </c>
       <c r="C117" s="9"/>
-      <c r="D117" s="308"/>
-      <c r="E117" s="309"/>
-      <c r="F117" s="309"/>
-      <c r="G117" s="309"/>
-      <c r="H117" s="309"/>
-      <c r="I117" s="310"/>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D117" s="313"/>
+      <c r="E117" s="314"/>
+      <c r="F117" s="314"/>
+      <c r="G117" s="314"/>
+      <c r="H117" s="314"/>
+      <c r="I117" s="315"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="13"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="13"/>
       <c r="F119" s="46"/>
       <c r="G119" s="46"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="13"/>
       <c r="F120" s="46"/>
       <c r="G120" s="46"/>
     </row>
-    <row r="121" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H121" s="55"/>
       <c r="I121" s="55"/>
     </row>
-    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7" t="s">
         <v>355</v>
       </c>
@@ -5530,17 +5488,17 @@
         <v>578840</v>
       </c>
       <c r="C122" s="15"/>
-      <c r="D122" s="282" t="s">
+      <c r="D122" s="287" t="s">
         <v>388</v>
       </c>
-      <c r="E122" s="283"/>
-      <c r="F122" s="283"/>
-      <c r="G122" s="283"/>
-      <c r="H122" s="283"/>
-      <c r="I122" s="283"/>
-      <c r="J122" s="284"/>
-    </row>
-    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E122" s="288"/>
+      <c r="F122" s="288"/>
+      <c r="G122" s="288"/>
+      <c r="H122" s="288"/>
+      <c r="I122" s="288"/>
+      <c r="J122" s="289"/>
+    </row>
+    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="10" t="s">
         <v>238</v>
       </c>
@@ -5548,15 +5506,15 @@
         <v>20000</v>
       </c>
       <c r="C123" s="15"/>
-      <c r="D123" s="285"/>
-      <c r="E123" s="286"/>
-      <c r="F123" s="286"/>
-      <c r="G123" s="286"/>
-      <c r="H123" s="286"/>
-      <c r="I123" s="286"/>
-      <c r="J123" s="287"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D123" s="290"/>
+      <c r="E123" s="291"/>
+      <c r="F123" s="291"/>
+      <c r="G123" s="291"/>
+      <c r="H123" s="291"/>
+      <c r="I123" s="291"/>
+      <c r="J123" s="292"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="24" t="s">
         <v>16</v>
       </c>
@@ -5565,53 +5523,53 @@
         <v>598840</v>
       </c>
       <c r="C124" s="15"/>
-      <c r="D124" s="285"/>
-      <c r="E124" s="286"/>
-      <c r="F124" s="286"/>
-      <c r="G124" s="286"/>
-      <c r="H124" s="286"/>
-      <c r="I124" s="286"/>
-      <c r="J124" s="287"/>
-    </row>
-    <row r="125" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D124" s="290"/>
+      <c r="E124" s="291"/>
+      <c r="F124" s="291"/>
+      <c r="G124" s="291"/>
+      <c r="H124" s="291"/>
+      <c r="I124" s="291"/>
+      <c r="J124" s="292"/>
+    </row>
+    <row r="125" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C125" s="16"/>
-      <c r="D125" s="285"/>
-      <c r="E125" s="286"/>
-      <c r="F125" s="286"/>
-      <c r="G125" s="286"/>
-      <c r="H125" s="286"/>
-      <c r="I125" s="286"/>
-      <c r="J125" s="287"/>
-    </row>
-    <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="291" t="s">
+      <c r="D125" s="290"/>
+      <c r="E125" s="291"/>
+      <c r="F125" s="291"/>
+      <c r="G125" s="291"/>
+      <c r="H125" s="291"/>
+      <c r="I125" s="291"/>
+      <c r="J125" s="292"/>
+    </row>
+    <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="296" t="s">
         <v>356</v>
       </c>
-      <c r="B126" s="293">
+      <c r="B126" s="298">
         <f>B124+B107+B117</f>
         <v>3100074.0390119967</v>
       </c>
       <c r="C126" s="9"/>
-      <c r="D126" s="285"/>
-      <c r="E126" s="286"/>
-      <c r="F126" s="286"/>
-      <c r="G126" s="286"/>
-      <c r="H126" s="286"/>
-      <c r="I126" s="286"/>
-      <c r="J126" s="287"/>
-    </row>
-    <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="292"/>
-      <c r="B127" s="294"/>
-      <c r="D127" s="288"/>
-      <c r="E127" s="289"/>
-      <c r="F127" s="289"/>
-      <c r="G127" s="289"/>
-      <c r="H127" s="289"/>
-      <c r="I127" s="289"/>
-      <c r="J127" s="290"/>
-    </row>
-    <row r="132" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D126" s="290"/>
+      <c r="E126" s="291"/>
+      <c r="F126" s="291"/>
+      <c r="G126" s="291"/>
+      <c r="H126" s="291"/>
+      <c r="I126" s="291"/>
+      <c r="J126" s="292"/>
+    </row>
+    <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="297"/>
+      <c r="B127" s="299"/>
+      <c r="D127" s="293"/>
+      <c r="E127" s="294"/>
+      <c r="F127" s="294"/>
+      <c r="G127" s="294"/>
+      <c r="H127" s="294"/>
+      <c r="I127" s="294"/>
+      <c r="J127" s="295"/>
+    </row>
+    <row r="132" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C132" s="46"/>
       <c r="D132" s="46"/>
       <c r="E132" s="46"/>
@@ -5619,7 +5577,7 @@
       <c r="G132" s="46"/>
       <c r="H132" s="46"/>
     </row>
-    <row r="133" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C133" s="46"/>
       <c r="D133" s="46"/>
       <c r="E133" s="46"/>
@@ -5627,23 +5585,23 @@
       <c r="G133" s="46"/>
       <c r="H133" s="46"/>
     </row>
-    <row r="134" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C134" s="46"/>
-      <c r="D134" s="264"/>
+      <c r="D134" s="263"/>
       <c r="E134" s="46"/>
       <c r="F134" s="46"/>
       <c r="G134" s="46"/>
       <c r="H134" s="46"/>
     </row>
-    <row r="135" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C135" s="46"/>
-      <c r="D135" s="264"/>
+      <c r="D135" s="263"/>
       <c r="E135" s="46"/>
       <c r="F135" s="46"/>
       <c r="G135" s="46"/>
       <c r="H135" s="46"/>
     </row>
-    <row r="136" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C136" s="46"/>
       <c r="D136" s="46"/>
       <c r="E136" s="46"/>
@@ -5651,7 +5609,7 @@
       <c r="G136" s="46"/>
       <c r="H136" s="46"/>
     </row>
-    <row r="137" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C137" s="46"/>
       <c r="D137" s="46"/>
       <c r="E137" s="46"/>
@@ -5659,7 +5617,7 @@
       <c r="G137" s="46"/>
       <c r="H137" s="46"/>
     </row>
-    <row r="138" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C138" s="46"/>
       <c r="D138" s="46"/>
       <c r="E138" s="46"/>
@@ -5667,7 +5625,7 @@
       <c r="G138" s="46"/>
       <c r="H138" s="46"/>
     </row>
-    <row r="139" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C139" s="46"/>
       <c r="D139" s="46"/>
       <c r="E139" s="46"/>
@@ -5675,7 +5633,7 @@
       <c r="G139" s="46"/>
       <c r="H139" s="46"/>
     </row>
-    <row r="140" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C140" s="46"/>
       <c r="D140" s="46"/>
       <c r="E140" s="46"/>
@@ -5683,7 +5641,7 @@
       <c r="G140" s="46"/>
       <c r="H140" s="46"/>
     </row>
-    <row r="141" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C141" s="46"/>
       <c r="D141" s="46"/>
       <c r="E141" s="46"/>
@@ -5691,7 +5649,7 @@
       <c r="G141" s="46"/>
       <c r="H141" s="46"/>
     </row>
-    <row r="142" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C142" s="46"/>
       <c r="D142" s="46"/>
       <c r="E142" s="46"/>
@@ -5701,15 +5659,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A14:J18"/>
-    <mergeCell ref="A20:J22"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A65:B65"/>
     <mergeCell ref="A70:C70"/>
     <mergeCell ref="A88:B88"/>
@@ -5722,6 +5671,15 @@
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="D114:I117"/>
     <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A14:J18"/>
+    <mergeCell ref="A20:J22"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5732,37 +5690,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DJ155"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="353" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="348" t="s">
         <v>298</v>
       </c>
-      <c r="B1" s="354"/>
-      <c r="C1" s="354"/>
-      <c r="D1" s="354"/>
-      <c r="E1" s="354"/>
+      <c r="B1" s="349"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="349"/>
       <c r="F1" s="103" t="s">
         <v>274</v>
       </c>
@@ -5774,20 +5732,20 @@
       <c r="L1" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="332">
+      <c r="M1" s="324">
         <f>RESUMEN!D79-N4</f>
         <v>26225955.399999999</v>
       </c>
-      <c r="N1" s="333"/>
+      <c r="N1" s="325"/>
       <c r="O1" s="104"/>
       <c r="P1" s="39"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="355"/>
-      <c r="B2" s="356"/>
-      <c r="C2" s="356"/>
-      <c r="D2" s="356"/>
-      <c r="E2" s="356"/>
+    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="350"/>
+      <c r="B2" s="351"/>
+      <c r="C2" s="351"/>
+      <c r="D2" s="351"/>
+      <c r="E2" s="351"/>
       <c r="F2" s="4" t="s">
         <v>273</v>
       </c>
@@ -5801,18 +5759,18 @@
       </c>
       <c r="M2" s="133"/>
       <c r="N2" s="134">
-        <f>26189635.28</f>
-        <v>26189635.280000001</v>
+        <f>M1</f>
+        <v>26225955.399999999</v>
       </c>
       <c r="O2" s="105"/>
       <c r="P2" s="39"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="355"/>
-      <c r="B3" s="356"/>
-      <c r="C3" s="356"/>
-      <c r="D3" s="356"/>
-      <c r="E3" s="356"/>
+    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="350"/>
+      <c r="B3" s="351"/>
+      <c r="C3" s="351"/>
+      <c r="D3" s="351"/>
+      <c r="E3" s="351"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -5830,12 +5788,12 @@
       <c r="O3" s="105"/>
       <c r="P3" s="39"/>
     </row>
-    <row r="4" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="355"/>
-      <c r="B4" s="356"/>
-      <c r="C4" s="356"/>
-      <c r="D4" s="356"/>
-      <c r="E4" s="356"/>
+    <row r="4" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="350"/>
+      <c r="B4" s="351"/>
+      <c r="C4" s="351"/>
+      <c r="D4" s="351"/>
+      <c r="E4" s="351"/>
       <c r="F4" s="4" t="s">
         <v>275</v>
       </c>
@@ -5854,12 +5812,12 @@
       <c r="O4" s="107"/>
       <c r="P4" s="6"/>
     </row>
-    <row r="5" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="357"/>
-      <c r="B5" s="358"/>
-      <c r="C5" s="358"/>
-      <c r="D5" s="358"/>
-      <c r="E5" s="358"/>
+    <row r="5" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="352"/>
+      <c r="B5" s="353"/>
+      <c r="C5" s="353"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="353"/>
       <c r="F5" s="108"/>
       <c r="G5" s="108"/>
       <c r="H5" s="108"/>
@@ -5872,98 +5830,98 @@
       <c r="O5" s="111"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="338" t="s">
+      <c r="C6" s="333" t="s">
         <v>368</v>
       </c>
-      <c r="D6" s="339"/>
-      <c r="E6" s="339"/>
-      <c r="F6" s="339"/>
-      <c r="G6" s="339"/>
-      <c r="H6" s="339"/>
-      <c r="I6" s="339"/>
-      <c r="J6" s="339"/>
-      <c r="K6" s="339"/>
-      <c r="L6" s="339"/>
-      <c r="M6" s="339"/>
-      <c r="N6" s="339"/>
-      <c r="O6" s="340"/>
+      <c r="D6" s="334"/>
+      <c r="E6" s="334"/>
+      <c r="F6" s="334"/>
+      <c r="G6" s="334"/>
+      <c r="H6" s="334"/>
+      <c r="I6" s="334"/>
+      <c r="J6" s="334"/>
+      <c r="K6" s="334"/>
+      <c r="L6" s="334"/>
+      <c r="M6" s="334"/>
+      <c r="N6" s="334"/>
+      <c r="O6" s="335"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="341"/>
-      <c r="D7" s="342"/>
-      <c r="E7" s="342"/>
-      <c r="F7" s="342"/>
-      <c r="G7" s="342"/>
-      <c r="H7" s="342"/>
-      <c r="I7" s="342"/>
-      <c r="J7" s="342"/>
-      <c r="K7" s="342"/>
-      <c r="L7" s="342"/>
-      <c r="M7" s="342"/>
-      <c r="N7" s="342"/>
-      <c r="O7" s="343"/>
+      <c r="C7" s="336"/>
+      <c r="D7" s="337"/>
+      <c r="E7" s="337"/>
+      <c r="F7" s="337"/>
+      <c r="G7" s="337"/>
+      <c r="H7" s="337"/>
+      <c r="I7" s="337"/>
+      <c r="J7" s="337"/>
+      <c r="K7" s="337"/>
+      <c r="L7" s="337"/>
+      <c r="M7" s="337"/>
+      <c r="N7" s="337"/>
+      <c r="O7" s="338"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="341"/>
-      <c r="D8" s="342"/>
-      <c r="E8" s="342"/>
-      <c r="F8" s="342"/>
-      <c r="G8" s="342"/>
-      <c r="H8" s="342"/>
-      <c r="I8" s="342"/>
-      <c r="J8" s="342"/>
-      <c r="K8" s="342"/>
-      <c r="L8" s="342"/>
-      <c r="M8" s="342"/>
-      <c r="N8" s="342"/>
-      <c r="O8" s="343"/>
+      <c r="C8" s="336"/>
+      <c r="D8" s="337"/>
+      <c r="E8" s="337"/>
+      <c r="F8" s="337"/>
+      <c r="G8" s="337"/>
+      <c r="H8" s="337"/>
+      <c r="I8" s="337"/>
+      <c r="J8" s="337"/>
+      <c r="K8" s="337"/>
+      <c r="L8" s="337"/>
+      <c r="M8" s="337"/>
+      <c r="N8" s="337"/>
+      <c r="O8" s="338"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="344"/>
-      <c r="D9" s="345"/>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
-      <c r="G9" s="345"/>
-      <c r="H9" s="345"/>
-      <c r="I9" s="345"/>
-      <c r="J9" s="345"/>
-      <c r="K9" s="345"/>
-      <c r="L9" s="345"/>
-      <c r="M9" s="345"/>
-      <c r="N9" s="345"/>
-      <c r="O9" s="346"/>
+      <c r="C9" s="339"/>
+      <c r="D9" s="340"/>
+      <c r="E9" s="340"/>
+      <c r="F9" s="340"/>
+      <c r="G9" s="340"/>
+      <c r="H9" s="340"/>
+      <c r="I9" s="340"/>
+      <c r="J9" s="340"/>
+      <c r="K9" s="340"/>
+      <c r="L9" s="340"/>
+      <c r="M9" s="340"/>
+      <c r="N9" s="340"/>
+      <c r="O9" s="341"/>
       <c r="Q9" s="55"/>
     </row>
-    <row r="10" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="347" t="s">
+      <c r="C10" s="342" t="s">
         <v>286</v>
       </c>
-      <c r="D10" s="348"/>
-      <c r="E10" s="348"/>
-      <c r="F10" s="348"/>
-      <c r="G10" s="348"/>
-      <c r="H10" s="348"/>
-      <c r="I10" s="348"/>
-      <c r="J10" s="348"/>
-      <c r="K10" s="348"/>
-      <c r="L10" s="348"/>
-      <c r="M10" s="348"/>
-      <c r="N10" s="348"/>
-      <c r="O10" s="349"/>
+      <c r="D10" s="343"/>
+      <c r="E10" s="343"/>
+      <c r="F10" s="343"/>
+      <c r="G10" s="343"/>
+      <c r="H10" s="343"/>
+      <c r="I10" s="343"/>
+      <c r="J10" s="343"/>
+      <c r="K10" s="343"/>
+      <c r="L10" s="343"/>
+      <c r="M10" s="343"/>
+      <c r="N10" s="343"/>
+      <c r="O10" s="344"/>
       <c r="Q10" t="s">
         <v>233</v>
       </c>
@@ -5972,22 +5930,22 @@
         <v>267678.10184399999</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="350"/>
-      <c r="D11" s="351"/>
-      <c r="E11" s="351"/>
-      <c r="F11" s="351"/>
-      <c r="G11" s="351"/>
-      <c r="H11" s="351"/>
-      <c r="I11" s="351"/>
-      <c r="J11" s="351"/>
-      <c r="K11" s="351"/>
-      <c r="L11" s="351"/>
-      <c r="M11" s="351"/>
-      <c r="N11" s="351"/>
-      <c r="O11" s="352"/>
+      <c r="C11" s="345"/>
+      <c r="D11" s="346"/>
+      <c r="E11" s="346"/>
+      <c r="F11" s="346"/>
+      <c r="G11" s="346"/>
+      <c r="H11" s="346"/>
+      <c r="I11" s="346"/>
+      <c r="J11" s="346"/>
+      <c r="K11" s="346"/>
+      <c r="L11" s="346"/>
+      <c r="M11" s="346"/>
+      <c r="N11" s="346"/>
+      <c r="O11" s="347"/>
       <c r="Q11" t="s">
         <v>234</v>
       </c>
@@ -5996,50 +5954,50 @@
         <v>317248.120704</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="323" t="s">
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="320" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="325" t="s">
+      <c r="B12" s="354" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="323" t="s">
+      <c r="C12" s="320" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="327" t="s">
+      <c r="D12" s="356" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="327" t="s">
+      <c r="E12" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F12" s="323" t="s">
+      <c r="F12" s="320" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="323" t="s">
+      <c r="G12" s="320" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="323" t="s">
+      <c r="H12" s="320" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="334" t="s">
+      <c r="I12" s="326" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="320" t="s">
+      <c r="J12" s="328" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="320" t="s">
+      <c r="K12" s="328" t="s">
         <v>366</v>
       </c>
-      <c r="L12" s="320" t="s">
+      <c r="L12" s="328" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="336" t="s">
+      <c r="M12" s="331" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="320" t="s">
+      <c r="N12" s="328" t="s">
         <v>260</v>
       </c>
-      <c r="O12" s="320" t="s">
+      <c r="O12" s="328" t="s">
         <v>259</v>
       </c>
       <c r="Q12" t="s">
@@ -6050,22 +6008,22 @@
         <v>299898.61410299997</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="324"/>
-      <c r="B13" s="326"/>
-      <c r="C13" s="324"/>
-      <c r="D13" s="328"/>
-      <c r="E13" s="328"/>
-      <c r="F13" s="324"/>
-      <c r="G13" s="324"/>
-      <c r="H13" s="324"/>
-      <c r="I13" s="335"/>
-      <c r="J13" s="321"/>
-      <c r="K13" s="321"/>
-      <c r="L13" s="321"/>
-      <c r="M13" s="337"/>
-      <c r="N13" s="321"/>
-      <c r="O13" s="321"/>
+    <row r="13" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="321"/>
+      <c r="B13" s="355"/>
+      <c r="C13" s="321"/>
+      <c r="D13" s="357"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="321"/>
+      <c r="G13" s="321"/>
+      <c r="H13" s="321"/>
+      <c r="I13" s="327"/>
+      <c r="J13" s="329"/>
+      <c r="K13" s="329"/>
+      <c r="L13" s="329"/>
+      <c r="M13" s="332"/>
+      <c r="N13" s="329"/>
+      <c r="O13" s="329"/>
       <c r="Q13" t="s">
         <v>236</v>
       </c>
@@ -6074,20 +6032,20 @@
         <v>369296.64050699997</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="324"/>
-      <c r="B14" s="326"/>
-      <c r="C14" s="324"/>
-      <c r="D14" s="328"/>
-      <c r="E14" s="328"/>
-      <c r="F14" s="324"/>
-      <c r="G14" s="324"/>
-      <c r="H14" s="324"/>
-      <c r="I14" s="335"/>
-      <c r="J14" s="321"/>
-      <c r="K14" s="322"/>
-      <c r="L14" s="322"/>
-      <c r="M14" s="337"/>
+    <row r="14" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="321"/>
+      <c r="B14" s="355"/>
+      <c r="C14" s="321"/>
+      <c r="D14" s="357"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="321"/>
+      <c r="G14" s="321"/>
+      <c r="H14" s="321"/>
+      <c r="I14" s="327"/>
+      <c r="J14" s="329"/>
+      <c r="K14" s="330"/>
+      <c r="L14" s="330"/>
+      <c r="M14" s="332"/>
       <c r="N14" s="84" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/09</v>
@@ -6104,7 +6062,7 @@
         <v>431259.16408199997</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="176" t="s">
         <v>114</v>
       </c>
@@ -6154,10 +6112,10 @@
       <c r="P15" s="70" t="s">
         <v>342</v>
       </c>
-      <c r="R15" s="329"/>
-      <c r="S15" s="329"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R15" s="319"/>
+      <c r="S15" s="319"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="23" t="s">
@@ -6203,10 +6161,10 @@
       <c r="P16" s="70" t="s">
         <v>341</v>
       </c>
-      <c r="R16" s="329"/>
-      <c r="S16" s="329"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R16" s="319"/>
+      <c r="S16" s="319"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>114</v>
       </c>
@@ -6223,7 +6181,7 @@
       <c r="F17" s="93">
         <v>1.21E-2</v>
       </c>
-      <c r="G17" s="257">
+      <c r="G17" s="256">
         <v>243852.859012</v>
       </c>
       <c r="H17" s="32">
@@ -6257,7 +6215,7 @@
       <c r="P17" s="70"/>
       <c r="S17" s="31"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>114</v>
       </c>
@@ -6289,7 +6247,7 @@
       <c r="L18" s="231">
         <v>369296.64050699997</v>
       </c>
-      <c r="M18" s="274">
+      <c r="M18" s="273">
         <v>0</v>
       </c>
       <c r="N18" s="223">
@@ -6303,28 +6261,28 @@
       <c r="P18" s="70"/>
       <c r="S18" s="31"/>
     </row>
-    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>114</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="258" t="s">
+      <c r="C19" s="257" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="259" t="s">
+      <c r="D19" s="258" t="s">
         <v>249</v>
       </c>
-      <c r="E19" s="259"/>
+      <c r="E19" s="258"/>
       <c r="F19" s="98">
         <v>1.7399999999999999E-2</v>
       </c>
       <c r="G19" s="99">
         <v>1296163.1476939998</v>
       </c>
-      <c r="H19" s="273">
+      <c r="H19" s="272">
         <v>1000000</v>
       </c>
-      <c r="I19" s="260">
+      <c r="I19" s="259">
         <f t="shared" si="0"/>
         <v>296163.14769399981</v>
       </c>
@@ -6337,7 +6295,7 @@
       <c r="L19" s="99">
         <v>431259.16408199997</v>
       </c>
-      <c r="M19" s="261">
+      <c r="M19" s="260">
         <v>0</v>
       </c>
       <c r="N19" s="96">
@@ -6351,7 +6309,7 @@
       <c r="P19" s="70"/>
       <c r="S19" s="31"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="37" t="s">
         <v>116</v>
       </c>
@@ -6386,25 +6344,25 @@
       </c>
       <c r="L20" s="129">
         <f>N$2*F20</f>
-        <v>492365.14326400001</v>
+        <v>493047.96152000001</v>
       </c>
       <c r="M20" s="135">
         <v>15000</v>
       </c>
       <c r="N20" s="130">
         <f>ROUND((L20+J20+I20+K20+M20),0) + P20</f>
-        <v>507365.01</v>
+        <v>508048.01</v>
       </c>
       <c r="O20" s="130">
         <f>ROUND((N20*6% + N20 ),0) + P20</f>
-        <v>537807.01</v>
+        <v>538531.01</v>
       </c>
       <c r="P20" s="85">
         <v>0.01</v>
       </c>
       <c r="S20" s="31"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="37" t="s">
         <v>117</v>
       </c>
@@ -6439,18 +6397,18 @@
       </c>
       <c r="L21" s="95">
         <f t="shared" ref="L21:L51" si="4">N$2*F21</f>
-        <v>219992.93635199999</v>
+        <v>220298.02535999997</v>
       </c>
       <c r="M21" s="135">
         <v>0</v>
       </c>
       <c r="N21" s="130">
         <f t="shared" ref="N21:N84" si="5">ROUND((L21+J21+I21+K21+M21),0) + P21</f>
-        <v>219993.02</v>
+        <v>220298.02</v>
       </c>
       <c r="O21" s="97">
         <f t="shared" ref="O21:O84" si="6">ROUND((N21*6% + N21 ),0) + P21</f>
-        <v>233193.02</v>
+        <v>233516.02</v>
       </c>
       <c r="P21" s="85">
         <f>P20+0.01</f>
@@ -6458,7 +6416,7 @@
       </c>
       <c r="S21" s="31"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="37" t="s">
         <v>116</v>
       </c>
@@ -6493,25 +6451,25 @@
       </c>
       <c r="L22" s="95">
         <f t="shared" si="4"/>
-        <v>526411.66912800004</v>
+        <v>527141.70354000002</v>
       </c>
       <c r="M22" s="135">
         <v>0</v>
       </c>
       <c r="N22" s="130">
         <f t="shared" si="5"/>
-        <v>526412.03</v>
+        <v>527142.03</v>
       </c>
       <c r="O22" s="97">
         <f t="shared" si="6"/>
-        <v>557997.03</v>
+        <v>558771.03</v>
       </c>
       <c r="P22" s="85">
         <f t="shared" ref="P22:P85" si="7">P21+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="37" t="s">
         <v>118</v>
       </c>
@@ -6548,18 +6506,18 @@
       </c>
       <c r="L23" s="95">
         <f t="shared" si="4"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M23" s="135">
         <v>0</v>
       </c>
       <c r="N23" s="130">
         <f t="shared" si="5"/>
-        <v>246183.04000000001</v>
+        <v>246524.04</v>
       </c>
       <c r="O23" s="97">
         <f t="shared" si="6"/>
-        <v>260954.04</v>
+        <v>261315.04</v>
       </c>
       <c r="P23" s="85">
         <f t="shared" si="7"/>
@@ -6569,7 +6527,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="37" t="s">
         <v>118</v>
       </c>
@@ -6606,25 +6564,25 @@
       </c>
       <c r="L24" s="95">
         <f t="shared" si="4"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M24" s="135">
         <v>0</v>
       </c>
       <c r="N24" s="130">
         <f t="shared" si="5"/>
-        <v>227850.05</v>
+        <v>228166.05</v>
       </c>
       <c r="O24" s="97">
         <f t="shared" si="6"/>
-        <v>241521.05</v>
+        <v>241856.05</v>
       </c>
       <c r="P24" s="85">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="37" t="s">
         <v>118</v>
       </c>
@@ -6660,25 +6618,25 @@
       </c>
       <c r="L25" s="95">
         <f t="shared" si="4"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M25" s="135">
         <v>0</v>
       </c>
       <c r="N25" s="130">
         <f t="shared" si="5"/>
-        <v>339456.06</v>
+        <v>339801.06</v>
       </c>
       <c r="O25" s="97">
         <f t="shared" si="6"/>
-        <v>359823.06</v>
+        <v>360189.06</v>
       </c>
       <c r="P25" s="85">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="37" t="s">
         <v>116</v>
       </c>
@@ -6714,25 +6672,25 @@
       </c>
       <c r="L26" s="95">
         <f t="shared" si="4"/>
-        <v>432128.98212000006</v>
+        <v>432728.26409999997</v>
       </c>
       <c r="M26" s="135">
         <v>0</v>
       </c>
       <c r="N26" s="130">
         <f t="shared" si="5"/>
-        <v>717182.07</v>
+        <v>717781.07</v>
       </c>
       <c r="O26" s="97">
         <f t="shared" si="6"/>
-        <v>760213.07</v>
+        <v>760848.07</v>
       </c>
       <c r="P26" s="85">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="37" t="s">
         <v>117</v>
       </c>
@@ -6767,25 +6725,25 @@
       </c>
       <c r="L27" s="95">
         <f t="shared" si="4"/>
-        <v>191184.33754400001</v>
+        <v>191449.47441999998</v>
       </c>
       <c r="M27" s="135">
         <v>20000</v>
       </c>
       <c r="N27" s="130">
         <f t="shared" si="5"/>
-        <v>211184.08</v>
+        <v>211449.08</v>
       </c>
       <c r="O27" s="97">
         <f t="shared" si="6"/>
-        <v>223855.08</v>
+        <v>224136.08</v>
       </c>
       <c r="P27" s="85">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="64" t="s">
         <v>116</v>
       </c>
@@ -6819,25 +6777,25 @@
       </c>
       <c r="L28" s="95">
         <f t="shared" si="4"/>
-        <v>466175.50798400003</v>
+        <v>466822.00611999998</v>
       </c>
       <c r="M28" s="135">
         <v>0</v>
       </c>
       <c r="N28" s="130">
         <f t="shared" si="5"/>
-        <v>1108396.0900000001</v>
+        <v>1109042.0900000001</v>
       </c>
       <c r="O28" s="97">
         <f t="shared" si="6"/>
-        <v>1174900.0900000001</v>
+        <v>1175585.0900000001</v>
       </c>
       <c r="P28" s="85">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="64" t="s">
         <v>118</v>
       </c>
@@ -6872,25 +6830,25 @@
       </c>
       <c r="L29" s="95">
         <f t="shared" si="4"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M29" s="135">
         <v>0</v>
       </c>
       <c r="N29" s="130">
         <f t="shared" si="5"/>
-        <v>246183.1</v>
+        <v>246524.1</v>
       </c>
       <c r="O29" s="97">
         <f t="shared" si="6"/>
-        <v>260954.1</v>
+        <v>261316.1</v>
       </c>
       <c r="P29" s="85">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="64" t="s">
         <v>118</v>
       </c>
@@ -6925,25 +6883,25 @@
       </c>
       <c r="L30" s="95">
         <f t="shared" si="4"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M30" s="135">
         <v>15000</v>
       </c>
       <c r="N30" s="130">
         <f t="shared" si="5"/>
-        <v>242850.11</v>
+        <v>243166.11</v>
       </c>
       <c r="O30" s="97">
         <f t="shared" si="6"/>
-        <v>257421.11</v>
+        <v>257756.11</v>
       </c>
       <c r="P30" s="85">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="64" t="s">
         <v>118</v>
       </c>
@@ -6975,25 +6933,25 @@
       </c>
       <c r="L31" s="231">
         <f t="shared" si="4"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M31" s="233">
         <v>0</v>
       </c>
       <c r="N31" s="234">
         <f t="shared" si="5"/>
-        <v>2143474.12</v>
+        <v>2143819.12</v>
       </c>
       <c r="O31" s="235">
         <f t="shared" si="6"/>
-        <v>2272083.12</v>
+        <v>2272448.12</v>
       </c>
       <c r="P31" s="85">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="64" t="s">
         <v>116</v>
       </c>
@@ -7028,25 +6986,25 @@
       </c>
       <c r="L32" s="95">
         <f t="shared" si="4"/>
-        <v>429510.01859200007</v>
+        <v>430105.66856000002</v>
       </c>
       <c r="M32" s="135">
         <v>0</v>
       </c>
       <c r="N32" s="130">
         <f t="shared" si="5"/>
-        <v>429510.13</v>
+        <v>430106.13</v>
       </c>
       <c r="O32" s="97">
         <f t="shared" si="6"/>
-        <v>455281.13</v>
+        <v>455912.13</v>
       </c>
       <c r="P32" s="85">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A33" s="37" t="s">
         <v>117</v>
       </c>
@@ -7083,25 +7041,25 @@
       </c>
       <c r="L33" s="95">
         <f t="shared" si="4"/>
-        <v>188565.37401600002</v>
+        <v>188826.87887999997</v>
       </c>
       <c r="M33" s="135">
         <v>0</v>
       </c>
       <c r="N33" s="130">
         <f t="shared" si="5"/>
-        <v>188921.14</v>
+        <v>189183.14</v>
       </c>
       <c r="O33" s="97">
         <f t="shared" si="6"/>
-        <v>200256.14</v>
+        <v>200534.14</v>
       </c>
       <c r="P33" s="85">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A34" s="37" t="s">
         <v>116</v>
       </c>
@@ -7136,25 +7094,25 @@
       </c>
       <c r="L34" s="95">
         <f t="shared" si="4"/>
-        <v>453080.690344</v>
+        <v>453709.02841999993</v>
       </c>
       <c r="M34" s="135">
         <v>30000</v>
       </c>
       <c r="N34" s="130">
         <f t="shared" si="5"/>
-        <v>483081.15</v>
+        <v>483709.15</v>
       </c>
       <c r="O34" s="97">
         <f t="shared" si="6"/>
-        <v>512066.15</v>
+        <v>512732.15</v>
       </c>
       <c r="P34" s="85">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A35" s="91" t="s">
         <v>118</v>
       </c>
@@ -7189,18 +7147,18 @@
       </c>
       <c r="L35" s="95">
         <f t="shared" si="4"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M35" s="135">
         <v>0</v>
       </c>
       <c r="N35" s="130">
         <f t="shared" si="5"/>
-        <v>246183.16</v>
+        <v>246524.16</v>
       </c>
       <c r="O35" s="97">
         <f t="shared" si="6"/>
-        <v>260954.16</v>
+        <v>261316.16</v>
       </c>
       <c r="P35" s="85">
         <f t="shared" si="7"/>
@@ -7210,7 +7168,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="37" t="s">
         <v>118</v>
       </c>
@@ -7247,25 +7205,25 @@
       </c>
       <c r="L36" s="95">
         <f t="shared" si="4"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M36" s="135">
         <v>0</v>
       </c>
       <c r="N36" s="130">
         <f t="shared" si="5"/>
-        <v>227850.17</v>
+        <v>228166.17</v>
       </c>
       <c r="O36" s="97">
         <f t="shared" si="6"/>
-        <v>241521.17</v>
+        <v>241856.17</v>
       </c>
       <c r="P36" s="85">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="37" t="s">
         <v>118</v>
       </c>
@@ -7297,25 +7255,25 @@
       </c>
       <c r="L37" s="231">
         <f t="shared" si="4"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M37" s="233">
         <v>0</v>
       </c>
       <c r="N37" s="234">
         <f t="shared" si="5"/>
-        <v>1625723.18</v>
+        <v>1626068.18</v>
       </c>
       <c r="O37" s="235">
         <f t="shared" si="6"/>
-        <v>1723267.18</v>
+        <v>1723632.18</v>
       </c>
       <c r="P37" s="85">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="37" t="s">
         <v>116</v>
       </c>
@@ -7352,18 +7310,18 @@
       </c>
       <c r="L38" s="95">
         <f t="shared" si="4"/>
-        <v>429510.01859200007</v>
+        <v>430105.66856000002</v>
       </c>
       <c r="M38" s="135">
         <v>0</v>
       </c>
       <c r="N38" s="130">
         <f t="shared" si="5"/>
-        <v>429510.19</v>
+        <v>430106.19</v>
       </c>
       <c r="O38" s="97">
         <f t="shared" si="6"/>
-        <v>455281.19</v>
+        <v>455913.19</v>
       </c>
       <c r="P38" s="85">
         <f t="shared" si="7"/>
@@ -7373,7 +7331,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A39" s="37" t="s">
         <v>117</v>
       </c>
@@ -7408,25 +7366,25 @@
       </c>
       <c r="L39" s="95">
         <f t="shared" si="4"/>
-        <v>188565.37401600002</v>
+        <v>188826.87887999997</v>
       </c>
       <c r="M39" s="135">
         <v>0</v>
       </c>
       <c r="N39" s="130">
         <f t="shared" si="5"/>
-        <v>188565.2</v>
+        <v>188827.2</v>
       </c>
       <c r="O39" s="97">
         <f t="shared" si="6"/>
-        <v>199879.2</v>
+        <v>200157.2</v>
       </c>
       <c r="P39" s="85">
         <f t="shared" si="7"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="64" t="s">
         <v>116</v>
       </c>
@@ -7461,18 +7419,18 @@
       </c>
       <c r="L40" s="95">
         <f t="shared" si="4"/>
-        <v>453080.690344</v>
+        <v>453709.02841999993</v>
       </c>
       <c r="M40" s="135">
         <v>15000</v>
       </c>
       <c r="N40" s="130">
         <f t="shared" si="5"/>
-        <v>468082.21</v>
+        <v>468710.21</v>
       </c>
       <c r="O40" s="97">
         <f t="shared" si="6"/>
-        <v>496167.21</v>
+        <v>496833.21</v>
       </c>
       <c r="P40" s="116">
         <f t="shared" si="7"/>
@@ -7579,7 +7537,7 @@
       <c r="DI40" s="46"/>
       <c r="DJ40" s="46"/>
     </row>
-    <row r="41" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="64" t="s">
         <v>118</v>
       </c>
@@ -7614,18 +7572,18 @@
       </c>
       <c r="L41" s="95">
         <f t="shared" si="4"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M41" s="135">
         <v>0</v>
       </c>
       <c r="N41" s="130">
         <f t="shared" si="5"/>
-        <v>246183.22</v>
+        <v>246524.22</v>
       </c>
       <c r="O41" s="97">
         <f t="shared" si="6"/>
-        <v>260954.22</v>
+        <v>261316.22</v>
       </c>
       <c r="P41" s="116">
         <f t="shared" si="7"/>
@@ -7732,7 +7690,7 @@
       <c r="DI41" s="46"/>
       <c r="DJ41" s="46"/>
     </row>
-    <row r="42" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="64" t="s">
         <v>118</v>
       </c>
@@ -7767,18 +7725,18 @@
       </c>
       <c r="L42" s="95">
         <f t="shared" si="4"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M42" s="135">
         <v>0</v>
       </c>
       <c r="N42" s="130">
         <f t="shared" si="5"/>
-        <v>227850.23</v>
+        <v>228166.23</v>
       </c>
       <c r="O42" s="97">
         <f t="shared" si="6"/>
-        <v>241521.23</v>
+        <v>241856.23</v>
       </c>
       <c r="P42" s="116">
         <f t="shared" si="7"/>
@@ -7885,7 +7843,7 @@
       <c r="DI42" s="46"/>
       <c r="DJ42" s="46"/>
     </row>
-    <row r="43" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="64" t="s">
         <v>118</v>
       </c>
@@ -7919,18 +7877,18 @@
       </c>
       <c r="L43" s="231">
         <f t="shared" si="4"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M43" s="233">
         <v>0</v>
       </c>
       <c r="N43" s="234">
         <f t="shared" si="5"/>
-        <v>1370943.24</v>
+        <v>1371288.24</v>
       </c>
       <c r="O43" s="235">
         <f t="shared" si="6"/>
-        <v>1453200.24</v>
+        <v>1453566.24</v>
       </c>
       <c r="P43" s="116">
         <f t="shared" si="7"/>
@@ -8035,7 +7993,7 @@
       <c r="DI43" s="46"/>
       <c r="DJ43" s="46"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="37" t="s">
         <v>116</v>
       </c>
@@ -8070,25 +8028,25 @@
       </c>
       <c r="L44" s="95">
         <f t="shared" si="4"/>
-        <v>429510.01859200007</v>
+        <v>430105.66856000002</v>
       </c>
       <c r="M44" s="135">
         <v>0</v>
       </c>
       <c r="N44" s="130">
         <f t="shared" si="5"/>
-        <v>429510.25</v>
+        <v>430106.25</v>
       </c>
       <c r="O44" s="97">
         <f t="shared" si="6"/>
-        <v>455281.25</v>
+        <v>455913.25</v>
       </c>
       <c r="P44" s="85">
         <f t="shared" si="7"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="37" t="s">
         <v>117</v>
       </c>
@@ -8125,25 +8083,25 @@
       </c>
       <c r="L45" s="95">
         <f t="shared" si="4"/>
-        <v>188565.37401600002</v>
+        <v>188826.87887999997</v>
       </c>
       <c r="M45" s="135">
         <v>0</v>
       </c>
       <c r="N45" s="130">
         <f t="shared" si="5"/>
-        <v>188565.26</v>
+        <v>188827.26</v>
       </c>
       <c r="O45" s="97">
         <f t="shared" si="6"/>
-        <v>199879.26</v>
+        <v>200157.26</v>
       </c>
       <c r="P45" s="85">
         <f t="shared" si="7"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="37" t="s">
         <v>116</v>
       </c>
@@ -8178,18 +8136,18 @@
       </c>
       <c r="L46" s="95">
         <f t="shared" si="4"/>
-        <v>453080.690344</v>
+        <v>453709.02841999993</v>
       </c>
       <c r="M46" s="135">
         <v>0</v>
       </c>
       <c r="N46" s="130">
         <f t="shared" si="5"/>
-        <v>453081.27</v>
+        <v>453709.27</v>
       </c>
       <c r="O46" s="97">
         <f t="shared" si="6"/>
-        <v>480266.27</v>
+        <v>480932.27</v>
       </c>
       <c r="P46" s="85">
         <f t="shared" si="7"/>
@@ -8202,7 +8160,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="115" t="s">
         <v>118</v>
       </c>
@@ -8237,25 +8195,25 @@
       </c>
       <c r="L47" s="95">
         <f t="shared" si="4"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M47" s="135">
         <v>15000</v>
       </c>
       <c r="N47" s="130">
         <f t="shared" si="5"/>
-        <v>261183.28</v>
+        <v>261524.28</v>
       </c>
       <c r="O47" s="97">
         <f t="shared" si="6"/>
-        <v>276854.28000000003</v>
+        <v>277216.28000000003</v>
       </c>
       <c r="P47" s="85">
         <f t="shared" si="7"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="37" t="s">
         <v>118</v>
       </c>
@@ -8292,25 +8250,25 @@
       </c>
       <c r="L48" s="95">
         <f t="shared" si="4"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M48" s="135">
         <v>40000</v>
       </c>
       <c r="N48" s="130">
         <f t="shared" si="5"/>
-        <v>267850.28999999998</v>
+        <v>268166.28999999998</v>
       </c>
       <c r="O48" s="97">
         <f t="shared" si="6"/>
-        <v>283921.28999999998</v>
+        <v>284256.28999999998</v>
       </c>
       <c r="P48" s="85">
         <f t="shared" si="7"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="37" t="s">
         <v>118</v>
       </c>
@@ -8345,25 +8303,25 @@
       </c>
       <c r="L49" s="95">
         <f t="shared" si="4"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M49" s="135">
         <v>0</v>
       </c>
       <c r="N49" s="130">
         <f t="shared" si="5"/>
-        <v>248802.3</v>
+        <v>249147.3</v>
       </c>
       <c r="O49" s="97">
         <f t="shared" si="6"/>
-        <v>263730.3</v>
+        <v>264096.3</v>
       </c>
       <c r="P49" s="85">
         <f t="shared" si="7"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="37" t="s">
         <v>116</v>
       </c>
@@ -8398,25 +8356,25 @@
       </c>
       <c r="L50" s="95">
         <f t="shared" si="4"/>
-        <v>429510.01859200007</v>
+        <v>430105.66856000002</v>
       </c>
       <c r="M50" s="135">
         <v>15000</v>
       </c>
       <c r="N50" s="130">
         <f t="shared" si="5"/>
-        <v>444510.31</v>
+        <v>445106.31</v>
       </c>
       <c r="O50" s="97">
         <f t="shared" si="6"/>
-        <v>471181.31</v>
+        <v>471813.31</v>
       </c>
       <c r="P50" s="85">
         <f t="shared" si="7"/>
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="37" t="s">
         <v>117</v>
       </c>
@@ -8450,18 +8408,18 @@
       </c>
       <c r="L51" s="95">
         <f t="shared" si="4"/>
-        <v>188565.37401600002</v>
+        <v>188826.87887999997</v>
       </c>
       <c r="M51" s="135">
         <v>0</v>
       </c>
       <c r="N51" s="130">
         <f t="shared" si="5"/>
-        <v>312953.32</v>
+        <v>313214.32</v>
       </c>
       <c r="O51" s="97">
         <f t="shared" si="6"/>
-        <v>331731.32</v>
+        <v>332007.32</v>
       </c>
       <c r="P51" s="85">
         <f t="shared" si="7"/>
@@ -8469,7 +8427,7 @@
       </c>
       <c r="Q51" s="31"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="37" t="s">
         <v>116</v>
       </c>
@@ -8504,18 +8462,18 @@
       </c>
       <c r="L52" s="95">
         <f t="shared" ref="L52:L83" si="13">N$2*F52</f>
-        <v>453080.690344</v>
+        <v>453709.02841999993</v>
       </c>
       <c r="M52" s="135">
         <v>15000</v>
       </c>
       <c r="N52" s="130">
         <f t="shared" si="5"/>
-        <v>468081.33</v>
+        <v>468709.33</v>
       </c>
       <c r="O52" s="97">
         <f t="shared" si="6"/>
-        <v>496166.33</v>
+        <v>496832.33</v>
       </c>
       <c r="P52" s="85">
         <f t="shared" si="7"/>
@@ -8523,7 +8481,7 @@
       </c>
       <c r="Q52" s="31"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="37" t="s">
         <v>118</v>
       </c>
@@ -8560,18 +8518,18 @@
       </c>
       <c r="L53" s="95">
         <f t="shared" si="13"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M53" s="135">
         <v>0</v>
       </c>
       <c r="N53" s="130">
         <f t="shared" si="5"/>
-        <v>246183.34</v>
+        <v>246524.34</v>
       </c>
       <c r="O53" s="97">
         <f t="shared" si="6"/>
-        <v>260954.34</v>
+        <v>261316.34</v>
       </c>
       <c r="P53" s="85">
         <f t="shared" si="7"/>
@@ -8581,7 +8539,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="37" t="s">
         <v>118</v>
       </c>
@@ -8616,25 +8574,25 @@
       </c>
       <c r="L54" s="95">
         <f t="shared" si="13"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M54" s="135">
         <v>0</v>
       </c>
       <c r="N54" s="130">
         <f t="shared" si="5"/>
-        <v>227850.35</v>
+        <v>228166.35</v>
       </c>
       <c r="O54" s="97">
         <f t="shared" si="6"/>
-        <v>241521.35</v>
+        <v>241856.35</v>
       </c>
       <c r="P54" s="85">
         <f t="shared" si="7"/>
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="64" t="s">
         <v>118</v>
       </c>
@@ -8669,25 +8627,25 @@
       </c>
       <c r="L55" s="95">
         <f t="shared" si="13"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M55" s="135">
         <v>0</v>
       </c>
       <c r="N55" s="130">
         <f t="shared" si="5"/>
-        <v>248802.36</v>
+        <v>249147.36</v>
       </c>
       <c r="O55" s="97">
         <f t="shared" si="6"/>
-        <v>263731.36</v>
+        <v>264096.36</v>
       </c>
       <c r="P55" s="85">
         <f t="shared" si="7"/>
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="37" t="s">
         <v>116</v>
       </c>
@@ -8722,18 +8680,18 @@
       </c>
       <c r="L56" s="95">
         <f t="shared" si="13"/>
-        <v>429510.01859200007</v>
+        <v>430105.66856000002</v>
       </c>
       <c r="M56" s="135">
         <v>0</v>
       </c>
       <c r="N56" s="130">
         <f t="shared" si="5"/>
-        <v>429510.37</v>
+        <v>430106.37</v>
       </c>
       <c r="O56" s="97">
         <f t="shared" si="6"/>
-        <v>455281.37</v>
+        <v>455913.37</v>
       </c>
       <c r="P56" s="85">
         <f t="shared" si="7"/>
@@ -8741,7 +8699,7 @@
       </c>
       <c r="R56" s="39"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="37" t="s">
         <v>117</v>
       </c>
@@ -8778,25 +8736,25 @@
       </c>
       <c r="L57" s="95">
         <f t="shared" si="13"/>
-        <v>188565.37401600002</v>
+        <v>188826.87887999997</v>
       </c>
       <c r="M57" s="135">
         <v>0</v>
       </c>
       <c r="N57" s="130">
         <f t="shared" si="5"/>
-        <v>188565.38</v>
+        <v>188827.38</v>
       </c>
       <c r="O57" s="97">
         <f t="shared" si="6"/>
-        <v>199879.38</v>
+        <v>200157.38</v>
       </c>
       <c r="P57" s="85">
         <f t="shared" si="7"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="37" t="s">
         <v>116</v>
       </c>
@@ -8831,25 +8789,25 @@
       </c>
       <c r="L58" s="95">
         <f t="shared" si="13"/>
-        <v>453080.690344</v>
+        <v>453709.02841999993</v>
       </c>
       <c r="M58" s="135">
         <v>0</v>
       </c>
       <c r="N58" s="130">
         <f t="shared" si="5"/>
-        <v>453081.39</v>
+        <v>453709.39</v>
       </c>
       <c r="O58" s="97">
         <f t="shared" si="6"/>
-        <v>480266.39</v>
+        <v>480932.39</v>
       </c>
       <c r="P58" s="85">
         <f t="shared" si="7"/>
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="37" t="s">
         <v>118</v>
       </c>
@@ -8886,25 +8844,25 @@
       </c>
       <c r="L59" s="95">
         <f t="shared" si="13"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M59" s="135">
         <v>15000</v>
       </c>
       <c r="N59" s="130">
         <f t="shared" si="5"/>
-        <v>261183.4</v>
+        <v>261524.4</v>
       </c>
       <c r="O59" s="97">
         <f t="shared" si="6"/>
-        <v>276854.40000000002</v>
+        <v>277216.40000000002</v>
       </c>
       <c r="P59" s="85">
         <f t="shared" si="7"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="64" t="s">
         <v>118</v>
       </c>
@@ -8939,18 +8897,18 @@
       </c>
       <c r="L60" s="95">
         <f t="shared" si="13"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M60" s="135">
         <v>0</v>
       </c>
       <c r="N60" s="130">
         <f t="shared" si="5"/>
-        <v>227850.41</v>
+        <v>228166.41</v>
       </c>
       <c r="O60" s="97">
         <f t="shared" si="6"/>
-        <v>241521.41</v>
+        <v>241856.41</v>
       </c>
       <c r="P60" s="85">
         <f t="shared" si="7"/>
@@ -8960,7 +8918,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="64" t="s">
         <v>118</v>
       </c>
@@ -8995,18 +8953,18 @@
       </c>
       <c r="L61" s="95">
         <f t="shared" si="13"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M61" s="135">
         <v>0</v>
       </c>
       <c r="N61" s="130">
         <f t="shared" si="5"/>
-        <v>248802.42</v>
+        <v>249147.42</v>
       </c>
       <c r="O61" s="97">
         <f t="shared" si="6"/>
-        <v>263731.42</v>
+        <v>264096.42</v>
       </c>
       <c r="P61" s="85">
         <f t="shared" si="7"/>
@@ -9016,7 +8974,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="64" t="s">
         <v>116</v>
       </c>
@@ -9050,25 +9008,25 @@
       </c>
       <c r="L62" s="95">
         <f t="shared" si="13"/>
-        <v>429510.01859200007</v>
+        <v>430105.66856000002</v>
       </c>
       <c r="M62" s="135">
         <v>0</v>
       </c>
       <c r="N62" s="130">
         <f t="shared" si="5"/>
-        <v>412513.43</v>
+        <v>413109.43</v>
       </c>
       <c r="O62" s="97">
         <f t="shared" si="6"/>
-        <v>437264.43</v>
+        <v>437896.43</v>
       </c>
       <c r="P62" s="85">
         <f t="shared" si="7"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="64" t="s">
         <v>117</v>
       </c>
@@ -9102,25 +9060,25 @@
       </c>
       <c r="L63" s="95">
         <f t="shared" si="13"/>
-        <v>188565.37401600002</v>
+        <v>188826.87887999997</v>
       </c>
       <c r="M63" s="135">
         <v>0</v>
       </c>
       <c r="N63" s="130">
         <f t="shared" si="5"/>
-        <v>181101.44</v>
+        <v>181363.44</v>
       </c>
       <c r="O63" s="97">
         <f t="shared" si="6"/>
-        <v>191968.44</v>
+        <v>192245.44</v>
       </c>
       <c r="P63" s="85">
         <f t="shared" si="7"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="64" t="s">
         <v>116</v>
       </c>
@@ -9155,25 +9113,25 @@
       </c>
       <c r="L64" s="95">
         <f t="shared" si="13"/>
-        <v>453080.690344</v>
+        <v>453709.02841999993</v>
       </c>
       <c r="M64" s="135">
         <v>20000</v>
       </c>
       <c r="N64" s="130">
         <f t="shared" si="5"/>
-        <v>473081.45</v>
+        <v>473709.45</v>
       </c>
       <c r="O64" s="97">
         <f t="shared" si="6"/>
-        <v>501466.45</v>
+        <v>502132.45</v>
       </c>
       <c r="P64" s="85">
         <f t="shared" si="7"/>
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="64" t="s">
         <v>118</v>
       </c>
@@ -9210,25 +9168,25 @@
       </c>
       <c r="L65" s="95">
         <f t="shared" si="13"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M65" s="135">
         <v>15000</v>
       </c>
       <c r="N65" s="130">
         <f t="shared" si="5"/>
-        <v>261183.46</v>
+        <v>261524.46</v>
       </c>
       <c r="O65" s="97">
         <f t="shared" si="6"/>
-        <v>276854.46000000002</v>
+        <v>277216.46000000002</v>
       </c>
       <c r="P65" s="116">
         <f t="shared" si="7"/>
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="64" t="s">
         <v>118</v>
       </c>
@@ -9263,25 +9221,25 @@
       </c>
       <c r="L66" s="95">
         <f t="shared" si="13"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M66" s="135">
         <v>0</v>
       </c>
       <c r="N66" s="130">
         <f t="shared" si="5"/>
-        <v>227850.47</v>
+        <v>228166.47</v>
       </c>
       <c r="O66" s="97">
         <f t="shared" si="6"/>
-        <v>241521.47</v>
+        <v>241856.47</v>
       </c>
       <c r="P66" s="116">
         <f t="shared" si="7"/>
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="64" t="s">
         <v>118</v>
       </c>
@@ -9315,18 +9273,18 @@
       </c>
       <c r="L67" s="95">
         <f t="shared" si="13"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M67" s="135">
         <v>0</v>
       </c>
       <c r="N67" s="130">
         <f t="shared" si="5"/>
-        <v>359884.48</v>
+        <v>360229.48</v>
       </c>
       <c r="O67" s="97">
         <f t="shared" si="6"/>
-        <v>381478.48</v>
+        <v>381843.48</v>
       </c>
       <c r="P67" s="116">
         <f t="shared" si="7"/>
@@ -9334,7 +9292,7 @@
       </c>
       <c r="S67" s="125"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="64" t="s">
         <v>116</v>
       </c>
@@ -9369,18 +9327,18 @@
       </c>
       <c r="L68" s="95">
         <f t="shared" si="13"/>
-        <v>429510.01859200007</v>
+        <v>430105.66856000002</v>
       </c>
       <c r="M68" s="135">
         <v>15000</v>
       </c>
       <c r="N68" s="130">
         <f t="shared" si="5"/>
-        <v>444510.49</v>
+        <v>445106.49</v>
       </c>
       <c r="O68" s="97">
         <f t="shared" si="6"/>
-        <v>471181.49</v>
+        <v>471813.49</v>
       </c>
       <c r="P68" s="85">
         <f t="shared" si="7"/>
@@ -9388,7 +9346,7 @@
       </c>
       <c r="S68" s="31"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="91" t="s">
         <v>117</v>
       </c>
@@ -9423,25 +9381,25 @@
       </c>
       <c r="L69" s="95">
         <f t="shared" si="13"/>
-        <v>188565.37401600002</v>
+        <v>188826.87887999997</v>
       </c>
       <c r="M69" s="135">
         <v>0</v>
       </c>
       <c r="N69" s="130">
         <f t="shared" si="5"/>
-        <v>188565.5</v>
+        <v>188827.5</v>
       </c>
       <c r="O69" s="97">
         <f t="shared" si="6"/>
-        <v>199879.5</v>
+        <v>200157.5</v>
       </c>
       <c r="P69" s="85">
         <f t="shared" si="7"/>
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="37" t="s">
         <v>116</v>
       </c>
@@ -9476,25 +9434,25 @@
       </c>
       <c r="L70" s="95">
         <f t="shared" si="13"/>
-        <v>453080.690344</v>
+        <v>453709.02841999993</v>
       </c>
       <c r="M70" s="241">
         <v>0</v>
       </c>
       <c r="N70" s="130">
         <f t="shared" si="5"/>
-        <v>453081.51</v>
+        <v>453709.51</v>
       </c>
       <c r="O70" s="97">
         <f t="shared" si="6"/>
-        <v>480266.51</v>
+        <v>480932.51</v>
       </c>
       <c r="P70" s="85">
         <f t="shared" si="7"/>
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="37" t="s">
         <v>118</v>
       </c>
@@ -9528,25 +9486,25 @@
       </c>
       <c r="L71" s="95">
         <f t="shared" si="13"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M71" s="135">
         <v>0</v>
       </c>
       <c r="N71" s="130">
         <f t="shared" si="5"/>
-        <v>408577.52</v>
+        <v>408919.52</v>
       </c>
       <c r="O71" s="97">
         <f t="shared" si="6"/>
-        <v>433092.52</v>
+        <v>433455.52</v>
       </c>
       <c r="P71" s="85">
         <f t="shared" si="7"/>
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="37" t="s">
         <v>118</v>
       </c>
@@ -9581,16 +9539,16 @@
       </c>
       <c r="L72" s="95">
         <f t="shared" si="13"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M72" s="135"/>
       <c r="N72" s="130">
         <f t="shared" si="5"/>
-        <v>227850.53</v>
+        <v>228166.53</v>
       </c>
       <c r="O72" s="97">
         <f t="shared" si="6"/>
-        <v>241522.53</v>
+        <v>241857.53</v>
       </c>
       <c r="P72" s="85">
         <f t="shared" si="7"/>
@@ -9600,7 +9558,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="37" t="s">
         <v>118</v>
       </c>
@@ -9632,25 +9590,25 @@
       </c>
       <c r="L73" s="231">
         <f t="shared" si="13"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M73" s="233">
         <v>0</v>
       </c>
       <c r="N73" s="234">
         <f t="shared" si="5"/>
-        <v>1049873.54</v>
+        <v>1050218.54</v>
       </c>
       <c r="O73" s="235">
         <f t="shared" si="6"/>
-        <v>1112866.54</v>
+        <v>1113232.54</v>
       </c>
       <c r="P73" s="85">
         <f t="shared" si="7"/>
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="37" t="s">
         <v>119</v>
       </c>
@@ -9685,18 +9643,18 @@
       </c>
       <c r="L74" s="95">
         <f t="shared" si="13"/>
-        <v>615456.42908000003</v>
+        <v>616309.95189999999</v>
       </c>
       <c r="M74" s="135">
         <v>0</v>
       </c>
       <c r="N74" s="130">
         <f t="shared" si="5"/>
-        <v>615456.55000000005</v>
+        <v>616310.55000000005</v>
       </c>
       <c r="O74" s="97">
         <f t="shared" si="6"/>
-        <v>652384.55000000005</v>
+        <v>653289.55000000005</v>
       </c>
       <c r="P74" s="85">
         <f t="shared" si="7"/>
@@ -9704,7 +9662,7 @@
       </c>
       <c r="Q74" s="46"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="37" t="s">
         <v>116</v>
       </c>
@@ -9739,25 +9697,25 @@
       </c>
       <c r="L75" s="95">
         <f t="shared" si="13"/>
-        <v>453080.690344</v>
+        <v>453709.02841999993</v>
       </c>
       <c r="M75" s="135">
         <v>0</v>
       </c>
       <c r="N75" s="130">
         <f t="shared" si="5"/>
-        <v>392770.56</v>
+        <v>393398.56</v>
       </c>
       <c r="O75" s="97">
         <f t="shared" si="6"/>
-        <v>416337.56</v>
+        <v>417002.56</v>
       </c>
       <c r="P75" s="85">
         <f t="shared" si="7"/>
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="37" t="s">
         <v>118</v>
       </c>
@@ -9792,25 +9750,25 @@
       </c>
       <c r="L76" s="95">
         <f t="shared" si="13"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M76" s="135">
         <v>0</v>
       </c>
       <c r="N76" s="130">
         <f t="shared" si="5"/>
-        <v>246183.57</v>
+        <v>246524.57</v>
       </c>
       <c r="O76" s="97">
         <f t="shared" si="6"/>
-        <v>260955.57</v>
+        <v>261316.57</v>
       </c>
       <c r="P76" s="85">
         <f t="shared" si="7"/>
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="37" t="s">
         <v>118</v>
       </c>
@@ -9847,25 +9805,25 @@
       </c>
       <c r="L77" s="95">
         <f t="shared" si="13"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M77" s="135">
         <v>0</v>
       </c>
       <c r="N77" s="130">
         <f t="shared" si="5"/>
-        <v>227850.58</v>
+        <v>228166.58</v>
       </c>
       <c r="O77" s="97">
         <f t="shared" si="6"/>
-        <v>241522.58</v>
+        <v>241857.58</v>
       </c>
       <c r="P77" s="85">
         <f t="shared" si="7"/>
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="64" t="s">
         <v>118</v>
       </c>
@@ -9899,25 +9857,25 @@
       </c>
       <c r="L78" s="95">
         <f t="shared" si="13"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M78" s="135">
         <v>0</v>
       </c>
       <c r="N78" s="130">
         <f t="shared" si="5"/>
-        <v>412924.59</v>
+        <v>413269.59</v>
       </c>
       <c r="O78" s="97">
         <f t="shared" si="6"/>
-        <v>437700.59</v>
+        <v>438066.59</v>
       </c>
       <c r="P78" s="85">
         <f t="shared" si="7"/>
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="64" t="s">
         <v>119</v>
       </c>
@@ -9952,25 +9910,25 @@
       </c>
       <c r="L79" s="95">
         <f t="shared" si="13"/>
-        <v>615456.42908000003</v>
+        <v>616309.95189999999</v>
       </c>
       <c r="M79" s="135">
         <v>0</v>
       </c>
       <c r="N79" s="130">
         <f t="shared" si="5"/>
-        <v>615456.6</v>
+        <v>616310.6</v>
       </c>
       <c r="O79" s="97">
         <f t="shared" si="6"/>
-        <v>652384.6</v>
+        <v>653289.6</v>
       </c>
       <c r="P79" s="85">
         <f t="shared" si="7"/>
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="37" t="s">
         <v>116</v>
       </c>
@@ -10005,25 +9963,25 @@
       </c>
       <c r="L80" s="95">
         <f t="shared" si="13"/>
-        <v>453080.690344</v>
+        <v>453709.02841999993</v>
       </c>
       <c r="M80" s="135">
         <v>0</v>
       </c>
       <c r="N80" s="130">
         <f t="shared" si="5"/>
-        <v>453081.61</v>
+        <v>453709.61</v>
       </c>
       <c r="O80" s="97">
         <f t="shared" si="6"/>
-        <v>480267.61</v>
+        <v>480932.61</v>
       </c>
       <c r="P80" s="85">
         <f t="shared" si="7"/>
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="37" t="s">
         <v>118</v>
       </c>
@@ -10057,7 +10015,7 @@
       </c>
       <c r="L81" s="231">
         <f t="shared" si="13"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M81" s="233">
         <f>24000+106464</f>
@@ -10065,18 +10023,18 @@
       </c>
       <c r="N81" s="234">
         <f t="shared" si="5"/>
-        <v>1372152.62</v>
+        <v>1372493.62</v>
       </c>
       <c r="O81" s="235">
         <f t="shared" si="6"/>
-        <v>1454482.62</v>
+        <v>1454843.62</v>
       </c>
       <c r="P81" s="85">
         <f t="shared" si="7"/>
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="37" t="s">
         <v>118</v>
       </c>
@@ -10113,25 +10071,25 @@
       </c>
       <c r="L82" s="95">
         <f t="shared" si="13"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M82" s="135">
         <v>0</v>
       </c>
       <c r="N82" s="130">
         <f t="shared" si="5"/>
-        <v>146675.63</v>
+        <v>146991.63</v>
       </c>
       <c r="O82" s="97">
         <f t="shared" si="6"/>
-        <v>155476.63</v>
+        <v>155811.63</v>
       </c>
       <c r="P82" s="85">
         <f t="shared" si="7"/>
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="37" t="s">
         <v>118</v>
       </c>
@@ -10166,18 +10124,18 @@
       </c>
       <c r="L83" s="95">
         <f t="shared" si="13"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M83" s="135">
         <v>0</v>
       </c>
       <c r="N83" s="130">
         <f t="shared" si="5"/>
-        <v>248802.64</v>
+        <v>249147.64</v>
       </c>
       <c r="O83" s="97">
         <f t="shared" si="6"/>
-        <v>263731.64</v>
+        <v>264096.64000000001</v>
       </c>
       <c r="P83" s="85">
         <f t="shared" si="7"/>
@@ -10187,7 +10145,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="37" t="s">
         <v>119</v>
       </c>
@@ -10222,25 +10180,25 @@
       </c>
       <c r="L84" s="95">
         <f t="shared" ref="L84:L115" si="20">N$2*F84</f>
-        <v>615456.42908000003</v>
+        <v>616309.95189999999</v>
       </c>
       <c r="M84" s="135">
         <v>15000</v>
       </c>
       <c r="N84" s="130">
         <f t="shared" si="5"/>
-        <v>630456.65</v>
+        <v>631310.65</v>
       </c>
       <c r="O84" s="97">
         <f t="shared" si="6"/>
-        <v>668284.65</v>
+        <v>669189.65</v>
       </c>
       <c r="P84" s="85">
         <f t="shared" si="7"/>
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="37" t="s">
         <v>116</v>
       </c>
@@ -10275,25 +10233,25 @@
       </c>
       <c r="L85" s="95">
         <f t="shared" si="20"/>
-        <v>453080.690344</v>
+        <v>453709.02841999993</v>
       </c>
       <c r="M85" s="135">
         <v>0</v>
       </c>
       <c r="N85" s="130">
         <f t="shared" ref="N85:N132" si="21">ROUND((L85+J85+I85+K85+M85),0) + P85</f>
-        <v>453081.66</v>
+        <v>453709.66</v>
       </c>
       <c r="O85" s="97">
         <f t="shared" ref="O85:O132" si="22">ROUND((N85*6% + N85 ),0) + P85</f>
-        <v>480267.66</v>
+        <v>480932.66</v>
       </c>
       <c r="P85" s="85">
         <f t="shared" si="7"/>
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="37" t="s">
         <v>118</v>
       </c>
@@ -10328,25 +10286,25 @@
       </c>
       <c r="L86" s="95">
         <f t="shared" si="20"/>
-        <v>246182.57163200001</v>
+        <v>246523.98076000001</v>
       </c>
       <c r="M86" s="135">
         <v>0</v>
       </c>
       <c r="N86" s="130">
         <f t="shared" si="21"/>
-        <v>246183.67</v>
+        <v>246524.67</v>
       </c>
       <c r="O86" s="97">
         <f t="shared" si="22"/>
-        <v>260955.67</v>
+        <v>261316.67</v>
       </c>
       <c r="P86" s="85">
         <f t="shared" ref="P86:P132" si="24">P85+0.01</f>
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="37" t="s">
         <v>118</v>
       </c>
@@ -10381,25 +10339,25 @@
       </c>
       <c r="L87" s="95">
         <f t="shared" si="20"/>
-        <v>227849.826936</v>
+        <v>228165.81197999997</v>
       </c>
       <c r="M87" s="135">
         <v>0</v>
       </c>
       <c r="N87" s="130">
         <f t="shared" si="21"/>
-        <v>227850.68</v>
+        <v>228166.68</v>
       </c>
       <c r="O87" s="97">
         <f t="shared" si="22"/>
-        <v>241522.68</v>
+        <v>241857.68</v>
       </c>
       <c r="P87" s="85">
         <f t="shared" si="24"/>
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="64" t="s">
         <v>118</v>
       </c>
@@ -10434,25 +10392,25 @@
       </c>
       <c r="L88" s="95">
         <f t="shared" si="20"/>
-        <v>248801.53516</v>
+        <v>249146.57629999999</v>
       </c>
       <c r="M88" s="135">
         <v>40000</v>
       </c>
       <c r="N88" s="130">
         <f t="shared" si="21"/>
-        <v>288802.69</v>
+        <v>289147.69</v>
       </c>
       <c r="O88" s="97">
         <f t="shared" si="22"/>
-        <v>306131.69</v>
+        <v>306497.69</v>
       </c>
       <c r="P88" s="85">
         <f t="shared" si="24"/>
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="64"/>
       <c r="B89" s="23"/>
       <c r="C89" s="23" t="s">
@@ -10486,25 +10444,25 @@
       </c>
       <c r="L89" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M89" s="135">
         <v>0</v>
       </c>
       <c r="N89" s="130">
         <f t="shared" si="21"/>
-        <v>60236.7</v>
+        <v>60320.7</v>
       </c>
       <c r="O89" s="97">
         <f t="shared" si="22"/>
-        <v>63851.7</v>
+        <v>63940.7</v>
       </c>
       <c r="P89" s="85">
         <f t="shared" si="24"/>
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="64"/>
       <c r="B90" s="23"/>
       <c r="C90" s="23" t="s">
@@ -10538,25 +10496,25 @@
       </c>
       <c r="L90" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M90" s="135">
         <v>0</v>
       </c>
       <c r="N90" s="130">
         <f t="shared" si="21"/>
-        <v>60236.71</v>
+        <v>60320.71</v>
       </c>
       <c r="O90" s="97">
         <f t="shared" si="22"/>
-        <v>63851.71</v>
+        <v>63940.71</v>
       </c>
       <c r="P90" s="85">
         <f t="shared" si="24"/>
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="64"/>
       <c r="B91" s="23"/>
       <c r="C91" s="23" t="s">
@@ -10590,25 +10548,25 @@
       </c>
       <c r="L91" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M91" s="135">
         <v>0</v>
       </c>
       <c r="N91" s="130">
         <f t="shared" si="21"/>
-        <v>60236.72</v>
+        <v>60320.72</v>
       </c>
       <c r="O91" s="97">
         <f t="shared" si="22"/>
-        <v>63851.72</v>
+        <v>63940.72</v>
       </c>
       <c r="P91" s="85">
         <f t="shared" si="24"/>
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="64"/>
       <c r="B92" s="23"/>
       <c r="C92" s="23" t="s">
@@ -10642,25 +10600,25 @@
       </c>
       <c r="L92" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M92" s="135">
         <v>0</v>
       </c>
       <c r="N92" s="130">
         <f t="shared" si="21"/>
-        <v>60236.73</v>
+        <v>60320.73</v>
       </c>
       <c r="O92" s="97">
         <f t="shared" si="22"/>
-        <v>63851.73</v>
+        <v>63940.73</v>
       </c>
       <c r="P92" s="85">
         <f t="shared" si="24"/>
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="64"/>
       <c r="B93" s="23"/>
       <c r="C93" s="119" t="s">
@@ -10694,18 +10652,18 @@
       </c>
       <c r="L93" s="123">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M93" s="135">
         <v>0</v>
       </c>
       <c r="N93" s="130">
         <f t="shared" si="21"/>
-        <v>60236.74</v>
+        <v>60320.74</v>
       </c>
       <c r="O93" s="124">
         <f t="shared" si="22"/>
-        <v>63851.74</v>
+        <v>63940.74</v>
       </c>
       <c r="P93" s="85">
         <f t="shared" si="24"/>
@@ -10715,7 +10673,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="64"/>
       <c r="B94" s="23"/>
       <c r="C94" s="23" t="s">
@@ -10749,25 +10707,25 @@
       </c>
       <c r="L94" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M94" s="135">
         <v>0</v>
       </c>
       <c r="N94" s="130">
         <f t="shared" si="21"/>
-        <v>60236.75</v>
+        <v>60320.75</v>
       </c>
       <c r="O94" s="97">
         <f t="shared" si="22"/>
-        <v>63851.75</v>
+        <v>63940.75</v>
       </c>
       <c r="P94" s="85">
         <f t="shared" si="24"/>
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="64"/>
       <c r="B95" s="23"/>
       <c r="C95" s="23" t="s">
@@ -10801,25 +10759,25 @@
       </c>
       <c r="L95" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M95" s="135">
         <v>0</v>
       </c>
       <c r="N95" s="130">
         <f t="shared" si="21"/>
-        <v>60236.76</v>
+        <v>60320.76</v>
       </c>
       <c r="O95" s="97">
         <f t="shared" si="22"/>
-        <v>63851.76</v>
+        <v>63940.76</v>
       </c>
       <c r="P95" s="85">
         <f t="shared" si="24"/>
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="64"/>
       <c r="B96" s="23"/>
       <c r="C96" s="23" t="s">
@@ -10853,25 +10811,25 @@
       </c>
       <c r="L96" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M96" s="135">
         <v>0</v>
       </c>
       <c r="N96" s="130">
         <f t="shared" si="21"/>
-        <v>60236.77</v>
+        <v>60320.77</v>
       </c>
       <c r="O96" s="97">
         <f t="shared" si="22"/>
-        <v>63851.77</v>
+        <v>63940.77</v>
       </c>
       <c r="P96" s="85">
         <f t="shared" si="24"/>
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="64"/>
       <c r="B97" s="23"/>
       <c r="C97" s="23" t="s">
@@ -10905,25 +10863,25 @@
       </c>
       <c r="L97" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M97" s="135">
         <v>0</v>
       </c>
       <c r="N97" s="130">
         <f t="shared" si="21"/>
-        <v>60236.78</v>
+        <v>60320.78</v>
       </c>
       <c r="O97" s="97">
         <f t="shared" si="22"/>
-        <v>63851.78</v>
+        <v>63940.78</v>
       </c>
       <c r="P97" s="85">
         <f t="shared" si="24"/>
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="64"/>
       <c r="B98" s="23"/>
       <c r="C98" s="23" t="s">
@@ -10957,25 +10915,25 @@
       </c>
       <c r="L98" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M98" s="135">
         <v>0</v>
       </c>
       <c r="N98" s="130">
         <f t="shared" si="21"/>
-        <v>60236.79</v>
+        <v>60320.79</v>
       </c>
       <c r="O98" s="97">
         <f t="shared" si="22"/>
-        <v>63851.79</v>
+        <v>63940.79</v>
       </c>
       <c r="P98" s="85">
         <f t="shared" si="24"/>
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="64"/>
       <c r="B99" s="23"/>
       <c r="C99" s="23" t="s">
@@ -11009,25 +10967,25 @@
       </c>
       <c r="L99" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M99" s="135">
         <v>0</v>
       </c>
       <c r="N99" s="130">
         <f t="shared" si="21"/>
-        <v>60236.800000000003</v>
+        <v>60320.800000000003</v>
       </c>
       <c r="O99" s="97">
         <f t="shared" si="22"/>
-        <v>63851.8</v>
+        <v>63940.800000000003</v>
       </c>
       <c r="P99" s="85">
         <f t="shared" si="24"/>
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="64"/>
       <c r="B100" s="23"/>
       <c r="C100" s="23" t="s">
@@ -11061,25 +11019,25 @@
       </c>
       <c r="L100" s="17">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M100" s="135">
         <v>0</v>
       </c>
       <c r="N100" s="130">
         <f t="shared" si="21"/>
-        <v>60236.81</v>
+        <v>60320.81</v>
       </c>
       <c r="O100" s="5">
         <f t="shared" si="22"/>
-        <v>63851.81</v>
+        <v>63940.81</v>
       </c>
       <c r="P100" s="85">
         <f t="shared" si="24"/>
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="64"/>
       <c r="B101" s="23"/>
       <c r="C101" s="23" t="s">
@@ -11113,25 +11071,25 @@
       </c>
       <c r="L101" s="17">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M101" s="135">
         <v>0</v>
       </c>
       <c r="N101" s="130">
         <f t="shared" si="21"/>
-        <v>60236.82</v>
+        <v>60320.82</v>
       </c>
       <c r="O101" s="5">
         <f t="shared" si="22"/>
-        <v>63851.82</v>
+        <v>63940.82</v>
       </c>
       <c r="P101" s="85">
         <f t="shared" si="24"/>
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="64"/>
       <c r="B102" s="23"/>
       <c r="C102" s="23" t="s">
@@ -11165,25 +11123,25 @@
       </c>
       <c r="L102" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M102" s="135">
         <v>0</v>
       </c>
       <c r="N102" s="130">
         <f t="shared" si="21"/>
-        <v>60236.83</v>
+        <v>60320.83</v>
       </c>
       <c r="O102" s="97">
         <f t="shared" si="22"/>
-        <v>63851.83</v>
+        <v>63940.83</v>
       </c>
       <c r="P102" s="85">
         <f t="shared" si="24"/>
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="64"/>
       <c r="B103" s="23"/>
       <c r="C103" s="23" t="s">
@@ -11217,25 +11175,25 @@
       </c>
       <c r="L103" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M103" s="135">
         <v>0</v>
       </c>
       <c r="N103" s="130">
         <f t="shared" si="21"/>
-        <v>60236.84</v>
+        <v>60320.84</v>
       </c>
       <c r="O103" s="97">
         <f t="shared" si="22"/>
-        <v>63851.839999999997</v>
+        <v>63940.84</v>
       </c>
       <c r="P103" s="85">
         <f t="shared" si="24"/>
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="64"/>
       <c r="B104" s="23"/>
       <c r="C104" s="23" t="s">
@@ -11269,25 +11227,25 @@
       </c>
       <c r="L104" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M104" s="135">
         <v>0</v>
       </c>
       <c r="N104" s="130">
         <f t="shared" si="21"/>
-        <v>60236.85</v>
+        <v>60320.85</v>
       </c>
       <c r="O104" s="97">
         <f t="shared" si="22"/>
-        <v>63851.85</v>
+        <v>63940.85</v>
       </c>
       <c r="P104" s="85">
         <f t="shared" si="24"/>
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="64"/>
       <c r="B105" s="23"/>
       <c r="C105" s="23" t="s">
@@ -11321,25 +11279,25 @@
       </c>
       <c r="L105" s="17">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M105" s="135">
         <v>0</v>
       </c>
       <c r="N105" s="130">
         <f t="shared" si="21"/>
-        <v>60236.86</v>
+        <v>60320.86</v>
       </c>
       <c r="O105" s="5">
         <f t="shared" si="22"/>
-        <v>63851.86</v>
+        <v>63940.86</v>
       </c>
       <c r="P105" s="85">
         <f t="shared" si="24"/>
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="64"/>
       <c r="B106" s="23"/>
       <c r="C106" s="23" t="s">
@@ -11373,25 +11331,25 @@
       </c>
       <c r="L106" s="17">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M106" s="135">
         <v>0</v>
       </c>
       <c r="N106" s="130">
         <f t="shared" si="21"/>
-        <v>60236.87</v>
+        <v>60320.87</v>
       </c>
       <c r="O106" s="5">
         <f t="shared" si="22"/>
-        <v>63851.87</v>
+        <v>63940.87</v>
       </c>
       <c r="P106" s="85">
         <f t="shared" si="24"/>
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="64"/>
       <c r="B107" s="23"/>
       <c r="C107" s="23" t="s">
@@ -11424,25 +11382,25 @@
       </c>
       <c r="L107" s="17">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M107" s="135">
         <v>0</v>
       </c>
       <c r="N107" s="130">
         <f t="shared" si="21"/>
-        <v>100797.88</v>
+        <v>100881.88</v>
       </c>
       <c r="O107" s="5">
         <f t="shared" si="22"/>
-        <v>106846.88</v>
+        <v>106935.88</v>
       </c>
       <c r="P107" s="85">
         <f t="shared" si="24"/>
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="64"/>
       <c r="B108" s="23"/>
       <c r="C108" s="23" t="s">
@@ -11475,25 +11433,25 @@
       </c>
       <c r="L108" s="17">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M108" s="135">
         <v>0</v>
       </c>
       <c r="N108" s="130">
         <f t="shared" si="21"/>
-        <v>87954.89</v>
+        <v>88038.89</v>
       </c>
       <c r="O108" s="5">
         <f t="shared" si="22"/>
-        <v>93232.89</v>
+        <v>93321.89</v>
       </c>
       <c r="P108" s="85">
         <f t="shared" si="24"/>
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="64"/>
       <c r="B109" s="23"/>
       <c r="C109" s="23" t="s">
@@ -11527,25 +11485,25 @@
       </c>
       <c r="L109" s="17">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M109" s="135">
         <v>0</v>
       </c>
       <c r="N109" s="130">
         <f t="shared" si="21"/>
-        <v>60236.9</v>
+        <v>60320.9</v>
       </c>
       <c r="O109" s="5">
         <f t="shared" si="22"/>
-        <v>63851.9</v>
+        <v>63940.9</v>
       </c>
       <c r="P109" s="85">
         <f t="shared" si="24"/>
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="64"/>
       <c r="B110" s="23"/>
       <c r="C110" s="23" t="s">
@@ -11579,25 +11537,25 @@
       </c>
       <c r="L110" s="17">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M110" s="135">
         <v>0</v>
       </c>
       <c r="N110" s="130">
         <f t="shared" si="21"/>
-        <v>60236.91</v>
+        <v>60320.91</v>
       </c>
       <c r="O110" s="5">
         <f t="shared" si="22"/>
-        <v>63851.91</v>
+        <v>63940.91</v>
       </c>
       <c r="P110" s="85">
         <f t="shared" si="24"/>
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="64"/>
       <c r="B111" s="23"/>
       <c r="C111" s="224" t="s">
@@ -11630,25 +11588,25 @@
       </c>
       <c r="L111" s="231">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M111" s="233">
         <v>0</v>
       </c>
       <c r="N111" s="234">
         <f t="shared" si="21"/>
-        <v>292458.92</v>
+        <v>292542.92</v>
       </c>
       <c r="O111" s="235">
         <f t="shared" si="22"/>
-        <v>310006.92</v>
+        <v>310095.92</v>
       </c>
       <c r="P111" s="85">
         <f t="shared" si="24"/>
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="64"/>
       <c r="B112" s="23"/>
       <c r="C112" s="23" t="s">
@@ -11682,25 +11640,25 @@
       </c>
       <c r="L112" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M112" s="135">
         <v>0</v>
       </c>
       <c r="N112" s="130">
         <f t="shared" si="21"/>
-        <v>60236.93</v>
+        <v>60320.93</v>
       </c>
       <c r="O112" s="97">
         <f t="shared" si="22"/>
-        <v>63851.93</v>
+        <v>63940.93</v>
       </c>
       <c r="P112" s="85">
         <f t="shared" si="24"/>
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="64"/>
       <c r="B113" s="23"/>
       <c r="C113" s="23" t="s">
@@ -11734,25 +11692,25 @@
       </c>
       <c r="L113" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M113" s="135">
         <v>0</v>
       </c>
       <c r="N113" s="130">
         <f t="shared" si="21"/>
-        <v>60236.94</v>
+        <v>60320.94</v>
       </c>
       <c r="O113" s="97">
         <f t="shared" si="22"/>
-        <v>63851.94</v>
+        <v>63940.94</v>
       </c>
       <c r="P113" s="85">
         <f t="shared" si="24"/>
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="64"/>
       <c r="B114" s="23"/>
       <c r="C114" s="23" t="s">
@@ -11785,25 +11743,25 @@
       </c>
       <c r="L114" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M114" s="135">
         <v>0</v>
       </c>
       <c r="N114" s="130">
         <f t="shared" si="21"/>
-        <v>57801.95</v>
+        <v>57885.95</v>
       </c>
       <c r="O114" s="97">
         <f t="shared" si="22"/>
-        <v>61270.95</v>
+        <v>61359.95</v>
       </c>
       <c r="P114" s="85">
         <f t="shared" si="24"/>
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="64"/>
       <c r="B115" s="23"/>
       <c r="C115" s="23" t="s">
@@ -11837,25 +11795,25 @@
       </c>
       <c r="L115" s="95">
         <f t="shared" si="20"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M115" s="135">
         <v>0</v>
       </c>
       <c r="N115" s="130">
         <f t="shared" si="21"/>
-        <v>60236.959999999999</v>
+        <v>60320.959999999999</v>
       </c>
       <c r="O115" s="97">
         <f t="shared" si="22"/>
-        <v>63851.96</v>
+        <v>63940.959999999999</v>
       </c>
       <c r="P115" s="85">
         <f t="shared" si="24"/>
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="64"/>
       <c r="B116" s="23"/>
       <c r="C116" s="23" t="s">
@@ -11889,25 +11847,25 @@
       </c>
       <c r="L116" s="95">
         <f t="shared" ref="L116:L132" si="30">N$2*F116</f>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M116" s="135">
         <v>0</v>
       </c>
       <c r="N116" s="130">
         <f t="shared" si="21"/>
-        <v>60236.97</v>
+        <v>60320.97</v>
       </c>
       <c r="O116" s="97">
         <f t="shared" si="22"/>
-        <v>63851.97</v>
+        <v>63940.97</v>
       </c>
       <c r="P116" s="85">
         <f t="shared" si="24"/>
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="64"/>
       <c r="B117" s="23"/>
       <c r="C117" s="23" t="s">
@@ -11942,25 +11900,25 @@
       </c>
       <c r="L117" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M117" s="135">
         <v>0</v>
       </c>
       <c r="N117" s="130">
         <f t="shared" si="21"/>
-        <v>100797.98</v>
+        <v>100881.98</v>
       </c>
       <c r="O117" s="97">
         <f t="shared" si="22"/>
-        <v>106846.98</v>
+        <v>106935.98</v>
       </c>
       <c r="P117" s="85">
         <f t="shared" si="24"/>
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="64"/>
       <c r="B118" s="23"/>
       <c r="C118" s="23" t="s">
@@ -11993,25 +11951,25 @@
       </c>
       <c r="L118" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M118" s="135">
         <v>0</v>
       </c>
       <c r="N118" s="130">
         <f t="shared" si="21"/>
-        <v>146019.99</v>
+        <v>146103.99</v>
       </c>
       <c r="O118" s="97">
         <f t="shared" si="22"/>
-        <v>154781.99</v>
+        <v>154870.99</v>
       </c>
       <c r="P118" s="85">
         <f t="shared" si="24"/>
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="64"/>
       <c r="B119" s="23"/>
       <c r="C119" s="23" t="s">
@@ -12047,18 +12005,18 @@
       </c>
       <c r="L119" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M119" s="135">
         <v>0</v>
       </c>
       <c r="N119" s="130">
         <f t="shared" si="21"/>
-        <v>60237</v>
+        <v>60321</v>
       </c>
       <c r="O119" s="97">
         <f t="shared" si="22"/>
-        <v>63852</v>
+        <v>63941</v>
       </c>
       <c r="P119" s="85">
         <f t="shared" si="24"/>
@@ -12068,7 +12026,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="80"/>
       <c r="B120" s="23"/>
       <c r="C120" s="23" t="s">
@@ -12102,25 +12060,25 @@
       </c>
       <c r="L120" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M120" s="135">
         <v>0</v>
       </c>
       <c r="N120" s="130">
         <f t="shared" si="21"/>
-        <v>60237.01</v>
+        <v>60321.01</v>
       </c>
       <c r="O120" s="97">
         <f t="shared" si="22"/>
-        <v>63852.01</v>
+        <v>63941.01</v>
       </c>
       <c r="P120" s="85">
         <f t="shared" si="24"/>
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="80"/>
       <c r="B121" s="23"/>
       <c r="C121" s="23" t="s">
@@ -12154,25 +12112,25 @@
       </c>
       <c r="L121" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M121" s="135">
         <v>0</v>
       </c>
       <c r="N121" s="130">
         <f t="shared" si="21"/>
-        <v>60237.02</v>
+        <v>60321.02</v>
       </c>
       <c r="O121" s="97">
         <f t="shared" si="22"/>
-        <v>63852.02</v>
+        <v>63941.02</v>
       </c>
       <c r="P121" s="85">
         <f t="shared" si="24"/>
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="80"/>
       <c r="B122" s="23"/>
       <c r="C122" s="23" t="s">
@@ -12208,25 +12166,25 @@
       </c>
       <c r="L122" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M122" s="135">
         <v>0</v>
       </c>
       <c r="N122" s="130">
         <f t="shared" si="21"/>
-        <v>60237.03</v>
+        <v>60321.03</v>
       </c>
       <c r="O122" s="97">
         <f t="shared" si="22"/>
-        <v>63852.03</v>
+        <v>63941.03</v>
       </c>
       <c r="P122" s="85">
         <f t="shared" si="24"/>
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="80"/>
       <c r="B123" s="23"/>
       <c r="C123" s="23" t="s">
@@ -12260,25 +12218,25 @@
       </c>
       <c r="L123" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M123" s="135">
         <v>0</v>
       </c>
       <c r="N123" s="130">
         <f t="shared" si="21"/>
-        <v>60237.04</v>
+        <v>60321.04</v>
       </c>
       <c r="O123" s="97">
         <f t="shared" si="22"/>
-        <v>63852.04</v>
+        <v>63941.04</v>
       </c>
       <c r="P123" s="85">
         <f t="shared" si="24"/>
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="80"/>
       <c r="B124" s="23"/>
       <c r="C124" s="23" t="s">
@@ -12312,25 +12270,25 @@
       </c>
       <c r="L124" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M124" s="135">
         <v>0</v>
       </c>
       <c r="N124" s="130">
         <f t="shared" si="21"/>
-        <v>60237.05</v>
+        <v>60321.05</v>
       </c>
       <c r="O124" s="97">
         <f t="shared" si="22"/>
-        <v>63852.05</v>
+        <v>63941.05</v>
       </c>
       <c r="P124" s="85">
         <f t="shared" si="24"/>
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="80"/>
       <c r="B125" s="23"/>
       <c r="C125" s="23" t="s">
@@ -12364,18 +12322,18 @@
       </c>
       <c r="L125" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M125" s="135">
         <v>0</v>
       </c>
       <c r="N125" s="130">
         <f t="shared" si="21"/>
-        <v>60237.06</v>
+        <v>60321.06</v>
       </c>
       <c r="O125" s="97">
         <f t="shared" si="22"/>
-        <v>63852.06</v>
+        <v>63941.06</v>
       </c>
       <c r="P125" s="85">
         <f t="shared" si="24"/>
@@ -12385,7 +12343,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="118"/>
       <c r="B126" s="113"/>
       <c r="C126" s="23" t="s">
@@ -12420,25 +12378,25 @@
       </c>
       <c r="L126" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M126" s="135">
         <v>0</v>
       </c>
       <c r="N126" s="130">
         <f t="shared" si="21"/>
-        <v>97888.07</v>
+        <v>97972.07</v>
       </c>
       <c r="O126" s="97">
         <f t="shared" si="22"/>
-        <v>103762.07</v>
+        <v>103851.07</v>
       </c>
       <c r="P126" s="85">
         <f t="shared" si="24"/>
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="118"/>
       <c r="B127" s="113"/>
       <c r="C127" s="23" t="s">
@@ -12472,25 +12430,25 @@
       </c>
       <c r="L127" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M127" s="135">
         <v>0</v>
       </c>
       <c r="N127" s="130">
         <f t="shared" si="21"/>
-        <v>60237.08</v>
+        <v>60321.08</v>
       </c>
       <c r="O127" s="97">
         <f t="shared" si="22"/>
-        <v>63852.08</v>
+        <v>63941.08</v>
       </c>
       <c r="P127" s="85">
         <f t="shared" si="24"/>
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="80"/>
       <c r="B128" s="23"/>
       <c r="C128" s="23" t="s">
@@ -12523,25 +12481,25 @@
       </c>
       <c r="L128" s="95">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M128" s="135">
         <v>0</v>
       </c>
       <c r="N128" s="130">
         <f t="shared" si="21"/>
-        <v>74878.09</v>
+        <v>74962.09</v>
       </c>
       <c r="O128" s="97">
         <f t="shared" si="22"/>
-        <v>79372.09</v>
+        <v>79461.09</v>
       </c>
       <c r="P128" s="85">
         <f t="shared" si="24"/>
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="80"/>
       <c r="B129" s="23"/>
       <c r="C129" s="23" t="s">
@@ -12574,25 +12532,25 @@
       </c>
       <c r="L129" s="17">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M129" s="135">
         <v>0</v>
       </c>
       <c r="N129" s="130">
         <f t="shared" si="21"/>
-        <v>57802.1</v>
+        <v>57886.1</v>
       </c>
       <c r="O129" s="5">
         <f t="shared" si="22"/>
-        <v>61271.1</v>
+        <v>61360.1</v>
       </c>
       <c r="P129" s="85">
         <f t="shared" si="24"/>
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="80"/>
       <c r="B130" s="23"/>
       <c r="C130" s="23" t="s">
@@ -12626,25 +12584,25 @@
       </c>
       <c r="L130" s="17">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M130" s="135">
         <v>0</v>
       </c>
       <c r="N130" s="130">
         <f t="shared" si="21"/>
-        <v>60237.11</v>
+        <v>60321.11</v>
       </c>
       <c r="O130" s="5">
         <f t="shared" si="22"/>
-        <v>63852.11</v>
+        <v>63941.11</v>
       </c>
       <c r="P130" s="85">
         <f t="shared" si="24"/>
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="80" t="s">
         <v>24</v>
       </c>
@@ -12680,25 +12638,25 @@
       </c>
       <c r="L131" s="17">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M131" s="135">
         <v>0</v>
       </c>
       <c r="N131" s="130">
         <f t="shared" si="21"/>
-        <v>60237.120000000003</v>
+        <v>60321.120000000003</v>
       </c>
       <c r="O131" s="5">
         <f t="shared" si="22"/>
-        <v>63852.12</v>
+        <v>63941.120000000003</v>
       </c>
       <c r="P131" s="85">
         <f t="shared" si="24"/>
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="80" t="s">
         <v>24</v>
       </c>
@@ -12734,25 +12692,25 @@
       </c>
       <c r="L132" s="17">
         <f t="shared" si="30"/>
-        <v>60236.161144000005</v>
+        <v>60319.697419999997</v>
       </c>
       <c r="M132" s="135">
         <v>0</v>
       </c>
       <c r="N132" s="130">
         <f t="shared" si="21"/>
-        <v>60237.13</v>
+        <v>60321.13</v>
       </c>
       <c r="O132" s="5">
         <f t="shared" si="22"/>
-        <v>63852.13</v>
+        <v>63941.13</v>
       </c>
       <c r="P132" s="85">
         <f t="shared" si="24"/>
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="34" t="s">
         <v>24</v>
       </c>
@@ -12771,7 +12729,7 @@
       <c r="N133" s="2"/>
       <c r="O133" s="5"/>
     </row>
-    <row r="134" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="18"/>
       <c r="B134" s="18"/>
       <c r="C134" s="18"/>
@@ -12800,7 +12758,7 @@
       </c>
       <c r="L134" s="19">
         <f>SUM(L15:L133)</f>
-        <v>26041741.451639973</v>
+        <v>26075519.163240064</v>
       </c>
       <c r="M134" s="117">
         <f t="shared" si="32"/>
@@ -12808,51 +12766,51 @@
       </c>
       <c r="N134" s="20">
         <f t="shared" si="32"/>
-        <v>36314162.326048389</v>
+        <v>36347958.326048382</v>
       </c>
       <c r="O134" s="19">
         <f t="shared" si="32"/>
-        <v>38493071.401011288</v>
+        <v>38528894.401011288</v>
       </c>
       <c r="Q134" s="39"/>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="L135" s="41">
         <f>L134-M1</f>
-        <v>-184213.94836002588</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="331"/>
-      <c r="D136" s="331"/>
-      <c r="E136" s="331"/>
-      <c r="F136" s="331"/>
-      <c r="G136" s="331"/>
-      <c r="H136" s="331"/>
-      <c r="I136" s="331"/>
-      <c r="J136" s="331"/>
-      <c r="K136" s="331"/>
-      <c r="L136" s="331"/>
-      <c r="M136" s="331"/>
-      <c r="N136" s="331"/>
-      <c r="O136" s="331"/>
-    </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C137" s="331"/>
-      <c r="D137" s="331"/>
-      <c r="E137" s="331"/>
-      <c r="F137" s="331"/>
-      <c r="G137" s="331"/>
-      <c r="H137" s="331"/>
-      <c r="I137" s="331"/>
-      <c r="J137" s="331"/>
-      <c r="K137" s="331"/>
-      <c r="L137" s="331"/>
-      <c r="M137" s="331"/>
-      <c r="N137" s="331"/>
-      <c r="O137" s="331"/>
-    </row>
-    <row r="138" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-150436.23675993457</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C136" s="323"/>
+      <c r="D136" s="323"/>
+      <c r="E136" s="323"/>
+      <c r="F136" s="323"/>
+      <c r="G136" s="323"/>
+      <c r="H136" s="323"/>
+      <c r="I136" s="323"/>
+      <c r="J136" s="323"/>
+      <c r="K136" s="323"/>
+      <c r="L136" s="323"/>
+      <c r="M136" s="323"/>
+      <c r="N136" s="323"/>
+      <c r="O136" s="323"/>
+    </row>
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C137" s="323"/>
+      <c r="D137" s="323"/>
+      <c r="E137" s="323"/>
+      <c r="F137" s="323"/>
+      <c r="G137" s="323"/>
+      <c r="H137" s="323"/>
+      <c r="I137" s="323"/>
+      <c r="J137" s="323"/>
+      <c r="K137" s="323"/>
+      <c r="L137" s="323"/>
+      <c r="M137" s="323"/>
+      <c r="N137" s="323"/>
+      <c r="O137" s="323"/>
+    </row>
+    <row r="138" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C138" s="49"/>
       <c r="D138" s="49"/>
       <c r="E138" s="49"/>
@@ -12867,129 +12825,129 @@
       <c r="N138" s="49"/>
       <c r="O138" s="49"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C139" s="281" t="s">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C139" s="286" t="s">
         <v>243</v>
       </c>
-      <c r="D139" s="281"/>
-      <c r="E139" s="281"/>
-      <c r="F139" s="281"/>
-      <c r="G139" s="281"/>
-      <c r="H139" s="281"/>
-      <c r="I139" s="281"/>
-      <c r="J139" s="281"/>
-      <c r="K139" s="281"/>
-      <c r="L139" s="281"/>
-      <c r="M139" s="281"/>
-      <c r="N139" s="281"/>
-      <c r="O139" s="281"/>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C140" s="281"/>
-      <c r="D140" s="281"/>
-      <c r="E140" s="281"/>
-      <c r="F140" s="281"/>
-      <c r="G140" s="281"/>
-      <c r="H140" s="281"/>
-      <c r="I140" s="281"/>
-      <c r="J140" s="281"/>
-      <c r="K140" s="281"/>
-      <c r="L140" s="281"/>
-      <c r="M140" s="281"/>
-      <c r="N140" s="281"/>
-      <c r="O140" s="281"/>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C141" s="281"/>
-      <c r="D141" s="281"/>
-      <c r="E141" s="281"/>
-      <c r="F141" s="281"/>
-      <c r="G141" s="281"/>
-      <c r="H141" s="281"/>
-      <c r="I141" s="281"/>
-      <c r="J141" s="281"/>
-      <c r="K141" s="281"/>
-      <c r="L141" s="281"/>
-      <c r="M141" s="281"/>
-      <c r="N141" s="281"/>
-      <c r="O141" s="281"/>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C142" s="281"/>
-      <c r="D142" s="281"/>
-      <c r="E142" s="281"/>
-      <c r="F142" s="281"/>
-      <c r="G142" s="281"/>
-      <c r="H142" s="281"/>
-      <c r="I142" s="281"/>
-      <c r="J142" s="281"/>
-      <c r="K142" s="281"/>
-      <c r="L142" s="281"/>
-      <c r="M142" s="281"/>
-      <c r="N142" s="281"/>
-      <c r="O142" s="281"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="281"/>
-      <c r="D143" s="281"/>
-      <c r="E143" s="281"/>
-      <c r="F143" s="281"/>
-      <c r="G143" s="281"/>
-      <c r="H143" s="281"/>
-      <c r="I143" s="281"/>
-      <c r="J143" s="281"/>
-      <c r="K143" s="281"/>
-      <c r="L143" s="281"/>
-      <c r="M143" s="281"/>
-      <c r="N143" s="281"/>
-      <c r="O143" s="281"/>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C144" s="281"/>
-      <c r="D144" s="281"/>
-      <c r="E144" s="281"/>
-      <c r="F144" s="281"/>
-      <c r="G144" s="281"/>
-      <c r="H144" s="281"/>
-      <c r="I144" s="281"/>
-      <c r="J144" s="281"/>
-      <c r="K144" s="281"/>
-      <c r="L144" s="281"/>
-      <c r="M144" s="281"/>
-      <c r="N144" s="281"/>
-      <c r="O144" s="281"/>
-    </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C145" s="281"/>
-      <c r="D145" s="281"/>
-      <c r="E145" s="281"/>
-      <c r="F145" s="281"/>
-      <c r="G145" s="281"/>
-      <c r="H145" s="281"/>
-      <c r="I145" s="281"/>
-      <c r="J145" s="281"/>
-      <c r="K145" s="281"/>
-      <c r="L145" s="281"/>
-      <c r="M145" s="281"/>
-      <c r="N145" s="281"/>
-      <c r="O145" s="281"/>
-    </row>
-    <row r="146" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C146" s="281"/>
-      <c r="D146" s="281"/>
-      <c r="E146" s="281"/>
-      <c r="F146" s="281"/>
-      <c r="G146" s="281"/>
-      <c r="H146" s="281"/>
-      <c r="I146" s="281"/>
-      <c r="J146" s="281"/>
-      <c r="K146" s="281"/>
-      <c r="L146" s="281"/>
-      <c r="M146" s="281"/>
-      <c r="N146" s="281"/>
-      <c r="O146" s="281"/>
-    </row>
-    <row r="147" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D139" s="286"/>
+      <c r="E139" s="286"/>
+      <c r="F139" s="286"/>
+      <c r="G139" s="286"/>
+      <c r="H139" s="286"/>
+      <c r="I139" s="286"/>
+      <c r="J139" s="286"/>
+      <c r="K139" s="286"/>
+      <c r="L139" s="286"/>
+      <c r="M139" s="286"/>
+      <c r="N139" s="286"/>
+      <c r="O139" s="286"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C140" s="286"/>
+      <c r="D140" s="286"/>
+      <c r="E140" s="286"/>
+      <c r="F140" s="286"/>
+      <c r="G140" s="286"/>
+      <c r="H140" s="286"/>
+      <c r="I140" s="286"/>
+      <c r="J140" s="286"/>
+      <c r="K140" s="286"/>
+      <c r="L140" s="286"/>
+      <c r="M140" s="286"/>
+      <c r="N140" s="286"/>
+      <c r="O140" s="286"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C141" s="286"/>
+      <c r="D141" s="286"/>
+      <c r="E141" s="286"/>
+      <c r="F141" s="286"/>
+      <c r="G141" s="286"/>
+      <c r="H141" s="286"/>
+      <c r="I141" s="286"/>
+      <c r="J141" s="286"/>
+      <c r="K141" s="286"/>
+      <c r="L141" s="286"/>
+      <c r="M141" s="286"/>
+      <c r="N141" s="286"/>
+      <c r="O141" s="286"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C142" s="286"/>
+      <c r="D142" s="286"/>
+      <c r="E142" s="286"/>
+      <c r="F142" s="286"/>
+      <c r="G142" s="286"/>
+      <c r="H142" s="286"/>
+      <c r="I142" s="286"/>
+      <c r="J142" s="286"/>
+      <c r="K142" s="286"/>
+      <c r="L142" s="286"/>
+      <c r="M142" s="286"/>
+      <c r="N142" s="286"/>
+      <c r="O142" s="286"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C143" s="286"/>
+      <c r="D143" s="286"/>
+      <c r="E143" s="286"/>
+      <c r="F143" s="286"/>
+      <c r="G143" s="286"/>
+      <c r="H143" s="286"/>
+      <c r="I143" s="286"/>
+      <c r="J143" s="286"/>
+      <c r="K143" s="286"/>
+      <c r="L143" s="286"/>
+      <c r="M143" s="286"/>
+      <c r="N143" s="286"/>
+      <c r="O143" s="286"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C144" s="286"/>
+      <c r="D144" s="286"/>
+      <c r="E144" s="286"/>
+      <c r="F144" s="286"/>
+      <c r="G144" s="286"/>
+      <c r="H144" s="286"/>
+      <c r="I144" s="286"/>
+      <c r="J144" s="286"/>
+      <c r="K144" s="286"/>
+      <c r="L144" s="286"/>
+      <c r="M144" s="286"/>
+      <c r="N144" s="286"/>
+      <c r="O144" s="286"/>
+    </row>
+    <row r="145" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C145" s="286"/>
+      <c r="D145" s="286"/>
+      <c r="E145" s="286"/>
+      <c r="F145" s="286"/>
+      <c r="G145" s="286"/>
+      <c r="H145" s="286"/>
+      <c r="I145" s="286"/>
+      <c r="J145" s="286"/>
+      <c r="K145" s="286"/>
+      <c r="L145" s="286"/>
+      <c r="M145" s="286"/>
+      <c r="N145" s="286"/>
+      <c r="O145" s="286"/>
+    </row>
+    <row r="146" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C146" s="286"/>
+      <c r="D146" s="286"/>
+      <c r="E146" s="286"/>
+      <c r="F146" s="286"/>
+      <c r="G146" s="286"/>
+      <c r="H146" s="286"/>
+      <c r="I146" s="286"/>
+      <c r="J146" s="286"/>
+      <c r="K146" s="286"/>
+      <c r="L146" s="286"/>
+      <c r="M146" s="286"/>
+      <c r="N146" s="286"/>
+      <c r="O146" s="286"/>
+    </row>
+    <row r="147" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="49"/>
       <c r="D147" s="49"/>
       <c r="E147" s="49"/>
@@ -13004,7 +12962,7 @@
       <c r="N147" s="49"/>
       <c r="O147" s="49"/>
     </row>
-    <row r="148" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C148" s="49"/>
       <c r="D148" s="49"/>
       <c r="E148" s="49"/>
@@ -13019,119 +12977,126 @@
       <c r="N148" s="49"/>
       <c r="O148" s="49"/>
     </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="330" t="s">
+    <row r="149" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C149" s="322" t="s">
         <v>242</v>
       </c>
-      <c r="D149" s="330"/>
-      <c r="E149" s="330"/>
-      <c r="F149" s="330"/>
-      <c r="G149" s="330"/>
-      <c r="H149" s="330"/>
-      <c r="I149" s="330"/>
-      <c r="J149" s="330"/>
-      <c r="K149" s="330"/>
-      <c r="L149" s="330"/>
-      <c r="M149" s="330"/>
-      <c r="N149" s="330"/>
-      <c r="O149" s="330"/>
-    </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="330"/>
-      <c r="D150" s="330"/>
-      <c r="E150" s="330"/>
-      <c r="F150" s="330"/>
-      <c r="G150" s="330"/>
-      <c r="H150" s="330"/>
-      <c r="I150" s="330"/>
-      <c r="J150" s="330"/>
-      <c r="K150" s="330"/>
-      <c r="L150" s="330"/>
-      <c r="M150" s="330"/>
-      <c r="N150" s="330"/>
-      <c r="O150" s="330"/>
-    </row>
-    <row r="151" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C151" s="330"/>
-      <c r="D151" s="330"/>
-      <c r="E151" s="330"/>
-      <c r="F151" s="330"/>
-      <c r="G151" s="330"/>
-      <c r="H151" s="330"/>
-      <c r="I151" s="330"/>
-      <c r="J151" s="330"/>
-      <c r="K151" s="330"/>
-      <c r="L151" s="330"/>
-      <c r="M151" s="330"/>
-      <c r="N151" s="330"/>
-      <c r="O151" s="330"/>
+      <c r="D149" s="322"/>
+      <c r="E149" s="322"/>
+      <c r="F149" s="322"/>
+      <c r="G149" s="322"/>
+      <c r="H149" s="322"/>
+      <c r="I149" s="322"/>
+      <c r="J149" s="322"/>
+      <c r="K149" s="322"/>
+      <c r="L149" s="322"/>
+      <c r="M149" s="322"/>
+      <c r="N149" s="322"/>
+      <c r="O149" s="322"/>
+    </row>
+    <row r="150" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C150" s="322"/>
+      <c r="D150" s="322"/>
+      <c r="E150" s="322"/>
+      <c r="F150" s="322"/>
+      <c r="G150" s="322"/>
+      <c r="H150" s="322"/>
+      <c r="I150" s="322"/>
+      <c r="J150" s="322"/>
+      <c r="K150" s="322"/>
+      <c r="L150" s="322"/>
+      <c r="M150" s="322"/>
+      <c r="N150" s="322"/>
+      <c r="O150" s="322"/>
+    </row>
+    <row r="151" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C151" s="322"/>
+      <c r="D151" s="322"/>
+      <c r="E151" s="322"/>
+      <c r="F151" s="322"/>
+      <c r="G151" s="322"/>
+      <c r="H151" s="322"/>
+      <c r="I151" s="322"/>
+      <c r="J151" s="322"/>
+      <c r="K151" s="322"/>
+      <c r="L151" s="322"/>
+      <c r="M151" s="322"/>
+      <c r="N151" s="322"/>
+      <c r="O151" s="322"/>
       <c r="Q151" s="55">
         <f>M1-L134</f>
-        <v>184213.94836002588</v>
-      </c>
-    </row>
-    <row r="152" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="330"/>
-      <c r="D152" s="330"/>
-      <c r="E152" s="330"/>
-      <c r="F152" s="330"/>
-      <c r="G152" s="330"/>
-      <c r="H152" s="330"/>
-      <c r="I152" s="330"/>
-      <c r="J152" s="330"/>
-      <c r="K152" s="330"/>
-      <c r="L152" s="330"/>
-      <c r="M152" s="330"/>
-      <c r="N152" s="330"/>
-      <c r="O152" s="330"/>
-    </row>
-    <row r="153" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="330"/>
-      <c r="D153" s="330"/>
-      <c r="E153" s="330"/>
-      <c r="F153" s="330"/>
-      <c r="G153" s="330"/>
-      <c r="H153" s="330"/>
-      <c r="I153" s="330"/>
-      <c r="J153" s="330"/>
-      <c r="K153" s="330"/>
-      <c r="L153" s="330"/>
-      <c r="M153" s="330"/>
-      <c r="N153" s="330"/>
-      <c r="O153" s="330"/>
-    </row>
-    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="330"/>
-      <c r="D154" s="330"/>
-      <c r="E154" s="330"/>
-      <c r="F154" s="330"/>
-      <c r="G154" s="330"/>
-      <c r="H154" s="330"/>
-      <c r="I154" s="330"/>
-      <c r="J154" s="330"/>
-      <c r="K154" s="330"/>
-      <c r="L154" s="330"/>
-      <c r="M154" s="330"/>
-      <c r="N154" s="330"/>
-      <c r="O154" s="330"/>
-    </row>
-    <row r="155" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C155" s="330"/>
-      <c r="D155" s="330"/>
-      <c r="E155" s="330"/>
-      <c r="F155" s="330"/>
-      <c r="G155" s="330"/>
-      <c r="H155" s="330"/>
-      <c r="I155" s="330"/>
-      <c r="J155" s="330"/>
-      <c r="K155" s="330"/>
-      <c r="L155" s="330"/>
-      <c r="M155" s="330"/>
-      <c r="N155" s="330"/>
-      <c r="O155" s="330"/>
+        <v>150436.23675993457</v>
+      </c>
+    </row>
+    <row r="152" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="322"/>
+      <c r="D152" s="322"/>
+      <c r="E152" s="322"/>
+      <c r="F152" s="322"/>
+      <c r="G152" s="322"/>
+      <c r="H152" s="322"/>
+      <c r="I152" s="322"/>
+      <c r="J152" s="322"/>
+      <c r="K152" s="322"/>
+      <c r="L152" s="322"/>
+      <c r="M152" s="322"/>
+      <c r="N152" s="322"/>
+      <c r="O152" s="322"/>
+    </row>
+    <row r="153" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="322"/>
+      <c r="D153" s="322"/>
+      <c r="E153" s="322"/>
+      <c r="F153" s="322"/>
+      <c r="G153" s="322"/>
+      <c r="H153" s="322"/>
+      <c r="I153" s="322"/>
+      <c r="J153" s="322"/>
+      <c r="K153" s="322"/>
+      <c r="L153" s="322"/>
+      <c r="M153" s="322"/>
+      <c r="N153" s="322"/>
+      <c r="O153" s="322"/>
+    </row>
+    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="322"/>
+      <c r="D154" s="322"/>
+      <c r="E154" s="322"/>
+      <c r="F154" s="322"/>
+      <c r="G154" s="322"/>
+      <c r="H154" s="322"/>
+      <c r="I154" s="322"/>
+      <c r="J154" s="322"/>
+      <c r="K154" s="322"/>
+      <c r="L154" s="322"/>
+      <c r="M154" s="322"/>
+      <c r="N154" s="322"/>
+      <c r="O154" s="322"/>
+    </row>
+    <row r="155" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C155" s="322"/>
+      <c r="D155" s="322"/>
+      <c r="E155" s="322"/>
+      <c r="F155" s="322"/>
+      <c r="G155" s="322"/>
+      <c r="H155" s="322"/>
+      <c r="I155" s="322"/>
+      <c r="J155" s="322"/>
+      <c r="K155" s="322"/>
+      <c r="L155" s="322"/>
+      <c r="M155" s="322"/>
+      <c r="N155" s="322"/>
+      <c r="O155" s="322"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="R15:S16"/>
     <mergeCell ref="G12:G14"/>
     <mergeCell ref="C149:O155"/>
@@ -13148,13 +13113,6 @@
     <mergeCell ref="C6:O9"/>
     <mergeCell ref="C10:O11"/>
     <mergeCell ref="A1:E5"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="E12:E14"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13165,29 +13123,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DJ82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.33203125" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.5703125" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="362" t="s">
         <v>300</v>
       </c>
@@ -13207,7 +13165,7 @@
       <c r="O1" s="363"/>
       <c r="R1" s="31"/>
     </row>
-    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="364"/>
       <c r="B2" s="364"/>
       <c r="C2" s="364"/>
@@ -13225,7 +13183,7 @@
       <c r="O2" s="365"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:27" s="166" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" s="166" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="359" t="s">
         <v>358</v>
       </c>
@@ -13256,89 +13214,89 @@
       <c r="Z3" s="167"/>
       <c r="AA3" s="167"/>
     </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="323" t="s">
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="320" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="323" t="s">
+      <c r="B4" s="320" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="323" t="s">
+      <c r="C4" s="320" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="323" t="s">
+      <c r="D4" s="320" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="320" t="s">
+      <c r="E4" s="328" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="320" t="s">
+      <c r="F4" s="328" t="s">
         <v>327</v>
       </c>
-      <c r="G4" s="320" t="s">
+      <c r="G4" s="328" t="s">
         <v>260</v>
       </c>
-      <c r="H4" s="320" t="s">
+      <c r="H4" s="328" t="s">
         <v>332</v>
       </c>
-      <c r="I4" s="320" t="s">
+      <c r="I4" s="328" t="s">
         <v>339</v>
       </c>
       <c r="J4" s="366" t="s">
         <v>328</v>
       </c>
       <c r="K4" s="83"/>
-      <c r="L4" s="371" t="s">
+      <c r="L4" s="370" t="s">
         <v>336</v>
       </c>
-      <c r="M4" s="320" t="s">
+      <c r="M4" s="328" t="s">
         <v>337</v>
       </c>
-      <c r="N4" s="320" t="s">
+      <c r="N4" s="328" t="s">
         <v>329</v>
       </c>
-      <c r="O4" s="320" t="s">
+      <c r="O4" s="328" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="31"/>
     </row>
-    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="324"/>
-      <c r="B5" s="324"/>
-      <c r="C5" s="324"/>
-      <c r="D5" s="324"/>
-      <c r="E5" s="321"/>
-      <c r="F5" s="321"/>
-      <c r="G5" s="321"/>
-      <c r="H5" s="321"/>
-      <c r="I5" s="321"/>
+    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="321"/>
+      <c r="B5" s="321"/>
+      <c r="C5" s="321"/>
+      <c r="D5" s="321"/>
+      <c r="E5" s="329"/>
+      <c r="F5" s="329"/>
+      <c r="G5" s="329"/>
+      <c r="H5" s="329"/>
+      <c r="I5" s="329"/>
       <c r="J5" s="367"/>
       <c r="K5" s="83"/>
-      <c r="L5" s="372"/>
-      <c r="M5" s="321"/>
-      <c r="N5" s="321"/>
-      <c r="O5" s="321"/>
+      <c r="L5" s="371"/>
+      <c r="M5" s="329"/>
+      <c r="N5" s="329"/>
+      <c r="O5" s="329"/>
       <c r="R5" s="31"/>
     </row>
-    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="370"/>
-      <c r="B6" s="370"/>
-      <c r="C6" s="370"/>
-      <c r="D6" s="370"/>
-      <c r="E6" s="369"/>
-      <c r="F6" s="369"/>
-      <c r="G6" s="369"/>
-      <c r="H6" s="369"/>
-      <c r="I6" s="369"/>
+    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="369"/>
+      <c r="B6" s="369"/>
+      <c r="C6" s="369"/>
+      <c r="D6" s="369"/>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="G6" s="358"/>
+      <c r="H6" s="358"/>
+      <c r="I6" s="358"/>
       <c r="J6" s="368"/>
       <c r="K6" s="136"/>
-      <c r="L6" s="373"/>
-      <c r="M6" s="369"/>
-      <c r="N6" s="369"/>
-      <c r="O6" s="369"/>
+      <c r="L6" s="372"/>
+      <c r="M6" s="358"/>
+      <c r="N6" s="358"/>
+      <c r="O6" s="358"/>
       <c r="R6" s="31"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="137" t="s">
         <v>109</v>
       </c>
@@ -13390,10 +13348,10 @@
       <c r="P7" s="70">
         <v>0.7</v>
       </c>
-      <c r="R7" s="329"/>
-      <c r="S7" s="329"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="R7" s="319"/>
+      <c r="S7" s="319"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="137" t="s">
         <v>308</v>
       </c>
@@ -13447,10 +13405,10 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="329"/>
-      <c r="S8" s="329"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="R8" s="319"/>
+      <c r="S8" s="319"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="137" t="s">
         <v>110</v>
       </c>
@@ -13506,7 +13464,7 @@
       </c>
       <c r="S9" s="31"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="137" t="s">
         <v>111</v>
       </c>
@@ -13561,7 +13519,7 @@
       </c>
       <c r="S10" s="31"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="141" t="s">
         <v>112</v>
       </c>
@@ -13616,7 +13574,7 @@
       </c>
       <c r="S11" s="31"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="144" t="s">
         <v>40</v>
       </c>
@@ -13672,7 +13630,7 @@
       </c>
       <c r="S12" s="31"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="137" t="s">
         <v>41</v>
       </c>
@@ -13727,7 +13685,7 @@
       </c>
       <c r="S13" s="31"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="137" t="s">
         <v>42</v>
       </c>
@@ -13783,7 +13741,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="137" t="s">
         <v>43</v>
       </c>
@@ -13839,7 +13797,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="137" t="s">
         <v>44</v>
       </c>
@@ -13893,7 +13851,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A17" s="137" t="s">
         <v>45</v>
       </c>
@@ -13949,7 +13907,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A18" s="137" t="s">
         <v>46</v>
       </c>
@@ -14005,7 +13963,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A19" s="137" t="s">
         <v>47</v>
       </c>
@@ -14059,7 +14017,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A20" s="137" t="s">
         <v>48</v>
       </c>
@@ -14113,7 +14071,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A21" s="137" t="s">
         <v>49</v>
       </c>
@@ -14167,7 +14125,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A22" s="137" t="s">
         <v>50</v>
       </c>
@@ -14221,7 +14179,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A23" s="137" t="s">
         <v>51</v>
       </c>
@@ -14275,7 +14233,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A24" s="137" t="s">
         <v>52</v>
       </c>
@@ -14329,7 +14287,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A25" s="137" t="s">
         <v>53</v>
       </c>
@@ -14383,7 +14341,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A26" s="137" t="s">
         <v>54</v>
       </c>
@@ -14439,7 +14397,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A27" s="137" t="s">
         <v>55</v>
       </c>
@@ -14497,7 +14455,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="28" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A28" s="137" t="s">
         <v>56</v>
       </c>
@@ -14551,7 +14509,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="29" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A29" s="137" t="s">
         <v>57</v>
       </c>
@@ -14603,7 +14561,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A30" s="137" t="s">
         <v>58</v>
       </c>
@@ -14660,7 +14618,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="31" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A31" s="137" t="s">
         <v>59</v>
       </c>
@@ -14716,7 +14674,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="137" t="s">
         <v>60</v>
       </c>
@@ -14871,7 +14829,7 @@
       <c r="DI32" s="46"/>
       <c r="DJ32" s="46"/>
     </row>
-    <row r="33" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="137" t="s">
         <v>61</v>
       </c>
@@ -15025,7 +14983,7 @@
       <c r="DI33" s="46"/>
       <c r="DJ33" s="46"/>
     </row>
-    <row r="34" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="137" t="s">
         <v>62</v>
       </c>
@@ -15181,7 +15139,7 @@
       <c r="DI34" s="46"/>
       <c r="DJ34" s="46"/>
     </row>
-    <row r="35" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="137" t="s">
         <v>63</v>
       </c>
@@ -15331,7 +15289,7 @@
       <c r="DI35" s="46"/>
       <c r="DJ35" s="46"/>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="137" t="s">
         <v>64</v>
       </c>
@@ -15387,7 +15345,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="137" t="s">
         <v>65</v>
       </c>
@@ -15441,7 +15399,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="137" t="s">
         <v>66</v>
       </c>
@@ -15503,7 +15461,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A39" s="137" t="s">
         <v>67</v>
       </c>
@@ -15559,7 +15517,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="40" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A40" s="137" t="s">
         <v>68</v>
       </c>
@@ -15613,7 +15571,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="41" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A41" s="137" t="s">
         <v>69</v>
       </c>
@@ -15667,7 +15625,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A42" s="137" t="s">
         <v>70</v>
       </c>
@@ -15723,7 +15681,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A43" s="137" t="s">
         <v>71</v>
       </c>
@@ -15780,7 +15738,7 @@
       </c>
       <c r="Q43" s="31"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="137" t="s">
         <v>72</v>
       </c>
@@ -15837,7 +15795,7 @@
       </c>
       <c r="Q44" s="31"/>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="137" t="s">
         <v>73</v>
       </c>
@@ -15894,7 +15852,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="137" t="s">
         <v>74</v>
       </c>
@@ -15948,7 +15906,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="137" t="s">
         <v>75</v>
       </c>
@@ -16002,7 +15960,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="137" t="s">
         <v>76</v>
       </c>
@@ -16059,7 +16017,7 @@
       </c>
       <c r="R48" s="39"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="137" t="s">
         <v>77</v>
       </c>
@@ -16113,7 +16071,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="137" t="s">
         <v>78</v>
       </c>
@@ -16170,7 +16128,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="137" t="s">
         <v>79</v>
       </c>
@@ -16224,7 +16182,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="137" t="s">
         <v>80</v>
       </c>
@@ -16281,7 +16239,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="137" t="s">
         <v>81</v>
       </c>
@@ -16340,7 +16298,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="137" t="s">
         <v>82</v>
       </c>
@@ -16396,7 +16354,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="137" t="s">
         <v>83</v>
       </c>
@@ -16450,7 +16408,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="137" t="s">
         <v>84</v>
       </c>
@@ -16506,7 +16464,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="137" t="s">
         <v>85</v>
       </c>
@@ -16562,7 +16520,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="137" t="s">
         <v>86</v>
       </c>
@@ -16618,7 +16576,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="137" t="s">
         <v>87</v>
       </c>
@@ -16675,7 +16633,7 @@
       </c>
       <c r="S59" s="125"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="137" t="s">
         <v>88</v>
       </c>
@@ -16732,7 +16690,7 @@
       </c>
       <c r="S60" s="31"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="137" t="s">
         <v>89</v>
       </c>
@@ -16787,7 +16745,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="137" t="s">
         <v>90</v>
       </c>
@@ -16843,7 +16801,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="137" t="s">
         <v>91</v>
       </c>
@@ -16897,7 +16855,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="137" t="s">
         <v>92</v>
       </c>
@@ -16954,7 +16912,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="137" t="s">
         <v>93</v>
       </c>
@@ -17011,7 +16969,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="137" t="s">
         <v>94</v>
       </c>
@@ -17068,7 +17026,7 @@
       </c>
       <c r="Q66" s="46"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="137" t="s">
         <v>95</v>
       </c>
@@ -17124,7 +17082,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="137" t="s">
         <v>96</v>
       </c>
@@ -17170,7 +17128,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="137" t="s">
         <v>97</v>
       </c>
@@ -17225,7 +17183,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="137" t="s">
         <v>98</v>
       </c>
@@ -17281,7 +17239,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="137" t="s">
         <v>99</v>
       </c>
@@ -17337,7 +17295,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="137" t="s">
         <v>100</v>
       </c>
@@ -17393,7 +17351,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="137" t="s">
         <v>101</v>
       </c>
@@ -17448,7 +17406,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="137" t="s">
         <v>102</v>
       </c>
@@ -17504,7 +17462,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="137" t="s">
         <v>103</v>
       </c>
@@ -17558,7 +17516,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="137" t="s">
         <v>104</v>
       </c>
@@ -17614,7 +17572,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="137" t="s">
         <v>105</v>
       </c>
@@ -17671,7 +17629,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="137" t="s">
         <v>106</v>
       </c>
@@ -17727,7 +17685,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="137" t="s">
         <v>107</v>
       </c>
@@ -17783,7 +17741,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="137" t="s">
         <v>108</v>
       </c>
@@ -17839,7 +17797,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="23"/>
       <c r="B81" s="23"/>
       <c r="C81" s="64"/>
@@ -17856,7 +17814,7 @@
       <c r="N81" s="96"/>
       <c r="O81" s="97"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="18"/>
       <c r="B82" s="18"/>
       <c r="C82" s="18"/>
@@ -17897,6 +17855,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="L4:L6"/>
     <mergeCell ref="M4:M6"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A1:O2"/>
@@ -17913,7 +17872,6 @@
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="H4:H6"/>
     <mergeCell ref="I4:I6"/>
-    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="85" orientation="landscape" r:id="rId1"/>
@@ -17923,14 +17881,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="C1:M17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K1" s="46"/>
       <c r="L1" s="46"/>
       <c r="M1" s="46"/>
     </row>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C2" s="242" t="s">
         <v>343</v>
       </c>
@@ -17947,7 +17905,7 @@
       <c r="L2" s="46"/>
       <c r="M2" s="46"/>
     </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C3" s="244" t="s">
         <v>344</v>
       </c>
@@ -17962,11 +17920,11 @@
       <c r="H3" s="172"/>
       <c r="I3" s="173"/>
       <c r="J3" s="174"/>
-      <c r="K3" s="263"/>
-      <c r="L3" s="263"/>
+      <c r="K3" s="262"/>
+      <c r="L3" s="262"/>
       <c r="M3" s="247"/>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C4" s="244" t="s">
         <v>346</v>
       </c>
@@ -17985,11 +17943,11 @@
       </c>
       <c r="I4" s="173"/>
       <c r="J4" s="174"/>
-      <c r="K4" s="263"/>
-      <c r="L4" s="263"/>
+      <c r="K4" s="262"/>
+      <c r="L4" s="262"/>
       <c r="M4" s="247"/>
     </row>
-    <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="168" t="s">
         <v>350</v>
       </c>
@@ -18000,62 +17958,62 @@
       <c r="H5" s="46"/>
       <c r="I5" s="46"/>
       <c r="J5" s="175"/>
-      <c r="K5" s="263"/>
-      <c r="L5" s="263"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
       <c r="M5" s="247"/>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C6" s="374" t="s">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C6" s="373" t="s">
         <v>377</v>
       </c>
-      <c r="D6" s="375"/>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
-      <c r="G6" s="375"/>
-      <c r="H6" s="375"/>
-      <c r="I6" s="375"/>
-      <c r="J6" s="376"/>
-      <c r="K6" s="262"/>
-      <c r="L6" s="262"/>
+      <c r="D6" s="374"/>
+      <c r="E6" s="374"/>
+      <c r="F6" s="374"/>
+      <c r="G6" s="374"/>
+      <c r="H6" s="374"/>
+      <c r="I6" s="374"/>
+      <c r="J6" s="375"/>
+      <c r="K6" s="261"/>
+      <c r="L6" s="261"/>
       <c r="M6" s="46"/>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="377"/>
-      <c r="D7" s="378"/>
-      <c r="E7" s="378"/>
-      <c r="F7" s="378"/>
-      <c r="G7" s="378"/>
-      <c r="H7" s="378"/>
-      <c r="I7" s="378"/>
-      <c r="J7" s="379"/>
-      <c r="K7" s="262"/>
-      <c r="L7" s="262"/>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C7" s="376"/>
+      <c r="D7" s="377"/>
+      <c r="E7" s="377"/>
+      <c r="F7" s="377"/>
+      <c r="G7" s="377"/>
+      <c r="H7" s="377"/>
+      <c r="I7" s="377"/>
+      <c r="J7" s="378"/>
+      <c r="K7" s="261"/>
+      <c r="L7" s="261"/>
       <c r="M7" s="46"/>
     </row>
-    <row r="8" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="380"/>
-      <c r="D8" s="381"/>
-      <c r="E8" s="381"/>
-      <c r="F8" s="381"/>
-      <c r="G8" s="381"/>
-      <c r="H8" s="381"/>
-      <c r="I8" s="381"/>
-      <c r="J8" s="382"/>
+    <row r="8" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="379"/>
+      <c r="D8" s="380"/>
+      <c r="E8" s="380"/>
+      <c r="F8" s="380"/>
+      <c r="G8" s="380"/>
+      <c r="H8" s="380"/>
+      <c r="I8" s="380"/>
+      <c r="J8" s="381"/>
       <c r="K8" s="46"/>
       <c r="L8" s="46"/>
       <c r="M8" s="46"/>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
       <c r="K9" s="46"/>
       <c r="L9" s="46"/>
       <c r="M9" s="46"/>
     </row>
-    <row r="10" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K10" s="46"/>
       <c r="L10" s="46"/>
       <c r="M10" s="46"/>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C11" s="248" t="s">
         <v>343</v>
       </c>
@@ -18069,7 +18027,7 @@
       <c r="I11" s="170"/>
       <c r="J11" s="171"/>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C12" s="250" t="s">
         <v>344</v>
       </c>
@@ -18086,11 +18044,11 @@
       </c>
       <c r="I12" s="173"/>
       <c r="J12" s="174"/>
-      <c r="K12" s="262"/>
-      <c r="L12" s="262"/>
-      <c r="M12" s="262"/>
-    </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="K12" s="261"/>
+      <c r="L12" s="261"/>
+      <c r="M12" s="261"/>
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C13" s="250" t="s">
         <v>346</v>
       </c>
@@ -18109,11 +18067,11 @@
       </c>
       <c r="I13" s="173"/>
       <c r="J13" s="174"/>
-      <c r="K13" s="262"/>
-      <c r="L13" s="262"/>
-      <c r="M13" s="262"/>
-    </row>
-    <row r="14" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="261"/>
+      <c r="L13" s="261"/>
+      <c r="M13" s="261"/>
+    </row>
+    <row r="14" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C14" s="168" t="s">
         <v>350</v>
       </c>
@@ -18124,47 +18082,47 @@
       <c r="H14" s="46"/>
       <c r="I14" s="46"/>
       <c r="J14" s="175"/>
-      <c r="K14" s="262"/>
-      <c r="L14" s="262"/>
-      <c r="M14" s="262"/>
-    </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="374" t="s">
+      <c r="K14" s="261"/>
+      <c r="L14" s="261"/>
+      <c r="M14" s="261"/>
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C15" s="373" t="s">
         <v>380</v>
       </c>
-      <c r="D15" s="375"/>
-      <c r="E15" s="375"/>
-      <c r="F15" s="375"/>
-      <c r="G15" s="375"/>
-      <c r="H15" s="375"/>
-      <c r="I15" s="375"/>
-      <c r="J15" s="376"/>
-      <c r="K15" s="262"/>
-      <c r="L15" s="262"/>
-      <c r="M15" s="262"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="377"/>
-      <c r="D16" s="378"/>
-      <c r="E16" s="378"/>
-      <c r="F16" s="378"/>
-      <c r="G16" s="378"/>
-      <c r="H16" s="378"/>
-      <c r="I16" s="378"/>
-      <c r="J16" s="379"/>
-      <c r="K16" s="262"/>
-      <c r="L16" s="262"/>
-      <c r="M16" s="262"/>
-    </row>
-    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="380"/>
-      <c r="D17" s="381"/>
-      <c r="E17" s="381"/>
-      <c r="F17" s="381"/>
-      <c r="G17" s="381"/>
-      <c r="H17" s="381"/>
-      <c r="I17" s="381"/>
-      <c r="J17" s="382"/>
+      <c r="D15" s="374"/>
+      <c r="E15" s="374"/>
+      <c r="F15" s="374"/>
+      <c r="G15" s="374"/>
+      <c r="H15" s="374"/>
+      <c r="I15" s="374"/>
+      <c r="J15" s="375"/>
+      <c r="K15" s="261"/>
+      <c r="L15" s="261"/>
+      <c r="M15" s="261"/>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C16" s="376"/>
+      <c r="D16" s="377"/>
+      <c r="E16" s="377"/>
+      <c r="F16" s="377"/>
+      <c r="G16" s="377"/>
+      <c r="H16" s="377"/>
+      <c r="I16" s="377"/>
+      <c r="J16" s="378"/>
+      <c r="K16" s="261"/>
+      <c r="L16" s="261"/>
+      <c r="M16" s="261"/>
+    </row>
+    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="379"/>
+      <c r="D17" s="380"/>
+      <c r="E17" s="380"/>
+      <c r="F17" s="380"/>
+      <c r="G17" s="380"/>
+      <c r="H17" s="380"/>
+      <c r="I17" s="380"/>
+      <c r="J17" s="381"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/EL MIRADOR/Agosto/Agosto - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Agosto/Agosto - EL MIRADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C477E8-B334-483B-BB06-7E08B931DCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F9C002-5B5D-4489-B12F-EFA983CA80F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$127</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2325,24 +2330,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2454,14 +2441,53 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2480,15 +2506,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2559,17 +2576,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2606,15 +2620,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2724,9 +2729,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2764,9 +2769,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2799,9 +2804,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2834,9 +2856,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3011,24 +3050,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N142"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.6640625" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" customWidth="1"/>
-    <col min="12" max="12" width="16.109375" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.33203125" customWidth="1"/>
+    <col min="17" max="17" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="68"/>
       <c r="B1" s="76"/>
       <c r="C1" s="81" t="s">
@@ -3042,7 +3081,7 @@
       <c r="I1" s="66"/>
       <c r="J1" s="67"/>
     </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="69"/>
       <c r="B2" s="77"/>
       <c r="C2" s="77" t="s">
@@ -3056,7 +3095,7 @@
       <c r="I2" s="78"/>
       <c r="J2" s="65"/>
     </row>
-    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="69"/>
       <c r="B3" s="77"/>
       <c r="C3" s="77" t="s">
@@ -3072,7 +3111,7 @@
       <c r="I3" s="78"/>
       <c r="J3" s="65"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="69"/>
       <c r="B4" s="77"/>
       <c r="C4" s="77" t="s">
@@ -3086,7 +3125,7 @@
       <c r="I4" s="78"/>
       <c r="J4" s="65"/>
     </row>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="72"/>
       <c r="B5" s="77"/>
       <c r="C5" s="77" t="s">
@@ -3102,7 +3141,7 @@
       <c r="I5" s="77"/>
       <c r="J5" s="73"/>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="72"/>
       <c r="B6" s="77"/>
       <c r="C6" s="77" t="s">
@@ -3116,7 +3155,7 @@
       <c r="I6" s="77"/>
       <c r="J6" s="73"/>
     </row>
-    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="74"/>
       <c r="B7" s="75"/>
       <c r="C7" s="75"/>
@@ -3128,115 +3167,115 @@
       <c r="I7" s="75"/>
       <c r="J7" s="79"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="276" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="313" t="s">
         <v>243</v>
       </c>
-      <c r="B14" s="276"/>
-      <c r="C14" s="276"/>
-      <c r="D14" s="276"/>
-      <c r="E14" s="276"/>
-      <c r="F14" s="276"/>
-      <c r="G14" s="276"/>
-      <c r="H14" s="276"/>
-      <c r="I14" s="276"/>
-      <c r="J14" s="276"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="276"/>
-      <c r="B15" s="276"/>
-      <c r="C15" s="276"/>
-      <c r="D15" s="276"/>
-      <c r="E15" s="276"/>
-      <c r="F15" s="276"/>
-      <c r="G15" s="276"/>
-      <c r="H15" s="276"/>
-      <c r="I15" s="276"/>
-      <c r="J15" s="276"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="276"/>
-      <c r="B16" s="276"/>
-      <c r="C16" s="276"/>
-      <c r="D16" s="276"/>
-      <c r="E16" s="276"/>
-      <c r="F16" s="276"/>
-      <c r="G16" s="276"/>
-      <c r="H16" s="276"/>
-      <c r="I16" s="276"/>
-      <c r="J16" s="276"/>
-    </row>
-    <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="276"/>
-      <c r="B17" s="276"/>
-      <c r="C17" s="276"/>
-      <c r="D17" s="276"/>
-      <c r="E17" s="276"/>
-      <c r="F17" s="276"/>
-      <c r="G17" s="276"/>
-      <c r="H17" s="276"/>
-      <c r="I17" s="276"/>
-      <c r="J17" s="276"/>
-    </row>
-    <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="276"/>
-      <c r="B18" s="276"/>
-      <c r="C18" s="276"/>
-      <c r="D18" s="276"/>
-      <c r="E18" s="276"/>
-      <c r="F18" s="276"/>
-      <c r="G18" s="276"/>
-      <c r="H18" s="276"/>
-      <c r="I18" s="276"/>
-      <c r="J18" s="276"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="313"/>
+      <c r="C14" s="313"/>
+      <c r="D14" s="313"/>
+      <c r="E14" s="313"/>
+      <c r="F14" s="313"/>
+      <c r="G14" s="313"/>
+      <c r="H14" s="313"/>
+      <c r="I14" s="313"/>
+      <c r="J14" s="313"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="313"/>
+      <c r="B15" s="313"/>
+      <c r="C15" s="313"/>
+      <c r="D15" s="313"/>
+      <c r="E15" s="313"/>
+      <c r="F15" s="313"/>
+      <c r="G15" s="313"/>
+      <c r="H15" s="313"/>
+      <c r="I15" s="313"/>
+      <c r="J15" s="313"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="313"/>
+      <c r="B16" s="313"/>
+      <c r="C16" s="313"/>
+      <c r="D16" s="313"/>
+      <c r="E16" s="313"/>
+      <c r="F16" s="313"/>
+      <c r="G16" s="313"/>
+      <c r="H16" s="313"/>
+      <c r="I16" s="313"/>
+      <c r="J16" s="313"/>
+    </row>
+    <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="313"/>
+      <c r="B17" s="313"/>
+      <c r="C17" s="313"/>
+      <c r="D17" s="313"/>
+      <c r="E17" s="313"/>
+      <c r="F17" s="313"/>
+      <c r="G17" s="313"/>
+      <c r="H17" s="313"/>
+      <c r="I17" s="313"/>
+      <c r="J17" s="313"/>
+    </row>
+    <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="313"/>
+      <c r="B18" s="313"/>
+      <c r="C18" s="313"/>
+      <c r="D18" s="313"/>
+      <c r="E18" s="313"/>
+      <c r="F18" s="313"/>
+      <c r="G18" s="313"/>
+      <c r="H18" s="313"/>
+      <c r="I18" s="313"/>
+      <c r="J18" s="313"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="H19" s="60"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="277" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="314" t="s">
         <v>381</v>
       </c>
-      <c r="B20" s="277"/>
-      <c r="C20" s="277"/>
-      <c r="D20" s="277"/>
-      <c r="E20" s="277"/>
-      <c r="F20" s="277"/>
-      <c r="G20" s="277"/>
-      <c r="H20" s="277"/>
-      <c r="I20" s="277"/>
-      <c r="J20" s="277"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="277"/>
-      <c r="B21" s="277"/>
-      <c r="C21" s="277"/>
-      <c r="D21" s="277"/>
-      <c r="E21" s="277"/>
-      <c r="F21" s="277"/>
-      <c r="G21" s="277"/>
-      <c r="H21" s="277"/>
-      <c r="I21" s="277"/>
-      <c r="J21" s="277"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="277"/>
-      <c r="B22" s="277"/>
-      <c r="C22" s="277"/>
-      <c r="D22" s="277"/>
-      <c r="E22" s="277"/>
-      <c r="F22" s="277"/>
-      <c r="G22" s="277"/>
-      <c r="H22" s="277"/>
-      <c r="I22" s="277"/>
-      <c r="J22" s="277"/>
-    </row>
-    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="314"/>
+      <c r="C20" s="314"/>
+      <c r="D20" s="314"/>
+      <c r="E20" s="314"/>
+      <c r="F20" s="314"/>
+      <c r="G20" s="314"/>
+      <c r="H20" s="314"/>
+      <c r="I20" s="314"/>
+      <c r="J20" s="314"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="314"/>
+      <c r="B21" s="314"/>
+      <c r="C21" s="314"/>
+      <c r="D21" s="314"/>
+      <c r="E21" s="314"/>
+      <c r="F21" s="314"/>
+      <c r="G21" s="314"/>
+      <c r="H21" s="314"/>
+      <c r="I21" s="314"/>
+      <c r="J21" s="314"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="314"/>
+      <c r="B22" s="314"/>
+      <c r="C22" s="314"/>
+      <c r="D22" s="314"/>
+      <c r="E22" s="314"/>
+      <c r="F22" s="314"/>
+      <c r="G22" s="314"/>
+      <c r="H22" s="314"/>
+      <c r="I22" s="314"/>
+      <c r="J22" s="314"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="56"/>
       <c r="B23" s="56"/>
       <c r="C23" s="56"/>
@@ -3248,7 +3287,7 @@
       <c r="I23" s="56"/>
       <c r="J23" s="56"/>
     </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="180" t="s">
         <v>18</v>
       </c>
@@ -3274,7 +3313,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="185" t="s">
         <v>335</v>
       </c>
@@ -3289,7 +3328,7 @@
       <c r="J25" s="186"/>
       <c r="L25" s="43"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="187" t="s">
         <v>359</v>
       </c>
@@ -3310,7 +3349,7 @@
       <c r="J26" s="157"/>
       <c r="L26" s="43"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="188" t="s">
         <v>35</v>
       </c>
@@ -3353,7 +3392,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="187" t="s">
         <v>232</v>
       </c>
@@ -3368,7 +3407,7 @@
       <c r="J28" s="186"/>
       <c r="L28" s="43"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="187"/>
       <c r="B29" s="157"/>
       <c r="C29" s="157"/>
@@ -3381,7 +3420,7 @@
       <c r="J29" s="186"/>
       <c r="L29" s="43"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="188" t="s">
         <v>16</v>
       </c>
@@ -3409,7 +3448,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="187" t="s">
         <v>228</v>
       </c>
@@ -3424,7 +3463,7 @@
       <c r="J31" s="190"/>
       <c r="L31" s="43"/>
     </row>
-    <row r="32" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="119" t="s">
         <v>351</v>
       </c>
@@ -3445,7 +3484,7 @@
       <c r="J32" s="190"/>
       <c r="L32" s="43"/>
     </row>
-    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="119" t="s">
         <v>231</v>
       </c>
@@ -3466,7 +3505,7 @@
       <c r="J33" s="190"/>
       <c r="L33" s="43"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="119"/>
       <c r="B34" s="119"/>
       <c r="C34" s="119"/>
@@ -3479,7 +3518,7 @@
       <c r="J34" s="190"/>
       <c r="L34" s="43"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="188" t="s">
         <v>230</v>
       </c>
@@ -3522,7 +3561,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="187" t="s">
         <v>1</v>
       </c>
@@ -3537,7 +3576,7 @@
       <c r="J36" s="157"/>
       <c r="L36" s="43"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="157"/>
       <c r="B37" s="157"/>
       <c r="C37" s="157"/>
@@ -3550,7 +3589,7 @@
       <c r="J37" s="157"/>
       <c r="L37" s="43"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="157"/>
       <c r="B38" s="157"/>
       <c r="C38" s="157"/>
@@ -3563,7 +3602,7 @@
       <c r="J38" s="157"/>
       <c r="L38" s="43"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="157"/>
       <c r="B39" s="157"/>
       <c r="C39" s="193"/>
@@ -3576,7 +3615,7 @@
       <c r="J39" s="157"/>
       <c r="L39" s="43"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="188" t="s">
         <v>229</v>
       </c>
@@ -3619,7 +3658,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="187" t="s">
         <v>221</v>
       </c>
@@ -3634,7 +3673,7 @@
       <c r="J41" s="267"/>
       <c r="L41" s="43"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="157" t="s">
         <v>225</v>
       </c>
@@ -3675,9 +3714,9 @@
       </c>
       <c r="L42" s="43"/>
     </row>
-    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="278"/>
-      <c r="B43" s="279"/>
+    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="315"/>
+      <c r="B43" s="316"/>
       <c r="C43" s="157"/>
       <c r="D43" s="32"/>
       <c r="E43" s="186"/>
@@ -3689,7 +3728,7 @@
       <c r="K43" s="31"/>
       <c r="L43" s="43"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="188" t="s">
         <v>2</v>
       </c>
@@ -3732,7 +3771,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="187" t="s">
         <v>3</v>
       </c>
@@ -3747,7 +3786,7 @@
       <c r="J45" s="157"/>
       <c r="L45" s="43"/>
     </row>
-    <row r="46" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="197" t="s">
         <v>371</v>
       </c>
@@ -3793,7 +3832,7 @@
       <c r="M46" s="55"/>
       <c r="N46" s="55"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="157" t="s">
         <v>226</v>
       </c>
@@ -3839,7 +3878,7 @@
       <c r="M47" s="55"/>
       <c r="N47" s="55"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="157" t="s">
         <v>227</v>
       </c>
@@ -3876,7 +3915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="197" t="s">
         <v>385</v>
       </c>
@@ -3907,7 +3946,7 @@
       <c r="M49" s="55"/>
       <c r="N49" s="55"/>
     </row>
-    <row r="50" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="274" t="s">
         <v>386</v>
       </c>
@@ -3944,7 +3983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="119" t="s">
         <v>257</v>
       </c>
@@ -3975,7 +4014,7 @@
       <c r="M51" s="55"/>
       <c r="N51" s="55"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="119" t="s">
         <v>258</v>
       </c>
@@ -4027,7 +4066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="199" t="s">
         <v>256</v>
       </c>
@@ -4060,7 +4099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="188" t="s">
         <v>4</v>
       </c>
@@ -4107,7 +4146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="157"/>
       <c r="B55" s="157"/>
       <c r="C55" s="157"/>
@@ -4120,7 +4159,7 @@
       <c r="J55" s="157"/>
       <c r="L55" s="43"/>
     </row>
-    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="157"/>
       <c r="B56" s="157"/>
       <c r="C56" s="157"/>
@@ -4133,7 +4172,7 @@
       <c r="J56" s="157"/>
       <c r="L56" s="43"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="187" t="s">
         <v>222</v>
       </c>
@@ -4148,7 +4187,7 @@
       <c r="J57" s="157"/>
       <c r="L57" s="43"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="191" t="s">
         <v>334</v>
       </c>
@@ -4177,11 +4216,11 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="280" t="s">
+    <row r="59" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="317" t="s">
         <v>396</v>
       </c>
-      <c r="B59" s="281"/>
+      <c r="B59" s="318"/>
       <c r="C59" s="119" t="s">
         <v>395</v>
       </c>
@@ -4221,11 +4260,11 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="280" t="s">
+    <row r="60" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="317" t="s">
         <v>394</v>
       </c>
-      <c r="B60" s="281"/>
+      <c r="B60" s="318"/>
       <c r="C60" s="119" t="s">
         <v>395</v>
       </c>
@@ -4265,7 +4304,7 @@
         <v>95700</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="274" t="s">
         <v>403</v>
       </c>
@@ -4309,7 +4348,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="239" t="s">
         <v>404</v>
       </c>
@@ -4353,7 +4392,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="274" t="s">
         <v>405</v>
       </c>
@@ -4382,7 +4421,7 @@
         <v>550000</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="274" t="s">
         <v>391</v>
       </c>
@@ -4426,7 +4465,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="274" t="s">
         <v>400</v>
       </c>
@@ -4470,7 +4509,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="253" t="s">
         <v>370</v>
       </c>
@@ -4514,7 +4553,7 @@
         <v>392015.8</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="188" t="s">
         <v>223</v>
       </c>
@@ -4559,7 +4598,7 @@
       <c r="M67" s="31"/>
       <c r="N67" s="31"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="187" t="s">
         <v>5</v>
       </c>
@@ -4574,7 +4613,7 @@
       <c r="J68" s="157"/>
       <c r="L68" s="43"/>
     </row>
-    <row r="69" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="202" t="s">
         <v>6</v>
       </c>
@@ -4616,12 +4655,12 @@
         <v>372</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="282" t="s">
+    <row r="70" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="276" t="s">
         <v>406</v>
       </c>
-      <c r="B70" s="283"/>
-      <c r="C70" s="284"/>
+      <c r="B70" s="277"/>
+      <c r="C70" s="278"/>
       <c r="D70" s="32">
         <v>0</v>
       </c>
@@ -4652,7 +4691,7 @@
       <c r="L70" s="43"/>
       <c r="N70" s="32"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="157"/>
       <c r="B71" s="157"/>
       <c r="C71" s="157"/>
@@ -4666,7 +4705,7 @@
       <c r="L71" s="43"/>
       <c r="N71" s="31"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="188" t="s">
         <v>7</v>
       </c>
@@ -4710,7 +4749,7 @@
       </c>
       <c r="N72" s="31"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="157" t="s">
         <v>26</v>
       </c>
@@ -4745,7 +4784,7 @@
       </c>
       <c r="L73" s="43"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="157" t="s">
         <v>27</v>
       </c>
@@ -4780,7 +4819,7 @@
       </c>
       <c r="L74" s="43"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="188" t="s">
         <v>224</v>
       </c>
@@ -4823,7 +4862,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="61"/>
       <c r="B76" s="61"/>
       <c r="C76" s="61"/>
@@ -4836,12 +4875,12 @@
       <c r="J76" s="61"/>
       <c r="L76" s="43"/>
     </row>
-    <row r="77" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="316" t="s">
+    <row r="77" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="310" t="s">
         <v>412</v>
       </c>
-      <c r="B77" s="317"/>
-      <c r="C77" s="318"/>
+      <c r="B77" s="311"/>
+      <c r="C77" s="312"/>
       <c r="D77" s="62">
         <f>24275955.4-15214817.97+1950000</f>
         <v>11011137.429999998</v>
@@ -4879,7 +4918,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="207"/>
       <c r="B78" s="208"/>
       <c r="C78" s="208"/>
@@ -4893,7 +4932,7 @@
       <c r="K78" s="31"/>
       <c r="L78" s="43"/>
     </row>
-    <row r="79" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="209" t="s">
         <v>28</v>
       </c>
@@ -4940,7 +4979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="56"/>
       <c r="B80" s="56"/>
       <c r="C80" s="56"/>
@@ -4952,7 +4991,7 @@
       <c r="I80" s="212"/>
       <c r="J80" s="56"/>
     </row>
-    <row r="81" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="213" t="s">
         <v>36</v>
       </c>
@@ -4966,7 +5005,7 @@
       <c r="I81" s="212"/>
       <c r="J81" s="56"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="215" t="s">
         <v>392</v>
       </c>
@@ -4982,7 +5021,7 @@
       <c r="I82" s="212"/>
       <c r="J82" s="56"/>
     </row>
-    <row r="83" spans="1:13" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="215" t="s">
         <v>393</v>
       </c>
@@ -4998,7 +5037,7 @@
       <c r="I83" s="212"/>
       <c r="J83" s="56"/>
     </row>
-    <row r="84" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="216" t="s">
         <v>16</v>
       </c>
@@ -5015,7 +5054,7 @@
       <c r="I84" s="212"/>
       <c r="J84" s="56"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="56"/>
       <c r="B85" s="56"/>
       <c r="C85" s="56"/>
@@ -5026,7 +5065,7 @@
       <c r="H85" s="31"/>
       <c r="I85" s="31"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="56"/>
       <c r="B86" s="56"/>
       <c r="C86" s="56"/>
@@ -5037,13 +5076,13 @@
       <c r="H86" s="40"/>
       <c r="I86" s="40"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A87" s="303" t="s">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" s="297" t="s">
         <v>32</v>
       </c>
-      <c r="B87" s="304"/>
-      <c r="C87" s="304"/>
-      <c r="D87" s="304"/>
+      <c r="B87" s="298"/>
+      <c r="C87" s="298"/>
+      <c r="D87" s="298"/>
       <c r="E87" s="51" t="s">
         <v>10</v>
       </c>
@@ -5063,9 +5102,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="274"/>
-      <c r="B88" s="285"/>
+      <c r="B88" s="279"/>
       <c r="C88" s="220"/>
       <c r="D88" s="32"/>
       <c r="E88" s="198">
@@ -5078,9 +5117,9 @@
       <c r="I88" s="42"/>
       <c r="J88" s="38"/>
     </row>
-    <row r="89" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="305"/>
-      <c r="B89" s="306"/>
+    <row r="89" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="299"/>
+      <c r="B89" s="300"/>
       <c r="C89" s="53"/>
       <c r="D89" s="32"/>
       <c r="E89" s="42"/>
@@ -5090,12 +5129,12 @@
       <c r="I89" s="42"/>
       <c r="J89" s="38"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A90" s="300" t="s">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" s="294" t="s">
         <v>16</v>
       </c>
-      <c r="B90" s="301"/>
-      <c r="C90" s="302"/>
+      <c r="B90" s="295"/>
+      <c r="C90" s="296"/>
       <c r="D90" s="50">
         <f>SUM(D88:D89)</f>
         <v>0</v>
@@ -5121,14 +5160,14 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E92" s="31"/>
       <c r="F92" s="31"/>
       <c r="G92" s="31"/>
       <c r="H92" s="31"/>
       <c r="I92" s="31"/>
     </row>
-    <row r="93" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="26" t="s">
         <v>29</v>
       </c>
@@ -5137,7 +5176,7 @@
         <v>26225955.399999999</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="28" t="s">
         <v>31</v>
       </c>
@@ -5145,45 +5184,45 @@
         <f>D79-D77</f>
         <v>15214817.970000001</v>
       </c>
-      <c r="D94" s="286" t="s">
+      <c r="D94" s="280" t="s">
         <v>373</v>
       </c>
-      <c r="E94" s="286"/>
-      <c r="F94" s="286"/>
-      <c r="G94" s="286"/>
-      <c r="H94" s="286"/>
-      <c r="I94" s="286"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D95" s="286"/>
-      <c r="E95" s="286"/>
-      <c r="F95" s="286"/>
-      <c r="G95" s="286"/>
-      <c r="H95" s="286"/>
-      <c r="I95" s="286"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D96" s="286"/>
-      <c r="E96" s="286"/>
-      <c r="F96" s="286"/>
-      <c r="G96" s="286"/>
-      <c r="H96" s="286"/>
-      <c r="I96" s="286"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E94" s="280"/>
+      <c r="F94" s="280"/>
+      <c r="G94" s="280"/>
+      <c r="H94" s="280"/>
+      <c r="I94" s="280"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D95" s="280"/>
+      <c r="E95" s="280"/>
+      <c r="F95" s="280"/>
+      <c r="G95" s="280"/>
+      <c r="H95" s="280"/>
+      <c r="I95" s="280"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D96" s="280"/>
+      <c r="E96" s="280"/>
+      <c r="F96" s="280"/>
+      <c r="G96" s="280"/>
+      <c r="H96" s="280"/>
+      <c r="I96" s="280"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>409</v>
       </c>
       <c r="B97" s="8"/>
       <c r="C97" s="9"/>
-      <c r="D97" s="286"/>
-      <c r="E97" s="286"/>
-      <c r="F97" s="286"/>
-      <c r="G97" s="286"/>
-      <c r="H97" s="286"/>
-      <c r="I97" s="286"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D97" s="280"/>
+      <c r="E97" s="280"/>
+      <c r="F97" s="280"/>
+      <c r="G97" s="280"/>
+      <c r="H97" s="280"/>
+      <c r="I97" s="280"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>20</v>
       </c>
@@ -5191,14 +5230,14 @@
         <v>1682660.59</v>
       </c>
       <c r="C98" s="11"/>
-      <c r="D98" s="286"/>
-      <c r="E98" s="286"/>
-      <c r="F98" s="286"/>
-      <c r="G98" s="286"/>
-      <c r="H98" s="286"/>
-      <c r="I98" s="286"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D98" s="280"/>
+      <c r="E98" s="280"/>
+      <c r="F98" s="280"/>
+      <c r="G98" s="280"/>
+      <c r="H98" s="280"/>
+      <c r="I98" s="280"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
         <v>21</v>
       </c>
@@ -5209,14 +5248,14 @@
       <c r="C99" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D99" s="286"/>
-      <c r="E99" s="286"/>
-      <c r="F99" s="286"/>
-      <c r="G99" s="286"/>
-      <c r="H99" s="286"/>
-      <c r="I99" s="286"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D99" s="280"/>
+      <c r="E99" s="280"/>
+      <c r="F99" s="280"/>
+      <c r="G99" s="280"/>
+      <c r="H99" s="280"/>
+      <c r="I99" s="280"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
         <v>338</v>
       </c>
@@ -5225,14 +5264,14 @@
         <v>0</v>
       </c>
       <c r="C100" s="11"/>
-      <c r="D100" s="286"/>
-      <c r="E100" s="286"/>
-      <c r="F100" s="286"/>
-      <c r="G100" s="286"/>
-      <c r="H100" s="286"/>
-      <c r="I100" s="286"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D100" s="280"/>
+      <c r="E100" s="280"/>
+      <c r="F100" s="280"/>
+      <c r="G100" s="280"/>
+      <c r="H100" s="280"/>
+      <c r="I100" s="280"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
         <v>34</v>
       </c>
@@ -5241,15 +5280,15 @@
         <v>-15214817.970000001</v>
       </c>
       <c r="C101" s="9"/>
-      <c r="D101" s="286"/>
-      <c r="E101" s="286"/>
-      <c r="F101" s="286"/>
-      <c r="G101" s="286"/>
-      <c r="H101" s="286"/>
-      <c r="I101" s="286"/>
+      <c r="D101" s="280"/>
+      <c r="E101" s="280"/>
+      <c r="F101" s="280"/>
+      <c r="G101" s="280"/>
+      <c r="H101" s="280"/>
+      <c r="I101" s="280"/>
       <c r="K101" s="32"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
         <v>33</v>
       </c>
@@ -5258,15 +5297,15 @@
         <v>0</v>
       </c>
       <c r="C102" s="9"/>
-      <c r="D102" s="286"/>
-      <c r="E102" s="286"/>
-      <c r="F102" s="286"/>
-      <c r="G102" s="286"/>
-      <c r="H102" s="286"/>
-      <c r="I102" s="286"/>
+      <c r="D102" s="280"/>
+      <c r="E102" s="280"/>
+      <c r="F102" s="280"/>
+      <c r="G102" s="280"/>
+      <c r="H102" s="280"/>
+      <c r="I102" s="280"/>
       <c r="K102" s="33"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
         <v>272</v>
       </c>
@@ -5275,15 +5314,15 @@
         <v>0</v>
       </c>
       <c r="C103" s="9"/>
-      <c r="D103" s="286"/>
-      <c r="E103" s="286"/>
-      <c r="F103" s="286"/>
-      <c r="G103" s="286"/>
-      <c r="H103" s="286"/>
-      <c r="I103" s="286"/>
+      <c r="D103" s="280"/>
+      <c r="E103" s="280"/>
+      <c r="F103" s="280"/>
+      <c r="G103" s="280"/>
+      <c r="H103" s="280"/>
+      <c r="I103" s="280"/>
       <c r="K103" s="33"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
         <v>410</v>
       </c>
@@ -5291,15 +5330,15 @@
         <v>-141000</v>
       </c>
       <c r="C104" s="9"/>
-      <c r="D104" s="286"/>
-      <c r="E104" s="286"/>
-      <c r="F104" s="286"/>
-      <c r="G104" s="286"/>
-      <c r="H104" s="286"/>
-      <c r="I104" s="286"/>
+      <c r="D104" s="280"/>
+      <c r="E104" s="280"/>
+      <c r="F104" s="280"/>
+      <c r="G104" s="280"/>
+      <c r="H104" s="280"/>
+      <c r="I104" s="280"/>
       <c r="K104" s="33"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
         <v>30</v>
       </c>
@@ -5308,14 +5347,14 @@
         <v>-20000</v>
       </c>
       <c r="C105" s="13"/>
-      <c r="D105" s="286"/>
-      <c r="E105" s="286"/>
-      <c r="F105" s="286"/>
-      <c r="G105" s="286"/>
-      <c r="H105" s="286"/>
-      <c r="I105" s="286"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D105" s="280"/>
+      <c r="E105" s="280"/>
+      <c r="F105" s="280"/>
+      <c r="G105" s="280"/>
+      <c r="H105" s="280"/>
+      <c r="I105" s="280"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
         <v>36</v>
       </c>
@@ -5324,14 +5363,14 @@
         <v>-406464</v>
       </c>
       <c r="C106" s="13"/>
-      <c r="D106" s="286"/>
-      <c r="E106" s="286"/>
-      <c r="F106" s="286"/>
-      <c r="G106" s="286"/>
-      <c r="H106" s="286"/>
-      <c r="I106" s="286"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D106" s="280"/>
+      <c r="E106" s="280"/>
+      <c r="F106" s="280"/>
+      <c r="G106" s="280"/>
+      <c r="H106" s="280"/>
+      <c r="I106" s="280"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
         <v>23</v>
       </c>
@@ -5340,37 +5379,37 @@
         <v>2575051.7590119969</v>
       </c>
       <c r="C107" s="44"/>
-      <c r="D107" s="286"/>
-      <c r="E107" s="286"/>
-      <c r="F107" s="286"/>
-      <c r="G107" s="286"/>
-      <c r="H107" s="286"/>
-      <c r="I107" s="286"/>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D107" s="280"/>
+      <c r="E107" s="280"/>
+      <c r="F107" s="280"/>
+      <c r="G107" s="280"/>
+      <c r="H107" s="280"/>
+      <c r="I107" s="280"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="13"/>
       <c r="C108" s="9"/>
-      <c r="D108" s="286"/>
-      <c r="E108" s="286"/>
-      <c r="F108" s="286"/>
-      <c r="G108" s="286"/>
-      <c r="H108" s="286"/>
-      <c r="I108" s="286"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D108" s="280"/>
+      <c r="E108" s="280"/>
+      <c r="F108" s="280"/>
+      <c r="G108" s="280"/>
+      <c r="H108" s="280"/>
+      <c r="I108" s="280"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>271</v>
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="9"/>
-      <c r="D109" s="286"/>
-      <c r="E109" s="286"/>
-      <c r="F109" s="286"/>
-      <c r="G109" s="286"/>
-      <c r="H109" s="286"/>
-      <c r="I109" s="286"/>
-    </row>
-    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D109" s="280"/>
+      <c r="E109" s="280"/>
+      <c r="F109" s="280"/>
+      <c r="G109" s="280"/>
+      <c r="H109" s="280"/>
+      <c r="I109" s="280"/>
+    </row>
+    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="177"/>
       <c r="B110" s="21">
         <v>0</v>
@@ -5379,7 +5418,7 @@
       <c r="D110" s="16"/>
       <c r="E110" s="16"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="24" t="s">
         <v>16</v>
       </c>
@@ -5390,17 +5429,17 @@
       <c r="C111" s="9"/>
       <c r="E111" s="16"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="13"/>
       <c r="C112" s="9"/>
       <c r="D112" s="16"/>
     </row>
-    <row r="113" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="13"/>
       <c r="C113" s="9"/>
       <c r="D113" s="16"/>
     </row>
-    <row r="114" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>19</v>
       </c>
@@ -5408,16 +5447,16 @@
         <v>-25817.72</v>
       </c>
       <c r="C114" s="9"/>
-      <c r="D114" s="307" t="s">
+      <c r="D114" s="301" t="s">
         <v>411</v>
       </c>
-      <c r="E114" s="308"/>
-      <c r="F114" s="308"/>
-      <c r="G114" s="308"/>
-      <c r="H114" s="308"/>
-      <c r="I114" s="309"/>
-    </row>
-    <row r="115" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E114" s="302"/>
+      <c r="F114" s="302"/>
+      <c r="G114" s="302"/>
+      <c r="H114" s="302"/>
+      <c r="I114" s="303"/>
+    </row>
+    <row r="115" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="179" t="s">
         <v>407</v>
       </c>
@@ -5425,14 +5464,14 @@
         <v>-24000</v>
       </c>
       <c r="C115" s="9"/>
-      <c r="D115" s="310"/>
-      <c r="E115" s="311"/>
-      <c r="F115" s="311"/>
-      <c r="G115" s="311"/>
-      <c r="H115" s="311"/>
-      <c r="I115" s="312"/>
-    </row>
-    <row r="116" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D115" s="304"/>
+      <c r="E115" s="305"/>
+      <c r="F115" s="305"/>
+      <c r="G115" s="305"/>
+      <c r="H115" s="305"/>
+      <c r="I115" s="306"/>
+    </row>
+    <row r="116" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="179" t="s">
         <v>408</v>
       </c>
@@ -5440,14 +5479,14 @@
         <v>-24000</v>
       </c>
       <c r="C116" s="9"/>
-      <c r="D116" s="310"/>
-      <c r="E116" s="311"/>
-      <c r="F116" s="311"/>
-      <c r="G116" s="311"/>
-      <c r="H116" s="311"/>
-      <c r="I116" s="312"/>
-    </row>
-    <row r="117" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D116" s="304"/>
+      <c r="E116" s="305"/>
+      <c r="F116" s="305"/>
+      <c r="G116" s="305"/>
+      <c r="H116" s="305"/>
+      <c r="I116" s="306"/>
+    </row>
+    <row r="117" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="24" t="s">
         <v>16</v>
       </c>
@@ -5456,31 +5495,31 @@
         <v>-73817.72</v>
       </c>
       <c r="C117" s="9"/>
-      <c r="D117" s="313"/>
-      <c r="E117" s="314"/>
-      <c r="F117" s="314"/>
-      <c r="G117" s="314"/>
-      <c r="H117" s="314"/>
-      <c r="I117" s="315"/>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D117" s="307"/>
+      <c r="E117" s="308"/>
+      <c r="F117" s="308"/>
+      <c r="G117" s="308"/>
+      <c r="H117" s="308"/>
+      <c r="I117" s="309"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="13"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="13"/>
       <c r="F119" s="46"/>
       <c r="G119" s="46"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="F120" s="46"/>
       <c r="G120" s="46"/>
     </row>
-    <row r="121" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H121" s="55"/>
       <c r="I121" s="55"/>
     </row>
-    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
         <v>355</v>
       </c>
@@ -5488,17 +5527,17 @@
         <v>578840</v>
       </c>
       <c r="C122" s="15"/>
-      <c r="D122" s="287" t="s">
+      <c r="D122" s="281" t="s">
         <v>388</v>
       </c>
-      <c r="E122" s="288"/>
-      <c r="F122" s="288"/>
-      <c r="G122" s="288"/>
-      <c r="H122" s="288"/>
-      <c r="I122" s="288"/>
-      <c r="J122" s="289"/>
-    </row>
-    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E122" s="282"/>
+      <c r="F122" s="282"/>
+      <c r="G122" s="282"/>
+      <c r="H122" s="282"/>
+      <c r="I122" s="282"/>
+      <c r="J122" s="283"/>
+    </row>
+    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
         <v>238</v>
       </c>
@@ -5506,15 +5545,15 @@
         <v>20000</v>
       </c>
       <c r="C123" s="15"/>
-      <c r="D123" s="290"/>
-      <c r="E123" s="291"/>
-      <c r="F123" s="291"/>
-      <c r="G123" s="291"/>
-      <c r="H123" s="291"/>
-      <c r="I123" s="291"/>
-      <c r="J123" s="292"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D123" s="284"/>
+      <c r="E123" s="285"/>
+      <c r="F123" s="285"/>
+      <c r="G123" s="285"/>
+      <c r="H123" s="285"/>
+      <c r="I123" s="285"/>
+      <c r="J123" s="286"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="24" t="s">
         <v>16</v>
       </c>
@@ -5523,53 +5562,53 @@
         <v>598840</v>
       </c>
       <c r="C124" s="15"/>
-      <c r="D124" s="290"/>
-      <c r="E124" s="291"/>
-      <c r="F124" s="291"/>
-      <c r="G124" s="291"/>
-      <c r="H124" s="291"/>
-      <c r="I124" s="291"/>
-      <c r="J124" s="292"/>
-    </row>
-    <row r="125" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D124" s="284"/>
+      <c r="E124" s="285"/>
+      <c r="F124" s="285"/>
+      <c r="G124" s="285"/>
+      <c r="H124" s="285"/>
+      <c r="I124" s="285"/>
+      <c r="J124" s="286"/>
+    </row>
+    <row r="125" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C125" s="16"/>
-      <c r="D125" s="290"/>
-      <c r="E125" s="291"/>
-      <c r="F125" s="291"/>
-      <c r="G125" s="291"/>
-      <c r="H125" s="291"/>
-      <c r="I125" s="291"/>
-      <c r="J125" s="292"/>
-    </row>
-    <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="296" t="s">
+      <c r="D125" s="284"/>
+      <c r="E125" s="285"/>
+      <c r="F125" s="285"/>
+      <c r="G125" s="285"/>
+      <c r="H125" s="285"/>
+      <c r="I125" s="285"/>
+      <c r="J125" s="286"/>
+    </row>
+    <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="290" t="s">
         <v>356</v>
       </c>
-      <c r="B126" s="298">
+      <c r="B126" s="292">
         <f>B124+B107+B117</f>
         <v>3100074.0390119967</v>
       </c>
       <c r="C126" s="9"/>
-      <c r="D126" s="290"/>
-      <c r="E126" s="291"/>
-      <c r="F126" s="291"/>
-      <c r="G126" s="291"/>
-      <c r="H126" s="291"/>
-      <c r="I126" s="291"/>
-      <c r="J126" s="292"/>
-    </row>
-    <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="297"/>
-      <c r="B127" s="299"/>
-      <c r="D127" s="293"/>
-      <c r="E127" s="294"/>
-      <c r="F127" s="294"/>
-      <c r="G127" s="294"/>
-      <c r="H127" s="294"/>
-      <c r="I127" s="294"/>
-      <c r="J127" s="295"/>
-    </row>
-    <row r="132" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="D126" s="284"/>
+      <c r="E126" s="285"/>
+      <c r="F126" s="285"/>
+      <c r="G126" s="285"/>
+      <c r="H126" s="285"/>
+      <c r="I126" s="285"/>
+      <c r="J126" s="286"/>
+    </row>
+    <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="291"/>
+      <c r="B127" s="293"/>
+      <c r="D127" s="287"/>
+      <c r="E127" s="288"/>
+      <c r="F127" s="288"/>
+      <c r="G127" s="288"/>
+      <c r="H127" s="288"/>
+      <c r="I127" s="288"/>
+      <c r="J127" s="289"/>
+    </row>
+    <row r="132" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C132" s="46"/>
       <c r="D132" s="46"/>
       <c r="E132" s="46"/>
@@ -5577,7 +5616,7 @@
       <c r="G132" s="46"/>
       <c r="H132" s="46"/>
     </row>
-    <row r="133" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C133" s="46"/>
       <c r="D133" s="46"/>
       <c r="E133" s="46"/>
@@ -5585,7 +5624,7 @@
       <c r="G133" s="46"/>
       <c r="H133" s="46"/>
     </row>
-    <row r="134" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C134" s="46"/>
       <c r="D134" s="263"/>
       <c r="E134" s="46"/>
@@ -5593,7 +5632,7 @@
       <c r="G134" s="46"/>
       <c r="H134" s="46"/>
     </row>
-    <row r="135" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C135" s="46"/>
       <c r="D135" s="263"/>
       <c r="E135" s="46"/>
@@ -5601,7 +5640,7 @@
       <c r="G135" s="46"/>
       <c r="H135" s="46"/>
     </row>
-    <row r="136" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C136" s="46"/>
       <c r="D136" s="46"/>
       <c r="E136" s="46"/>
@@ -5609,7 +5648,7 @@
       <c r="G136" s="46"/>
       <c r="H136" s="46"/>
     </row>
-    <row r="137" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C137" s="46"/>
       <c r="D137" s="46"/>
       <c r="E137" s="46"/>
@@ -5617,7 +5656,7 @@
       <c r="G137" s="46"/>
       <c r="H137" s="46"/>
     </row>
-    <row r="138" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C138" s="46"/>
       <c r="D138" s="46"/>
       <c r="E138" s="46"/>
@@ -5625,7 +5664,7 @@
       <c r="G138" s="46"/>
       <c r="H138" s="46"/>
     </row>
-    <row r="139" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C139" s="46"/>
       <c r="D139" s="46"/>
       <c r="E139" s="46"/>
@@ -5633,7 +5672,7 @@
       <c r="G139" s="46"/>
       <c r="H139" s="46"/>
     </row>
-    <row r="140" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C140" s="46"/>
       <c r="D140" s="46"/>
       <c r="E140" s="46"/>
@@ -5641,7 +5680,7 @@
       <c r="G140" s="46"/>
       <c r="H140" s="46"/>
     </row>
-    <row r="141" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C141" s="46"/>
       <c r="D141" s="46"/>
       <c r="E141" s="46"/>
@@ -5649,7 +5688,7 @@
       <c r="G141" s="46"/>
       <c r="H141" s="46"/>
     </row>
-    <row r="142" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C142" s="46"/>
       <c r="D142" s="46"/>
       <c r="E142" s="46"/>
@@ -5659,6 +5698,15 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A14:J18"/>
+    <mergeCell ref="A20:J22"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A65:B65"/>
     <mergeCell ref="A70:C70"/>
     <mergeCell ref="A88:B88"/>
@@ -5671,15 +5719,6 @@
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="D114:I117"/>
     <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A14:J18"/>
-    <mergeCell ref="A20:J22"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5690,37 +5729,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DJ155"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" customWidth="1"/>
-    <col min="5" max="5" width="25.5546875" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.5546875" customWidth="1"/>
-    <col min="14" max="14" width="17.33203125" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" customWidth="1"/>
-    <col min="16" max="16" width="11.44140625" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" customWidth="1"/>
-    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="348" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="352" t="s">
         <v>298</v>
       </c>
-      <c r="B1" s="349"/>
-      <c r="C1" s="349"/>
-      <c r="D1" s="349"/>
-      <c r="E1" s="349"/>
+      <c r="B1" s="353"/>
+      <c r="C1" s="353"/>
+      <c r="D1" s="353"/>
+      <c r="E1" s="353"/>
       <c r="F1" s="103" t="s">
         <v>274</v>
       </c>
@@ -5732,20 +5771,20 @@
       <c r="L1" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="324">
+      <c r="M1" s="331">
         <f>RESUMEN!D79-N4</f>
         <v>26225955.399999999</v>
       </c>
-      <c r="N1" s="325"/>
+      <c r="N1" s="332"/>
       <c r="O1" s="104"/>
       <c r="P1" s="39"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="350"/>
-      <c r="B2" s="351"/>
-      <c r="C2" s="351"/>
-      <c r="D2" s="351"/>
-      <c r="E2" s="351"/>
+    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="354"/>
+      <c r="B2" s="355"/>
+      <c r="C2" s="355"/>
+      <c r="D2" s="355"/>
+      <c r="E2" s="355"/>
       <c r="F2" s="4" t="s">
         <v>273</v>
       </c>
@@ -5765,12 +5804,12 @@
       <c r="O2" s="105"/>
       <c r="P2" s="39"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="350"/>
-      <c r="B3" s="351"/>
-      <c r="C3" s="351"/>
-      <c r="D3" s="351"/>
-      <c r="E3" s="351"/>
+    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="354"/>
+      <c r="B3" s="355"/>
+      <c r="C3" s="355"/>
+      <c r="D3" s="355"/>
+      <c r="E3" s="355"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -5788,12 +5827,12 @@
       <c r="O3" s="105"/>
       <c r="P3" s="39"/>
     </row>
-    <row r="4" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="350"/>
-      <c r="B4" s="351"/>
-      <c r="C4" s="351"/>
-      <c r="D4" s="351"/>
-      <c r="E4" s="351"/>
+    <row r="4" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="354"/>
+      <c r="B4" s="355"/>
+      <c r="C4" s="355"/>
+      <c r="D4" s="355"/>
+      <c r="E4" s="355"/>
       <c r="F4" s="4" t="s">
         <v>275</v>
       </c>
@@ -5812,12 +5851,12 @@
       <c r="O4" s="107"/>
       <c r="P4" s="6"/>
     </row>
-    <row r="5" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="352"/>
-      <c r="B5" s="353"/>
-      <c r="C5" s="353"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="353"/>
+    <row r="5" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="356"/>
+      <c r="B5" s="357"/>
+      <c r="C5" s="357"/>
+      <c r="D5" s="357"/>
+      <c r="E5" s="357"/>
       <c r="F5" s="108"/>
       <c r="G5" s="108"/>
       <c r="H5" s="108"/>
@@ -5830,98 +5869,98 @@
       <c r="O5" s="111"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="333" t="s">
+      <c r="C6" s="337" t="s">
         <v>368</v>
       </c>
-      <c r="D6" s="334"/>
-      <c r="E6" s="334"/>
-      <c r="F6" s="334"/>
-      <c r="G6" s="334"/>
-      <c r="H6" s="334"/>
-      <c r="I6" s="334"/>
-      <c r="J6" s="334"/>
-      <c r="K6" s="334"/>
-      <c r="L6" s="334"/>
-      <c r="M6" s="334"/>
-      <c r="N6" s="334"/>
-      <c r="O6" s="335"/>
+      <c r="D6" s="338"/>
+      <c r="E6" s="338"/>
+      <c r="F6" s="338"/>
+      <c r="G6" s="338"/>
+      <c r="H6" s="338"/>
+      <c r="I6" s="338"/>
+      <c r="J6" s="338"/>
+      <c r="K6" s="338"/>
+      <c r="L6" s="338"/>
+      <c r="M6" s="338"/>
+      <c r="N6" s="338"/>
+      <c r="O6" s="339"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="336"/>
-      <c r="D7" s="337"/>
-      <c r="E7" s="337"/>
-      <c r="F7" s="337"/>
-      <c r="G7" s="337"/>
-      <c r="H7" s="337"/>
-      <c r="I7" s="337"/>
-      <c r="J7" s="337"/>
-      <c r="K7" s="337"/>
-      <c r="L7" s="337"/>
-      <c r="M7" s="337"/>
-      <c r="N7" s="337"/>
-      <c r="O7" s="338"/>
+      <c r="C7" s="340"/>
+      <c r="D7" s="341"/>
+      <c r="E7" s="341"/>
+      <c r="F7" s="341"/>
+      <c r="G7" s="341"/>
+      <c r="H7" s="341"/>
+      <c r="I7" s="341"/>
+      <c r="J7" s="341"/>
+      <c r="K7" s="341"/>
+      <c r="L7" s="341"/>
+      <c r="M7" s="341"/>
+      <c r="N7" s="341"/>
+      <c r="O7" s="342"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="336"/>
-      <c r="D8" s="337"/>
-      <c r="E8" s="337"/>
-      <c r="F8" s="337"/>
-      <c r="G8" s="337"/>
-      <c r="H8" s="337"/>
-      <c r="I8" s="337"/>
-      <c r="J8" s="337"/>
-      <c r="K8" s="337"/>
-      <c r="L8" s="337"/>
-      <c r="M8" s="337"/>
-      <c r="N8" s="337"/>
-      <c r="O8" s="338"/>
+      <c r="C8" s="340"/>
+      <c r="D8" s="341"/>
+      <c r="E8" s="341"/>
+      <c r="F8" s="341"/>
+      <c r="G8" s="341"/>
+      <c r="H8" s="341"/>
+      <c r="I8" s="341"/>
+      <c r="J8" s="341"/>
+      <c r="K8" s="341"/>
+      <c r="L8" s="341"/>
+      <c r="M8" s="341"/>
+      <c r="N8" s="341"/>
+      <c r="O8" s="342"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="339"/>
-      <c r="D9" s="340"/>
-      <c r="E9" s="340"/>
-      <c r="F9" s="340"/>
-      <c r="G9" s="340"/>
-      <c r="H9" s="340"/>
-      <c r="I9" s="340"/>
-      <c r="J9" s="340"/>
-      <c r="K9" s="340"/>
-      <c r="L9" s="340"/>
-      <c r="M9" s="340"/>
-      <c r="N9" s="340"/>
-      <c r="O9" s="341"/>
+      <c r="C9" s="343"/>
+      <c r="D9" s="344"/>
+      <c r="E9" s="344"/>
+      <c r="F9" s="344"/>
+      <c r="G9" s="344"/>
+      <c r="H9" s="344"/>
+      <c r="I9" s="344"/>
+      <c r="J9" s="344"/>
+      <c r="K9" s="344"/>
+      <c r="L9" s="344"/>
+      <c r="M9" s="344"/>
+      <c r="N9" s="344"/>
+      <c r="O9" s="345"/>
       <c r="Q9" s="55"/>
     </row>
-    <row r="10" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="342" t="s">
+      <c r="C10" s="346" t="s">
         <v>286</v>
       </c>
-      <c r="D10" s="343"/>
-      <c r="E10" s="343"/>
-      <c r="F10" s="343"/>
-      <c r="G10" s="343"/>
-      <c r="H10" s="343"/>
-      <c r="I10" s="343"/>
-      <c r="J10" s="343"/>
-      <c r="K10" s="343"/>
-      <c r="L10" s="343"/>
-      <c r="M10" s="343"/>
-      <c r="N10" s="343"/>
-      <c r="O10" s="344"/>
+      <c r="D10" s="347"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
+      <c r="G10" s="347"/>
+      <c r="H10" s="347"/>
+      <c r="I10" s="347"/>
+      <c r="J10" s="347"/>
+      <c r="K10" s="347"/>
+      <c r="L10" s="347"/>
+      <c r="M10" s="347"/>
+      <c r="N10" s="347"/>
+      <c r="O10" s="348"/>
       <c r="Q10" t="s">
         <v>233</v>
       </c>
@@ -5930,22 +5969,22 @@
         <v>267678.10184399999</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="345"/>
-      <c r="D11" s="346"/>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
-      <c r="G11" s="346"/>
-      <c r="H11" s="346"/>
-      <c r="I11" s="346"/>
-      <c r="J11" s="346"/>
-      <c r="K11" s="346"/>
-      <c r="L11" s="346"/>
-      <c r="M11" s="346"/>
-      <c r="N11" s="346"/>
-      <c r="O11" s="347"/>
+      <c r="C11" s="349"/>
+      <c r="D11" s="350"/>
+      <c r="E11" s="350"/>
+      <c r="F11" s="350"/>
+      <c r="G11" s="350"/>
+      <c r="H11" s="350"/>
+      <c r="I11" s="350"/>
+      <c r="J11" s="350"/>
+      <c r="K11" s="350"/>
+      <c r="L11" s="350"/>
+      <c r="M11" s="350"/>
+      <c r="N11" s="350"/>
+      <c r="O11" s="351"/>
       <c r="Q11" t="s">
         <v>234</v>
       </c>
@@ -5954,50 +5993,50 @@
         <v>317248.120704</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="320" t="s">
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="322" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="354" t="s">
+      <c r="B12" s="324" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="320" t="s">
+      <c r="C12" s="322" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="356" t="s">
+      <c r="D12" s="326" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="356" t="s">
+      <c r="E12" s="326" t="s">
         <v>250</v>
       </c>
-      <c r="F12" s="320" t="s">
+      <c r="F12" s="322" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="320" t="s">
+      <c r="G12" s="322" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="320" t="s">
+      <c r="H12" s="322" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="326" t="s">
+      <c r="I12" s="333" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="328" t="s">
+      <c r="J12" s="319" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="328" t="s">
+      <c r="K12" s="319" t="s">
         <v>366</v>
       </c>
-      <c r="L12" s="328" t="s">
+      <c r="L12" s="319" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="331" t="s">
+      <c r="M12" s="335" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="328" t="s">
+      <c r="N12" s="319" t="s">
         <v>260</v>
       </c>
-      <c r="O12" s="328" t="s">
+      <c r="O12" s="319" t="s">
         <v>259</v>
       </c>
       <c r="Q12" t="s">
@@ -6008,22 +6047,22 @@
         <v>299898.61410299997</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="321"/>
-      <c r="B13" s="355"/>
-      <c r="C13" s="321"/>
-      <c r="D13" s="357"/>
-      <c r="E13" s="357"/>
-      <c r="F13" s="321"/>
-      <c r="G13" s="321"/>
-      <c r="H13" s="321"/>
-      <c r="I13" s="327"/>
-      <c r="J13" s="329"/>
-      <c r="K13" s="329"/>
-      <c r="L13" s="329"/>
-      <c r="M13" s="332"/>
-      <c r="N13" s="329"/>
-      <c r="O13" s="329"/>
+    <row r="13" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="323"/>
+      <c r="B13" s="325"/>
+      <c r="C13" s="323"/>
+      <c r="D13" s="327"/>
+      <c r="E13" s="327"/>
+      <c r="F13" s="323"/>
+      <c r="G13" s="323"/>
+      <c r="H13" s="323"/>
+      <c r="I13" s="334"/>
+      <c r="J13" s="320"/>
+      <c r="K13" s="320"/>
+      <c r="L13" s="320"/>
+      <c r="M13" s="336"/>
+      <c r="N13" s="320"/>
+      <c r="O13" s="320"/>
       <c r="Q13" t="s">
         <v>236</v>
       </c>
@@ -6032,20 +6071,20 @@
         <v>369296.64050699997</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="321"/>
-      <c r="B14" s="355"/>
-      <c r="C14" s="321"/>
-      <c r="D14" s="357"/>
-      <c r="E14" s="357"/>
-      <c r="F14" s="321"/>
-      <c r="G14" s="321"/>
-      <c r="H14" s="321"/>
-      <c r="I14" s="327"/>
-      <c r="J14" s="329"/>
-      <c r="K14" s="330"/>
-      <c r="L14" s="330"/>
-      <c r="M14" s="332"/>
+    <row r="14" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="323"/>
+      <c r="B14" s="325"/>
+      <c r="C14" s="323"/>
+      <c r="D14" s="327"/>
+      <c r="E14" s="327"/>
+      <c r="F14" s="323"/>
+      <c r="G14" s="323"/>
+      <c r="H14" s="323"/>
+      <c r="I14" s="334"/>
+      <c r="J14" s="320"/>
+      <c r="K14" s="321"/>
+      <c r="L14" s="321"/>
+      <c r="M14" s="336"/>
       <c r="N14" s="84" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/09</v>
@@ -6062,7 +6101,7 @@
         <v>431259.16408199997</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="176" t="s">
         <v>114</v>
       </c>
@@ -6112,10 +6151,10 @@
       <c r="P15" s="70" t="s">
         <v>342</v>
       </c>
-      <c r="R15" s="319"/>
-      <c r="S15" s="319"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R15" s="328"/>
+      <c r="S15" s="328"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="23" t="s">
@@ -6161,10 +6200,10 @@
       <c r="P16" s="70" t="s">
         <v>341</v>
       </c>
-      <c r="R16" s="319"/>
-      <c r="S16" s="319"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R16" s="328"/>
+      <c r="S16" s="328"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>114</v>
       </c>
@@ -6215,7 +6254,7 @@
       <c r="P17" s="70"/>
       <c r="S17" s="31"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>114</v>
       </c>
@@ -6261,7 +6300,7 @@
       <c r="P18" s="70"/>
       <c r="S18" s="31"/>
     </row>
-    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>114</v>
       </c>
@@ -6309,7 +6348,7 @@
       <c r="P19" s="70"/>
       <c r="S19" s="31"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
         <v>116</v>
       </c>
@@ -6362,7 +6401,7 @@
       </c>
       <c r="S20" s="31"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
         <v>117</v>
       </c>
@@ -6416,7 +6455,7 @@
       </c>
       <c r="S21" s="31"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
         <v>116</v>
       </c>
@@ -6469,7 +6508,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
         <v>118</v>
       </c>
@@ -6527,7 +6566,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="37" t="s">
         <v>118</v>
       </c>
@@ -6582,7 +6621,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="37" t="s">
         <v>118</v>
       </c>
@@ -6636,7 +6675,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="37" t="s">
         <v>116</v>
       </c>
@@ -6690,7 +6729,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="37" t="s">
         <v>117</v>
       </c>
@@ -6743,7 +6782,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="64" t="s">
         <v>116</v>
       </c>
@@ -6795,7 +6834,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="64" t="s">
         <v>118</v>
       </c>
@@ -6848,7 +6887,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="64" t="s">
         <v>118</v>
       </c>
@@ -6901,7 +6940,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="64" t="s">
         <v>118</v>
       </c>
@@ -6951,7 +6990,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="64" t="s">
         <v>116</v>
       </c>
@@ -7004,7 +7043,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A33" s="37" t="s">
         <v>117</v>
       </c>
@@ -7059,7 +7098,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A34" s="37" t="s">
         <v>116</v>
       </c>
@@ -7112,7 +7151,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A35" s="91" t="s">
         <v>118</v>
       </c>
@@ -7168,7 +7207,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A36" s="37" t="s">
         <v>118</v>
       </c>
@@ -7223,7 +7262,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A37" s="37" t="s">
         <v>118</v>
       </c>
@@ -7273,7 +7312,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
         <v>116</v>
       </c>
@@ -7331,7 +7370,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A39" s="37" t="s">
         <v>117</v>
       </c>
@@ -7384,7 +7423,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="64" t="s">
         <v>116</v>
       </c>
@@ -7537,7 +7576,7 @@
       <c r="DI40" s="46"/>
       <c r="DJ40" s="46"/>
     </row>
-    <row r="41" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="64" t="s">
         <v>118</v>
       </c>
@@ -7690,7 +7729,7 @@
       <c r="DI41" s="46"/>
       <c r="DJ41" s="46"/>
     </row>
-    <row r="42" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="64" t="s">
         <v>118</v>
       </c>
@@ -7843,7 +7882,7 @@
       <c r="DI42" s="46"/>
       <c r="DJ42" s="46"/>
     </row>
-    <row r="43" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="64" t="s">
         <v>118</v>
       </c>
@@ -7993,7 +8032,7 @@
       <c r="DI43" s="46"/>
       <c r="DJ43" s="46"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A44" s="37" t="s">
         <v>116</v>
       </c>
@@ -8046,7 +8085,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A45" s="37" t="s">
         <v>117</v>
       </c>
@@ -8101,7 +8140,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A46" s="37" t="s">
         <v>116</v>
       </c>
@@ -8160,7 +8199,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A47" s="115" t="s">
         <v>118</v>
       </c>
@@ -8213,7 +8252,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A48" s="37" t="s">
         <v>118</v>
       </c>
@@ -8268,7 +8307,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="37" t="s">
         <v>118</v>
       </c>
@@ -8321,7 +8360,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="37" t="s">
         <v>116</v>
       </c>
@@ -8374,7 +8413,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="37" t="s">
         <v>117</v>
       </c>
@@ -8427,7 +8466,7 @@
       </c>
       <c r="Q51" s="31"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="37" t="s">
         <v>116</v>
       </c>
@@ -8481,7 +8520,7 @@
       </c>
       <c r="Q52" s="31"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="37" t="s">
         <v>118</v>
       </c>
@@ -8539,7 +8578,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="37" t="s">
         <v>118</v>
       </c>
@@ -8592,7 +8631,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="64" t="s">
         <v>118</v>
       </c>
@@ -8645,7 +8684,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="37" t="s">
         <v>116</v>
       </c>
@@ -8699,7 +8738,7 @@
       </c>
       <c r="R56" s="39"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="37" t="s">
         <v>117</v>
       </c>
@@ -8754,7 +8793,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="37" t="s">
         <v>116</v>
       </c>
@@ -8807,7 +8846,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="37" t="s">
         <v>118</v>
       </c>
@@ -8862,7 +8901,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="64" t="s">
         <v>118</v>
       </c>
@@ -8918,7 +8957,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="64" t="s">
         <v>118</v>
       </c>
@@ -8974,7 +9013,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="64" t="s">
         <v>116</v>
       </c>
@@ -9026,7 +9065,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="64" t="s">
         <v>117</v>
       </c>
@@ -9078,7 +9117,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="64" t="s">
         <v>116</v>
       </c>
@@ -9131,7 +9170,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="64" t="s">
         <v>118</v>
       </c>
@@ -9186,7 +9225,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="64" t="s">
         <v>118</v>
       </c>
@@ -9239,7 +9278,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="64" t="s">
         <v>118</v>
       </c>
@@ -9292,7 +9331,7 @@
       </c>
       <c r="S67" s="125"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="64" t="s">
         <v>116</v>
       </c>
@@ -9346,7 +9385,7 @@
       </c>
       <c r="S68" s="31"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="91" t="s">
         <v>117</v>
       </c>
@@ -9399,7 +9438,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="37" t="s">
         <v>116</v>
       </c>
@@ -9452,7 +9491,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="37" t="s">
         <v>118</v>
       </c>
@@ -9504,7 +9543,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="37" t="s">
         <v>118</v>
       </c>
@@ -9558,7 +9597,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="37" t="s">
         <v>118</v>
       </c>
@@ -9608,7 +9647,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="37" t="s">
         <v>119</v>
       </c>
@@ -9662,7 +9701,7 @@
       </c>
       <c r="Q74" s="46"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="37" t="s">
         <v>116</v>
       </c>
@@ -9715,7 +9754,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="37" t="s">
         <v>118</v>
       </c>
@@ -9768,7 +9807,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="37" t="s">
         <v>118</v>
       </c>
@@ -9823,7 +9862,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="64" t="s">
         <v>118</v>
       </c>
@@ -9875,7 +9914,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="64" t="s">
         <v>119</v>
       </c>
@@ -9928,7 +9967,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="37" t="s">
         <v>116</v>
       </c>
@@ -9981,7 +10020,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="37" t="s">
         <v>118</v>
       </c>
@@ -10034,7 +10073,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="37" t="s">
         <v>118</v>
       </c>
@@ -10089,7 +10128,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="37" t="s">
         <v>118</v>
       </c>
@@ -10145,7 +10184,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="37" t="s">
         <v>119</v>
       </c>
@@ -10198,7 +10237,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="37" t="s">
         <v>116</v>
       </c>
@@ -10251,7 +10290,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="37" t="s">
         <v>118</v>
       </c>
@@ -10304,7 +10343,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="37" t="s">
         <v>118</v>
       </c>
@@ -10357,7 +10396,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="64" t="s">
         <v>118</v>
       </c>
@@ -10410,7 +10449,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="64"/>
       <c r="B89" s="23"/>
       <c r="C89" s="23" t="s">
@@ -10462,7 +10501,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="64"/>
       <c r="B90" s="23"/>
       <c r="C90" s="23" t="s">
@@ -10514,7 +10553,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="64"/>
       <c r="B91" s="23"/>
       <c r="C91" s="23" t="s">
@@ -10566,7 +10605,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="64"/>
       <c r="B92" s="23"/>
       <c r="C92" s="23" t="s">
@@ -10618,7 +10657,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="64"/>
       <c r="B93" s="23"/>
       <c r="C93" s="119" t="s">
@@ -10673,7 +10712,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="64"/>
       <c r="B94" s="23"/>
       <c r="C94" s="23" t="s">
@@ -10725,7 +10764,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="64"/>
       <c r="B95" s="23"/>
       <c r="C95" s="23" t="s">
@@ -10777,7 +10816,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="64"/>
       <c r="B96" s="23"/>
       <c r="C96" s="23" t="s">
@@ -10829,7 +10868,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="64"/>
       <c r="B97" s="23"/>
       <c r="C97" s="23" t="s">
@@ -10881,7 +10920,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="64"/>
       <c r="B98" s="23"/>
       <c r="C98" s="23" t="s">
@@ -10933,7 +10972,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="64"/>
       <c r="B99" s="23"/>
       <c r="C99" s="23" t="s">
@@ -10985,7 +11024,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="64"/>
       <c r="B100" s="23"/>
       <c r="C100" s="23" t="s">
@@ -11037,7 +11076,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="64"/>
       <c r="B101" s="23"/>
       <c r="C101" s="23" t="s">
@@ -11089,7 +11128,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="64"/>
       <c r="B102" s="23"/>
       <c r="C102" s="23" t="s">
@@ -11141,7 +11180,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="64"/>
       <c r="B103" s="23"/>
       <c r="C103" s="23" t="s">
@@ -11193,7 +11232,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="64"/>
       <c r="B104" s="23"/>
       <c r="C104" s="23" t="s">
@@ -11245,7 +11284,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="64"/>
       <c r="B105" s="23"/>
       <c r="C105" s="23" t="s">
@@ -11297,7 +11336,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="64"/>
       <c r="B106" s="23"/>
       <c r="C106" s="23" t="s">
@@ -11349,7 +11388,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="64"/>
       <c r="B107" s="23"/>
       <c r="C107" s="23" t="s">
@@ -11400,7 +11439,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="64"/>
       <c r="B108" s="23"/>
       <c r="C108" s="23" t="s">
@@ -11451,7 +11490,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="64"/>
       <c r="B109" s="23"/>
       <c r="C109" s="23" t="s">
@@ -11503,7 +11542,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="64"/>
       <c r="B110" s="23"/>
       <c r="C110" s="23" t="s">
@@ -11555,7 +11594,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="64"/>
       <c r="B111" s="23"/>
       <c r="C111" s="224" t="s">
@@ -11606,7 +11645,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="64"/>
       <c r="B112" s="23"/>
       <c r="C112" s="23" t="s">
@@ -11658,7 +11697,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="64"/>
       <c r="B113" s="23"/>
       <c r="C113" s="23" t="s">
@@ -11710,7 +11749,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="64"/>
       <c r="B114" s="23"/>
       <c r="C114" s="23" t="s">
@@ -11761,7 +11800,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="64"/>
       <c r="B115" s="23"/>
       <c r="C115" s="23" t="s">
@@ -11813,7 +11852,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="64"/>
       <c r="B116" s="23"/>
       <c r="C116" s="23" t="s">
@@ -11865,7 +11904,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="64"/>
       <c r="B117" s="23"/>
       <c r="C117" s="23" t="s">
@@ -11918,7 +11957,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="64"/>
       <c r="B118" s="23"/>
       <c r="C118" s="23" t="s">
@@ -11969,7 +12008,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="64"/>
       <c r="B119" s="23"/>
       <c r="C119" s="23" t="s">
@@ -12026,7 +12065,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="80"/>
       <c r="B120" s="23"/>
       <c r="C120" s="23" t="s">
@@ -12078,7 +12117,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="80"/>
       <c r="B121" s="23"/>
       <c r="C121" s="23" t="s">
@@ -12130,7 +12169,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="80"/>
       <c r="B122" s="23"/>
       <c r="C122" s="23" t="s">
@@ -12184,7 +12223,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="80"/>
       <c r="B123" s="23"/>
       <c r="C123" s="23" t="s">
@@ -12236,7 +12275,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="80"/>
       <c r="B124" s="23"/>
       <c r="C124" s="23" t="s">
@@ -12288,7 +12327,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="80"/>
       <c r="B125" s="23"/>
       <c r="C125" s="23" t="s">
@@ -12343,7 +12382,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="118"/>
       <c r="B126" s="113"/>
       <c r="C126" s="23" t="s">
@@ -12396,7 +12435,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="118"/>
       <c r="B127" s="113"/>
       <c r="C127" s="23" t="s">
@@ -12448,7 +12487,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="80"/>
       <c r="B128" s="23"/>
       <c r="C128" s="23" t="s">
@@ -12499,7 +12538,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="80"/>
       <c r="B129" s="23"/>
       <c r="C129" s="23" t="s">
@@ -12550,7 +12589,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="80"/>
       <c r="B130" s="23"/>
       <c r="C130" s="23" t="s">
@@ -12602,7 +12641,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="80" t="s">
         <v>24</v>
       </c>
@@ -12656,7 +12695,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="80" t="s">
         <v>24</v>
       </c>
@@ -12710,7 +12749,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="34" t="s">
         <v>24</v>
       </c>
@@ -12729,7 +12768,7 @@
       <c r="N133" s="2"/>
       <c r="O133" s="5"/>
     </row>
-    <row r="134" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="18"/>
       <c r="B134" s="18"/>
       <c r="C134" s="18"/>
@@ -12774,43 +12813,43 @@
       </c>
       <c r="Q134" s="39"/>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="L135" s="41">
         <f>L134-M1</f>
         <v>-150436.23675993457</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="323"/>
-      <c r="D136" s="323"/>
-      <c r="E136" s="323"/>
-      <c r="F136" s="323"/>
-      <c r="G136" s="323"/>
-      <c r="H136" s="323"/>
-      <c r="I136" s="323"/>
-      <c r="J136" s="323"/>
-      <c r="K136" s="323"/>
-      <c r="L136" s="323"/>
-      <c r="M136" s="323"/>
-      <c r="N136" s="323"/>
-      <c r="O136" s="323"/>
-    </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C137" s="323"/>
-      <c r="D137" s="323"/>
-      <c r="E137" s="323"/>
-      <c r="F137" s="323"/>
-      <c r="G137" s="323"/>
-      <c r="H137" s="323"/>
-      <c r="I137" s="323"/>
-      <c r="J137" s="323"/>
-      <c r="K137" s="323"/>
-      <c r="L137" s="323"/>
-      <c r="M137" s="323"/>
-      <c r="N137" s="323"/>
-      <c r="O137" s="323"/>
-    </row>
-    <row r="138" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C136" s="330"/>
+      <c r="D136" s="330"/>
+      <c r="E136" s="330"/>
+      <c r="F136" s="330"/>
+      <c r="G136" s="330"/>
+      <c r="H136" s="330"/>
+      <c r="I136" s="330"/>
+      <c r="J136" s="330"/>
+      <c r="K136" s="330"/>
+      <c r="L136" s="330"/>
+      <c r="M136" s="330"/>
+      <c r="N136" s="330"/>
+      <c r="O136" s="330"/>
+    </row>
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C137" s="330"/>
+      <c r="D137" s="330"/>
+      <c r="E137" s="330"/>
+      <c r="F137" s="330"/>
+      <c r="G137" s="330"/>
+      <c r="H137" s="330"/>
+      <c r="I137" s="330"/>
+      <c r="J137" s="330"/>
+      <c r="K137" s="330"/>
+      <c r="L137" s="330"/>
+      <c r="M137" s="330"/>
+      <c r="N137" s="330"/>
+      <c r="O137" s="330"/>
+    </row>
+    <row r="138" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C138" s="49"/>
       <c r="D138" s="49"/>
       <c r="E138" s="49"/>
@@ -12825,129 +12864,129 @@
       <c r="N138" s="49"/>
       <c r="O138" s="49"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C139" s="286" t="s">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C139" s="280" t="s">
         <v>243</v>
       </c>
-      <c r="D139" s="286"/>
-      <c r="E139" s="286"/>
-      <c r="F139" s="286"/>
-      <c r="G139" s="286"/>
-      <c r="H139" s="286"/>
-      <c r="I139" s="286"/>
-      <c r="J139" s="286"/>
-      <c r="K139" s="286"/>
-      <c r="L139" s="286"/>
-      <c r="M139" s="286"/>
-      <c r="N139" s="286"/>
-      <c r="O139" s="286"/>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C140" s="286"/>
-      <c r="D140" s="286"/>
-      <c r="E140" s="286"/>
-      <c r="F140" s="286"/>
-      <c r="G140" s="286"/>
-      <c r="H140" s="286"/>
-      <c r="I140" s="286"/>
-      <c r="J140" s="286"/>
-      <c r="K140" s="286"/>
-      <c r="L140" s="286"/>
-      <c r="M140" s="286"/>
-      <c r="N140" s="286"/>
-      <c r="O140" s="286"/>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C141" s="286"/>
-      <c r="D141" s="286"/>
-      <c r="E141" s="286"/>
-      <c r="F141" s="286"/>
-      <c r="G141" s="286"/>
-      <c r="H141" s="286"/>
-      <c r="I141" s="286"/>
-      <c r="J141" s="286"/>
-      <c r="K141" s="286"/>
-      <c r="L141" s="286"/>
-      <c r="M141" s="286"/>
-      <c r="N141" s="286"/>
-      <c r="O141" s="286"/>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C142" s="286"/>
-      <c r="D142" s="286"/>
-      <c r="E142" s="286"/>
-      <c r="F142" s="286"/>
-      <c r="G142" s="286"/>
-      <c r="H142" s="286"/>
-      <c r="I142" s="286"/>
-      <c r="J142" s="286"/>
-      <c r="K142" s="286"/>
-      <c r="L142" s="286"/>
-      <c r="M142" s="286"/>
-      <c r="N142" s="286"/>
-      <c r="O142" s="286"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C143" s="286"/>
-      <c r="D143" s="286"/>
-      <c r="E143" s="286"/>
-      <c r="F143" s="286"/>
-      <c r="G143" s="286"/>
-      <c r="H143" s="286"/>
-      <c r="I143" s="286"/>
-      <c r="J143" s="286"/>
-      <c r="K143" s="286"/>
-      <c r="L143" s="286"/>
-      <c r="M143" s="286"/>
-      <c r="N143" s="286"/>
-      <c r="O143" s="286"/>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C144" s="286"/>
-      <c r="D144" s="286"/>
-      <c r="E144" s="286"/>
-      <c r="F144" s="286"/>
-      <c r="G144" s="286"/>
-      <c r="H144" s="286"/>
-      <c r="I144" s="286"/>
-      <c r="J144" s="286"/>
-      <c r="K144" s="286"/>
-      <c r="L144" s="286"/>
-      <c r="M144" s="286"/>
-      <c r="N144" s="286"/>
-      <c r="O144" s="286"/>
-    </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C145" s="286"/>
-      <c r="D145" s="286"/>
-      <c r="E145" s="286"/>
-      <c r="F145" s="286"/>
-      <c r="G145" s="286"/>
-      <c r="H145" s="286"/>
-      <c r="I145" s="286"/>
-      <c r="J145" s="286"/>
-      <c r="K145" s="286"/>
-      <c r="L145" s="286"/>
-      <c r="M145" s="286"/>
-      <c r="N145" s="286"/>
-      <c r="O145" s="286"/>
-    </row>
-    <row r="146" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C146" s="286"/>
-      <c r="D146" s="286"/>
-      <c r="E146" s="286"/>
-      <c r="F146" s="286"/>
-      <c r="G146" s="286"/>
-      <c r="H146" s="286"/>
-      <c r="I146" s="286"/>
-      <c r="J146" s="286"/>
-      <c r="K146" s="286"/>
-      <c r="L146" s="286"/>
-      <c r="M146" s="286"/>
-      <c r="N146" s="286"/>
-      <c r="O146" s="286"/>
-    </row>
-    <row r="147" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D139" s="280"/>
+      <c r="E139" s="280"/>
+      <c r="F139" s="280"/>
+      <c r="G139" s="280"/>
+      <c r="H139" s="280"/>
+      <c r="I139" s="280"/>
+      <c r="J139" s="280"/>
+      <c r="K139" s="280"/>
+      <c r="L139" s="280"/>
+      <c r="M139" s="280"/>
+      <c r="N139" s="280"/>
+      <c r="O139" s="280"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C140" s="280"/>
+      <c r="D140" s="280"/>
+      <c r="E140" s="280"/>
+      <c r="F140" s="280"/>
+      <c r="G140" s="280"/>
+      <c r="H140" s="280"/>
+      <c r="I140" s="280"/>
+      <c r="J140" s="280"/>
+      <c r="K140" s="280"/>
+      <c r="L140" s="280"/>
+      <c r="M140" s="280"/>
+      <c r="N140" s="280"/>
+      <c r="O140" s="280"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C141" s="280"/>
+      <c r="D141" s="280"/>
+      <c r="E141" s="280"/>
+      <c r="F141" s="280"/>
+      <c r="G141" s="280"/>
+      <c r="H141" s="280"/>
+      <c r="I141" s="280"/>
+      <c r="J141" s="280"/>
+      <c r="K141" s="280"/>
+      <c r="L141" s="280"/>
+      <c r="M141" s="280"/>
+      <c r="N141" s="280"/>
+      <c r="O141" s="280"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C142" s="280"/>
+      <c r="D142" s="280"/>
+      <c r="E142" s="280"/>
+      <c r="F142" s="280"/>
+      <c r="G142" s="280"/>
+      <c r="H142" s="280"/>
+      <c r="I142" s="280"/>
+      <c r="J142" s="280"/>
+      <c r="K142" s="280"/>
+      <c r="L142" s="280"/>
+      <c r="M142" s="280"/>
+      <c r="N142" s="280"/>
+      <c r="O142" s="280"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C143" s="280"/>
+      <c r="D143" s="280"/>
+      <c r="E143" s="280"/>
+      <c r="F143" s="280"/>
+      <c r="G143" s="280"/>
+      <c r="H143" s="280"/>
+      <c r="I143" s="280"/>
+      <c r="J143" s="280"/>
+      <c r="K143" s="280"/>
+      <c r="L143" s="280"/>
+      <c r="M143" s="280"/>
+      <c r="N143" s="280"/>
+      <c r="O143" s="280"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C144" s="280"/>
+      <c r="D144" s="280"/>
+      <c r="E144" s="280"/>
+      <c r="F144" s="280"/>
+      <c r="G144" s="280"/>
+      <c r="H144" s="280"/>
+      <c r="I144" s="280"/>
+      <c r="J144" s="280"/>
+      <c r="K144" s="280"/>
+      <c r="L144" s="280"/>
+      <c r="M144" s="280"/>
+      <c r="N144" s="280"/>
+      <c r="O144" s="280"/>
+    </row>
+    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C145" s="280"/>
+      <c r="D145" s="280"/>
+      <c r="E145" s="280"/>
+      <c r="F145" s="280"/>
+      <c r="G145" s="280"/>
+      <c r="H145" s="280"/>
+      <c r="I145" s="280"/>
+      <c r="J145" s="280"/>
+      <c r="K145" s="280"/>
+      <c r="L145" s="280"/>
+      <c r="M145" s="280"/>
+      <c r="N145" s="280"/>
+      <c r="O145" s="280"/>
+    </row>
+    <row r="146" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C146" s="280"/>
+      <c r="D146" s="280"/>
+      <c r="E146" s="280"/>
+      <c r="F146" s="280"/>
+      <c r="G146" s="280"/>
+      <c r="H146" s="280"/>
+      <c r="I146" s="280"/>
+      <c r="J146" s="280"/>
+      <c r="K146" s="280"/>
+      <c r="L146" s="280"/>
+      <c r="M146" s="280"/>
+      <c r="N146" s="280"/>
+      <c r="O146" s="280"/>
+    </row>
+    <row r="147" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C147" s="49"/>
       <c r="D147" s="49"/>
       <c r="E147" s="49"/>
@@ -12962,7 +13001,7 @@
       <c r="N147" s="49"/>
       <c r="O147" s="49"/>
     </row>
-    <row r="148" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C148" s="49"/>
       <c r="D148" s="49"/>
       <c r="E148" s="49"/>
@@ -12977,126 +13016,119 @@
       <c r="N148" s="49"/>
       <c r="O148" s="49"/>
     </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C149" s="322" t="s">
+    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C149" s="329" t="s">
         <v>242</v>
       </c>
-      <c r="D149" s="322"/>
-      <c r="E149" s="322"/>
-      <c r="F149" s="322"/>
-      <c r="G149" s="322"/>
-      <c r="H149" s="322"/>
-      <c r="I149" s="322"/>
-      <c r="J149" s="322"/>
-      <c r="K149" s="322"/>
-      <c r="L149" s="322"/>
-      <c r="M149" s="322"/>
-      <c r="N149" s="322"/>
-      <c r="O149" s="322"/>
-    </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C150" s="322"/>
-      <c r="D150" s="322"/>
-      <c r="E150" s="322"/>
-      <c r="F150" s="322"/>
-      <c r="G150" s="322"/>
-      <c r="H150" s="322"/>
-      <c r="I150" s="322"/>
-      <c r="J150" s="322"/>
-      <c r="K150" s="322"/>
-      <c r="L150" s="322"/>
-      <c r="M150" s="322"/>
-      <c r="N150" s="322"/>
-      <c r="O150" s="322"/>
-    </row>
-    <row r="151" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C151" s="322"/>
-      <c r="D151" s="322"/>
-      <c r="E151" s="322"/>
-      <c r="F151" s="322"/>
-      <c r="G151" s="322"/>
-      <c r="H151" s="322"/>
-      <c r="I151" s="322"/>
-      <c r="J151" s="322"/>
-      <c r="K151" s="322"/>
-      <c r="L151" s="322"/>
-      <c r="M151" s="322"/>
-      <c r="N151" s="322"/>
-      <c r="O151" s="322"/>
+      <c r="D149" s="329"/>
+      <c r="E149" s="329"/>
+      <c r="F149" s="329"/>
+      <c r="G149" s="329"/>
+      <c r="H149" s="329"/>
+      <c r="I149" s="329"/>
+      <c r="J149" s="329"/>
+      <c r="K149" s="329"/>
+      <c r="L149" s="329"/>
+      <c r="M149" s="329"/>
+      <c r="N149" s="329"/>
+      <c r="O149" s="329"/>
+    </row>
+    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C150" s="329"/>
+      <c r="D150" s="329"/>
+      <c r="E150" s="329"/>
+      <c r="F150" s="329"/>
+      <c r="G150" s="329"/>
+      <c r="H150" s="329"/>
+      <c r="I150" s="329"/>
+      <c r="J150" s="329"/>
+      <c r="K150" s="329"/>
+      <c r="L150" s="329"/>
+      <c r="M150" s="329"/>
+      <c r="N150" s="329"/>
+      <c r="O150" s="329"/>
+    </row>
+    <row r="151" spans="3:17" x14ac:dyDescent="0.25">
+      <c r="C151" s="329"/>
+      <c r="D151" s="329"/>
+      <c r="E151" s="329"/>
+      <c r="F151" s="329"/>
+      <c r="G151" s="329"/>
+      <c r="H151" s="329"/>
+      <c r="I151" s="329"/>
+      <c r="J151" s="329"/>
+      <c r="K151" s="329"/>
+      <c r="L151" s="329"/>
+      <c r="M151" s="329"/>
+      <c r="N151" s="329"/>
+      <c r="O151" s="329"/>
       <c r="Q151" s="55">
         <f>M1-L134</f>
         <v>150436.23675993457</v>
       </c>
     </row>
-    <row r="152" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="322"/>
-      <c r="D152" s="322"/>
-      <c r="E152" s="322"/>
-      <c r="F152" s="322"/>
-      <c r="G152" s="322"/>
-      <c r="H152" s="322"/>
-      <c r="I152" s="322"/>
-      <c r="J152" s="322"/>
-      <c r="K152" s="322"/>
-      <c r="L152" s="322"/>
-      <c r="M152" s="322"/>
-      <c r="N152" s="322"/>
-      <c r="O152" s="322"/>
-    </row>
-    <row r="153" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="322"/>
-      <c r="D153" s="322"/>
-      <c r="E153" s="322"/>
-      <c r="F153" s="322"/>
-      <c r="G153" s="322"/>
-      <c r="H153" s="322"/>
-      <c r="I153" s="322"/>
-      <c r="J153" s="322"/>
-      <c r="K153" s="322"/>
-      <c r="L153" s="322"/>
-      <c r="M153" s="322"/>
-      <c r="N153" s="322"/>
-      <c r="O153" s="322"/>
-    </row>
-    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="322"/>
-      <c r="D154" s="322"/>
-      <c r="E154" s="322"/>
-      <c r="F154" s="322"/>
-      <c r="G154" s="322"/>
-      <c r="H154" s="322"/>
-      <c r="I154" s="322"/>
-      <c r="J154" s="322"/>
-      <c r="K154" s="322"/>
-      <c r="L154" s="322"/>
-      <c r="M154" s="322"/>
-      <c r="N154" s="322"/>
-      <c r="O154" s="322"/>
-    </row>
-    <row r="155" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C155" s="322"/>
-      <c r="D155" s="322"/>
-      <c r="E155" s="322"/>
-      <c r="F155" s="322"/>
-      <c r="G155" s="322"/>
-      <c r="H155" s="322"/>
-      <c r="I155" s="322"/>
-      <c r="J155" s="322"/>
-      <c r="K155" s="322"/>
-      <c r="L155" s="322"/>
-      <c r="M155" s="322"/>
-      <c r="N155" s="322"/>
-      <c r="O155" s="322"/>
+    <row r="152" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C152" s="329"/>
+      <c r="D152" s="329"/>
+      <c r="E152" s="329"/>
+      <c r="F152" s="329"/>
+      <c r="G152" s="329"/>
+      <c r="H152" s="329"/>
+      <c r="I152" s="329"/>
+      <c r="J152" s="329"/>
+      <c r="K152" s="329"/>
+      <c r="L152" s="329"/>
+      <c r="M152" s="329"/>
+      <c r="N152" s="329"/>
+      <c r="O152" s="329"/>
+    </row>
+    <row r="153" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C153" s="329"/>
+      <c r="D153" s="329"/>
+      <c r="E153" s="329"/>
+      <c r="F153" s="329"/>
+      <c r="G153" s="329"/>
+      <c r="H153" s="329"/>
+      <c r="I153" s="329"/>
+      <c r="J153" s="329"/>
+      <c r="K153" s="329"/>
+      <c r="L153" s="329"/>
+      <c r="M153" s="329"/>
+      <c r="N153" s="329"/>
+      <c r="O153" s="329"/>
+    </row>
+    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C154" s="329"/>
+      <c r="D154" s="329"/>
+      <c r="E154" s="329"/>
+      <c r="F154" s="329"/>
+      <c r="G154" s="329"/>
+      <c r="H154" s="329"/>
+      <c r="I154" s="329"/>
+      <c r="J154" s="329"/>
+      <c r="K154" s="329"/>
+      <c r="L154" s="329"/>
+      <c r="M154" s="329"/>
+      <c r="N154" s="329"/>
+      <c r="O154" s="329"/>
+    </row>
+    <row r="155" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C155" s="329"/>
+      <c r="D155" s="329"/>
+      <c r="E155" s="329"/>
+      <c r="F155" s="329"/>
+      <c r="G155" s="329"/>
+      <c r="H155" s="329"/>
+      <c r="I155" s="329"/>
+      <c r="J155" s="329"/>
+      <c r="K155" s="329"/>
+      <c r="L155" s="329"/>
+      <c r="M155" s="329"/>
+      <c r="N155" s="329"/>
+      <c r="O155" s="329"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="E12:E14"/>
     <mergeCell ref="R15:S16"/>
     <mergeCell ref="G12:G14"/>
     <mergeCell ref="C149:O155"/>
@@ -13113,6 +13145,13 @@
     <mergeCell ref="C6:O9"/>
     <mergeCell ref="C10:O11"/>
     <mergeCell ref="A1:E5"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="E12:E14"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13123,84 +13162,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DJ82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.28515625" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" customWidth="1"/>
-    <col min="13" max="13" width="16.5546875" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" customWidth="1"/>
-    <col min="15" max="15" width="19.5546875" customWidth="1"/>
-    <col min="16" max="16" width="7.6640625" customWidth="1"/>
-    <col min="17" max="17" width="43.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" customWidth="1"/>
+    <col min="17" max="17" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="362" t="s">
+    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="365" t="s">
         <v>300</v>
       </c>
-      <c r="B1" s="362"/>
-      <c r="C1" s="362"/>
-      <c r="D1" s="362"/>
-      <c r="E1" s="362"/>
-      <c r="F1" s="362"/>
-      <c r="G1" s="362"/>
-      <c r="H1" s="362"/>
-      <c r="I1" s="362"/>
-      <c r="J1" s="362"/>
-      <c r="K1" s="362"/>
-      <c r="L1" s="362"/>
-      <c r="M1" s="362"/>
-      <c r="N1" s="362"/>
-      <c r="O1" s="363"/>
+      <c r="B1" s="365"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
+      <c r="K1" s="365"/>
+      <c r="L1" s="365"/>
+      <c r="M1" s="365"/>
+      <c r="N1" s="365"/>
+      <c r="O1" s="366"/>
       <c r="R1" s="31"/>
     </row>
-    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="364"/>
-      <c r="B2" s="364"/>
-      <c r="C2" s="364"/>
-      <c r="D2" s="364"/>
-      <c r="E2" s="364"/>
-      <c r="F2" s="364"/>
-      <c r="G2" s="364"/>
-      <c r="H2" s="364"/>
-      <c r="I2" s="364"/>
-      <c r="J2" s="364"/>
-      <c r="K2" s="364"/>
-      <c r="L2" s="364"/>
-      <c r="M2" s="364"/>
-      <c r="N2" s="364"/>
-      <c r="O2" s="365"/>
+    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="367"/>
+      <c r="B2" s="367"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="367"/>
+      <c r="J2" s="367"/>
+      <c r="K2" s="367"/>
+      <c r="L2" s="367"/>
+      <c r="M2" s="367"/>
+      <c r="N2" s="367"/>
+      <c r="O2" s="368"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:27" s="166" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="359" t="s">
+    <row r="3" spans="1:27" s="166" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="362" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="360"/>
-      <c r="C3" s="360"/>
-      <c r="D3" s="360"/>
-      <c r="E3" s="360"/>
-      <c r="F3" s="360"/>
-      <c r="G3" s="360"/>
-      <c r="H3" s="360"/>
-      <c r="I3" s="360"/>
-      <c r="J3" s="360"/>
-      <c r="K3" s="360"/>
-      <c r="L3" s="360"/>
-      <c r="M3" s="360"/>
-      <c r="N3" s="360"/>
-      <c r="O3" s="361"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
+      <c r="M3" s="363"/>
+      <c r="N3" s="363"/>
+      <c r="O3" s="364"/>
       <c r="P3" s="167"/>
       <c r="Q3" s="167"/>
       <c r="R3" s="167"/>
@@ -13214,89 +13253,89 @@
       <c r="Z3" s="167"/>
       <c r="AA3" s="167"/>
     </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="320" t="s">
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="322" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="320" t="s">
+      <c r="B4" s="322" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="320" t="s">
+      <c r="C4" s="322" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="320" t="s">
+      <c r="D4" s="322" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="328" t="s">
+      <c r="E4" s="319" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="328" t="s">
+      <c r="F4" s="319" t="s">
         <v>327</v>
       </c>
-      <c r="G4" s="328" t="s">
+      <c r="G4" s="319" t="s">
         <v>260</v>
       </c>
-      <c r="H4" s="328" t="s">
+      <c r="H4" s="319" t="s">
         <v>332</v>
       </c>
-      <c r="I4" s="328" t="s">
+      <c r="I4" s="319" t="s">
         <v>339</v>
       </c>
-      <c r="J4" s="366" t="s">
+      <c r="J4" s="369" t="s">
         <v>328</v>
       </c>
       <c r="K4" s="83"/>
-      <c r="L4" s="370" t="s">
+      <c r="L4" s="358" t="s">
         <v>336</v>
       </c>
-      <c r="M4" s="328" t="s">
+      <c r="M4" s="319" t="s">
         <v>337</v>
       </c>
-      <c r="N4" s="328" t="s">
+      <c r="N4" s="319" t="s">
         <v>329</v>
       </c>
-      <c r="O4" s="328" t="s">
+      <c r="O4" s="319" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="31"/>
     </row>
-    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="321"/>
-      <c r="B5" s="321"/>
-      <c r="C5" s="321"/>
-      <c r="D5" s="321"/>
-      <c r="E5" s="329"/>
-      <c r="F5" s="329"/>
-      <c r="G5" s="329"/>
-      <c r="H5" s="329"/>
-      <c r="I5" s="329"/>
-      <c r="J5" s="367"/>
+    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="323"/>
+      <c r="B5" s="323"/>
+      <c r="C5" s="323"/>
+      <c r="D5" s="323"/>
+      <c r="E5" s="320"/>
+      <c r="F5" s="320"/>
+      <c r="G5" s="320"/>
+      <c r="H5" s="320"/>
+      <c r="I5" s="320"/>
+      <c r="J5" s="370"/>
       <c r="K5" s="83"/>
-      <c r="L5" s="371"/>
-      <c r="M5" s="329"/>
-      <c r="N5" s="329"/>
-      <c r="O5" s="329"/>
+      <c r="L5" s="359"/>
+      <c r="M5" s="320"/>
+      <c r="N5" s="320"/>
+      <c r="O5" s="320"/>
       <c r="R5" s="31"/>
     </row>
-    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="369"/>
-      <c r="B6" s="369"/>
-      <c r="C6" s="369"/>
-      <c r="D6" s="369"/>
-      <c r="E6" s="358"/>
-      <c r="F6" s="358"/>
-      <c r="G6" s="358"/>
-      <c r="H6" s="358"/>
-      <c r="I6" s="358"/>
-      <c r="J6" s="368"/>
+    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="372"/>
+      <c r="B6" s="372"/>
+      <c r="C6" s="372"/>
+      <c r="D6" s="372"/>
+      <c r="E6" s="361"/>
+      <c r="F6" s="361"/>
+      <c r="G6" s="361"/>
+      <c r="H6" s="361"/>
+      <c r="I6" s="361"/>
+      <c r="J6" s="371"/>
       <c r="K6" s="136"/>
-      <c r="L6" s="372"/>
-      <c r="M6" s="358"/>
-      <c r="N6" s="358"/>
-      <c r="O6" s="358"/>
+      <c r="L6" s="360"/>
+      <c r="M6" s="361"/>
+      <c r="N6" s="361"/>
+      <c r="O6" s="361"/>
       <c r="R6" s="31"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="137" t="s">
         <v>109</v>
       </c>
@@ -13348,10 +13387,10 @@
       <c r="P7" s="70">
         <v>0.7</v>
       </c>
-      <c r="R7" s="319"/>
-      <c r="S7" s="319"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="R7" s="328"/>
+      <c r="S7" s="328"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="137" t="s">
         <v>308</v>
       </c>
@@ -13405,10 +13444,10 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="319"/>
-      <c r="S8" s="319"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="R8" s="328"/>
+      <c r="S8" s="328"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="137" t="s">
         <v>110</v>
       </c>
@@ -13464,7 +13503,7 @@
       </c>
       <c r="S9" s="31"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="137" t="s">
         <v>111</v>
       </c>
@@ -13519,7 +13558,7 @@
       </c>
       <c r="S10" s="31"/>
     </row>
-    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="141" t="s">
         <v>112</v>
       </c>
@@ -13574,7 +13613,7 @@
       </c>
       <c r="S11" s="31"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="144" t="s">
         <v>40</v>
       </c>
@@ -13630,7 +13669,7 @@
       </c>
       <c r="S12" s="31"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="137" t="s">
         <v>41</v>
       </c>
@@ -13685,7 +13724,7 @@
       </c>
       <c r="S13" s="31"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="137" t="s">
         <v>42</v>
       </c>
@@ -13741,7 +13780,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="137" t="s">
         <v>43</v>
       </c>
@@ -13797,7 +13836,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="137" t="s">
         <v>44</v>
       </c>
@@ -13851,7 +13890,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A17" s="137" t="s">
         <v>45</v>
       </c>
@@ -13907,7 +13946,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A18" s="137" t="s">
         <v>46</v>
       </c>
@@ -13963,7 +14002,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A19" s="137" t="s">
         <v>47</v>
       </c>
@@ -14017,7 +14056,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A20" s="137" t="s">
         <v>48</v>
       </c>
@@ -14071,7 +14110,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A21" s="137" t="s">
         <v>49</v>
       </c>
@@ -14125,7 +14164,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A22" s="137" t="s">
         <v>50</v>
       </c>
@@ -14179,7 +14218,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A23" s="137" t="s">
         <v>51</v>
       </c>
@@ -14233,7 +14272,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A24" s="137" t="s">
         <v>52</v>
       </c>
@@ -14287,7 +14326,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A25" s="137" t="s">
         <v>53</v>
       </c>
@@ -14341,7 +14380,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A26" s="137" t="s">
         <v>54</v>
       </c>
@@ -14397,7 +14436,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A27" s="137" t="s">
         <v>55</v>
       </c>
@@ -14455,7 +14494,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="28" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A28" s="137" t="s">
         <v>56</v>
       </c>
@@ -14509,7 +14548,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="29" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A29" s="137" t="s">
         <v>57</v>
       </c>
@@ -14561,7 +14600,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A30" s="137" t="s">
         <v>58</v>
       </c>
@@ -14618,7 +14657,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="31" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A31" s="137" t="s">
         <v>59</v>
       </c>
@@ -14674,7 +14713,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="137" t="s">
         <v>60</v>
       </c>
@@ -14829,7 +14868,7 @@
       <c r="DI32" s="46"/>
       <c r="DJ32" s="46"/>
     </row>
-    <row r="33" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="137" t="s">
         <v>61</v>
       </c>
@@ -14983,7 +15022,7 @@
       <c r="DI33" s="46"/>
       <c r="DJ33" s="46"/>
     </row>
-    <row r="34" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="137" t="s">
         <v>62</v>
       </c>
@@ -15139,7 +15178,7 @@
       <c r="DI34" s="46"/>
       <c r="DJ34" s="46"/>
     </row>
-    <row r="35" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="137" t="s">
         <v>63</v>
       </c>
@@ -15289,7 +15328,7 @@
       <c r="DI35" s="46"/>
       <c r="DJ35" s="46"/>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A36" s="137" t="s">
         <v>64</v>
       </c>
@@ -15345,7 +15384,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A37" s="137" t="s">
         <v>65</v>
       </c>
@@ -15399,7 +15438,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A38" s="137" t="s">
         <v>66</v>
       </c>
@@ -15461,7 +15500,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A39" s="137" t="s">
         <v>67</v>
       </c>
@@ -15517,7 +15556,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="40" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A40" s="137" t="s">
         <v>68</v>
       </c>
@@ -15571,7 +15610,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="41" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A41" s="137" t="s">
         <v>69</v>
       </c>
@@ -15625,7 +15664,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A42" s="137" t="s">
         <v>70</v>
       </c>
@@ -15681,7 +15720,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A43" s="137" t="s">
         <v>71</v>
       </c>
@@ -15738,7 +15777,7 @@
       </c>
       <c r="Q43" s="31"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A44" s="137" t="s">
         <v>72</v>
       </c>
@@ -15795,7 +15834,7 @@
       </c>
       <c r="Q44" s="31"/>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A45" s="137" t="s">
         <v>73</v>
       </c>
@@ -15852,7 +15891,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A46" s="137" t="s">
         <v>74</v>
       </c>
@@ -15906,7 +15945,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A47" s="137" t="s">
         <v>75</v>
       </c>
@@ -15960,7 +15999,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
       <c r="A48" s="137" t="s">
         <v>76</v>
       </c>
@@ -16017,7 +16056,7 @@
       </c>
       <c r="R48" s="39"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="137" t="s">
         <v>77</v>
       </c>
@@ -16071,7 +16110,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="137" t="s">
         <v>78</v>
       </c>
@@ -16128,7 +16167,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="137" t="s">
         <v>79</v>
       </c>
@@ -16182,7 +16221,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="137" t="s">
         <v>80</v>
       </c>
@@ -16239,7 +16278,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="137" t="s">
         <v>81</v>
       </c>
@@ -16298,7 +16337,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="137" t="s">
         <v>82</v>
       </c>
@@ -16354,7 +16393,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="137" t="s">
         <v>83</v>
       </c>
@@ -16408,7 +16447,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="137" t="s">
         <v>84</v>
       </c>
@@ -16464,7 +16503,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="137" t="s">
         <v>85</v>
       </c>
@@ -16520,7 +16559,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="137" t="s">
         <v>86</v>
       </c>
@@ -16576,7 +16615,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="137" t="s">
         <v>87</v>
       </c>
@@ -16633,7 +16672,7 @@
       </c>
       <c r="S59" s="125"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="137" t="s">
         <v>88</v>
       </c>
@@ -16690,7 +16729,7 @@
       </c>
       <c r="S60" s="31"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="137" t="s">
         <v>89</v>
       </c>
@@ -16745,7 +16784,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="137" t="s">
         <v>90</v>
       </c>
@@ -16801,7 +16840,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="137" t="s">
         <v>91</v>
       </c>
@@ -16855,7 +16894,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="137" t="s">
         <v>92</v>
       </c>
@@ -16912,7 +16951,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="137" t="s">
         <v>93</v>
       </c>
@@ -16969,7 +17008,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="137" t="s">
         <v>94</v>
       </c>
@@ -17026,7 +17065,7 @@
       </c>
       <c r="Q66" s="46"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="137" t="s">
         <v>95</v>
       </c>
@@ -17082,7 +17121,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="137" t="s">
         <v>96</v>
       </c>
@@ -17128,7 +17167,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="137" t="s">
         <v>97</v>
       </c>
@@ -17183,7 +17222,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="137" t="s">
         <v>98</v>
       </c>
@@ -17239,7 +17278,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="137" t="s">
         <v>99</v>
       </c>
@@ -17295,7 +17334,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="137" t="s">
         <v>100</v>
       </c>
@@ -17351,7 +17390,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="137" t="s">
         <v>101</v>
       </c>
@@ -17406,7 +17445,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="137" t="s">
         <v>102</v>
       </c>
@@ -17462,7 +17501,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="137" t="s">
         <v>103</v>
       </c>
@@ -17516,7 +17555,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="137" t="s">
         <v>104</v>
       </c>
@@ -17572,7 +17611,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="137" t="s">
         <v>105</v>
       </c>
@@ -17629,7 +17668,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="137" t="s">
         <v>106</v>
       </c>
@@ -17685,7 +17724,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="137" t="s">
         <v>107</v>
       </c>
@@ -17741,7 +17780,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="137" t="s">
         <v>108</v>
       </c>
@@ -17797,7 +17836,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="23"/>
       <c r="B81" s="23"/>
       <c r="C81" s="64"/>
@@ -17814,7 +17853,7 @@
       <c r="N81" s="96"/>
       <c r="O81" s="97"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="18"/>
       <c r="B82" s="18"/>
       <c r="C82" s="18"/>
@@ -17855,6 +17894,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="I4:I6"/>
     <mergeCell ref="L4:L6"/>
     <mergeCell ref="M4:M6"/>
     <mergeCell ref="A3:O3"/>
@@ -17871,7 +17911,6 @@
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="H4:H6"/>
-    <mergeCell ref="I4:I6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="85" orientation="landscape" r:id="rId1"/>
@@ -17881,14 +17920,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="C1:M17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K1" s="46"/>
       <c r="L1" s="46"/>
       <c r="M1" s="46"/>
     </row>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C2" s="242" t="s">
         <v>343</v>
       </c>
@@ -17905,7 +17944,7 @@
       <c r="L2" s="46"/>
       <c r="M2" s="46"/>
     </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C3" s="244" t="s">
         <v>344</v>
       </c>
@@ -17924,7 +17963,7 @@
       <c r="L3" s="262"/>
       <c r="M3" s="247"/>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C4" s="244" t="s">
         <v>346</v>
       </c>
@@ -17947,7 +17986,7 @@
       <c r="L4" s="262"/>
       <c r="M4" s="247"/>
     </row>
-    <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" s="168" t="s">
         <v>350</v>
       </c>
@@ -17962,7 +18001,7 @@
       <c r="L5" s="262"/>
       <c r="M5" s="247"/>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C6" s="373" t="s">
         <v>377</v>
       </c>
@@ -17977,7 +18016,7 @@
       <c r="L6" s="261"/>
       <c r="M6" s="46"/>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C7" s="376"/>
       <c r="D7" s="377"/>
       <c r="E7" s="377"/>
@@ -17990,7 +18029,7 @@
       <c r="L7" s="261"/>
       <c r="M7" s="46"/>
     </row>
-    <row r="8" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C8" s="379"/>
       <c r="D8" s="380"/>
       <c r="E8" s="380"/>
@@ -18003,17 +18042,17 @@
       <c r="L8" s="46"/>
       <c r="M8" s="46"/>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
       <c r="K9" s="46"/>
       <c r="L9" s="46"/>
       <c r="M9" s="46"/>
     </row>
-    <row r="10" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K10" s="46"/>
       <c r="L10" s="46"/>
       <c r="M10" s="46"/>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C11" s="248" t="s">
         <v>343</v>
       </c>
@@ -18027,7 +18066,7 @@
       <c r="I11" s="170"/>
       <c r="J11" s="171"/>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C12" s="250" t="s">
         <v>344</v>
       </c>
@@ -18048,7 +18087,7 @@
       <c r="L12" s="261"/>
       <c r="M12" s="261"/>
     </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C13" s="250" t="s">
         <v>346</v>
       </c>
@@ -18071,7 +18110,7 @@
       <c r="L13" s="261"/>
       <c r="M13" s="261"/>
     </row>
-    <row r="14" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="168" t="s">
         <v>350</v>
       </c>
@@ -18086,7 +18125,7 @@
       <c r="L14" s="261"/>
       <c r="M14" s="261"/>
     </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C15" s="373" t="s">
         <v>380</v>
       </c>
@@ -18101,7 +18140,7 @@
       <c r="L15" s="261"/>
       <c r="M15" s="261"/>
     </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C16" s="376"/>
       <c r="D16" s="377"/>
       <c r="E16" s="377"/>
@@ -18114,7 +18153,7 @@
       <c r="L16" s="261"/>
       <c r="M16" s="261"/>
     </row>
-    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C17" s="379"/>
       <c r="D17" s="380"/>
       <c r="E17" s="380"/>

--- a/2026/EL MIRADOR/Agosto/Agosto - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Agosto/Agosto - EL MIRADOR.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F9C002-5B5D-4489-B12F-EFA983CA80F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04427F6-5836-4974-A00D-FFCDBED56E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
     <sheet name="ARBA" sheetId="4" r:id="rId3"/>
-    <sheet name="ANOTACIONES" sheetId="3" r:id="rId4"/>
+    <sheet name="DEUDA AYALA" sheetId="5" r:id="rId4"/>
+    <sheet name="ANOTACIONES" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">ARBA!$A$1:$O$82</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'DEUDA AYALA'!$C$3:$H$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$156</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$127</definedName>
   </definedNames>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="422">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1283,6 +1285,30 @@
   </si>
   <si>
     <t>SE PRORRATEA EN LOCALES:</t>
+  </si>
+  <si>
+    <t>DEUDA SR. AYALA AL 04/09/2026</t>
+  </si>
+  <si>
+    <t>UF:</t>
+  </si>
+  <si>
+    <t>Propietario:</t>
+  </si>
+  <si>
+    <t>Deuda a abonar antes del 17/09</t>
+  </si>
+  <si>
+    <t>Deuda ARBA 3F</t>
+  </si>
+  <si>
+    <t>Deuda ARBA 4F</t>
+  </si>
+  <si>
+    <t>Deuda ARBA 5F</t>
+  </si>
+  <si>
+    <t>TOTAL DEUDA</t>
   </si>
 </sst>
 </file>
@@ -1961,7 +1987,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="382">
+  <cellXfs count="401">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2330,6 +2356,24 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2441,53 +2485,14 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2506,6 +2511,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2576,6 +2590,21 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2583,9 +2612,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="23" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2647,6 +2673,43 @@
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3172,108 +3235,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="313" t="s">
+      <c r="A14" s="276" t="s">
         <v>243</v>
       </c>
-      <c r="B14" s="313"/>
-      <c r="C14" s="313"/>
-      <c r="D14" s="313"/>
-      <c r="E14" s="313"/>
-      <c r="F14" s="313"/>
-      <c r="G14" s="313"/>
-      <c r="H14" s="313"/>
-      <c r="I14" s="313"/>
-      <c r="J14" s="313"/>
+      <c r="B14" s="276"/>
+      <c r="C14" s="276"/>
+      <c r="D14" s="276"/>
+      <c r="E14" s="276"/>
+      <c r="F14" s="276"/>
+      <c r="G14" s="276"/>
+      <c r="H14" s="276"/>
+      <c r="I14" s="276"/>
+      <c r="J14" s="276"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="313"/>
-      <c r="B15" s="313"/>
-      <c r="C15" s="313"/>
-      <c r="D15" s="313"/>
-      <c r="E15" s="313"/>
-      <c r="F15" s="313"/>
-      <c r="G15" s="313"/>
-      <c r="H15" s="313"/>
-      <c r="I15" s="313"/>
-      <c r="J15" s="313"/>
+      <c r="A15" s="276"/>
+      <c r="B15" s="276"/>
+      <c r="C15" s="276"/>
+      <c r="D15" s="276"/>
+      <c r="E15" s="276"/>
+      <c r="F15" s="276"/>
+      <c r="G15" s="276"/>
+      <c r="H15" s="276"/>
+      <c r="I15" s="276"/>
+      <c r="J15" s="276"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="313"/>
-      <c r="B16" s="313"/>
-      <c r="C16" s="313"/>
-      <c r="D16" s="313"/>
-      <c r="E16" s="313"/>
-      <c r="F16" s="313"/>
-      <c r="G16" s="313"/>
-      <c r="H16" s="313"/>
-      <c r="I16" s="313"/>
-      <c r="J16" s="313"/>
+      <c r="A16" s="276"/>
+      <c r="B16" s="276"/>
+      <c r="C16" s="276"/>
+      <c r="D16" s="276"/>
+      <c r="E16" s="276"/>
+      <c r="F16" s="276"/>
+      <c r="G16" s="276"/>
+      <c r="H16" s="276"/>
+      <c r="I16" s="276"/>
+      <c r="J16" s="276"/>
     </row>
     <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="313"/>
-      <c r="B17" s="313"/>
-      <c r="C17" s="313"/>
-      <c r="D17" s="313"/>
-      <c r="E17" s="313"/>
-      <c r="F17" s="313"/>
-      <c r="G17" s="313"/>
-      <c r="H17" s="313"/>
-      <c r="I17" s="313"/>
-      <c r="J17" s="313"/>
+      <c r="A17" s="276"/>
+      <c r="B17" s="276"/>
+      <c r="C17" s="276"/>
+      <c r="D17" s="276"/>
+      <c r="E17" s="276"/>
+      <c r="F17" s="276"/>
+      <c r="G17" s="276"/>
+      <c r="H17" s="276"/>
+      <c r="I17" s="276"/>
+      <c r="J17" s="276"/>
     </row>
     <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="313"/>
-      <c r="B18" s="313"/>
-      <c r="C18" s="313"/>
-      <c r="D18" s="313"/>
-      <c r="E18" s="313"/>
-      <c r="F18" s="313"/>
-      <c r="G18" s="313"/>
-      <c r="H18" s="313"/>
-      <c r="I18" s="313"/>
-      <c r="J18" s="313"/>
+      <c r="A18" s="276"/>
+      <c r="B18" s="276"/>
+      <c r="C18" s="276"/>
+      <c r="D18" s="276"/>
+      <c r="E18" s="276"/>
+      <c r="F18" s="276"/>
+      <c r="G18" s="276"/>
+      <c r="H18" s="276"/>
+      <c r="I18" s="276"/>
+      <c r="J18" s="276"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="H19" s="60"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="314" t="s">
+      <c r="A20" s="277" t="s">
         <v>381</v>
       </c>
-      <c r="B20" s="314"/>
-      <c r="C20" s="314"/>
-      <c r="D20" s="314"/>
-      <c r="E20" s="314"/>
-      <c r="F20" s="314"/>
-      <c r="G20" s="314"/>
-      <c r="H20" s="314"/>
-      <c r="I20" s="314"/>
-      <c r="J20" s="314"/>
+      <c r="B20" s="277"/>
+      <c r="C20" s="277"/>
+      <c r="D20" s="277"/>
+      <c r="E20" s="277"/>
+      <c r="F20" s="277"/>
+      <c r="G20" s="277"/>
+      <c r="H20" s="277"/>
+      <c r="I20" s="277"/>
+      <c r="J20" s="277"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="314"/>
-      <c r="B21" s="314"/>
-      <c r="C21" s="314"/>
-      <c r="D21" s="314"/>
-      <c r="E21" s="314"/>
-      <c r="F21" s="314"/>
-      <c r="G21" s="314"/>
-      <c r="H21" s="314"/>
-      <c r="I21" s="314"/>
-      <c r="J21" s="314"/>
+      <c r="A21" s="277"/>
+      <c r="B21" s="277"/>
+      <c r="C21" s="277"/>
+      <c r="D21" s="277"/>
+      <c r="E21" s="277"/>
+      <c r="F21" s="277"/>
+      <c r="G21" s="277"/>
+      <c r="H21" s="277"/>
+      <c r="I21" s="277"/>
+      <c r="J21" s="277"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="314"/>
-      <c r="B22" s="314"/>
-      <c r="C22" s="314"/>
-      <c r="D22" s="314"/>
-      <c r="E22" s="314"/>
-      <c r="F22" s="314"/>
-      <c r="G22" s="314"/>
-      <c r="H22" s="314"/>
-      <c r="I22" s="314"/>
-      <c r="J22" s="314"/>
+      <c r="A22" s="277"/>
+      <c r="B22" s="277"/>
+      <c r="C22" s="277"/>
+      <c r="D22" s="277"/>
+      <c r="E22" s="277"/>
+      <c r="F22" s="277"/>
+      <c r="G22" s="277"/>
+      <c r="H22" s="277"/>
+      <c r="I22" s="277"/>
+      <c r="J22" s="277"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="56"/>
@@ -3715,8 +3778,8 @@
       <c r="L42" s="43"/>
     </row>
     <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="315"/>
-      <c r="B43" s="316"/>
+      <c r="A43" s="278"/>
+      <c r="B43" s="279"/>
       <c r="C43" s="157"/>
       <c r="D43" s="32"/>
       <c r="E43" s="186"/>
@@ -4217,10 +4280,10 @@
       </c>
     </row>
     <row r="59" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="317" t="s">
+      <c r="A59" s="280" t="s">
         <v>396</v>
       </c>
-      <c r="B59" s="318"/>
+      <c r="B59" s="281"/>
       <c r="C59" s="119" t="s">
         <v>395</v>
       </c>
@@ -4261,10 +4324,10 @@
       </c>
     </row>
     <row r="60" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="317" t="s">
+      <c r="A60" s="280" t="s">
         <v>394</v>
       </c>
-      <c r="B60" s="318"/>
+      <c r="B60" s="281"/>
       <c r="C60" s="119" t="s">
         <v>395</v>
       </c>
@@ -4656,11 +4719,11 @@
       </c>
     </row>
     <row r="70" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="276" t="s">
+      <c r="A70" s="282" t="s">
         <v>406</v>
       </c>
-      <c r="B70" s="277"/>
-      <c r="C70" s="278"/>
+      <c r="B70" s="283"/>
+      <c r="C70" s="284"/>
       <c r="D70" s="32">
         <v>0</v>
       </c>
@@ -4876,11 +4939,11 @@
       <c r="L76" s="43"/>
     </row>
     <row r="77" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="310" t="s">
+      <c r="A77" s="316" t="s">
         <v>412</v>
       </c>
-      <c r="B77" s="311"/>
-      <c r="C77" s="312"/>
+      <c r="B77" s="317"/>
+      <c r="C77" s="318"/>
       <c r="D77" s="62">
         <f>24275955.4-15214817.97+1950000</f>
         <v>11011137.429999998</v>
@@ -5077,12 +5140,12 @@
       <c r="I86" s="40"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="297" t="s">
+      <c r="A87" s="303" t="s">
         <v>32</v>
       </c>
-      <c r="B87" s="298"/>
-      <c r="C87" s="298"/>
-      <c r="D87" s="298"/>
+      <c r="B87" s="304"/>
+      <c r="C87" s="304"/>
+      <c r="D87" s="304"/>
       <c r="E87" s="51" t="s">
         <v>10</v>
       </c>
@@ -5104,7 +5167,7 @@
     </row>
     <row r="88" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="274"/>
-      <c r="B88" s="279"/>
+      <c r="B88" s="285"/>
       <c r="C88" s="220"/>
       <c r="D88" s="32"/>
       <c r="E88" s="198">
@@ -5118,8 +5181,8 @@
       <c r="J88" s="38"/>
     </row>
     <row r="89" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="299"/>
-      <c r="B89" s="300"/>
+      <c r="A89" s="305"/>
+      <c r="B89" s="306"/>
       <c r="C89" s="53"/>
       <c r="D89" s="32"/>
       <c r="E89" s="42"/>
@@ -5130,11 +5193,11 @@
       <c r="J89" s="38"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="294" t="s">
+      <c r="A90" s="300" t="s">
         <v>16</v>
       </c>
-      <c r="B90" s="295"/>
-      <c r="C90" s="296"/>
+      <c r="B90" s="301"/>
+      <c r="C90" s="302"/>
       <c r="D90" s="50">
         <f>SUM(D88:D89)</f>
         <v>0</v>
@@ -5184,30 +5247,30 @@
         <f>D79-D77</f>
         <v>15214817.970000001</v>
       </c>
-      <c r="D94" s="280" t="s">
+      <c r="D94" s="286" t="s">
         <v>373</v>
       </c>
-      <c r="E94" s="280"/>
-      <c r="F94" s="280"/>
-      <c r="G94" s="280"/>
-      <c r="H94" s="280"/>
-      <c r="I94" s="280"/>
+      <c r="E94" s="286"/>
+      <c r="F94" s="286"/>
+      <c r="G94" s="286"/>
+      <c r="H94" s="286"/>
+      <c r="I94" s="286"/>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D95" s="280"/>
-      <c r="E95" s="280"/>
-      <c r="F95" s="280"/>
-      <c r="G95" s="280"/>
-      <c r="H95" s="280"/>
-      <c r="I95" s="280"/>
+      <c r="D95" s="286"/>
+      <c r="E95" s="286"/>
+      <c r="F95" s="286"/>
+      <c r="G95" s="286"/>
+      <c r="H95" s="286"/>
+      <c r="I95" s="286"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D96" s="280"/>
-      <c r="E96" s="280"/>
-      <c r="F96" s="280"/>
-      <c r="G96" s="280"/>
-      <c r="H96" s="280"/>
-      <c r="I96" s="280"/>
+      <c r="D96" s="286"/>
+      <c r="E96" s="286"/>
+      <c r="F96" s="286"/>
+      <c r="G96" s="286"/>
+      <c r="H96" s="286"/>
+      <c r="I96" s="286"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
@@ -5215,12 +5278,12 @@
       </c>
       <c r="B97" s="8"/>
       <c r="C97" s="9"/>
-      <c r="D97" s="280"/>
-      <c r="E97" s="280"/>
-      <c r="F97" s="280"/>
-      <c r="G97" s="280"/>
-      <c r="H97" s="280"/>
-      <c r="I97" s="280"/>
+      <c r="D97" s="286"/>
+      <c r="E97" s="286"/>
+      <c r="F97" s="286"/>
+      <c r="G97" s="286"/>
+      <c r="H97" s="286"/>
+      <c r="I97" s="286"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
@@ -5230,12 +5293,12 @@
         <v>1682660.59</v>
       </c>
       <c r="C98" s="11"/>
-      <c r="D98" s="280"/>
-      <c r="E98" s="280"/>
-      <c r="F98" s="280"/>
-      <c r="G98" s="280"/>
-      <c r="H98" s="280"/>
-      <c r="I98" s="280"/>
+      <c r="D98" s="286"/>
+      <c r="E98" s="286"/>
+      <c r="F98" s="286"/>
+      <c r="G98" s="286"/>
+      <c r="H98" s="286"/>
+      <c r="I98" s="286"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
@@ -5248,12 +5311,12 @@
       <c r="C99" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D99" s="280"/>
-      <c r="E99" s="280"/>
-      <c r="F99" s="280"/>
-      <c r="G99" s="280"/>
-      <c r="H99" s="280"/>
-      <c r="I99" s="280"/>
+      <c r="D99" s="286"/>
+      <c r="E99" s="286"/>
+      <c r="F99" s="286"/>
+      <c r="G99" s="286"/>
+      <c r="H99" s="286"/>
+      <c r="I99" s="286"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
@@ -5264,12 +5327,12 @@
         <v>0</v>
       </c>
       <c r="C100" s="11"/>
-      <c r="D100" s="280"/>
-      <c r="E100" s="280"/>
-      <c r="F100" s="280"/>
-      <c r="G100" s="280"/>
-      <c r="H100" s="280"/>
-      <c r="I100" s="280"/>
+      <c r="D100" s="286"/>
+      <c r="E100" s="286"/>
+      <c r="F100" s="286"/>
+      <c r="G100" s="286"/>
+      <c r="H100" s="286"/>
+      <c r="I100" s="286"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
@@ -5280,12 +5343,12 @@
         <v>-15214817.970000001</v>
       </c>
       <c r="C101" s="9"/>
-      <c r="D101" s="280"/>
-      <c r="E101" s="280"/>
-      <c r="F101" s="280"/>
-      <c r="G101" s="280"/>
-      <c r="H101" s="280"/>
-      <c r="I101" s="280"/>
+      <c r="D101" s="286"/>
+      <c r="E101" s="286"/>
+      <c r="F101" s="286"/>
+      <c r="G101" s="286"/>
+      <c r="H101" s="286"/>
+      <c r="I101" s="286"/>
       <c r="K101" s="32"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5297,12 +5360,12 @@
         <v>0</v>
       </c>
       <c r="C102" s="9"/>
-      <c r="D102" s="280"/>
-      <c r="E102" s="280"/>
-      <c r="F102" s="280"/>
-      <c r="G102" s="280"/>
-      <c r="H102" s="280"/>
-      <c r="I102" s="280"/>
+      <c r="D102" s="286"/>
+      <c r="E102" s="286"/>
+      <c r="F102" s="286"/>
+      <c r="G102" s="286"/>
+      <c r="H102" s="286"/>
+      <c r="I102" s="286"/>
       <c r="K102" s="33"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5314,12 +5377,12 @@
         <v>0</v>
       </c>
       <c r="C103" s="9"/>
-      <c r="D103" s="280"/>
-      <c r="E103" s="280"/>
-      <c r="F103" s="280"/>
-      <c r="G103" s="280"/>
-      <c r="H103" s="280"/>
-      <c r="I103" s="280"/>
+      <c r="D103" s="286"/>
+      <c r="E103" s="286"/>
+      <c r="F103" s="286"/>
+      <c r="G103" s="286"/>
+      <c r="H103" s="286"/>
+      <c r="I103" s="286"/>
       <c r="K103" s="33"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5330,12 +5393,12 @@
         <v>-141000</v>
       </c>
       <c r="C104" s="9"/>
-      <c r="D104" s="280"/>
-      <c r="E104" s="280"/>
-      <c r="F104" s="280"/>
-      <c r="G104" s="280"/>
-      <c r="H104" s="280"/>
-      <c r="I104" s="280"/>
+      <c r="D104" s="286"/>
+      <c r="E104" s="286"/>
+      <c r="F104" s="286"/>
+      <c r="G104" s="286"/>
+      <c r="H104" s="286"/>
+      <c r="I104" s="286"/>
       <c r="K104" s="33"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5347,12 +5410,12 @@
         <v>-20000</v>
       </c>
       <c r="C105" s="13"/>
-      <c r="D105" s="280"/>
-      <c r="E105" s="280"/>
-      <c r="F105" s="280"/>
-      <c r="G105" s="280"/>
-      <c r="H105" s="280"/>
-      <c r="I105" s="280"/>
+      <c r="D105" s="286"/>
+      <c r="E105" s="286"/>
+      <c r="F105" s="286"/>
+      <c r="G105" s="286"/>
+      <c r="H105" s="286"/>
+      <c r="I105" s="286"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
@@ -5363,12 +5426,12 @@
         <v>-406464</v>
       </c>
       <c r="C106" s="13"/>
-      <c r="D106" s="280"/>
-      <c r="E106" s="280"/>
-      <c r="F106" s="280"/>
-      <c r="G106" s="280"/>
-      <c r="H106" s="280"/>
-      <c r="I106" s="280"/>
+      <c r="D106" s="286"/>
+      <c r="E106" s="286"/>
+      <c r="F106" s="286"/>
+      <c r="G106" s="286"/>
+      <c r="H106" s="286"/>
+      <c r="I106" s="286"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
@@ -5379,22 +5442,22 @@
         <v>2575051.7590119969</v>
       </c>
       <c r="C107" s="44"/>
-      <c r="D107" s="280"/>
-      <c r="E107" s="280"/>
-      <c r="F107" s="280"/>
-      <c r="G107" s="280"/>
-      <c r="H107" s="280"/>
-      <c r="I107" s="280"/>
+      <c r="D107" s="286"/>
+      <c r="E107" s="286"/>
+      <c r="F107" s="286"/>
+      <c r="G107" s="286"/>
+      <c r="H107" s="286"/>
+      <c r="I107" s="286"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="13"/>
       <c r="C108" s="9"/>
-      <c r="D108" s="280"/>
-      <c r="E108" s="280"/>
-      <c r="F108" s="280"/>
-      <c r="G108" s="280"/>
-      <c r="H108" s="280"/>
-      <c r="I108" s="280"/>
+      <c r="D108" s="286"/>
+      <c r="E108" s="286"/>
+      <c r="F108" s="286"/>
+      <c r="G108" s="286"/>
+      <c r="H108" s="286"/>
+      <c r="I108" s="286"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
@@ -5402,12 +5465,12 @@
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="9"/>
-      <c r="D109" s="280"/>
-      <c r="E109" s="280"/>
-      <c r="F109" s="280"/>
-      <c r="G109" s="280"/>
-      <c r="H109" s="280"/>
-      <c r="I109" s="280"/>
+      <c r="D109" s="286"/>
+      <c r="E109" s="286"/>
+      <c r="F109" s="286"/>
+      <c r="G109" s="286"/>
+      <c r="H109" s="286"/>
+      <c r="I109" s="286"/>
     </row>
     <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="177"/>
@@ -5447,14 +5510,14 @@
         <v>-25817.72</v>
       </c>
       <c r="C114" s="9"/>
-      <c r="D114" s="301" t="s">
+      <c r="D114" s="307" t="s">
         <v>411</v>
       </c>
-      <c r="E114" s="302"/>
-      <c r="F114" s="302"/>
-      <c r="G114" s="302"/>
-      <c r="H114" s="302"/>
-      <c r="I114" s="303"/>
+      <c r="E114" s="308"/>
+      <c r="F114" s="308"/>
+      <c r="G114" s="308"/>
+      <c r="H114" s="308"/>
+      <c r="I114" s="309"/>
     </row>
     <row r="115" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="179" t="s">
@@ -5464,12 +5527,12 @@
         <v>-24000</v>
       </c>
       <c r="C115" s="9"/>
-      <c r="D115" s="304"/>
-      <c r="E115" s="305"/>
-      <c r="F115" s="305"/>
-      <c r="G115" s="305"/>
-      <c r="H115" s="305"/>
-      <c r="I115" s="306"/>
+      <c r="D115" s="310"/>
+      <c r="E115" s="311"/>
+      <c r="F115" s="311"/>
+      <c r="G115" s="311"/>
+      <c r="H115" s="311"/>
+      <c r="I115" s="312"/>
     </row>
     <row r="116" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="179" t="s">
@@ -5479,12 +5542,12 @@
         <v>-24000</v>
       </c>
       <c r="C116" s="9"/>
-      <c r="D116" s="304"/>
-      <c r="E116" s="305"/>
-      <c r="F116" s="305"/>
-      <c r="G116" s="305"/>
-      <c r="H116" s="305"/>
-      <c r="I116" s="306"/>
+      <c r="D116" s="310"/>
+      <c r="E116" s="311"/>
+      <c r="F116" s="311"/>
+      <c r="G116" s="311"/>
+      <c r="H116" s="311"/>
+      <c r="I116" s="312"/>
     </row>
     <row r="117" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="24" t="s">
@@ -5495,12 +5558,12 @@
         <v>-73817.72</v>
       </c>
       <c r="C117" s="9"/>
-      <c r="D117" s="307"/>
-      <c r="E117" s="308"/>
-      <c r="F117" s="308"/>
-      <c r="G117" s="308"/>
-      <c r="H117" s="308"/>
-      <c r="I117" s="309"/>
+      <c r="D117" s="313"/>
+      <c r="E117" s="314"/>
+      <c r="F117" s="314"/>
+      <c r="G117" s="314"/>
+      <c r="H117" s="314"/>
+      <c r="I117" s="315"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="13"/>
@@ -5527,15 +5590,15 @@
         <v>578840</v>
       </c>
       <c r="C122" s="15"/>
-      <c r="D122" s="281" t="s">
+      <c r="D122" s="287" t="s">
         <v>388</v>
       </c>
-      <c r="E122" s="282"/>
-      <c r="F122" s="282"/>
-      <c r="G122" s="282"/>
-      <c r="H122" s="282"/>
-      <c r="I122" s="282"/>
-      <c r="J122" s="283"/>
+      <c r="E122" s="288"/>
+      <c r="F122" s="288"/>
+      <c r="G122" s="288"/>
+      <c r="H122" s="288"/>
+      <c r="I122" s="288"/>
+      <c r="J122" s="289"/>
     </row>
     <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
@@ -5545,13 +5608,13 @@
         <v>20000</v>
       </c>
       <c r="C123" s="15"/>
-      <c r="D123" s="284"/>
-      <c r="E123" s="285"/>
-      <c r="F123" s="285"/>
-      <c r="G123" s="285"/>
-      <c r="H123" s="285"/>
-      <c r="I123" s="285"/>
-      <c r="J123" s="286"/>
+      <c r="D123" s="290"/>
+      <c r="E123" s="291"/>
+      <c r="F123" s="291"/>
+      <c r="G123" s="291"/>
+      <c r="H123" s="291"/>
+      <c r="I123" s="291"/>
+      <c r="J123" s="292"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="24" t="s">
@@ -5562,51 +5625,51 @@
         <v>598840</v>
       </c>
       <c r="C124" s="15"/>
-      <c r="D124" s="284"/>
-      <c r="E124" s="285"/>
-      <c r="F124" s="285"/>
-      <c r="G124" s="285"/>
-      <c r="H124" s="285"/>
-      <c r="I124" s="285"/>
-      <c r="J124" s="286"/>
+      <c r="D124" s="290"/>
+      <c r="E124" s="291"/>
+      <c r="F124" s="291"/>
+      <c r="G124" s="291"/>
+      <c r="H124" s="291"/>
+      <c r="I124" s="291"/>
+      <c r="J124" s="292"/>
     </row>
     <row r="125" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C125" s="16"/>
-      <c r="D125" s="284"/>
-      <c r="E125" s="285"/>
-      <c r="F125" s="285"/>
-      <c r="G125" s="285"/>
-      <c r="H125" s="285"/>
-      <c r="I125" s="285"/>
-      <c r="J125" s="286"/>
+      <c r="D125" s="290"/>
+      <c r="E125" s="291"/>
+      <c r="F125" s="291"/>
+      <c r="G125" s="291"/>
+      <c r="H125" s="291"/>
+      <c r="I125" s="291"/>
+      <c r="J125" s="292"/>
     </row>
     <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="290" t="s">
+      <c r="A126" s="296" t="s">
         <v>356</v>
       </c>
-      <c r="B126" s="292">
+      <c r="B126" s="298">
         <f>B124+B107+B117</f>
         <v>3100074.0390119967</v>
       </c>
       <c r="C126" s="9"/>
-      <c r="D126" s="284"/>
-      <c r="E126" s="285"/>
-      <c r="F126" s="285"/>
-      <c r="G126" s="285"/>
-      <c r="H126" s="285"/>
-      <c r="I126" s="285"/>
-      <c r="J126" s="286"/>
+      <c r="D126" s="290"/>
+      <c r="E126" s="291"/>
+      <c r="F126" s="291"/>
+      <c r="G126" s="291"/>
+      <c r="H126" s="291"/>
+      <c r="I126" s="291"/>
+      <c r="J126" s="292"/>
     </row>
     <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="291"/>
-      <c r="B127" s="293"/>
-      <c r="D127" s="287"/>
-      <c r="E127" s="288"/>
-      <c r="F127" s="288"/>
-      <c r="G127" s="288"/>
-      <c r="H127" s="288"/>
-      <c r="I127" s="288"/>
-      <c r="J127" s="289"/>
+      <c r="A127" s="297"/>
+      <c r="B127" s="299"/>
+      <c r="D127" s="293"/>
+      <c r="E127" s="294"/>
+      <c r="F127" s="294"/>
+      <c r="G127" s="294"/>
+      <c r="H127" s="294"/>
+      <c r="I127" s="294"/>
+      <c r="J127" s="295"/>
     </row>
     <row r="132" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C132" s="46"/>
@@ -5698,15 +5761,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A14:J18"/>
-    <mergeCell ref="A20:J22"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A65:B65"/>
     <mergeCell ref="A70:C70"/>
     <mergeCell ref="A88:B88"/>
@@ -5719,6 +5773,15 @@
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="D114:I117"/>
     <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A14:J18"/>
+    <mergeCell ref="A20:J22"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5753,13 +5816,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="352" t="s">
+      <c r="A1" s="348" t="s">
         <v>298</v>
       </c>
-      <c r="B1" s="353"/>
-      <c r="C1" s="353"/>
-      <c r="D1" s="353"/>
-      <c r="E1" s="353"/>
+      <c r="B1" s="349"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="349"/>
       <c r="F1" s="103" t="s">
         <v>274</v>
       </c>
@@ -5771,20 +5834,20 @@
       <c r="L1" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="331">
+      <c r="M1" s="324">
         <f>RESUMEN!D79-N4</f>
         <v>26225955.399999999</v>
       </c>
-      <c r="N1" s="332"/>
+      <c r="N1" s="325"/>
       <c r="O1" s="104"/>
       <c r="P1" s="39"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="354"/>
-      <c r="B2" s="355"/>
-      <c r="C2" s="355"/>
-      <c r="D2" s="355"/>
-      <c r="E2" s="355"/>
+      <c r="A2" s="350"/>
+      <c r="B2" s="351"/>
+      <c r="C2" s="351"/>
+      <c r="D2" s="351"/>
+      <c r="E2" s="351"/>
       <c r="F2" s="4" t="s">
         <v>273</v>
       </c>
@@ -5805,11 +5868,11 @@
       <c r="P2" s="39"/>
     </row>
     <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="354"/>
-      <c r="B3" s="355"/>
-      <c r="C3" s="355"/>
-      <c r="D3" s="355"/>
-      <c r="E3" s="355"/>
+      <c r="A3" s="350"/>
+      <c r="B3" s="351"/>
+      <c r="C3" s="351"/>
+      <c r="D3" s="351"/>
+      <c r="E3" s="351"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -5828,11 +5891,11 @@
       <c r="P3" s="39"/>
     </row>
     <row r="4" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="354"/>
-      <c r="B4" s="355"/>
-      <c r="C4" s="355"/>
-      <c r="D4" s="355"/>
-      <c r="E4" s="355"/>
+      <c r="A4" s="350"/>
+      <c r="B4" s="351"/>
+      <c r="C4" s="351"/>
+      <c r="D4" s="351"/>
+      <c r="E4" s="351"/>
       <c r="F4" s="4" t="s">
         <v>275</v>
       </c>
@@ -5852,11 +5915,11 @@
       <c r="P4" s="6"/>
     </row>
     <row r="5" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="356"/>
-      <c r="B5" s="357"/>
-      <c r="C5" s="357"/>
-      <c r="D5" s="357"/>
-      <c r="E5" s="357"/>
+      <c r="A5" s="352"/>
+      <c r="B5" s="353"/>
+      <c r="C5" s="353"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="353"/>
       <c r="F5" s="108"/>
       <c r="G5" s="108"/>
       <c r="H5" s="108"/>
@@ -5872,95 +5935,95 @@
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="337" t="s">
+      <c r="C6" s="333" t="s">
         <v>368</v>
       </c>
-      <c r="D6" s="338"/>
-      <c r="E6" s="338"/>
-      <c r="F6" s="338"/>
-      <c r="G6" s="338"/>
-      <c r="H6" s="338"/>
-      <c r="I6" s="338"/>
-      <c r="J6" s="338"/>
-      <c r="K6" s="338"/>
-      <c r="L6" s="338"/>
-      <c r="M6" s="338"/>
-      <c r="N6" s="338"/>
-      <c r="O6" s="339"/>
+      <c r="D6" s="334"/>
+      <c r="E6" s="334"/>
+      <c r="F6" s="334"/>
+      <c r="G6" s="334"/>
+      <c r="H6" s="334"/>
+      <c r="I6" s="334"/>
+      <c r="J6" s="334"/>
+      <c r="K6" s="334"/>
+      <c r="L6" s="334"/>
+      <c r="M6" s="334"/>
+      <c r="N6" s="334"/>
+      <c r="O6" s="335"/>
       <c r="P6" s="6"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="340"/>
-      <c r="D7" s="341"/>
-      <c r="E7" s="341"/>
-      <c r="F7" s="341"/>
-      <c r="G7" s="341"/>
-      <c r="H7" s="341"/>
-      <c r="I7" s="341"/>
-      <c r="J7" s="341"/>
-      <c r="K7" s="341"/>
-      <c r="L7" s="341"/>
-      <c r="M7" s="341"/>
-      <c r="N7" s="341"/>
-      <c r="O7" s="342"/>
+      <c r="C7" s="336"/>
+      <c r="D7" s="337"/>
+      <c r="E7" s="337"/>
+      <c r="F7" s="337"/>
+      <c r="G7" s="337"/>
+      <c r="H7" s="337"/>
+      <c r="I7" s="337"/>
+      <c r="J7" s="337"/>
+      <c r="K7" s="337"/>
+      <c r="L7" s="337"/>
+      <c r="M7" s="337"/>
+      <c r="N7" s="337"/>
+      <c r="O7" s="338"/>
       <c r="P7" s="6"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="340"/>
-      <c r="D8" s="341"/>
-      <c r="E8" s="341"/>
-      <c r="F8" s="341"/>
-      <c r="G8" s="341"/>
-      <c r="H8" s="341"/>
-      <c r="I8" s="341"/>
-      <c r="J8" s="341"/>
-      <c r="K8" s="341"/>
-      <c r="L8" s="341"/>
-      <c r="M8" s="341"/>
-      <c r="N8" s="341"/>
-      <c r="O8" s="342"/>
+      <c r="C8" s="336"/>
+      <c r="D8" s="337"/>
+      <c r="E8" s="337"/>
+      <c r="F8" s="337"/>
+      <c r="G8" s="337"/>
+      <c r="H8" s="337"/>
+      <c r="I8" s="337"/>
+      <c r="J8" s="337"/>
+      <c r="K8" s="337"/>
+      <c r="L8" s="337"/>
+      <c r="M8" s="337"/>
+      <c r="N8" s="337"/>
+      <c r="O8" s="338"/>
       <c r="P8" s="6"/>
     </row>
     <row r="9" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="343"/>
-      <c r="D9" s="344"/>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
-      <c r="G9" s="344"/>
-      <c r="H9" s="344"/>
-      <c r="I9" s="344"/>
-      <c r="J9" s="344"/>
-      <c r="K9" s="344"/>
-      <c r="L9" s="344"/>
-      <c r="M9" s="344"/>
-      <c r="N9" s="344"/>
-      <c r="O9" s="345"/>
+      <c r="C9" s="339"/>
+      <c r="D9" s="340"/>
+      <c r="E9" s="340"/>
+      <c r="F9" s="340"/>
+      <c r="G9" s="340"/>
+      <c r="H9" s="340"/>
+      <c r="I9" s="340"/>
+      <c r="J9" s="340"/>
+      <c r="K9" s="340"/>
+      <c r="L9" s="340"/>
+      <c r="M9" s="340"/>
+      <c r="N9" s="340"/>
+      <c r="O9" s="341"/>
       <c r="Q9" s="55"/>
     </row>
     <row r="10" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="346" t="s">
+      <c r="C10" s="342" t="s">
         <v>286</v>
       </c>
-      <c r="D10" s="347"/>
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
-      <c r="G10" s="347"/>
-      <c r="H10" s="347"/>
-      <c r="I10" s="347"/>
-      <c r="J10" s="347"/>
-      <c r="K10" s="347"/>
-      <c r="L10" s="347"/>
-      <c r="M10" s="347"/>
-      <c r="N10" s="347"/>
-      <c r="O10" s="348"/>
+      <c r="D10" s="343"/>
+      <c r="E10" s="343"/>
+      <c r="F10" s="343"/>
+      <c r="G10" s="343"/>
+      <c r="H10" s="343"/>
+      <c r="I10" s="343"/>
+      <c r="J10" s="343"/>
+      <c r="K10" s="343"/>
+      <c r="L10" s="343"/>
+      <c r="M10" s="343"/>
+      <c r="N10" s="343"/>
+      <c r="O10" s="344"/>
       <c r="Q10" t="s">
         <v>233</v>
       </c>
@@ -5972,19 +6035,19 @@
     <row r="11" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="349"/>
-      <c r="D11" s="350"/>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
-      <c r="G11" s="350"/>
-      <c r="H11" s="350"/>
-      <c r="I11" s="350"/>
-      <c r="J11" s="350"/>
-      <c r="K11" s="350"/>
-      <c r="L11" s="350"/>
-      <c r="M11" s="350"/>
-      <c r="N11" s="350"/>
-      <c r="O11" s="351"/>
+      <c r="C11" s="345"/>
+      <c r="D11" s="346"/>
+      <c r="E11" s="346"/>
+      <c r="F11" s="346"/>
+      <c r="G11" s="346"/>
+      <c r="H11" s="346"/>
+      <c r="I11" s="346"/>
+      <c r="J11" s="346"/>
+      <c r="K11" s="346"/>
+      <c r="L11" s="346"/>
+      <c r="M11" s="346"/>
+      <c r="N11" s="346"/>
+      <c r="O11" s="347"/>
       <c r="Q11" t="s">
         <v>234</v>
       </c>
@@ -5994,49 +6057,49 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="322" t="s">
+      <c r="A12" s="320" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="324" t="s">
+      <c r="B12" s="354" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="322" t="s">
+      <c r="C12" s="320" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="326" t="s">
+      <c r="D12" s="356" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="326" t="s">
+      <c r="E12" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F12" s="322" t="s">
+      <c r="F12" s="320" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="322" t="s">
+      <c r="G12" s="320" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="322" t="s">
+      <c r="H12" s="320" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="333" t="s">
+      <c r="I12" s="326" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="319" t="s">
+      <c r="J12" s="328" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="319" t="s">
+      <c r="K12" s="328" t="s">
         <v>366</v>
       </c>
-      <c r="L12" s="319" t="s">
+      <c r="L12" s="328" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="335" t="s">
+      <c r="M12" s="331" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="319" t="s">
+      <c r="N12" s="328" t="s">
         <v>260</v>
       </c>
-      <c r="O12" s="319" t="s">
+      <c r="O12" s="328" t="s">
         <v>259</v>
       </c>
       <c r="Q12" t="s">
@@ -6048,21 +6111,21 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="323"/>
-      <c r="B13" s="325"/>
-      <c r="C13" s="323"/>
-      <c r="D13" s="327"/>
-      <c r="E13" s="327"/>
-      <c r="F13" s="323"/>
-      <c r="G13" s="323"/>
-      <c r="H13" s="323"/>
-      <c r="I13" s="334"/>
-      <c r="J13" s="320"/>
-      <c r="K13" s="320"/>
-      <c r="L13" s="320"/>
-      <c r="M13" s="336"/>
-      <c r="N13" s="320"/>
-      <c r="O13" s="320"/>
+      <c r="A13" s="321"/>
+      <c r="B13" s="355"/>
+      <c r="C13" s="321"/>
+      <c r="D13" s="357"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="321"/>
+      <c r="G13" s="321"/>
+      <c r="H13" s="321"/>
+      <c r="I13" s="327"/>
+      <c r="J13" s="329"/>
+      <c r="K13" s="329"/>
+      <c r="L13" s="329"/>
+      <c r="M13" s="332"/>
+      <c r="N13" s="329"/>
+      <c r="O13" s="329"/>
       <c r="Q13" t="s">
         <v>236</v>
       </c>
@@ -6072,19 +6135,19 @@
       </c>
     </row>
     <row r="14" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="323"/>
-      <c r="B14" s="325"/>
-      <c r="C14" s="323"/>
-      <c r="D14" s="327"/>
-      <c r="E14" s="327"/>
-      <c r="F14" s="323"/>
-      <c r="G14" s="323"/>
-      <c r="H14" s="323"/>
-      <c r="I14" s="334"/>
-      <c r="J14" s="320"/>
-      <c r="K14" s="321"/>
-      <c r="L14" s="321"/>
-      <c r="M14" s="336"/>
+      <c r="A14" s="321"/>
+      <c r="B14" s="355"/>
+      <c r="C14" s="321"/>
+      <c r="D14" s="357"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="321"/>
+      <c r="G14" s="321"/>
+      <c r="H14" s="321"/>
+      <c r="I14" s="327"/>
+      <c r="J14" s="329"/>
+      <c r="K14" s="330"/>
+      <c r="L14" s="330"/>
+      <c r="M14" s="332"/>
       <c r="N14" s="84" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/09</v>
@@ -6151,8 +6214,8 @@
       <c r="P15" s="70" t="s">
         <v>342</v>
       </c>
-      <c r="R15" s="328"/>
-      <c r="S15" s="328"/>
+      <c r="R15" s="319"/>
+      <c r="S15" s="319"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
@@ -6200,8 +6263,8 @@
       <c r="P16" s="70" t="s">
         <v>341</v>
       </c>
-      <c r="R16" s="328"/>
-      <c r="S16" s="328"/>
+      <c r="R16" s="319"/>
+      <c r="S16" s="319"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
@@ -12820,34 +12883,34 @@
       </c>
     </row>
     <row r="136" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="330"/>
-      <c r="D136" s="330"/>
-      <c r="E136" s="330"/>
-      <c r="F136" s="330"/>
-      <c r="G136" s="330"/>
-      <c r="H136" s="330"/>
-      <c r="I136" s="330"/>
-      <c r="J136" s="330"/>
-      <c r="K136" s="330"/>
-      <c r="L136" s="330"/>
-      <c r="M136" s="330"/>
-      <c r="N136" s="330"/>
-      <c r="O136" s="330"/>
+      <c r="C136" s="323"/>
+      <c r="D136" s="323"/>
+      <c r="E136" s="323"/>
+      <c r="F136" s="323"/>
+      <c r="G136" s="323"/>
+      <c r="H136" s="323"/>
+      <c r="I136" s="323"/>
+      <c r="J136" s="323"/>
+      <c r="K136" s="323"/>
+      <c r="L136" s="323"/>
+      <c r="M136" s="323"/>
+      <c r="N136" s="323"/>
+      <c r="O136" s="323"/>
     </row>
     <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C137" s="330"/>
-      <c r="D137" s="330"/>
-      <c r="E137" s="330"/>
-      <c r="F137" s="330"/>
-      <c r="G137" s="330"/>
-      <c r="H137" s="330"/>
-      <c r="I137" s="330"/>
-      <c r="J137" s="330"/>
-      <c r="K137" s="330"/>
-      <c r="L137" s="330"/>
-      <c r="M137" s="330"/>
-      <c r="N137" s="330"/>
-      <c r="O137" s="330"/>
+      <c r="C137" s="323"/>
+      <c r="D137" s="323"/>
+      <c r="E137" s="323"/>
+      <c r="F137" s="323"/>
+      <c r="G137" s="323"/>
+      <c r="H137" s="323"/>
+      <c r="I137" s="323"/>
+      <c r="J137" s="323"/>
+      <c r="K137" s="323"/>
+      <c r="L137" s="323"/>
+      <c r="M137" s="323"/>
+      <c r="N137" s="323"/>
+      <c r="O137" s="323"/>
     </row>
     <row r="138" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C138" s="49"/>
@@ -12865,126 +12928,126 @@
       <c r="O138" s="49"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C139" s="280" t="s">
+      <c r="C139" s="286" t="s">
         <v>243</v>
       </c>
-      <c r="D139" s="280"/>
-      <c r="E139" s="280"/>
-      <c r="F139" s="280"/>
-      <c r="G139" s="280"/>
-      <c r="H139" s="280"/>
-      <c r="I139" s="280"/>
-      <c r="J139" s="280"/>
-      <c r="K139" s="280"/>
-      <c r="L139" s="280"/>
-      <c r="M139" s="280"/>
-      <c r="N139" s="280"/>
-      <c r="O139" s="280"/>
+      <c r="D139" s="286"/>
+      <c r="E139" s="286"/>
+      <c r="F139" s="286"/>
+      <c r="G139" s="286"/>
+      <c r="H139" s="286"/>
+      <c r="I139" s="286"/>
+      <c r="J139" s="286"/>
+      <c r="K139" s="286"/>
+      <c r="L139" s="286"/>
+      <c r="M139" s="286"/>
+      <c r="N139" s="286"/>
+      <c r="O139" s="286"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C140" s="280"/>
-      <c r="D140" s="280"/>
-      <c r="E140" s="280"/>
-      <c r="F140" s="280"/>
-      <c r="G140" s="280"/>
-      <c r="H140" s="280"/>
-      <c r="I140" s="280"/>
-      <c r="J140" s="280"/>
-      <c r="K140" s="280"/>
-      <c r="L140" s="280"/>
-      <c r="M140" s="280"/>
-      <c r="N140" s="280"/>
-      <c r="O140" s="280"/>
+      <c r="C140" s="286"/>
+      <c r="D140" s="286"/>
+      <c r="E140" s="286"/>
+      <c r="F140" s="286"/>
+      <c r="G140" s="286"/>
+      <c r="H140" s="286"/>
+      <c r="I140" s="286"/>
+      <c r="J140" s="286"/>
+      <c r="K140" s="286"/>
+      <c r="L140" s="286"/>
+      <c r="M140" s="286"/>
+      <c r="N140" s="286"/>
+      <c r="O140" s="286"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C141" s="280"/>
-      <c r="D141" s="280"/>
-      <c r="E141" s="280"/>
-      <c r="F141" s="280"/>
-      <c r="G141" s="280"/>
-      <c r="H141" s="280"/>
-      <c r="I141" s="280"/>
-      <c r="J141" s="280"/>
-      <c r="K141" s="280"/>
-      <c r="L141" s="280"/>
-      <c r="M141" s="280"/>
-      <c r="N141" s="280"/>
-      <c r="O141" s="280"/>
+      <c r="C141" s="286"/>
+      <c r="D141" s="286"/>
+      <c r="E141" s="286"/>
+      <c r="F141" s="286"/>
+      <c r="G141" s="286"/>
+      <c r="H141" s="286"/>
+      <c r="I141" s="286"/>
+      <c r="J141" s="286"/>
+      <c r="K141" s="286"/>
+      <c r="L141" s="286"/>
+      <c r="M141" s="286"/>
+      <c r="N141" s="286"/>
+      <c r="O141" s="286"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C142" s="280"/>
-      <c r="D142" s="280"/>
-      <c r="E142" s="280"/>
-      <c r="F142" s="280"/>
-      <c r="G142" s="280"/>
-      <c r="H142" s="280"/>
-      <c r="I142" s="280"/>
-      <c r="J142" s="280"/>
-      <c r="K142" s="280"/>
-      <c r="L142" s="280"/>
-      <c r="M142" s="280"/>
-      <c r="N142" s="280"/>
-      <c r="O142" s="280"/>
+      <c r="C142" s="286"/>
+      <c r="D142" s="286"/>
+      <c r="E142" s="286"/>
+      <c r="F142" s="286"/>
+      <c r="G142" s="286"/>
+      <c r="H142" s="286"/>
+      <c r="I142" s="286"/>
+      <c r="J142" s="286"/>
+      <c r="K142" s="286"/>
+      <c r="L142" s="286"/>
+      <c r="M142" s="286"/>
+      <c r="N142" s="286"/>
+      <c r="O142" s="286"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="280"/>
-      <c r="D143" s="280"/>
-      <c r="E143" s="280"/>
-      <c r="F143" s="280"/>
-      <c r="G143" s="280"/>
-      <c r="H143" s="280"/>
-      <c r="I143" s="280"/>
-      <c r="J143" s="280"/>
-      <c r="K143" s="280"/>
-      <c r="L143" s="280"/>
-      <c r="M143" s="280"/>
-      <c r="N143" s="280"/>
-      <c r="O143" s="280"/>
+      <c r="C143" s="286"/>
+      <c r="D143" s="286"/>
+      <c r="E143" s="286"/>
+      <c r="F143" s="286"/>
+      <c r="G143" s="286"/>
+      <c r="H143" s="286"/>
+      <c r="I143" s="286"/>
+      <c r="J143" s="286"/>
+      <c r="K143" s="286"/>
+      <c r="L143" s="286"/>
+      <c r="M143" s="286"/>
+      <c r="N143" s="286"/>
+      <c r="O143" s="286"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C144" s="280"/>
-      <c r="D144" s="280"/>
-      <c r="E144" s="280"/>
-      <c r="F144" s="280"/>
-      <c r="G144" s="280"/>
-      <c r="H144" s="280"/>
-      <c r="I144" s="280"/>
-      <c r="J144" s="280"/>
-      <c r="K144" s="280"/>
-      <c r="L144" s="280"/>
-      <c r="M144" s="280"/>
-      <c r="N144" s="280"/>
-      <c r="O144" s="280"/>
+      <c r="C144" s="286"/>
+      <c r="D144" s="286"/>
+      <c r="E144" s="286"/>
+      <c r="F144" s="286"/>
+      <c r="G144" s="286"/>
+      <c r="H144" s="286"/>
+      <c r="I144" s="286"/>
+      <c r="J144" s="286"/>
+      <c r="K144" s="286"/>
+      <c r="L144" s="286"/>
+      <c r="M144" s="286"/>
+      <c r="N144" s="286"/>
+      <c r="O144" s="286"/>
     </row>
     <row r="145" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C145" s="280"/>
-      <c r="D145" s="280"/>
-      <c r="E145" s="280"/>
-      <c r="F145" s="280"/>
-      <c r="G145" s="280"/>
-      <c r="H145" s="280"/>
-      <c r="I145" s="280"/>
-      <c r="J145" s="280"/>
-      <c r="K145" s="280"/>
-      <c r="L145" s="280"/>
-      <c r="M145" s="280"/>
-      <c r="N145" s="280"/>
-      <c r="O145" s="280"/>
+      <c r="C145" s="286"/>
+      <c r="D145" s="286"/>
+      <c r="E145" s="286"/>
+      <c r="F145" s="286"/>
+      <c r="G145" s="286"/>
+      <c r="H145" s="286"/>
+      <c r="I145" s="286"/>
+      <c r="J145" s="286"/>
+      <c r="K145" s="286"/>
+      <c r="L145" s="286"/>
+      <c r="M145" s="286"/>
+      <c r="N145" s="286"/>
+      <c r="O145" s="286"/>
     </row>
     <row r="146" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C146" s="280"/>
-      <c r="D146" s="280"/>
-      <c r="E146" s="280"/>
-      <c r="F146" s="280"/>
-      <c r="G146" s="280"/>
-      <c r="H146" s="280"/>
-      <c r="I146" s="280"/>
-      <c r="J146" s="280"/>
-      <c r="K146" s="280"/>
-      <c r="L146" s="280"/>
-      <c r="M146" s="280"/>
-      <c r="N146" s="280"/>
-      <c r="O146" s="280"/>
+      <c r="C146" s="286"/>
+      <c r="D146" s="286"/>
+      <c r="E146" s="286"/>
+      <c r="F146" s="286"/>
+      <c r="G146" s="286"/>
+      <c r="H146" s="286"/>
+      <c r="I146" s="286"/>
+      <c r="J146" s="286"/>
+      <c r="K146" s="286"/>
+      <c r="L146" s="286"/>
+      <c r="M146" s="286"/>
+      <c r="N146" s="286"/>
+      <c r="O146" s="286"/>
     </row>
     <row r="147" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C147" s="49"/>
@@ -13017,118 +13080,125 @@
       <c r="O148" s="49"/>
     </row>
     <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="329" t="s">
+      <c r="C149" s="322" t="s">
         <v>242</v>
       </c>
-      <c r="D149" s="329"/>
-      <c r="E149" s="329"/>
-      <c r="F149" s="329"/>
-      <c r="G149" s="329"/>
-      <c r="H149" s="329"/>
-      <c r="I149" s="329"/>
-      <c r="J149" s="329"/>
-      <c r="K149" s="329"/>
-      <c r="L149" s="329"/>
-      <c r="M149" s="329"/>
-      <c r="N149" s="329"/>
-      <c r="O149" s="329"/>
+      <c r="D149" s="322"/>
+      <c r="E149" s="322"/>
+      <c r="F149" s="322"/>
+      <c r="G149" s="322"/>
+      <c r="H149" s="322"/>
+      <c r="I149" s="322"/>
+      <c r="J149" s="322"/>
+      <c r="K149" s="322"/>
+      <c r="L149" s="322"/>
+      <c r="M149" s="322"/>
+      <c r="N149" s="322"/>
+      <c r="O149" s="322"/>
     </row>
     <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="329"/>
-      <c r="D150" s="329"/>
-      <c r="E150" s="329"/>
-      <c r="F150" s="329"/>
-      <c r="G150" s="329"/>
-      <c r="H150" s="329"/>
-      <c r="I150" s="329"/>
-      <c r="J150" s="329"/>
-      <c r="K150" s="329"/>
-      <c r="L150" s="329"/>
-      <c r="M150" s="329"/>
-      <c r="N150" s="329"/>
-      <c r="O150" s="329"/>
+      <c r="C150" s="322"/>
+      <c r="D150" s="322"/>
+      <c r="E150" s="322"/>
+      <c r="F150" s="322"/>
+      <c r="G150" s="322"/>
+      <c r="H150" s="322"/>
+      <c r="I150" s="322"/>
+      <c r="J150" s="322"/>
+      <c r="K150" s="322"/>
+      <c r="L150" s="322"/>
+      <c r="M150" s="322"/>
+      <c r="N150" s="322"/>
+      <c r="O150" s="322"/>
     </row>
     <row r="151" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C151" s="329"/>
-      <c r="D151" s="329"/>
-      <c r="E151" s="329"/>
-      <c r="F151" s="329"/>
-      <c r="G151" s="329"/>
-      <c r="H151" s="329"/>
-      <c r="I151" s="329"/>
-      <c r="J151" s="329"/>
-      <c r="K151" s="329"/>
-      <c r="L151" s="329"/>
-      <c r="M151" s="329"/>
-      <c r="N151" s="329"/>
-      <c r="O151" s="329"/>
+      <c r="C151" s="322"/>
+      <c r="D151" s="322"/>
+      <c r="E151" s="322"/>
+      <c r="F151" s="322"/>
+      <c r="G151" s="322"/>
+      <c r="H151" s="322"/>
+      <c r="I151" s="322"/>
+      <c r="J151" s="322"/>
+      <c r="K151" s="322"/>
+      <c r="L151" s="322"/>
+      <c r="M151" s="322"/>
+      <c r="N151" s="322"/>
+      <c r="O151" s="322"/>
       <c r="Q151" s="55">
         <f>M1-L134</f>
         <v>150436.23675993457</v>
       </c>
     </row>
     <row r="152" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="329"/>
-      <c r="D152" s="329"/>
-      <c r="E152" s="329"/>
-      <c r="F152" s="329"/>
-      <c r="G152" s="329"/>
-      <c r="H152" s="329"/>
-      <c r="I152" s="329"/>
-      <c r="J152" s="329"/>
-      <c r="K152" s="329"/>
-      <c r="L152" s="329"/>
-      <c r="M152" s="329"/>
-      <c r="N152" s="329"/>
-      <c r="O152" s="329"/>
+      <c r="C152" s="322"/>
+      <c r="D152" s="322"/>
+      <c r="E152" s="322"/>
+      <c r="F152" s="322"/>
+      <c r="G152" s="322"/>
+      <c r="H152" s="322"/>
+      <c r="I152" s="322"/>
+      <c r="J152" s="322"/>
+      <c r="K152" s="322"/>
+      <c r="L152" s="322"/>
+      <c r="M152" s="322"/>
+      <c r="N152" s="322"/>
+      <c r="O152" s="322"/>
     </row>
     <row r="153" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="329"/>
-      <c r="D153" s="329"/>
-      <c r="E153" s="329"/>
-      <c r="F153" s="329"/>
-      <c r="G153" s="329"/>
-      <c r="H153" s="329"/>
-      <c r="I153" s="329"/>
-      <c r="J153" s="329"/>
-      <c r="K153" s="329"/>
-      <c r="L153" s="329"/>
-      <c r="M153" s="329"/>
-      <c r="N153" s="329"/>
-      <c r="O153" s="329"/>
+      <c r="C153" s="322"/>
+      <c r="D153" s="322"/>
+      <c r="E153" s="322"/>
+      <c r="F153" s="322"/>
+      <c r="G153" s="322"/>
+      <c r="H153" s="322"/>
+      <c r="I153" s="322"/>
+      <c r="J153" s="322"/>
+      <c r="K153" s="322"/>
+      <c r="L153" s="322"/>
+      <c r="M153" s="322"/>
+      <c r="N153" s="322"/>
+      <c r="O153" s="322"/>
     </row>
     <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="329"/>
-      <c r="D154" s="329"/>
-      <c r="E154" s="329"/>
-      <c r="F154" s="329"/>
-      <c r="G154" s="329"/>
-      <c r="H154" s="329"/>
-      <c r="I154" s="329"/>
-      <c r="J154" s="329"/>
-      <c r="K154" s="329"/>
-      <c r="L154" s="329"/>
-      <c r="M154" s="329"/>
-      <c r="N154" s="329"/>
-      <c r="O154" s="329"/>
+      <c r="C154" s="322"/>
+      <c r="D154" s="322"/>
+      <c r="E154" s="322"/>
+      <c r="F154" s="322"/>
+      <c r="G154" s="322"/>
+      <c r="H154" s="322"/>
+      <c r="I154" s="322"/>
+      <c r="J154" s="322"/>
+      <c r="K154" s="322"/>
+      <c r="L154" s="322"/>
+      <c r="M154" s="322"/>
+      <c r="N154" s="322"/>
+      <c r="O154" s="322"/>
     </row>
     <row r="155" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C155" s="329"/>
-      <c r="D155" s="329"/>
-      <c r="E155" s="329"/>
-      <c r="F155" s="329"/>
-      <c r="G155" s="329"/>
-      <c r="H155" s="329"/>
-      <c r="I155" s="329"/>
-      <c r="J155" s="329"/>
-      <c r="K155" s="329"/>
-      <c r="L155" s="329"/>
-      <c r="M155" s="329"/>
-      <c r="N155" s="329"/>
-      <c r="O155" s="329"/>
+      <c r="C155" s="322"/>
+      <c r="D155" s="322"/>
+      <c r="E155" s="322"/>
+      <c r="F155" s="322"/>
+      <c r="G155" s="322"/>
+      <c r="H155" s="322"/>
+      <c r="I155" s="322"/>
+      <c r="J155" s="322"/>
+      <c r="K155" s="322"/>
+      <c r="L155" s="322"/>
+      <c r="M155" s="322"/>
+      <c r="N155" s="322"/>
+      <c r="O155" s="322"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="R15:S16"/>
     <mergeCell ref="G12:G14"/>
     <mergeCell ref="C149:O155"/>
@@ -13145,13 +13215,6 @@
     <mergeCell ref="C6:O9"/>
     <mergeCell ref="C10:O11"/>
     <mergeCell ref="A1:E5"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="E12:E14"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13254,67 +13317,67 @@
       <c r="AA3" s="167"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="322" t="s">
+      <c r="A4" s="320" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="322" t="s">
+      <c r="B4" s="320" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="322" t="s">
+      <c r="C4" s="320" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="322" t="s">
+      <c r="D4" s="320" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="319" t="s">
+      <c r="E4" s="328" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="319" t="s">
+      <c r="F4" s="328" t="s">
         <v>327</v>
       </c>
-      <c r="G4" s="319" t="s">
+      <c r="G4" s="328" t="s">
         <v>260</v>
       </c>
-      <c r="H4" s="319" t="s">
+      <c r="H4" s="328" t="s">
         <v>332</v>
       </c>
-      <c r="I4" s="319" t="s">
+      <c r="I4" s="328" t="s">
         <v>339</v>
       </c>
       <c r="J4" s="369" t="s">
         <v>328</v>
       </c>
       <c r="K4" s="83"/>
-      <c r="L4" s="358" t="s">
+      <c r="L4" s="359" t="s">
         <v>336</v>
       </c>
-      <c r="M4" s="319" t="s">
+      <c r="M4" s="328" t="s">
         <v>337</v>
       </c>
-      <c r="N4" s="319" t="s">
+      <c r="N4" s="328" t="s">
         <v>329</v>
       </c>
-      <c r="O4" s="319" t="s">
+      <c r="O4" s="328" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="31"/>
     </row>
     <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="323"/>
-      <c r="B5" s="323"/>
-      <c r="C5" s="323"/>
-      <c r="D5" s="323"/>
-      <c r="E5" s="320"/>
-      <c r="F5" s="320"/>
-      <c r="G5" s="320"/>
-      <c r="H5" s="320"/>
-      <c r="I5" s="320"/>
+      <c r="A5" s="321"/>
+      <c r="B5" s="321"/>
+      <c r="C5" s="321"/>
+      <c r="D5" s="321"/>
+      <c r="E5" s="329"/>
+      <c r="F5" s="329"/>
+      <c r="G5" s="329"/>
+      <c r="H5" s="329"/>
+      <c r="I5" s="329"/>
       <c r="J5" s="370"/>
       <c r="K5" s="83"/>
-      <c r="L5" s="359"/>
-      <c r="M5" s="320"/>
-      <c r="N5" s="320"/>
-      <c r="O5" s="320"/>
+      <c r="L5" s="360"/>
+      <c r="M5" s="329"/>
+      <c r="N5" s="329"/>
+      <c r="O5" s="329"/>
       <c r="R5" s="31"/>
     </row>
     <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -13322,17 +13385,17 @@
       <c r="B6" s="372"/>
       <c r="C6" s="372"/>
       <c r="D6" s="372"/>
-      <c r="E6" s="361"/>
-      <c r="F6" s="361"/>
-      <c r="G6" s="361"/>
-      <c r="H6" s="361"/>
-      <c r="I6" s="361"/>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="G6" s="358"/>
+      <c r="H6" s="358"/>
+      <c r="I6" s="358"/>
       <c r="J6" s="371"/>
       <c r="K6" s="136"/>
-      <c r="L6" s="360"/>
-      <c r="M6" s="361"/>
-      <c r="N6" s="361"/>
-      <c r="O6" s="361"/>
+      <c r="L6" s="361"/>
+      <c r="M6" s="358"/>
+      <c r="N6" s="358"/>
+      <c r="O6" s="358"/>
       <c r="R6" s="31"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -13387,8 +13450,8 @@
       <c r="P7" s="70">
         <v>0.7</v>
       </c>
-      <c r="R7" s="328"/>
-      <c r="S7" s="328"/>
+      <c r="R7" s="319"/>
+      <c r="S7" s="319"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="137" t="s">
@@ -13444,8 +13507,8 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="328"/>
-      <c r="S8" s="328"/>
+      <c r="R8" s="319"/>
+      <c r="S8" s="319"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="137" t="s">
@@ -17894,11 +17957,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="L4:L6"/>
-    <mergeCell ref="M4:M6"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A1:O2"/>
     <mergeCell ref="R7:S8"/>
     <mergeCell ref="J4:J6"/>
     <mergeCell ref="N4:N6"/>
@@ -17911,6 +17969,11 @@
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="H4:H6"/>
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M4:M6"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A1:O2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="85" orientation="landscape" r:id="rId1"/>
@@ -17918,6 +17981,232 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F334087C-F49A-40D2-A732-EFA1FDB50C59}">
+  <dimension ref="C2:H20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="382" t="s">
+        <v>414</v>
+      </c>
+      <c r="D3" s="383"/>
+      <c r="E3" s="383"/>
+      <c r="F3" s="383"/>
+      <c r="G3" s="383"/>
+      <c r="H3" s="384"/>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C4" s="385" t="s">
+        <v>415</v>
+      </c>
+      <c r="D4" s="386" t="s">
+        <v>416</v>
+      </c>
+      <c r="E4" s="386"/>
+      <c r="F4" s="386"/>
+      <c r="G4" s="386" t="s">
+        <v>417</v>
+      </c>
+      <c r="H4" s="387"/>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" s="388" t="str">
+        <f>PRORRATEO!C31</f>
+        <v>3ºF</v>
+      </c>
+      <c r="D5" s="389" t="str">
+        <f>PRORRATEO!D31</f>
+        <v>Ayala, Roberto Adrian</v>
+      </c>
+      <c r="E5" s="389"/>
+      <c r="F5" s="389"/>
+      <c r="G5" s="390">
+        <f>PRORRATEO!N31</f>
+        <v>2143819.12</v>
+      </c>
+      <c r="H5" s="391"/>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" s="388"/>
+      <c r="D6" s="389"/>
+      <c r="E6" s="389"/>
+      <c r="F6" s="389"/>
+      <c r="G6" s="389"/>
+      <c r="H6" s="392"/>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" s="388"/>
+      <c r="D7" s="389"/>
+      <c r="E7" s="389"/>
+      <c r="F7" s="389"/>
+      <c r="G7" s="389" t="s">
+        <v>418</v>
+      </c>
+      <c r="H7" s="392"/>
+    </row>
+    <row r="8" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="393"/>
+      <c r="D8" s="394"/>
+      <c r="E8" s="394"/>
+      <c r="F8" s="394"/>
+      <c r="G8" s="395">
+        <v>0</v>
+      </c>
+      <c r="H8" s="396"/>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="385" t="s">
+        <v>415</v>
+      </c>
+      <c r="D9" s="386" t="s">
+        <v>416</v>
+      </c>
+      <c r="E9" s="386"/>
+      <c r="F9" s="386"/>
+      <c r="G9" s="386" t="s">
+        <v>417</v>
+      </c>
+      <c r="H9" s="387"/>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="388" t="str">
+        <f>PRORRATEO!C37</f>
+        <v>4ºF</v>
+      </c>
+      <c r="D10" s="389" t="str">
+        <f>PRORRATEO!D37</f>
+        <v>Ayala, Roberto Adrian</v>
+      </c>
+      <c r="E10" s="389"/>
+      <c r="F10" s="389"/>
+      <c r="G10" s="390">
+        <f>PRORRATEO!N37</f>
+        <v>1626068.18</v>
+      </c>
+      <c r="H10" s="391"/>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="388"/>
+      <c r="D11" s="389"/>
+      <c r="E11" s="389"/>
+      <c r="F11" s="389"/>
+      <c r="G11" s="389"/>
+      <c r="H11" s="392"/>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="388"/>
+      <c r="D12" s="389"/>
+      <c r="E12" s="389"/>
+      <c r="F12" s="389"/>
+      <c r="G12" s="389" t="s">
+        <v>419</v>
+      </c>
+      <c r="H12" s="392"/>
+    </row>
+    <row r="13" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="393"/>
+      <c r="D13" s="394"/>
+      <c r="E13" s="394"/>
+      <c r="F13" s="394"/>
+      <c r="G13" s="395">
+        <v>0</v>
+      </c>
+      <c r="H13" s="396"/>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="385" t="s">
+        <v>415</v>
+      </c>
+      <c r="D14" s="386" t="s">
+        <v>416</v>
+      </c>
+      <c r="E14" s="386"/>
+      <c r="F14" s="386"/>
+      <c r="G14" s="386" t="s">
+        <v>417</v>
+      </c>
+      <c r="H14" s="387"/>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="388" t="str">
+        <f>PRORRATEO!C43</f>
+        <v>5ºF</v>
+      </c>
+      <c r="D15" s="389" t="str">
+        <f>PRORRATEO!D43</f>
+        <v>Ayala, Agustin</v>
+      </c>
+      <c r="E15" s="389"/>
+      <c r="F15" s="389"/>
+      <c r="G15" s="390">
+        <f>PRORRATEO!N43</f>
+        <v>1371288.24</v>
+      </c>
+      <c r="H15" s="391"/>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C16" s="388"/>
+      <c r="D16" s="389"/>
+      <c r="E16" s="389"/>
+      <c r="F16" s="389"/>
+      <c r="G16" s="389"/>
+      <c r="H16" s="392"/>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C17" s="388"/>
+      <c r="D17" s="389"/>
+      <c r="E17" s="389"/>
+      <c r="F17" s="389"/>
+      <c r="G17" s="389" t="s">
+        <v>420</v>
+      </c>
+      <c r="H17" s="392"/>
+    </row>
+    <row r="18" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="393"/>
+      <c r="D18" s="394"/>
+      <c r="E18" s="394"/>
+      <c r="F18" s="394"/>
+      <c r="G18" s="395">
+        <v>0</v>
+      </c>
+      <c r="H18" s="396"/>
+    </row>
+    <row r="19" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="397" t="s">
+        <v>421</v>
+      </c>
+      <c r="D20" s="398"/>
+      <c r="E20" s="398"/>
+      <c r="F20" s="398"/>
+      <c r="G20" s="399">
+        <f>G15+G10+G5</f>
+        <v>5141175.54</v>
+      </c>
+      <c r="H20" s="400"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G13:H13"/>
+  </mergeCells>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="115" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="C1:M17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/2026/EL MIRADOR/Agosto/Agosto - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Agosto/Agosto - EL MIRADOR.xlsx
@@ -1,41 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04427F6-5836-4974-A00D-FFCDBED56E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81945496-AA6C-4D8F-921B-690FACB71AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
     <sheet name="ARBA" sheetId="4" r:id="rId3"/>
-    <sheet name="DEUDA AYALA" sheetId="5" r:id="rId4"/>
-    <sheet name="ANOTACIONES" sheetId="3" r:id="rId5"/>
+    <sheet name="ANOTACIONES" sheetId="3" r:id="rId4"/>
+    <sheet name="DEUDA AYALA" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">ARBA!$A$1:$O$82</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'DEUDA AYALA'!$C$3:$H$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'DEUDA AYALA'!$C$3:$H$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$156</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$127</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="419">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1173,21 +1168,6 @@
     <t>Di mito, Vicente Argentino - Cerantes , Mabel</t>
   </si>
   <si>
-    <t>9D</t>
-  </si>
-  <si>
-    <t>El mirador 9D: El mes pasado deposito $141.000 (ya chequeado) y no se lo imputamos - Este mes debe abonar; 162.394,46</t>
-  </si>
-  <si>
-    <t>12F</t>
-  </si>
-  <si>
-    <t>Catalina (la Vieja)</t>
-  </si>
-  <si>
-    <t>Deposito $13070,64 11/08</t>
-  </si>
-  <si>
     <t>VTO 17/09</t>
   </si>
   <si>
@@ -1309,6 +1289,12 @@
   </si>
   <si>
     <t>TOTAL DEUDA</t>
+  </si>
+  <si>
+    <t>Local 2</t>
+  </si>
+  <si>
+    <t>Pago $34.752 y $770.504 de expensas y arba</t>
   </si>
 </sst>
 </file>
@@ -1987,7 +1973,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="401">
+  <cellXfs count="395">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2318,11 +2304,6 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2335,8 +2316,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="10" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2350,29 +2329,20 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="10" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2485,14 +2455,53 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2511,15 +2520,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2590,20 +2590,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2635,17 +2635,32 @@
     <xf numFmtId="1" fontId="19" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2674,43 +2689,8 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
@@ -2792,9 +2772,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2832,9 +2812,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2867,26 +2847,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2919,26 +2882,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3113,24 +3059,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N142"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="68"/>
       <c r="B1" s="76"/>
       <c r="C1" s="81" t="s">
@@ -3144,7 +3090,7 @@
       <c r="I1" s="66"/>
       <c r="J1" s="67"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="69"/>
       <c r="B2" s="77"/>
       <c r="C2" s="77" t="s">
@@ -3158,7 +3104,7 @@
       <c r="I2" s="78"/>
       <c r="J2" s="65"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="69"/>
       <c r="B3" s="77"/>
       <c r="C3" s="77" t="s">
@@ -3174,7 +3120,7 @@
       <c r="I3" s="78"/>
       <c r="J3" s="65"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="69"/>
       <c r="B4" s="77"/>
       <c r="C4" s="77" t="s">
@@ -3188,11 +3134,11 @@
       <c r="I4" s="78"/>
       <c r="J4" s="65"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="72"/>
       <c r="B5" s="77"/>
       <c r="C5" s="77" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D5" s="77"/>
       <c r="E5" s="77" t="s">
@@ -3204,7 +3150,7 @@
       <c r="I5" s="77"/>
       <c r="J5" s="73"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="72"/>
       <c r="B6" s="77"/>
       <c r="C6" s="77" t="s">
@@ -3218,7 +3164,7 @@
       <c r="I6" s="77"/>
       <c r="J6" s="73"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="74"/>
       <c r="B7" s="75"/>
       <c r="C7" s="75"/>
@@ -3230,115 +3176,115 @@
       <c r="I7" s="75"/>
       <c r="J7" s="79"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="276" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="315" t="s">
         <v>243</v>
       </c>
-      <c r="B14" s="276"/>
-      <c r="C14" s="276"/>
-      <c r="D14" s="276"/>
-      <c r="E14" s="276"/>
-      <c r="F14" s="276"/>
-      <c r="G14" s="276"/>
-      <c r="H14" s="276"/>
-      <c r="I14" s="276"/>
-      <c r="J14" s="276"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="276"/>
-      <c r="B15" s="276"/>
-      <c r="C15" s="276"/>
-      <c r="D15" s="276"/>
-      <c r="E15" s="276"/>
-      <c r="F15" s="276"/>
-      <c r="G15" s="276"/>
-      <c r="H15" s="276"/>
-      <c r="I15" s="276"/>
-      <c r="J15" s="276"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="276"/>
-      <c r="B16" s="276"/>
-      <c r="C16" s="276"/>
-      <c r="D16" s="276"/>
-      <c r="E16" s="276"/>
-      <c r="F16" s="276"/>
-      <c r="G16" s="276"/>
-      <c r="H16" s="276"/>
-      <c r="I16" s="276"/>
-      <c r="J16" s="276"/>
-    </row>
-    <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="276"/>
-      <c r="B17" s="276"/>
-      <c r="C17" s="276"/>
-      <c r="D17" s="276"/>
-      <c r="E17" s="276"/>
-      <c r="F17" s="276"/>
-      <c r="G17" s="276"/>
-      <c r="H17" s="276"/>
-      <c r="I17" s="276"/>
-      <c r="J17" s="276"/>
-    </row>
-    <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="276"/>
-      <c r="B18" s="276"/>
-      <c r="C18" s="276"/>
-      <c r="D18" s="276"/>
-      <c r="E18" s="276"/>
-      <c r="F18" s="276"/>
-      <c r="G18" s="276"/>
-      <c r="H18" s="276"/>
-      <c r="I18" s="276"/>
-      <c r="J18" s="276"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="315"/>
+      <c r="C14" s="315"/>
+      <c r="D14" s="315"/>
+      <c r="E14" s="315"/>
+      <c r="F14" s="315"/>
+      <c r="G14" s="315"/>
+      <c r="H14" s="315"/>
+      <c r="I14" s="315"/>
+      <c r="J14" s="315"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="315"/>
+      <c r="B15" s="315"/>
+      <c r="C15" s="315"/>
+      <c r="D15" s="315"/>
+      <c r="E15" s="315"/>
+      <c r="F15" s="315"/>
+      <c r="G15" s="315"/>
+      <c r="H15" s="315"/>
+      <c r="I15" s="315"/>
+      <c r="J15" s="315"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="315"/>
+      <c r="B16" s="315"/>
+      <c r="C16" s="315"/>
+      <c r="D16" s="315"/>
+      <c r="E16" s="315"/>
+      <c r="F16" s="315"/>
+      <c r="G16" s="315"/>
+      <c r="H16" s="315"/>
+      <c r="I16" s="315"/>
+      <c r="J16" s="315"/>
+    </row>
+    <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="315"/>
+      <c r="B17" s="315"/>
+      <c r="C17" s="315"/>
+      <c r="D17" s="315"/>
+      <c r="E17" s="315"/>
+      <c r="F17" s="315"/>
+      <c r="G17" s="315"/>
+      <c r="H17" s="315"/>
+      <c r="I17" s="315"/>
+      <c r="J17" s="315"/>
+    </row>
+    <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="315"/>
+      <c r="B18" s="315"/>
+      <c r="C18" s="315"/>
+      <c r="D18" s="315"/>
+      <c r="E18" s="315"/>
+      <c r="F18" s="315"/>
+      <c r="G18" s="315"/>
+      <c r="H18" s="315"/>
+      <c r="I18" s="315"/>
+      <c r="J18" s="315"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="H19" s="60"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="277" t="s">
-        <v>381</v>
-      </c>
-      <c r="B20" s="277"/>
-      <c r="C20" s="277"/>
-      <c r="D20" s="277"/>
-      <c r="E20" s="277"/>
-      <c r="F20" s="277"/>
-      <c r="G20" s="277"/>
-      <c r="H20" s="277"/>
-      <c r="I20" s="277"/>
-      <c r="J20" s="277"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="277"/>
-      <c r="B21" s="277"/>
-      <c r="C21" s="277"/>
-      <c r="D21" s="277"/>
-      <c r="E21" s="277"/>
-      <c r="F21" s="277"/>
-      <c r="G21" s="277"/>
-      <c r="H21" s="277"/>
-      <c r="I21" s="277"/>
-      <c r="J21" s="277"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="277"/>
-      <c r="B22" s="277"/>
-      <c r="C22" s="277"/>
-      <c r="D22" s="277"/>
-      <c r="E22" s="277"/>
-      <c r="F22" s="277"/>
-      <c r="G22" s="277"/>
-      <c r="H22" s="277"/>
-      <c r="I22" s="277"/>
-      <c r="J22" s="277"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="316" t="s">
+        <v>376</v>
+      </c>
+      <c r="B20" s="316"/>
+      <c r="C20" s="316"/>
+      <c r="D20" s="316"/>
+      <c r="E20" s="316"/>
+      <c r="F20" s="316"/>
+      <c r="G20" s="316"/>
+      <c r="H20" s="316"/>
+      <c r="I20" s="316"/>
+      <c r="J20" s="316"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="316"/>
+      <c r="B21" s="316"/>
+      <c r="C21" s="316"/>
+      <c r="D21" s="316"/>
+      <c r="E21" s="316"/>
+      <c r="F21" s="316"/>
+      <c r="G21" s="316"/>
+      <c r="H21" s="316"/>
+      <c r="I21" s="316"/>
+      <c r="J21" s="316"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="316"/>
+      <c r="B22" s="316"/>
+      <c r="C22" s="316"/>
+      <c r="D22" s="316"/>
+      <c r="E22" s="316"/>
+      <c r="F22" s="316"/>
+      <c r="G22" s="316"/>
+      <c r="H22" s="316"/>
+      <c r="I22" s="316"/>
+      <c r="J22" s="316"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="56"/>
       <c r="B23" s="56"/>
       <c r="C23" s="56"/>
@@ -3346,11 +3292,11 @@
       <c r="E23" s="56"/>
       <c r="F23" s="56"/>
       <c r="G23" s="56"/>
-      <c r="H23" s="264"/>
+      <c r="H23" s="257"/>
       <c r="I23" s="56"/>
       <c r="J23" s="56"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="180" t="s">
         <v>18</v>
       </c>
@@ -3372,11 +3318,11 @@
       <c r="I24" s="184" t="s">
         <v>168</v>
       </c>
-      <c r="J24" s="265" t="s">
+      <c r="J24" s="258" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="185" t="s">
         <v>335</v>
       </c>
@@ -3391,15 +3337,15 @@
       <c r="J25" s="186"/>
       <c r="L25" s="43"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="187" t="s">
         <v>359</v>
       </c>
       <c r="B26" s="157" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C26" s="157" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D26" s="155">
         <v>3000000</v>
@@ -3412,7 +3358,7 @@
       <c r="J26" s="157"/>
       <c r="L26" s="43"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="188" t="s">
         <v>35</v>
       </c>
@@ -3455,7 +3401,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="187" t="s">
         <v>232</v>
       </c>
@@ -3470,7 +3416,7 @@
       <c r="J28" s="186"/>
       <c r="L28" s="43"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="187"/>
       <c r="B29" s="157"/>
       <c r="C29" s="157"/>
@@ -3483,7 +3429,7 @@
       <c r="J29" s="186"/>
       <c r="L29" s="43"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="188" t="s">
         <v>16</v>
       </c>
@@ -3501,7 +3447,7 @@
       <c r="G30" s="30"/>
       <c r="H30" s="30"/>
       <c r="I30" s="30"/>
-      <c r="J30" s="266"/>
+      <c r="J30" s="259"/>
       <c r="K30" s="31">
         <f>E30+J30+F30+G30+H30+I30</f>
         <v>0</v>
@@ -3511,7 +3457,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="187" t="s">
         <v>228</v>
       </c>
@@ -3526,12 +3472,12 @@
       <c r="J31" s="190"/>
       <c r="L31" s="43"/>
     </row>
-    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="119" t="s">
         <v>351</v>
       </c>
       <c r="B32" s="119" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C32" s="222" t="s">
         <v>367</v>
@@ -3547,12 +3493,12 @@
       <c r="J32" s="190"/>
       <c r="L32" s="43"/>
     </row>
-    <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="119" t="s">
         <v>231</v>
       </c>
       <c r="B33" s="119" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C33" s="222" t="s">
         <v>367</v>
@@ -3568,7 +3514,7 @@
       <c r="J33" s="190"/>
       <c r="L33" s="43"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="119"/>
       <c r="B34" s="119"/>
       <c r="C34" s="119"/>
@@ -3581,7 +3527,7 @@
       <c r="J34" s="190"/>
       <c r="L34" s="43"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="188" t="s">
         <v>230</v>
       </c>
@@ -3624,7 +3570,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="187" t="s">
         <v>1</v>
       </c>
@@ -3639,7 +3585,7 @@
       <c r="J36" s="157"/>
       <c r="L36" s="43"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="157"/>
       <c r="B37" s="157"/>
       <c r="C37" s="157"/>
@@ -3652,7 +3598,7 @@
       <c r="J37" s="157"/>
       <c r="L37" s="43"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="157"/>
       <c r="B38" s="157"/>
       <c r="C38" s="157"/>
@@ -3665,7 +3611,7 @@
       <c r="J38" s="157"/>
       <c r="L38" s="43"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="157"/>
       <c r="B39" s="157"/>
       <c r="C39" s="193"/>
@@ -3678,7 +3624,7 @@
       <c r="J39" s="157"/>
       <c r="L39" s="43"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="188" t="s">
         <v>229</v>
       </c>
@@ -3721,7 +3667,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="187" t="s">
         <v>221</v>
       </c>
@@ -3733,10 +3679,10 @@
       <c r="G41" s="195"/>
       <c r="H41" s="195"/>
       <c r="I41" s="195"/>
-      <c r="J41" s="267"/>
+      <c r="J41" s="260"/>
       <c r="L41" s="43"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="157" t="s">
         <v>225</v>
       </c>
@@ -3777,9 +3723,9 @@
       </c>
       <c r="L42" s="43"/>
     </row>
-    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="278"/>
-      <c r="B43" s="279"/>
+    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="317"/>
+      <c r="B43" s="318"/>
       <c r="C43" s="157"/>
       <c r="D43" s="32"/>
       <c r="E43" s="186"/>
@@ -3791,7 +3737,7 @@
       <c r="K43" s="31"/>
       <c r="L43" s="43"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="188" t="s">
         <v>2</v>
       </c>
@@ -3834,7 +3780,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="187" t="s">
         <v>3</v>
       </c>
@@ -3849,15 +3795,15 @@
       <c r="J45" s="157"/>
       <c r="L45" s="43"/>
     </row>
-    <row r="46" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="197" t="s">
         <v>371</v>
       </c>
       <c r="B46" s="157"/>
       <c r="C46" s="240" t="s">
-        <v>390</v>
-      </c>
-      <c r="D46" s="268">
+        <v>385</v>
+      </c>
+      <c r="D46" s="261">
         <v>209128.04</v>
       </c>
       <c r="E46" s="198">
@@ -3895,15 +3841,15 @@
       <c r="M46" s="55"/>
       <c r="N46" s="55"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="157" t="s">
         <v>226</v>
       </c>
       <c r="B47" s="157"/>
       <c r="C47" s="240" t="s">
-        <v>397</v>
-      </c>
-      <c r="D47" s="268">
+        <v>392</v>
+      </c>
+      <c r="D47" s="261">
         <v>6120722.7199999997</v>
       </c>
       <c r="E47" s="198">
@@ -3941,13 +3887,13 @@
       <c r="M47" s="55"/>
       <c r="N47" s="55"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="157" t="s">
         <v>227</v>
       </c>
       <c r="B48" s="157"/>
       <c r="C48" s="157" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D48" s="32">
         <v>169491.21</v>
@@ -3978,13 +3924,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="197" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B49" s="157"/>
       <c r="C49" s="222" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D49" s="32">
         <v>427893</v>
@@ -4009,13 +3955,13 @@
       <c r="M49" s="55"/>
       <c r="N49" s="55"/>
     </row>
-    <row r="50" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="274" t="s">
-        <v>386</v>
-      </c>
-      <c r="B50" s="275"/>
+    <row r="50" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="276" t="s">
+        <v>381</v>
+      </c>
+      <c r="B50" s="277"/>
       <c r="C50" s="240" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D50" s="32">
         <v>55000</v>
@@ -4046,13 +3992,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="119" t="s">
         <v>257</v>
       </c>
       <c r="B51" s="220"/>
       <c r="C51" s="240" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D51" s="32">
         <v>8561.76</v>
@@ -4077,13 +4023,13 @@
       <c r="M51" s="55"/>
       <c r="N51" s="55"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="119" t="s">
         <v>258</v>
       </c>
       <c r="B52" s="119"/>
       <c r="C52" s="240" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D52" s="32">
         <v>1744954.66</v>
@@ -4129,7 +4075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="199" t="s">
         <v>256</v>
       </c>
@@ -4162,7 +4108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="188" t="s">
         <v>4</v>
       </c>
@@ -4209,7 +4155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="157"/>
       <c r="B55" s="157"/>
       <c r="C55" s="157"/>
@@ -4222,7 +4168,7 @@
       <c r="J55" s="157"/>
       <c r="L55" s="43"/>
     </row>
-    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="157"/>
       <c r="B56" s="157"/>
       <c r="C56" s="157"/>
@@ -4235,7 +4181,7 @@
       <c r="J56" s="157"/>
       <c r="L56" s="43"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="187" t="s">
         <v>222</v>
       </c>
@@ -4250,13 +4196,13 @@
       <c r="J57" s="157"/>
       <c r="L57" s="43"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="191" t="s">
         <v>334</v>
       </c>
       <c r="B58" s="201"/>
       <c r="C58" s="119" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D58" s="32">
         <v>230000</v>
@@ -4279,13 +4225,13 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="280" t="s">
-        <v>396</v>
-      </c>
-      <c r="B59" s="281"/>
+    <row r="59" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="319" t="s">
+        <v>391</v>
+      </c>
+      <c r="B59" s="320"/>
       <c r="C59" s="119" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D59" s="32">
         <v>230000</v>
@@ -4323,13 +4269,13 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="280" t="s">
-        <v>394</v>
-      </c>
-      <c r="B60" s="281"/>
+    <row r="60" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="319" t="s">
+        <v>389</v>
+      </c>
+      <c r="B60" s="320"/>
       <c r="C60" s="119" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D60" s="32">
         <v>95700</v>
@@ -4367,13 +4313,13 @@
         <v>95700</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="274" t="s">
-        <v>403</v>
-      </c>
-      <c r="B61" s="275"/>
+    <row r="61" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="276" t="s">
+        <v>398</v>
+      </c>
+      <c r="B61" s="277"/>
       <c r="C61" s="119" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D61" s="32">
         <v>130000</v>
@@ -4411,13 +4357,13 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="239" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B62" s="220"/>
       <c r="C62" s="119" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D62" s="32">
         <v>24000</v>
@@ -4455,13 +4401,13 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="274" t="s">
-        <v>405</v>
-      </c>
-      <c r="B63" s="275"/>
+    <row r="63" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="276" t="s">
+        <v>400</v>
+      </c>
+      <c r="B63" s="277"/>
       <c r="C63" s="240" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D63" s="32">
         <v>550000</v>
@@ -4484,13 +4430,13 @@
         <v>550000</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="274" t="s">
-        <v>391</v>
-      </c>
-      <c r="B64" s="275"/>
+    <row r="64" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="276" t="s">
+        <v>386</v>
+      </c>
+      <c r="B64" s="277"/>
       <c r="C64" s="240" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D64" s="32">
         <v>250000</v>
@@ -4528,13 +4474,13 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="274" t="s">
-        <v>400</v>
-      </c>
-      <c r="B65" s="275"/>
+    <row r="65" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="276" t="s">
+        <v>395</v>
+      </c>
+      <c r="B65" s="277"/>
       <c r="C65" s="240" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D65" s="32">
         <v>120000</v>
@@ -4572,13 +4518,13 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="253" t="s">
+    <row r="66" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="248" t="s">
         <v>370</v>
       </c>
-      <c r="B66" s="254"/>
+      <c r="B66" s="249"/>
       <c r="C66" s="240" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D66" s="32">
         <v>392015.8</v>
@@ -4616,7 +4562,7 @@
         <v>392015.8</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="188" t="s">
         <v>223</v>
       </c>
@@ -4661,7 +4607,7 @@
       <c r="M67" s="31"/>
       <c r="N67" s="31"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="187" t="s">
         <v>5</v>
       </c>
@@ -4676,15 +4622,15 @@
       <c r="J68" s="157"/>
       <c r="L68" s="43"/>
     </row>
-    <row r="69" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="202" t="s">
         <v>6</v>
       </c>
       <c r="B69" s="157" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C69" s="157" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D69" s="32">
         <v>949849</v>
@@ -4718,12 +4664,12 @@
         <v>372</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="282" t="s">
-        <v>406</v>
-      </c>
-      <c r="B70" s="283"/>
-      <c r="C70" s="284"/>
+    <row r="70" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="278" t="s">
+        <v>401</v>
+      </c>
+      <c r="B70" s="279"/>
+      <c r="C70" s="280"/>
       <c r="D70" s="32">
         <v>0</v>
       </c>
@@ -4754,7 +4700,7 @@
       <c r="L70" s="43"/>
       <c r="N70" s="32"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="157"/>
       <c r="B71" s="157"/>
       <c r="C71" s="157"/>
@@ -4768,7 +4714,7 @@
       <c r="L71" s="43"/>
       <c r="N71" s="31"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="188" t="s">
         <v>7</v>
       </c>
@@ -4812,7 +4758,7 @@
       </c>
       <c r="N72" s="31"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="157" t="s">
         <v>26</v>
       </c>
@@ -4847,7 +4793,7 @@
       </c>
       <c r="L73" s="43"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="157" t="s">
         <v>27</v>
       </c>
@@ -4882,7 +4828,7 @@
       </c>
       <c r="L74" s="43"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="188" t="s">
         <v>224</v>
       </c>
@@ -4925,7 +4871,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="61"/>
       <c r="B76" s="61"/>
       <c r="C76" s="61"/>
@@ -4938,12 +4884,12 @@
       <c r="J76" s="61"/>
       <c r="L76" s="43"/>
     </row>
-    <row r="77" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="316" t="s">
-        <v>412</v>
-      </c>
-      <c r="B77" s="317"/>
-      <c r="C77" s="318"/>
+    <row r="77" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="312" t="s">
+        <v>407</v>
+      </c>
+      <c r="B77" s="313"/>
+      <c r="C77" s="314"/>
       <c r="D77" s="62">
         <f>24275955.4-15214817.97+1950000</f>
         <v>11011137.429999998</v>
@@ -4968,7 +4914,7 @@
         <f>$D77*1.49%</f>
         <v>164065.94770699996</v>
       </c>
-      <c r="J77" s="269">
+      <c r="J77" s="262">
         <f>D77*1.74%</f>
         <v>191593.79128199996</v>
       </c>
@@ -4981,7 +4927,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="207"/>
       <c r="B78" s="208"/>
       <c r="C78" s="208"/>
@@ -4991,11 +4937,11 @@
       <c r="G78" s="63"/>
       <c r="H78" s="63"/>
       <c r="I78" s="63"/>
-      <c r="J78" s="270"/>
+      <c r="J78" s="263"/>
       <c r="K78" s="31"/>
       <c r="L78" s="43"/>
     </row>
-    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="209" t="s">
         <v>28</v>
       </c>
@@ -5042,7 +4988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="56"/>
       <c r="B80" s="56"/>
       <c r="C80" s="56"/>
@@ -5054,7 +5000,7 @@
       <c r="I80" s="212"/>
       <c r="J80" s="56"/>
     </row>
-    <row r="81" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="213" t="s">
         <v>36</v>
       </c>
@@ -5068,12 +5014,12 @@
       <c r="I81" s="212"/>
       <c r="J81" s="56"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="215" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B82" s="56"/>
-      <c r="C82" s="271">
+      <c r="C82" s="264">
         <v>300000</v>
       </c>
       <c r="D82" s="56"/>
@@ -5084,12 +5030,12 @@
       <c r="I82" s="212"/>
       <c r="J82" s="56"/>
     </row>
-    <row r="83" spans="1:13" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="215" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B83" s="56"/>
-      <c r="C83" s="271">
+      <c r="C83" s="264">
         <v>106464</v>
       </c>
       <c r="D83" s="212"/>
@@ -5100,7 +5046,7 @@
       <c r="I83" s="212"/>
       <c r="J83" s="56"/>
     </row>
-    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="216" t="s">
         <v>16</v>
       </c>
@@ -5117,7 +5063,7 @@
       <c r="I84" s="212"/>
       <c r="J84" s="56"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="56"/>
       <c r="B85" s="56"/>
       <c r="C85" s="56"/>
@@ -5128,7 +5074,7 @@
       <c r="H85" s="31"/>
       <c r="I85" s="31"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="56"/>
       <c r="B86" s="56"/>
       <c r="C86" s="56"/>
@@ -5139,13 +5085,13 @@
       <c r="H86" s="40"/>
       <c r="I86" s="40"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="303" t="s">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="299" t="s">
         <v>32</v>
       </c>
-      <c r="B87" s="304"/>
-      <c r="C87" s="304"/>
-      <c r="D87" s="304"/>
+      <c r="B87" s="300"/>
+      <c r="C87" s="300"/>
+      <c r="D87" s="300"/>
       <c r="E87" s="51" t="s">
         <v>10</v>
       </c>
@@ -5165,9 +5111,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="274"/>
-      <c r="B88" s="285"/>
+    <row r="88" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="276"/>
+      <c r="B88" s="281"/>
       <c r="C88" s="220"/>
       <c r="D88" s="32"/>
       <c r="E88" s="198">
@@ -5180,9 +5126,9 @@
       <c r="I88" s="42"/>
       <c r="J88" s="38"/>
     </row>
-    <row r="89" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="305"/>
-      <c r="B89" s="306"/>
+    <row r="89" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="301"/>
+      <c r="B89" s="302"/>
       <c r="C89" s="53"/>
       <c r="D89" s="32"/>
       <c r="E89" s="42"/>
@@ -5192,12 +5138,12 @@
       <c r="I89" s="42"/>
       <c r="J89" s="38"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="300" t="s">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="296" t="s">
         <v>16</v>
       </c>
-      <c r="B90" s="301"/>
-      <c r="C90" s="302"/>
+      <c r="B90" s="297"/>
+      <c r="C90" s="298"/>
       <c r="D90" s="50">
         <f>SUM(D88:D89)</f>
         <v>0</v>
@@ -5223,14 +5169,14 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E92" s="31"/>
       <c r="F92" s="31"/>
       <c r="G92" s="31"/>
       <c r="H92" s="31"/>
       <c r="I92" s="31"/>
     </row>
-    <row r="93" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="26" t="s">
         <v>29</v>
       </c>
@@ -5239,7 +5185,7 @@
         <v>26225955.399999999</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="28" t="s">
         <v>31</v>
       </c>
@@ -5247,45 +5193,45 @@
         <f>D79-D77</f>
         <v>15214817.970000001</v>
       </c>
-      <c r="D94" s="286" t="s">
+      <c r="D94" s="282" t="s">
         <v>373</v>
       </c>
-      <c r="E94" s="286"/>
-      <c r="F94" s="286"/>
-      <c r="G94" s="286"/>
-      <c r="H94" s="286"/>
-      <c r="I94" s="286"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D95" s="286"/>
-      <c r="E95" s="286"/>
-      <c r="F95" s="286"/>
-      <c r="G95" s="286"/>
-      <c r="H95" s="286"/>
-      <c r="I95" s="286"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D96" s="286"/>
-      <c r="E96" s="286"/>
-      <c r="F96" s="286"/>
-      <c r="G96" s="286"/>
-      <c r="H96" s="286"/>
-      <c r="I96" s="286"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E94" s="282"/>
+      <c r="F94" s="282"/>
+      <c r="G94" s="282"/>
+      <c r="H94" s="282"/>
+      <c r="I94" s="282"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D95" s="282"/>
+      <c r="E95" s="282"/>
+      <c r="F95" s="282"/>
+      <c r="G95" s="282"/>
+      <c r="H95" s="282"/>
+      <c r="I95" s="282"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D96" s="282"/>
+      <c r="E96" s="282"/>
+      <c r="F96" s="282"/>
+      <c r="G96" s="282"/>
+      <c r="H96" s="282"/>
+      <c r="I96" s="282"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B97" s="8"/>
       <c r="C97" s="9"/>
-      <c r="D97" s="286"/>
-      <c r="E97" s="286"/>
-      <c r="F97" s="286"/>
-      <c r="G97" s="286"/>
-      <c r="H97" s="286"/>
-      <c r="I97" s="286"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D97" s="282"/>
+      <c r="E97" s="282"/>
+      <c r="F97" s="282"/>
+      <c r="G97" s="282"/>
+      <c r="H97" s="282"/>
+      <c r="I97" s="282"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>20</v>
       </c>
@@ -5293,14 +5239,14 @@
         <v>1682660.59</v>
       </c>
       <c r="C98" s="11"/>
-      <c r="D98" s="286"/>
-      <c r="E98" s="286"/>
-      <c r="F98" s="286"/>
-      <c r="G98" s="286"/>
-      <c r="H98" s="286"/>
-      <c r="I98" s="286"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D98" s="282"/>
+      <c r="E98" s="282"/>
+      <c r="F98" s="282"/>
+      <c r="G98" s="282"/>
+      <c r="H98" s="282"/>
+      <c r="I98" s="282"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
         <v>21</v>
       </c>
@@ -5311,14 +5257,14 @@
       <c r="C99" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D99" s="286"/>
-      <c r="E99" s="286"/>
-      <c r="F99" s="286"/>
-      <c r="G99" s="286"/>
-      <c r="H99" s="286"/>
-      <c r="I99" s="286"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D99" s="282"/>
+      <c r="E99" s="282"/>
+      <c r="F99" s="282"/>
+      <c r="G99" s="282"/>
+      <c r="H99" s="282"/>
+      <c r="I99" s="282"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
         <v>338</v>
       </c>
@@ -5327,14 +5273,14 @@
         <v>0</v>
       </c>
       <c r="C100" s="11"/>
-      <c r="D100" s="286"/>
-      <c r="E100" s="286"/>
-      <c r="F100" s="286"/>
-      <c r="G100" s="286"/>
-      <c r="H100" s="286"/>
-      <c r="I100" s="286"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D100" s="282"/>
+      <c r="E100" s="282"/>
+      <c r="F100" s="282"/>
+      <c r="G100" s="282"/>
+      <c r="H100" s="282"/>
+      <c r="I100" s="282"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
         <v>34</v>
       </c>
@@ -5343,15 +5289,15 @@
         <v>-15214817.970000001</v>
       </c>
       <c r="C101" s="9"/>
-      <c r="D101" s="286"/>
-      <c r="E101" s="286"/>
-      <c r="F101" s="286"/>
-      <c r="G101" s="286"/>
-      <c r="H101" s="286"/>
-      <c r="I101" s="286"/>
+      <c r="D101" s="282"/>
+      <c r="E101" s="282"/>
+      <c r="F101" s="282"/>
+      <c r="G101" s="282"/>
+      <c r="H101" s="282"/>
+      <c r="I101" s="282"/>
       <c r="K101" s="32"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="12" t="s">
         <v>33</v>
       </c>
@@ -5360,15 +5306,15 @@
         <v>0</v>
       </c>
       <c r="C102" s="9"/>
-      <c r="D102" s="286"/>
-      <c r="E102" s="286"/>
-      <c r="F102" s="286"/>
-      <c r="G102" s="286"/>
-      <c r="H102" s="286"/>
-      <c r="I102" s="286"/>
+      <c r="D102" s="282"/>
+      <c r="E102" s="282"/>
+      <c r="F102" s="282"/>
+      <c r="G102" s="282"/>
+      <c r="H102" s="282"/>
+      <c r="I102" s="282"/>
       <c r="K102" s="33"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="12" t="s">
         <v>272</v>
       </c>
@@ -5377,31 +5323,31 @@
         <v>0</v>
       </c>
       <c r="C103" s="9"/>
-      <c r="D103" s="286"/>
-      <c r="E103" s="286"/>
-      <c r="F103" s="286"/>
-      <c r="G103" s="286"/>
-      <c r="H103" s="286"/>
-      <c r="I103" s="286"/>
+      <c r="D103" s="282"/>
+      <c r="E103" s="282"/>
+      <c r="F103" s="282"/>
+      <c r="G103" s="282"/>
+      <c r="H103" s="282"/>
+      <c r="I103" s="282"/>
       <c r="K103" s="33"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="12" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B104" s="54">
         <v>-141000</v>
       </c>
       <c r="C104" s="9"/>
-      <c r="D104" s="286"/>
-      <c r="E104" s="286"/>
-      <c r="F104" s="286"/>
-      <c r="G104" s="286"/>
-      <c r="H104" s="286"/>
-      <c r="I104" s="286"/>
+      <c r="D104" s="282"/>
+      <c r="E104" s="282"/>
+      <c r="F104" s="282"/>
+      <c r="G104" s="282"/>
+      <c r="H104" s="282"/>
+      <c r="I104" s="282"/>
       <c r="K104" s="33"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="12" t="s">
         <v>30</v>
       </c>
@@ -5410,14 +5356,14 @@
         <v>-20000</v>
       </c>
       <c r="C105" s="13"/>
-      <c r="D105" s="286"/>
-      <c r="E105" s="286"/>
-      <c r="F105" s="286"/>
-      <c r="G105" s="286"/>
-      <c r="H105" s="286"/>
-      <c r="I105" s="286"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D105" s="282"/>
+      <c r="E105" s="282"/>
+      <c r="F105" s="282"/>
+      <c r="G105" s="282"/>
+      <c r="H105" s="282"/>
+      <c r="I105" s="282"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="12" t="s">
         <v>36</v>
       </c>
@@ -5426,14 +5372,14 @@
         <v>-406464</v>
       </c>
       <c r="C106" s="13"/>
-      <c r="D106" s="286"/>
-      <c r="E106" s="286"/>
-      <c r="F106" s="286"/>
-      <c r="G106" s="286"/>
-      <c r="H106" s="286"/>
-      <c r="I106" s="286"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D106" s="282"/>
+      <c r="E106" s="282"/>
+      <c r="F106" s="282"/>
+      <c r="G106" s="282"/>
+      <c r="H106" s="282"/>
+      <c r="I106" s="282"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
         <v>23</v>
       </c>
@@ -5442,37 +5388,37 @@
         <v>2575051.7590119969</v>
       </c>
       <c r="C107" s="44"/>
-      <c r="D107" s="286"/>
-      <c r="E107" s="286"/>
-      <c r="F107" s="286"/>
-      <c r="G107" s="286"/>
-      <c r="H107" s="286"/>
-      <c r="I107" s="286"/>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D107" s="282"/>
+      <c r="E107" s="282"/>
+      <c r="F107" s="282"/>
+      <c r="G107" s="282"/>
+      <c r="H107" s="282"/>
+      <c r="I107" s="282"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="13"/>
       <c r="C108" s="9"/>
-      <c r="D108" s="286"/>
-      <c r="E108" s="286"/>
-      <c r="F108" s="286"/>
-      <c r="G108" s="286"/>
-      <c r="H108" s="286"/>
-      <c r="I108" s="286"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D108" s="282"/>
+      <c r="E108" s="282"/>
+      <c r="F108" s="282"/>
+      <c r="G108" s="282"/>
+      <c r="H108" s="282"/>
+      <c r="I108" s="282"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
         <v>271</v>
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="9"/>
-      <c r="D109" s="286"/>
-      <c r="E109" s="286"/>
-      <c r="F109" s="286"/>
-      <c r="G109" s="286"/>
-      <c r="H109" s="286"/>
-      <c r="I109" s="286"/>
-    </row>
-    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D109" s="282"/>
+      <c r="E109" s="282"/>
+      <c r="F109" s="282"/>
+      <c r="G109" s="282"/>
+      <c r="H109" s="282"/>
+      <c r="I109" s="282"/>
+    </row>
+    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="177"/>
       <c r="B110" s="21">
         <v>0</v>
@@ -5481,7 +5427,7 @@
       <c r="D110" s="16"/>
       <c r="E110" s="16"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="24" t="s">
         <v>16</v>
       </c>
@@ -5492,17 +5438,17 @@
       <c r="C111" s="9"/>
       <c r="E111" s="16"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="13"/>
       <c r="C112" s="9"/>
       <c r="D112" s="16"/>
     </row>
-    <row r="113" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="13"/>
       <c r="C113" s="9"/>
       <c r="D113" s="16"/>
     </row>
-    <row r="114" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="s">
         <v>19</v>
       </c>
@@ -5510,46 +5456,46 @@
         <v>-25817.72</v>
       </c>
       <c r="C114" s="9"/>
-      <c r="D114" s="307" t="s">
-        <v>411</v>
-      </c>
-      <c r="E114" s="308"/>
-      <c r="F114" s="308"/>
-      <c r="G114" s="308"/>
-      <c r="H114" s="308"/>
-      <c r="I114" s="309"/>
-    </row>
-    <row r="115" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D114" s="303" t="s">
+        <v>406</v>
+      </c>
+      <c r="E114" s="304"/>
+      <c r="F114" s="304"/>
+      <c r="G114" s="304"/>
+      <c r="H114" s="304"/>
+      <c r="I114" s="305"/>
+    </row>
+    <row r="115" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="179" t="s">
-        <v>407</v>
-      </c>
-      <c r="B115" s="255">
+        <v>402</v>
+      </c>
+      <c r="B115" s="250">
         <v>-24000</v>
       </c>
       <c r="C115" s="9"/>
-      <c r="D115" s="310"/>
-      <c r="E115" s="311"/>
-      <c r="F115" s="311"/>
-      <c r="G115" s="311"/>
-      <c r="H115" s="311"/>
-      <c r="I115" s="312"/>
-    </row>
-    <row r="116" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D115" s="306"/>
+      <c r="E115" s="307"/>
+      <c r="F115" s="307"/>
+      <c r="G115" s="307"/>
+      <c r="H115" s="307"/>
+      <c r="I115" s="308"/>
+    </row>
+    <row r="116" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="179" t="s">
-        <v>408</v>
-      </c>
-      <c r="B116" s="255">
+        <v>403</v>
+      </c>
+      <c r="B116" s="250">
         <v>-24000</v>
       </c>
       <c r="C116" s="9"/>
-      <c r="D116" s="310"/>
-      <c r="E116" s="311"/>
-      <c r="F116" s="311"/>
-      <c r="G116" s="311"/>
-      <c r="H116" s="311"/>
-      <c r="I116" s="312"/>
-    </row>
-    <row r="117" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D116" s="306"/>
+      <c r="E116" s="307"/>
+      <c r="F116" s="307"/>
+      <c r="G116" s="307"/>
+      <c r="H116" s="307"/>
+      <c r="I116" s="308"/>
+    </row>
+    <row r="117" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="24" t="s">
         <v>16</v>
       </c>
@@ -5558,31 +5504,31 @@
         <v>-73817.72</v>
       </c>
       <c r="C117" s="9"/>
-      <c r="D117" s="313"/>
-      <c r="E117" s="314"/>
-      <c r="F117" s="314"/>
-      <c r="G117" s="314"/>
-      <c r="H117" s="314"/>
-      <c r="I117" s="315"/>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D117" s="309"/>
+      <c r="E117" s="310"/>
+      <c r="F117" s="310"/>
+      <c r="G117" s="310"/>
+      <c r="H117" s="310"/>
+      <c r="I117" s="311"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="13"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="13"/>
       <c r="F119" s="46"/>
       <c r="G119" s="46"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="13"/>
       <c r="F120" s="46"/>
       <c r="G120" s="46"/>
     </row>
-    <row r="121" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H121" s="55"/>
       <c r="I121" s="55"/>
     </row>
-    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7" t="s">
         <v>355</v>
       </c>
@@ -5590,17 +5536,17 @@
         <v>578840</v>
       </c>
       <c r="C122" s="15"/>
-      <c r="D122" s="287" t="s">
-        <v>388</v>
-      </c>
-      <c r="E122" s="288"/>
-      <c r="F122" s="288"/>
-      <c r="G122" s="288"/>
-      <c r="H122" s="288"/>
-      <c r="I122" s="288"/>
-      <c r="J122" s="289"/>
-    </row>
-    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D122" s="283" t="s">
+        <v>383</v>
+      </c>
+      <c r="E122" s="284"/>
+      <c r="F122" s="284"/>
+      <c r="G122" s="284"/>
+      <c r="H122" s="284"/>
+      <c r="I122" s="284"/>
+      <c r="J122" s="285"/>
+    </row>
+    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="10" t="s">
         <v>238</v>
       </c>
@@ -5608,15 +5554,15 @@
         <v>20000</v>
       </c>
       <c r="C123" s="15"/>
-      <c r="D123" s="290"/>
-      <c r="E123" s="291"/>
-      <c r="F123" s="291"/>
-      <c r="G123" s="291"/>
-      <c r="H123" s="291"/>
-      <c r="I123" s="291"/>
-      <c r="J123" s="292"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D123" s="286"/>
+      <c r="E123" s="287"/>
+      <c r="F123" s="287"/>
+      <c r="G123" s="287"/>
+      <c r="H123" s="287"/>
+      <c r="I123" s="287"/>
+      <c r="J123" s="288"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="24" t="s">
         <v>16</v>
       </c>
@@ -5625,53 +5571,53 @@
         <v>598840</v>
       </c>
       <c r="C124" s="15"/>
-      <c r="D124" s="290"/>
-      <c r="E124" s="291"/>
-      <c r="F124" s="291"/>
-      <c r="G124" s="291"/>
-      <c r="H124" s="291"/>
-      <c r="I124" s="291"/>
-      <c r="J124" s="292"/>
-    </row>
-    <row r="125" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D124" s="286"/>
+      <c r="E124" s="287"/>
+      <c r="F124" s="287"/>
+      <c r="G124" s="287"/>
+      <c r="H124" s="287"/>
+      <c r="I124" s="287"/>
+      <c r="J124" s="288"/>
+    </row>
+    <row r="125" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C125" s="16"/>
-      <c r="D125" s="290"/>
-      <c r="E125" s="291"/>
-      <c r="F125" s="291"/>
-      <c r="G125" s="291"/>
-      <c r="H125" s="291"/>
-      <c r="I125" s="291"/>
-      <c r="J125" s="292"/>
-    </row>
-    <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="296" t="s">
+      <c r="D125" s="286"/>
+      <c r="E125" s="287"/>
+      <c r="F125" s="287"/>
+      <c r="G125" s="287"/>
+      <c r="H125" s="287"/>
+      <c r="I125" s="287"/>
+      <c r="J125" s="288"/>
+    </row>
+    <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="292" t="s">
         <v>356</v>
       </c>
-      <c r="B126" s="298">
+      <c r="B126" s="294">
         <f>B124+B107+B117</f>
         <v>3100074.0390119967</v>
       </c>
       <c r="C126" s="9"/>
-      <c r="D126" s="290"/>
-      <c r="E126" s="291"/>
-      <c r="F126" s="291"/>
-      <c r="G126" s="291"/>
-      <c r="H126" s="291"/>
-      <c r="I126" s="291"/>
-      <c r="J126" s="292"/>
-    </row>
-    <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="297"/>
-      <c r="B127" s="299"/>
-      <c r="D127" s="293"/>
-      <c r="E127" s="294"/>
-      <c r="F127" s="294"/>
-      <c r="G127" s="294"/>
-      <c r="H127" s="294"/>
-      <c r="I127" s="294"/>
-      <c r="J127" s="295"/>
-    </row>
-    <row r="132" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D126" s="286"/>
+      <c r="E126" s="287"/>
+      <c r="F126" s="287"/>
+      <c r="G126" s="287"/>
+      <c r="H126" s="287"/>
+      <c r="I126" s="287"/>
+      <c r="J126" s="288"/>
+    </row>
+    <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="293"/>
+      <c r="B127" s="295"/>
+      <c r="D127" s="289"/>
+      <c r="E127" s="290"/>
+      <c r="F127" s="290"/>
+      <c r="G127" s="290"/>
+      <c r="H127" s="290"/>
+      <c r="I127" s="290"/>
+      <c r="J127" s="291"/>
+    </row>
+    <row r="132" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C132" s="46"/>
       <c r="D132" s="46"/>
       <c r="E132" s="46"/>
@@ -5679,7 +5625,7 @@
       <c r="G132" s="46"/>
       <c r="H132" s="46"/>
     </row>
-    <row r="133" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C133" s="46"/>
       <c r="D133" s="46"/>
       <c r="E133" s="46"/>
@@ -5687,23 +5633,23 @@
       <c r="G133" s="46"/>
       <c r="H133" s="46"/>
     </row>
-    <row r="134" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C134" s="46"/>
-      <c r="D134" s="263"/>
+      <c r="D134" s="256"/>
       <c r="E134" s="46"/>
       <c r="F134" s="46"/>
       <c r="G134" s="46"/>
       <c r="H134" s="46"/>
     </row>
-    <row r="135" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C135" s="46"/>
-      <c r="D135" s="263"/>
+      <c r="D135" s="256"/>
       <c r="E135" s="46"/>
       <c r="F135" s="46"/>
       <c r="G135" s="46"/>
       <c r="H135" s="46"/>
     </row>
-    <row r="136" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C136" s="46"/>
       <c r="D136" s="46"/>
       <c r="E136" s="46"/>
@@ -5711,7 +5657,7 @@
       <c r="G136" s="46"/>
       <c r="H136" s="46"/>
     </row>
-    <row r="137" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C137" s="46"/>
       <c r="D137" s="46"/>
       <c r="E137" s="46"/>
@@ -5719,7 +5665,7 @@
       <c r="G137" s="46"/>
       <c r="H137" s="46"/>
     </row>
-    <row r="138" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C138" s="46"/>
       <c r="D138" s="46"/>
       <c r="E138" s="46"/>
@@ -5727,7 +5673,7 @@
       <c r="G138" s="46"/>
       <c r="H138" s="46"/>
     </row>
-    <row r="139" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C139" s="46"/>
       <c r="D139" s="46"/>
       <c r="E139" s="46"/>
@@ -5735,7 +5681,7 @@
       <c r="G139" s="46"/>
       <c r="H139" s="46"/>
     </row>
-    <row r="140" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C140" s="46"/>
       <c r="D140" s="46"/>
       <c r="E140" s="46"/>
@@ -5743,7 +5689,7 @@
       <c r="G140" s="46"/>
       <c r="H140" s="46"/>
     </row>
-    <row r="141" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C141" s="46"/>
       <c r="D141" s="46"/>
       <c r="E141" s="46"/>
@@ -5751,7 +5697,7 @@
       <c r="G141" s="46"/>
       <c r="H141" s="46"/>
     </row>
-    <row r="142" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C142" s="46"/>
       <c r="D142" s="46"/>
       <c r="E142" s="46"/>
@@ -5761,6 +5707,15 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A14:J18"/>
+    <mergeCell ref="A20:J22"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A65:B65"/>
     <mergeCell ref="A70:C70"/>
     <mergeCell ref="A88:B88"/>
@@ -5773,15 +5728,6 @@
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="D114:I117"/>
     <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A14:J18"/>
-    <mergeCell ref="A20:J22"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5792,37 +5738,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DJ155"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="348" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="354" t="s">
         <v>298</v>
       </c>
-      <c r="B1" s="349"/>
-      <c r="C1" s="349"/>
-      <c r="D1" s="349"/>
-      <c r="E1" s="349"/>
+      <c r="B1" s="355"/>
+      <c r="C1" s="355"/>
+      <c r="D1" s="355"/>
+      <c r="E1" s="355"/>
       <c r="F1" s="103" t="s">
         <v>274</v>
       </c>
@@ -5834,20 +5780,20 @@
       <c r="L1" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="324">
+      <c r="M1" s="333">
         <f>RESUMEN!D79-N4</f>
         <v>26225955.399999999</v>
       </c>
-      <c r="N1" s="325"/>
+      <c r="N1" s="334"/>
       <c r="O1" s="104"/>
       <c r="P1" s="39"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="350"/>
-      <c r="B2" s="351"/>
-      <c r="C2" s="351"/>
-      <c r="D2" s="351"/>
-      <c r="E2" s="351"/>
+    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="356"/>
+      <c r="B2" s="357"/>
+      <c r="C2" s="357"/>
+      <c r="D2" s="357"/>
+      <c r="E2" s="357"/>
       <c r="F2" s="4" t="s">
         <v>273</v>
       </c>
@@ -5867,12 +5813,12 @@
       <c r="O2" s="105"/>
       <c r="P2" s="39"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="350"/>
-      <c r="B3" s="351"/>
-      <c r="C3" s="351"/>
-      <c r="D3" s="351"/>
-      <c r="E3" s="351"/>
+    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="356"/>
+      <c r="B3" s="357"/>
+      <c r="C3" s="357"/>
+      <c r="D3" s="357"/>
+      <c r="E3" s="357"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -5880,7 +5826,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="133" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="M3" s="133"/>
       <c r="N3" s="134">
@@ -5890,12 +5836,12 @@
       <c r="O3" s="105"/>
       <c r="P3" s="39"/>
     </row>
-    <row r="4" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="350"/>
-      <c r="B4" s="351"/>
-      <c r="C4" s="351"/>
-      <c r="D4" s="351"/>
-      <c r="E4" s="351"/>
+    <row r="4" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="356"/>
+      <c r="B4" s="357"/>
+      <c r="C4" s="357"/>
+      <c r="D4" s="357"/>
+      <c r="E4" s="357"/>
       <c r="F4" s="4" t="s">
         <v>275</v>
       </c>
@@ -5914,12 +5860,12 @@
       <c r="O4" s="107"/>
       <c r="P4" s="6"/>
     </row>
-    <row r="5" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="352"/>
-      <c r="B5" s="353"/>
-      <c r="C5" s="353"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="353"/>
+    <row r="5" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="358"/>
+      <c r="B5" s="359"/>
+      <c r="C5" s="359"/>
+      <c r="D5" s="359"/>
+      <c r="E5" s="359"/>
       <c r="F5" s="108"/>
       <c r="G5" s="108"/>
       <c r="H5" s="108"/>
@@ -5932,98 +5878,98 @@
       <c r="O5" s="111"/>
       <c r="P5" s="6"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="333" t="s">
+      <c r="C6" s="339" t="s">
         <v>368</v>
       </c>
-      <c r="D6" s="334"/>
-      <c r="E6" s="334"/>
-      <c r="F6" s="334"/>
-      <c r="G6" s="334"/>
-      <c r="H6" s="334"/>
-      <c r="I6" s="334"/>
-      <c r="J6" s="334"/>
-      <c r="K6" s="334"/>
-      <c r="L6" s="334"/>
-      <c r="M6" s="334"/>
-      <c r="N6" s="334"/>
-      <c r="O6" s="335"/>
+      <c r="D6" s="340"/>
+      <c r="E6" s="340"/>
+      <c r="F6" s="340"/>
+      <c r="G6" s="340"/>
+      <c r="H6" s="340"/>
+      <c r="I6" s="340"/>
+      <c r="J6" s="340"/>
+      <c r="K6" s="340"/>
+      <c r="L6" s="340"/>
+      <c r="M6" s="340"/>
+      <c r="N6" s="340"/>
+      <c r="O6" s="341"/>
       <c r="P6" s="6"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="336"/>
-      <c r="D7" s="337"/>
-      <c r="E7" s="337"/>
-      <c r="F7" s="337"/>
-      <c r="G7" s="337"/>
-      <c r="H7" s="337"/>
-      <c r="I7" s="337"/>
-      <c r="J7" s="337"/>
-      <c r="K7" s="337"/>
-      <c r="L7" s="337"/>
-      <c r="M7" s="337"/>
-      <c r="N7" s="337"/>
-      <c r="O7" s="338"/>
+      <c r="C7" s="342"/>
+      <c r="D7" s="343"/>
+      <c r="E7" s="343"/>
+      <c r="F7" s="343"/>
+      <c r="G7" s="343"/>
+      <c r="H7" s="343"/>
+      <c r="I7" s="343"/>
+      <c r="J7" s="343"/>
+      <c r="K7" s="343"/>
+      <c r="L7" s="343"/>
+      <c r="M7" s="343"/>
+      <c r="N7" s="343"/>
+      <c r="O7" s="344"/>
       <c r="P7" s="6"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="336"/>
-      <c r="D8" s="337"/>
-      <c r="E8" s="337"/>
-      <c r="F8" s="337"/>
-      <c r="G8" s="337"/>
-      <c r="H8" s="337"/>
-      <c r="I8" s="337"/>
-      <c r="J8" s="337"/>
-      <c r="K8" s="337"/>
-      <c r="L8" s="337"/>
-      <c r="M8" s="337"/>
-      <c r="N8" s="337"/>
-      <c r="O8" s="338"/>
+      <c r="C8" s="342"/>
+      <c r="D8" s="343"/>
+      <c r="E8" s="343"/>
+      <c r="F8" s="343"/>
+      <c r="G8" s="343"/>
+      <c r="H8" s="343"/>
+      <c r="I8" s="343"/>
+      <c r="J8" s="343"/>
+      <c r="K8" s="343"/>
+      <c r="L8" s="343"/>
+      <c r="M8" s="343"/>
+      <c r="N8" s="343"/>
+      <c r="O8" s="344"/>
       <c r="P8" s="6"/>
     </row>
-    <row r="9" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="339"/>
-      <c r="D9" s="340"/>
-      <c r="E9" s="340"/>
-      <c r="F9" s="340"/>
-      <c r="G9" s="340"/>
-      <c r="H9" s="340"/>
-      <c r="I9" s="340"/>
-      <c r="J9" s="340"/>
-      <c r="K9" s="340"/>
-      <c r="L9" s="340"/>
-      <c r="M9" s="340"/>
-      <c r="N9" s="340"/>
-      <c r="O9" s="341"/>
+      <c r="C9" s="345"/>
+      <c r="D9" s="346"/>
+      <c r="E9" s="346"/>
+      <c r="F9" s="346"/>
+      <c r="G9" s="346"/>
+      <c r="H9" s="346"/>
+      <c r="I9" s="346"/>
+      <c r="J9" s="346"/>
+      <c r="K9" s="346"/>
+      <c r="L9" s="346"/>
+      <c r="M9" s="346"/>
+      <c r="N9" s="346"/>
+      <c r="O9" s="347"/>
       <c r="Q9" s="55"/>
     </row>
-    <row r="10" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="342" t="s">
+      <c r="C10" s="348" t="s">
         <v>286</v>
       </c>
-      <c r="D10" s="343"/>
-      <c r="E10" s="343"/>
-      <c r="F10" s="343"/>
-      <c r="G10" s="343"/>
-      <c r="H10" s="343"/>
-      <c r="I10" s="343"/>
-      <c r="J10" s="343"/>
-      <c r="K10" s="343"/>
-      <c r="L10" s="343"/>
-      <c r="M10" s="343"/>
-      <c r="N10" s="343"/>
-      <c r="O10" s="344"/>
+      <c r="D10" s="349"/>
+      <c r="E10" s="349"/>
+      <c r="F10" s="349"/>
+      <c r="G10" s="349"/>
+      <c r="H10" s="349"/>
+      <c r="I10" s="349"/>
+      <c r="J10" s="349"/>
+      <c r="K10" s="349"/>
+      <c r="L10" s="349"/>
+      <c r="M10" s="349"/>
+      <c r="N10" s="349"/>
+      <c r="O10" s="350"/>
       <c r="Q10" t="s">
         <v>233</v>
       </c>
@@ -6032,22 +5978,22 @@
         <v>267678.10184399999</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="345"/>
-      <c r="D11" s="346"/>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
-      <c r="G11" s="346"/>
-      <c r="H11" s="346"/>
-      <c r="I11" s="346"/>
-      <c r="J11" s="346"/>
-      <c r="K11" s="346"/>
-      <c r="L11" s="346"/>
-      <c r="M11" s="346"/>
-      <c r="N11" s="346"/>
-      <c r="O11" s="347"/>
+      <c r="C11" s="351"/>
+      <c r="D11" s="352"/>
+      <c r="E11" s="352"/>
+      <c r="F11" s="352"/>
+      <c r="G11" s="352"/>
+      <c r="H11" s="352"/>
+      <c r="I11" s="352"/>
+      <c r="J11" s="352"/>
+      <c r="K11" s="352"/>
+      <c r="L11" s="352"/>
+      <c r="M11" s="352"/>
+      <c r="N11" s="352"/>
+      <c r="O11" s="353"/>
       <c r="Q11" t="s">
         <v>234</v>
       </c>
@@ -6056,50 +6002,50 @@
         <v>317248.120704</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="320" t="s">
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="324" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="354" t="s">
+      <c r="B12" s="326" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="320" t="s">
+      <c r="C12" s="324" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="356" t="s">
+      <c r="D12" s="328" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="356" t="s">
+      <c r="E12" s="328" t="s">
         <v>250</v>
       </c>
-      <c r="F12" s="320" t="s">
+      <c r="F12" s="324" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="320" t="s">
+      <c r="G12" s="324" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="320" t="s">
+      <c r="H12" s="324" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="326" t="s">
+      <c r="I12" s="335" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="328" t="s">
+      <c r="J12" s="321" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="328" t="s">
+      <c r="K12" s="321" t="s">
         <v>366</v>
       </c>
-      <c r="L12" s="328" t="s">
+      <c r="L12" s="321" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="331" t="s">
+      <c r="M12" s="337" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="328" t="s">
+      <c r="N12" s="321" t="s">
         <v>260</v>
       </c>
-      <c r="O12" s="328" t="s">
+      <c r="O12" s="321" t="s">
         <v>259</v>
       </c>
       <c r="Q12" t="s">
@@ -6110,22 +6056,22 @@
         <v>299898.61410299997</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="321"/>
-      <c r="B13" s="355"/>
-      <c r="C13" s="321"/>
-      <c r="D13" s="357"/>
-      <c r="E13" s="357"/>
-      <c r="F13" s="321"/>
-      <c r="G13" s="321"/>
-      <c r="H13" s="321"/>
-      <c r="I13" s="327"/>
-      <c r="J13" s="329"/>
-      <c r="K13" s="329"/>
-      <c r="L13" s="329"/>
-      <c r="M13" s="332"/>
-      <c r="N13" s="329"/>
-      <c r="O13" s="329"/>
+    <row r="13" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="325"/>
+      <c r="B13" s="327"/>
+      <c r="C13" s="325"/>
+      <c r="D13" s="329"/>
+      <c r="E13" s="329"/>
+      <c r="F13" s="325"/>
+      <c r="G13" s="325"/>
+      <c r="H13" s="325"/>
+      <c r="I13" s="336"/>
+      <c r="J13" s="322"/>
+      <c r="K13" s="322"/>
+      <c r="L13" s="322"/>
+      <c r="M13" s="338"/>
+      <c r="N13" s="322"/>
+      <c r="O13" s="322"/>
       <c r="Q13" t="s">
         <v>236</v>
       </c>
@@ -6134,20 +6080,20 @@
         <v>369296.64050699997</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="321"/>
-      <c r="B14" s="355"/>
-      <c r="C14" s="321"/>
-      <c r="D14" s="357"/>
-      <c r="E14" s="357"/>
-      <c r="F14" s="321"/>
-      <c r="G14" s="321"/>
-      <c r="H14" s="321"/>
-      <c r="I14" s="327"/>
-      <c r="J14" s="329"/>
-      <c r="K14" s="330"/>
-      <c r="L14" s="330"/>
-      <c r="M14" s="332"/>
+    <row r="14" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="325"/>
+      <c r="B14" s="327"/>
+      <c r="C14" s="325"/>
+      <c r="D14" s="329"/>
+      <c r="E14" s="329"/>
+      <c r="F14" s="325"/>
+      <c r="G14" s="325"/>
+      <c r="H14" s="325"/>
+      <c r="I14" s="336"/>
+      <c r="J14" s="322"/>
+      <c r="K14" s="323"/>
+      <c r="L14" s="323"/>
+      <c r="M14" s="338"/>
       <c r="N14" s="84" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/09</v>
@@ -6164,7 +6110,7 @@
         <v>431259.16408199997</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="176" t="s">
         <v>114</v>
       </c>
@@ -6214,16 +6160,16 @@
       <c r="P15" s="70" t="s">
         <v>342</v>
       </c>
-      <c r="R15" s="319"/>
-      <c r="S15" s="319"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R15" s="330"/>
+      <c r="S15" s="330"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="393" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="64" t="s">
+      <c r="D16" s="394" t="s">
         <v>296</v>
       </c>
       <c r="E16" s="131"/>
@@ -6263,10 +6209,10 @@
       <c r="P16" s="70" t="s">
         <v>341</v>
       </c>
-      <c r="R16" s="319"/>
-      <c r="S16" s="319"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R16" s="330"/>
+      <c r="S16" s="330"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>114</v>
       </c>
@@ -6283,7 +6229,7 @@
       <c r="F17" s="93">
         <v>1.21E-2</v>
       </c>
-      <c r="G17" s="256">
+      <c r="G17" s="251">
         <v>243852.859012</v>
       </c>
       <c r="H17" s="32">
@@ -6317,7 +6263,7 @@
       <c r="P17" s="70"/>
       <c r="S17" s="31"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>114</v>
       </c>
@@ -6349,7 +6295,7 @@
       <c r="L18" s="231">
         <v>369296.64050699997</v>
       </c>
-      <c r="M18" s="273">
+      <c r="M18" s="266">
         <v>0</v>
       </c>
       <c r="N18" s="223">
@@ -6363,28 +6309,28 @@
       <c r="P18" s="70"/>
       <c r="S18" s="31"/>
     </row>
-    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>114</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="257" t="s">
+      <c r="C19" s="252" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="258" t="s">
+      <c r="D19" s="253" t="s">
         <v>249</v>
       </c>
-      <c r="E19" s="258"/>
+      <c r="E19" s="253"/>
       <c r="F19" s="98">
         <v>1.7399999999999999E-2</v>
       </c>
       <c r="G19" s="99">
         <v>1296163.1476939998</v>
       </c>
-      <c r="H19" s="272">
+      <c r="H19" s="265">
         <v>1000000</v>
       </c>
-      <c r="I19" s="259">
+      <c r="I19" s="254">
         <f t="shared" si="0"/>
         <v>296163.14769399981</v>
       </c>
@@ -6397,7 +6343,7 @@
       <c r="L19" s="99">
         <v>431259.16408199997</v>
       </c>
-      <c r="M19" s="260">
+      <c r="M19" s="255">
         <v>0</v>
       </c>
       <c r="N19" s="96">
@@ -6411,7 +6357,7 @@
       <c r="P19" s="70"/>
       <c r="S19" s="31"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="37" t="s">
         <v>116</v>
       </c>
@@ -6464,7 +6410,7 @@
       </c>
       <c r="S20" s="31"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="37" t="s">
         <v>117</v>
       </c>
@@ -6518,7 +6464,7 @@
       </c>
       <c r="S21" s="31"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="37" t="s">
         <v>116</v>
       </c>
@@ -6571,7 +6517,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="37" t="s">
         <v>118</v>
       </c>
@@ -6629,7 +6575,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="37" t="s">
         <v>118</v>
       </c>
@@ -6684,7 +6630,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="37" t="s">
         <v>118</v>
       </c>
@@ -6738,7 +6684,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="37" t="s">
         <v>116</v>
       </c>
@@ -6792,7 +6738,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="37" t="s">
         <v>117</v>
       </c>
@@ -6845,7 +6791,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="64" t="s">
         <v>116</v>
       </c>
@@ -6897,7 +6843,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="64" t="s">
         <v>118</v>
       </c>
@@ -6950,7 +6896,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="64" t="s">
         <v>118</v>
       </c>
@@ -7003,7 +6949,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="64" t="s">
         <v>118</v>
       </c>
@@ -7053,7 +6999,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="64" t="s">
         <v>116</v>
       </c>
@@ -7106,7 +7052,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A33" s="37" t="s">
         <v>117</v>
       </c>
@@ -7161,7 +7107,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A34" s="37" t="s">
         <v>116</v>
       </c>
@@ -7214,7 +7160,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A35" s="91" t="s">
         <v>118</v>
       </c>
@@ -7270,7 +7216,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="37" t="s">
         <v>118</v>
       </c>
@@ -7325,7 +7271,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="37" t="s">
         <v>118</v>
       </c>
@@ -7375,7 +7321,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="37" t="s">
         <v>116</v>
       </c>
@@ -7433,7 +7379,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A39" s="37" t="s">
         <v>117</v>
       </c>
@@ -7486,7 +7432,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="64" t="s">
         <v>116</v>
       </c>
@@ -7639,7 +7585,7 @@
       <c r="DI40" s="46"/>
       <c r="DJ40" s="46"/>
     </row>
-    <row r="41" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="64" t="s">
         <v>118</v>
       </c>
@@ -7792,7 +7738,7 @@
       <c r="DI41" s="46"/>
       <c r="DJ41" s="46"/>
     </row>
-    <row r="42" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="64" t="s">
         <v>118</v>
       </c>
@@ -7945,7 +7891,7 @@
       <c r="DI42" s="46"/>
       <c r="DJ42" s="46"/>
     </row>
-    <row r="43" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="64" t="s">
         <v>118</v>
       </c>
@@ -8095,7 +8041,7 @@
       <c r="DI43" s="46"/>
       <c r="DJ43" s="46"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="37" t="s">
         <v>116</v>
       </c>
@@ -8148,7 +8094,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="37" t="s">
         <v>117</v>
       </c>
@@ -8203,7 +8149,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="37" t="s">
         <v>116</v>
       </c>
@@ -8262,7 +8208,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="115" t="s">
         <v>118</v>
       </c>
@@ -8315,7 +8261,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="37" t="s">
         <v>118</v>
       </c>
@@ -8370,7 +8316,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="37" t="s">
         <v>118</v>
       </c>
@@ -8423,7 +8369,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="37" t="s">
         <v>116</v>
       </c>
@@ -8476,7 +8422,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="37" t="s">
         <v>117</v>
       </c>
@@ -8529,7 +8475,7 @@
       </c>
       <c r="Q51" s="31"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="37" t="s">
         <v>116</v>
       </c>
@@ -8583,7 +8529,7 @@
       </c>
       <c r="Q52" s="31"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="37" t="s">
         <v>118</v>
       </c>
@@ -8641,7 +8587,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="37" t="s">
         <v>118</v>
       </c>
@@ -8694,7 +8640,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="64" t="s">
         <v>118</v>
       </c>
@@ -8747,7 +8693,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="37" t="s">
         <v>116</v>
       </c>
@@ -8801,7 +8747,7 @@
       </c>
       <c r="R56" s="39"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="37" t="s">
         <v>117</v>
       </c>
@@ -8856,7 +8802,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="37" t="s">
         <v>116</v>
       </c>
@@ -8909,7 +8855,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="37" t="s">
         <v>118</v>
       </c>
@@ -8964,7 +8910,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="64" t="s">
         <v>118</v>
       </c>
@@ -9020,7 +8966,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="64" t="s">
         <v>118</v>
       </c>
@@ -9076,7 +9022,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="64" t="s">
         <v>116</v>
       </c>
@@ -9128,7 +9074,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="64" t="s">
         <v>117</v>
       </c>
@@ -9180,7 +9126,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="64" t="s">
         <v>116</v>
       </c>
@@ -9233,7 +9179,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="64" t="s">
         <v>118</v>
       </c>
@@ -9288,7 +9234,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="64" t="s">
         <v>118</v>
       </c>
@@ -9341,7 +9287,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="64" t="s">
         <v>118</v>
       </c>
@@ -9394,7 +9340,7 @@
       </c>
       <c r="S67" s="125"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="64" t="s">
         <v>116</v>
       </c>
@@ -9448,7 +9394,7 @@
       </c>
       <c r="S68" s="31"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="91" t="s">
         <v>117</v>
       </c>
@@ -9501,7 +9447,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="37" t="s">
         <v>116</v>
       </c>
@@ -9554,7 +9500,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="37" t="s">
         <v>118</v>
       </c>
@@ -9606,7 +9552,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="37" t="s">
         <v>118</v>
       </c>
@@ -9660,7 +9606,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="37" t="s">
         <v>118</v>
       </c>
@@ -9710,7 +9656,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="37" t="s">
         <v>119</v>
       </c>
@@ -9764,7 +9710,7 @@
       </c>
       <c r="Q74" s="46"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="37" t="s">
         <v>116</v>
       </c>
@@ -9817,7 +9763,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="37" t="s">
         <v>118</v>
       </c>
@@ -9870,7 +9816,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="37" t="s">
         <v>118</v>
       </c>
@@ -9925,7 +9871,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="64" t="s">
         <v>118</v>
       </c>
@@ -9977,7 +9923,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="64" t="s">
         <v>119</v>
       </c>
@@ -10030,7 +9976,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="37" t="s">
         <v>116</v>
       </c>
@@ -10083,7 +10029,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="37" t="s">
         <v>118</v>
       </c>
@@ -10136,7 +10082,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="37" t="s">
         <v>118</v>
       </c>
@@ -10191,7 +10137,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="37" t="s">
         <v>118</v>
       </c>
@@ -10247,7 +10193,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="37" t="s">
         <v>119</v>
       </c>
@@ -10300,7 +10246,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="37" t="s">
         <v>116</v>
       </c>
@@ -10353,7 +10299,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="37" t="s">
         <v>118</v>
       </c>
@@ -10406,7 +10352,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="37" t="s">
         <v>118</v>
       </c>
@@ -10459,7 +10405,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="64" t="s">
         <v>118</v>
       </c>
@@ -10512,7 +10458,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="64"/>
       <c r="B89" s="23"/>
       <c r="C89" s="23" t="s">
@@ -10564,7 +10510,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="64"/>
       <c r="B90" s="23"/>
       <c r="C90" s="23" t="s">
@@ -10616,7 +10562,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="64"/>
       <c r="B91" s="23"/>
       <c r="C91" s="23" t="s">
@@ -10668,7 +10614,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="64"/>
       <c r="B92" s="23"/>
       <c r="C92" s="23" t="s">
@@ -10720,7 +10666,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="64"/>
       <c r="B93" s="23"/>
       <c r="C93" s="119" t="s">
@@ -10775,7 +10721,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="64"/>
       <c r="B94" s="23"/>
       <c r="C94" s="23" t="s">
@@ -10827,7 +10773,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="64"/>
       <c r="B95" s="23"/>
       <c r="C95" s="23" t="s">
@@ -10879,7 +10825,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="64"/>
       <c r="B96" s="23"/>
       <c r="C96" s="23" t="s">
@@ -10931,7 +10877,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="64"/>
       <c r="B97" s="23"/>
       <c r="C97" s="23" t="s">
@@ -10983,7 +10929,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="64"/>
       <c r="B98" s="23"/>
       <c r="C98" s="23" t="s">
@@ -11035,7 +10981,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="64"/>
       <c r="B99" s="23"/>
       <c r="C99" s="23" t="s">
@@ -11087,7 +11033,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="64"/>
       <c r="B100" s="23"/>
       <c r="C100" s="23" t="s">
@@ -11139,7 +11085,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="64"/>
       <c r="B101" s="23"/>
       <c r="C101" s="23" t="s">
@@ -11191,7 +11137,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="64"/>
       <c r="B102" s="23"/>
       <c r="C102" s="23" t="s">
@@ -11243,7 +11189,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="64"/>
       <c r="B103" s="23"/>
       <c r="C103" s="23" t="s">
@@ -11295,7 +11241,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="64"/>
       <c r="B104" s="23"/>
       <c r="C104" s="23" t="s">
@@ -11347,7 +11293,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="64"/>
       <c r="B105" s="23"/>
       <c r="C105" s="23" t="s">
@@ -11399,7 +11345,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="64"/>
       <c r="B106" s="23"/>
       <c r="C106" s="23" t="s">
@@ -11451,7 +11397,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="64"/>
       <c r="B107" s="23"/>
       <c r="C107" s="23" t="s">
@@ -11502,7 +11448,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="64"/>
       <c r="B108" s="23"/>
       <c r="C108" s="23" t="s">
@@ -11553,7 +11499,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="64"/>
       <c r="B109" s="23"/>
       <c r="C109" s="23" t="s">
@@ -11605,7 +11551,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="64"/>
       <c r="B110" s="23"/>
       <c r="C110" s="23" t="s">
@@ -11657,7 +11603,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="64"/>
       <c r="B111" s="23"/>
       <c r="C111" s="224" t="s">
@@ -11708,7 +11654,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="64"/>
       <c r="B112" s="23"/>
       <c r="C112" s="23" t="s">
@@ -11760,7 +11706,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="64"/>
       <c r="B113" s="23"/>
       <c r="C113" s="23" t="s">
@@ -11812,7 +11758,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="64"/>
       <c r="B114" s="23"/>
       <c r="C114" s="23" t="s">
@@ -11863,7 +11809,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="64"/>
       <c r="B115" s="23"/>
       <c r="C115" s="23" t="s">
@@ -11915,7 +11861,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="64"/>
       <c r="B116" s="23"/>
       <c r="C116" s="23" t="s">
@@ -11967,7 +11913,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="64"/>
       <c r="B117" s="23"/>
       <c r="C117" s="23" t="s">
@@ -12020,7 +11966,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="64"/>
       <c r="B118" s="23"/>
       <c r="C118" s="23" t="s">
@@ -12071,7 +12017,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="64"/>
       <c r="B119" s="23"/>
       <c r="C119" s="23" t="s">
@@ -12128,7 +12074,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="80"/>
       <c r="B120" s="23"/>
       <c r="C120" s="23" t="s">
@@ -12180,7 +12126,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="80"/>
       <c r="B121" s="23"/>
       <c r="C121" s="23" t="s">
@@ -12232,7 +12178,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="80"/>
       <c r="B122" s="23"/>
       <c r="C122" s="23" t="s">
@@ -12286,7 +12232,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="80"/>
       <c r="B123" s="23"/>
       <c r="C123" s="23" t="s">
@@ -12338,7 +12284,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="80"/>
       <c r="B124" s="23"/>
       <c r="C124" s="23" t="s">
@@ -12390,7 +12336,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="80"/>
       <c r="B125" s="23"/>
       <c r="C125" s="23" t="s">
@@ -12445,7 +12391,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="118"/>
       <c r="B126" s="113"/>
       <c r="C126" s="23" t="s">
@@ -12498,7 +12444,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="118"/>
       <c r="B127" s="113"/>
       <c r="C127" s="23" t="s">
@@ -12550,7 +12496,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="80"/>
       <c r="B128" s="23"/>
       <c r="C128" s="23" t="s">
@@ -12601,7 +12547,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="80"/>
       <c r="B129" s="23"/>
       <c r="C129" s="23" t="s">
@@ -12652,7 +12598,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="80"/>
       <c r="B130" s="23"/>
       <c r="C130" s="23" t="s">
@@ -12704,7 +12650,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="80" t="s">
         <v>24</v>
       </c>
@@ -12758,7 +12704,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="80" t="s">
         <v>24</v>
       </c>
@@ -12812,7 +12758,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="34" t="s">
         <v>24</v>
       </c>
@@ -12831,7 +12777,7 @@
       <c r="N133" s="2"/>
       <c r="O133" s="5"/>
     </row>
-    <row r="134" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="18"/>
       <c r="B134" s="18"/>
       <c r="C134" s="18"/>
@@ -12876,43 +12822,43 @@
       </c>
       <c r="Q134" s="39"/>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="L135" s="41">
         <f>L134-M1</f>
         <v>-150436.23675993457</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="323"/>
-      <c r="D136" s="323"/>
-      <c r="E136" s="323"/>
-      <c r="F136" s="323"/>
-      <c r="G136" s="323"/>
-      <c r="H136" s="323"/>
-      <c r="I136" s="323"/>
-      <c r="J136" s="323"/>
-      <c r="K136" s="323"/>
-      <c r="L136" s="323"/>
-      <c r="M136" s="323"/>
-      <c r="N136" s="323"/>
-      <c r="O136" s="323"/>
-    </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C137" s="323"/>
-      <c r="D137" s="323"/>
-      <c r="E137" s="323"/>
-      <c r="F137" s="323"/>
-      <c r="G137" s="323"/>
-      <c r="H137" s="323"/>
-      <c r="I137" s="323"/>
-      <c r="J137" s="323"/>
-      <c r="K137" s="323"/>
-      <c r="L137" s="323"/>
-      <c r="M137" s="323"/>
-      <c r="N137" s="323"/>
-      <c r="O137" s="323"/>
-    </row>
-    <row r="138" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C136" s="332"/>
+      <c r="D136" s="332"/>
+      <c r="E136" s="332"/>
+      <c r="F136" s="332"/>
+      <c r="G136" s="332"/>
+      <c r="H136" s="332"/>
+      <c r="I136" s="332"/>
+      <c r="J136" s="332"/>
+      <c r="K136" s="332"/>
+      <c r="L136" s="332"/>
+      <c r="M136" s="332"/>
+      <c r="N136" s="332"/>
+      <c r="O136" s="332"/>
+    </row>
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C137" s="332"/>
+      <c r="D137" s="332"/>
+      <c r="E137" s="332"/>
+      <c r="F137" s="332"/>
+      <c r="G137" s="332"/>
+      <c r="H137" s="332"/>
+      <c r="I137" s="332"/>
+      <c r="J137" s="332"/>
+      <c r="K137" s="332"/>
+      <c r="L137" s="332"/>
+      <c r="M137" s="332"/>
+      <c r="N137" s="332"/>
+      <c r="O137" s="332"/>
+    </row>
+    <row r="138" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C138" s="49"/>
       <c r="D138" s="49"/>
       <c r="E138" s="49"/>
@@ -12927,129 +12873,129 @@
       <c r="N138" s="49"/>
       <c r="O138" s="49"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C139" s="286" t="s">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C139" s="282" t="s">
         <v>243</v>
       </c>
-      <c r="D139" s="286"/>
-      <c r="E139" s="286"/>
-      <c r="F139" s="286"/>
-      <c r="G139" s="286"/>
-      <c r="H139" s="286"/>
-      <c r="I139" s="286"/>
-      <c r="J139" s="286"/>
-      <c r="K139" s="286"/>
-      <c r="L139" s="286"/>
-      <c r="M139" s="286"/>
-      <c r="N139" s="286"/>
-      <c r="O139" s="286"/>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C140" s="286"/>
-      <c r="D140" s="286"/>
-      <c r="E140" s="286"/>
-      <c r="F140" s="286"/>
-      <c r="G140" s="286"/>
-      <c r="H140" s="286"/>
-      <c r="I140" s="286"/>
-      <c r="J140" s="286"/>
-      <c r="K140" s="286"/>
-      <c r="L140" s="286"/>
-      <c r="M140" s="286"/>
-      <c r="N140" s="286"/>
-      <c r="O140" s="286"/>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C141" s="286"/>
-      <c r="D141" s="286"/>
-      <c r="E141" s="286"/>
-      <c r="F141" s="286"/>
-      <c r="G141" s="286"/>
-      <c r="H141" s="286"/>
-      <c r="I141" s="286"/>
-      <c r="J141" s="286"/>
-      <c r="K141" s="286"/>
-      <c r="L141" s="286"/>
-      <c r="M141" s="286"/>
-      <c r="N141" s="286"/>
-      <c r="O141" s="286"/>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C142" s="286"/>
-      <c r="D142" s="286"/>
-      <c r="E142" s="286"/>
-      <c r="F142" s="286"/>
-      <c r="G142" s="286"/>
-      <c r="H142" s="286"/>
-      <c r="I142" s="286"/>
-      <c r="J142" s="286"/>
-      <c r="K142" s="286"/>
-      <c r="L142" s="286"/>
-      <c r="M142" s="286"/>
-      <c r="N142" s="286"/>
-      <c r="O142" s="286"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="286"/>
-      <c r="D143" s="286"/>
-      <c r="E143" s="286"/>
-      <c r="F143" s="286"/>
-      <c r="G143" s="286"/>
-      <c r="H143" s="286"/>
-      <c r="I143" s="286"/>
-      <c r="J143" s="286"/>
-      <c r="K143" s="286"/>
-      <c r="L143" s="286"/>
-      <c r="M143" s="286"/>
-      <c r="N143" s="286"/>
-      <c r="O143" s="286"/>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C144" s="286"/>
-      <c r="D144" s="286"/>
-      <c r="E144" s="286"/>
-      <c r="F144" s="286"/>
-      <c r="G144" s="286"/>
-      <c r="H144" s="286"/>
-      <c r="I144" s="286"/>
-      <c r="J144" s="286"/>
-      <c r="K144" s="286"/>
-      <c r="L144" s="286"/>
-      <c r="M144" s="286"/>
-      <c r="N144" s="286"/>
-      <c r="O144" s="286"/>
-    </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C145" s="286"/>
-      <c r="D145" s="286"/>
-      <c r="E145" s="286"/>
-      <c r="F145" s="286"/>
-      <c r="G145" s="286"/>
-      <c r="H145" s="286"/>
-      <c r="I145" s="286"/>
-      <c r="J145" s="286"/>
-      <c r="K145" s="286"/>
-      <c r="L145" s="286"/>
-      <c r="M145" s="286"/>
-      <c r="N145" s="286"/>
-      <c r="O145" s="286"/>
-    </row>
-    <row r="146" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C146" s="286"/>
-      <c r="D146" s="286"/>
-      <c r="E146" s="286"/>
-      <c r="F146" s="286"/>
-      <c r="G146" s="286"/>
-      <c r="H146" s="286"/>
-      <c r="I146" s="286"/>
-      <c r="J146" s="286"/>
-      <c r="K146" s="286"/>
-      <c r="L146" s="286"/>
-      <c r="M146" s="286"/>
-      <c r="N146" s="286"/>
-      <c r="O146" s="286"/>
-    </row>
-    <row r="147" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D139" s="282"/>
+      <c r="E139" s="282"/>
+      <c r="F139" s="282"/>
+      <c r="G139" s="282"/>
+      <c r="H139" s="282"/>
+      <c r="I139" s="282"/>
+      <c r="J139" s="282"/>
+      <c r="K139" s="282"/>
+      <c r="L139" s="282"/>
+      <c r="M139" s="282"/>
+      <c r="N139" s="282"/>
+      <c r="O139" s="282"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C140" s="282"/>
+      <c r="D140" s="282"/>
+      <c r="E140" s="282"/>
+      <c r="F140" s="282"/>
+      <c r="G140" s="282"/>
+      <c r="H140" s="282"/>
+      <c r="I140" s="282"/>
+      <c r="J140" s="282"/>
+      <c r="K140" s="282"/>
+      <c r="L140" s="282"/>
+      <c r="M140" s="282"/>
+      <c r="N140" s="282"/>
+      <c r="O140" s="282"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C141" s="282"/>
+      <c r="D141" s="282"/>
+      <c r="E141" s="282"/>
+      <c r="F141" s="282"/>
+      <c r="G141" s="282"/>
+      <c r="H141" s="282"/>
+      <c r="I141" s="282"/>
+      <c r="J141" s="282"/>
+      <c r="K141" s="282"/>
+      <c r="L141" s="282"/>
+      <c r="M141" s="282"/>
+      <c r="N141" s="282"/>
+      <c r="O141" s="282"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C142" s="282"/>
+      <c r="D142" s="282"/>
+      <c r="E142" s="282"/>
+      <c r="F142" s="282"/>
+      <c r="G142" s="282"/>
+      <c r="H142" s="282"/>
+      <c r="I142" s="282"/>
+      <c r="J142" s="282"/>
+      <c r="K142" s="282"/>
+      <c r="L142" s="282"/>
+      <c r="M142" s="282"/>
+      <c r="N142" s="282"/>
+      <c r="O142" s="282"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C143" s="282"/>
+      <c r="D143" s="282"/>
+      <c r="E143" s="282"/>
+      <c r="F143" s="282"/>
+      <c r="G143" s="282"/>
+      <c r="H143" s="282"/>
+      <c r="I143" s="282"/>
+      <c r="J143" s="282"/>
+      <c r="K143" s="282"/>
+      <c r="L143" s="282"/>
+      <c r="M143" s="282"/>
+      <c r="N143" s="282"/>
+      <c r="O143" s="282"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C144" s="282"/>
+      <c r="D144" s="282"/>
+      <c r="E144" s="282"/>
+      <c r="F144" s="282"/>
+      <c r="G144" s="282"/>
+      <c r="H144" s="282"/>
+      <c r="I144" s="282"/>
+      <c r="J144" s="282"/>
+      <c r="K144" s="282"/>
+      <c r="L144" s="282"/>
+      <c r="M144" s="282"/>
+      <c r="N144" s="282"/>
+      <c r="O144" s="282"/>
+    </row>
+    <row r="145" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C145" s="282"/>
+      <c r="D145" s="282"/>
+      <c r="E145" s="282"/>
+      <c r="F145" s="282"/>
+      <c r="G145" s="282"/>
+      <c r="H145" s="282"/>
+      <c r="I145" s="282"/>
+      <c r="J145" s="282"/>
+      <c r="K145" s="282"/>
+      <c r="L145" s="282"/>
+      <c r="M145" s="282"/>
+      <c r="N145" s="282"/>
+      <c r="O145" s="282"/>
+    </row>
+    <row r="146" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C146" s="282"/>
+      <c r="D146" s="282"/>
+      <c r="E146" s="282"/>
+      <c r="F146" s="282"/>
+      <c r="G146" s="282"/>
+      <c r="H146" s="282"/>
+      <c r="I146" s="282"/>
+      <c r="J146" s="282"/>
+      <c r="K146" s="282"/>
+      <c r="L146" s="282"/>
+      <c r="M146" s="282"/>
+      <c r="N146" s="282"/>
+      <c r="O146" s="282"/>
+    </row>
+    <row r="147" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="49"/>
       <c r="D147" s="49"/>
       <c r="E147" s="49"/>
@@ -13064,7 +13010,7 @@
       <c r="N147" s="49"/>
       <c r="O147" s="49"/>
     </row>
-    <row r="148" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C148" s="49"/>
       <c r="D148" s="49"/>
       <c r="E148" s="49"/>
@@ -13079,126 +13025,119 @@
       <c r="N148" s="49"/>
       <c r="O148" s="49"/>
     </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="322" t="s">
+    <row r="149" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C149" s="331" t="s">
         <v>242</v>
       </c>
-      <c r="D149" s="322"/>
-      <c r="E149" s="322"/>
-      <c r="F149" s="322"/>
-      <c r="G149" s="322"/>
-      <c r="H149" s="322"/>
-      <c r="I149" s="322"/>
-      <c r="J149" s="322"/>
-      <c r="K149" s="322"/>
-      <c r="L149" s="322"/>
-      <c r="M149" s="322"/>
-      <c r="N149" s="322"/>
-      <c r="O149" s="322"/>
-    </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="322"/>
-      <c r="D150" s="322"/>
-      <c r="E150" s="322"/>
-      <c r="F150" s="322"/>
-      <c r="G150" s="322"/>
-      <c r="H150" s="322"/>
-      <c r="I150" s="322"/>
-      <c r="J150" s="322"/>
-      <c r="K150" s="322"/>
-      <c r="L150" s="322"/>
-      <c r="M150" s="322"/>
-      <c r="N150" s="322"/>
-      <c r="O150" s="322"/>
-    </row>
-    <row r="151" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C151" s="322"/>
-      <c r="D151" s="322"/>
-      <c r="E151" s="322"/>
-      <c r="F151" s="322"/>
-      <c r="G151" s="322"/>
-      <c r="H151" s="322"/>
-      <c r="I151" s="322"/>
-      <c r="J151" s="322"/>
-      <c r="K151" s="322"/>
-      <c r="L151" s="322"/>
-      <c r="M151" s="322"/>
-      <c r="N151" s="322"/>
-      <c r="O151" s="322"/>
+      <c r="D149" s="331"/>
+      <c r="E149" s="331"/>
+      <c r="F149" s="331"/>
+      <c r="G149" s="331"/>
+      <c r="H149" s="331"/>
+      <c r="I149" s="331"/>
+      <c r="J149" s="331"/>
+      <c r="K149" s="331"/>
+      <c r="L149" s="331"/>
+      <c r="M149" s="331"/>
+      <c r="N149" s="331"/>
+      <c r="O149" s="331"/>
+    </row>
+    <row r="150" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C150" s="331"/>
+      <c r="D150" s="331"/>
+      <c r="E150" s="331"/>
+      <c r="F150" s="331"/>
+      <c r="G150" s="331"/>
+      <c r="H150" s="331"/>
+      <c r="I150" s="331"/>
+      <c r="J150" s="331"/>
+      <c r="K150" s="331"/>
+      <c r="L150" s="331"/>
+      <c r="M150" s="331"/>
+      <c r="N150" s="331"/>
+      <c r="O150" s="331"/>
+    </row>
+    <row r="151" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C151" s="331"/>
+      <c r="D151" s="331"/>
+      <c r="E151" s="331"/>
+      <c r="F151" s="331"/>
+      <c r="G151" s="331"/>
+      <c r="H151" s="331"/>
+      <c r="I151" s="331"/>
+      <c r="J151" s="331"/>
+      <c r="K151" s="331"/>
+      <c r="L151" s="331"/>
+      <c r="M151" s="331"/>
+      <c r="N151" s="331"/>
+      <c r="O151" s="331"/>
       <c r="Q151" s="55">
         <f>M1-L134</f>
         <v>150436.23675993457</v>
       </c>
     </row>
-    <row r="152" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="322"/>
-      <c r="D152" s="322"/>
-      <c r="E152" s="322"/>
-      <c r="F152" s="322"/>
-      <c r="G152" s="322"/>
-      <c r="H152" s="322"/>
-      <c r="I152" s="322"/>
-      <c r="J152" s="322"/>
-      <c r="K152" s="322"/>
-      <c r="L152" s="322"/>
-      <c r="M152" s="322"/>
-      <c r="N152" s="322"/>
-      <c r="O152" s="322"/>
-    </row>
-    <row r="153" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="322"/>
-      <c r="D153" s="322"/>
-      <c r="E153" s="322"/>
-      <c r="F153" s="322"/>
-      <c r="G153" s="322"/>
-      <c r="H153" s="322"/>
-      <c r="I153" s="322"/>
-      <c r="J153" s="322"/>
-      <c r="K153" s="322"/>
-      <c r="L153" s="322"/>
-      <c r="M153" s="322"/>
-      <c r="N153" s="322"/>
-      <c r="O153" s="322"/>
-    </row>
-    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="322"/>
-      <c r="D154" s="322"/>
-      <c r="E154" s="322"/>
-      <c r="F154" s="322"/>
-      <c r="G154" s="322"/>
-      <c r="H154" s="322"/>
-      <c r="I154" s="322"/>
-      <c r="J154" s="322"/>
-      <c r="K154" s="322"/>
-      <c r="L154" s="322"/>
-      <c r="M154" s="322"/>
-      <c r="N154" s="322"/>
-      <c r="O154" s="322"/>
-    </row>
-    <row r="155" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C155" s="322"/>
-      <c r="D155" s="322"/>
-      <c r="E155" s="322"/>
-      <c r="F155" s="322"/>
-      <c r="G155" s="322"/>
-      <c r="H155" s="322"/>
-      <c r="I155" s="322"/>
-      <c r="J155" s="322"/>
-      <c r="K155" s="322"/>
-      <c r="L155" s="322"/>
-      <c r="M155" s="322"/>
-      <c r="N155" s="322"/>
-      <c r="O155" s="322"/>
+    <row r="152" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="331"/>
+      <c r="D152" s="331"/>
+      <c r="E152" s="331"/>
+      <c r="F152" s="331"/>
+      <c r="G152" s="331"/>
+      <c r="H152" s="331"/>
+      <c r="I152" s="331"/>
+      <c r="J152" s="331"/>
+      <c r="K152" s="331"/>
+      <c r="L152" s="331"/>
+      <c r="M152" s="331"/>
+      <c r="N152" s="331"/>
+      <c r="O152" s="331"/>
+    </row>
+    <row r="153" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="331"/>
+      <c r="D153" s="331"/>
+      <c r="E153" s="331"/>
+      <c r="F153" s="331"/>
+      <c r="G153" s="331"/>
+      <c r="H153" s="331"/>
+      <c r="I153" s="331"/>
+      <c r="J153" s="331"/>
+      <c r="K153" s="331"/>
+      <c r="L153" s="331"/>
+      <c r="M153" s="331"/>
+      <c r="N153" s="331"/>
+      <c r="O153" s="331"/>
+    </row>
+    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="331"/>
+      <c r="D154" s="331"/>
+      <c r="E154" s="331"/>
+      <c r="F154" s="331"/>
+      <c r="G154" s="331"/>
+      <c r="H154" s="331"/>
+      <c r="I154" s="331"/>
+      <c r="J154" s="331"/>
+      <c r="K154" s="331"/>
+      <c r="L154" s="331"/>
+      <c r="M154" s="331"/>
+      <c r="N154" s="331"/>
+      <c r="O154" s="331"/>
+    </row>
+    <row r="155" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C155" s="331"/>
+      <c r="D155" s="331"/>
+      <c r="E155" s="331"/>
+      <c r="F155" s="331"/>
+      <c r="G155" s="331"/>
+      <c r="H155" s="331"/>
+      <c r="I155" s="331"/>
+      <c r="J155" s="331"/>
+      <c r="K155" s="331"/>
+      <c r="L155" s="331"/>
+      <c r="M155" s="331"/>
+      <c r="N155" s="331"/>
+      <c r="O155" s="331"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="E12:E14"/>
     <mergeCell ref="R15:S16"/>
     <mergeCell ref="G12:G14"/>
     <mergeCell ref="C149:O155"/>
@@ -13215,6 +13154,13 @@
     <mergeCell ref="C6:O9"/>
     <mergeCell ref="C10:O11"/>
     <mergeCell ref="A1:E5"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="E12:E14"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13225,84 +13171,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DJ82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.33203125" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.5703125" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="365" t="s">
+    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="371" t="s">
         <v>300</v>
       </c>
-      <c r="B1" s="365"/>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="365"/>
-      <c r="G1" s="365"/>
-      <c r="H1" s="365"/>
-      <c r="I1" s="365"/>
-      <c r="J1" s="365"/>
-      <c r="K1" s="365"/>
-      <c r="L1" s="365"/>
-      <c r="M1" s="365"/>
-      <c r="N1" s="365"/>
-      <c r="O1" s="366"/>
+      <c r="B1" s="371"/>
+      <c r="C1" s="371"/>
+      <c r="D1" s="371"/>
+      <c r="E1" s="371"/>
+      <c r="F1" s="371"/>
+      <c r="G1" s="371"/>
+      <c r="H1" s="371"/>
+      <c r="I1" s="371"/>
+      <c r="J1" s="371"/>
+      <c r="K1" s="371"/>
+      <c r="L1" s="371"/>
+      <c r="M1" s="371"/>
+      <c r="N1" s="371"/>
+      <c r="O1" s="372"/>
       <c r="R1" s="31"/>
     </row>
-    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="367"/>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
-      <c r="H2" s="367"/>
-      <c r="I2" s="367"/>
-      <c r="J2" s="367"/>
-      <c r="K2" s="367"/>
-      <c r="L2" s="367"/>
-      <c r="M2" s="367"/>
-      <c r="N2" s="367"/>
-      <c r="O2" s="368"/>
+    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="373"/>
+      <c r="B2" s="373"/>
+      <c r="C2" s="373"/>
+      <c r="D2" s="373"/>
+      <c r="E2" s="373"/>
+      <c r="F2" s="373"/>
+      <c r="G2" s="373"/>
+      <c r="H2" s="373"/>
+      <c r="I2" s="373"/>
+      <c r="J2" s="373"/>
+      <c r="K2" s="373"/>
+      <c r="L2" s="373"/>
+      <c r="M2" s="373"/>
+      <c r="N2" s="373"/>
+      <c r="O2" s="374"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:27" s="166" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="362" t="s">
+    <row r="3" spans="1:27" s="166" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="368" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
-      <c r="M3" s="363"/>
-      <c r="N3" s="363"/>
-      <c r="O3" s="364"/>
+      <c r="B3" s="369"/>
+      <c r="C3" s="369"/>
+      <c r="D3" s="369"/>
+      <c r="E3" s="369"/>
+      <c r="F3" s="369"/>
+      <c r="G3" s="369"/>
+      <c r="H3" s="369"/>
+      <c r="I3" s="369"/>
+      <c r="J3" s="369"/>
+      <c r="K3" s="369"/>
+      <c r="L3" s="369"/>
+      <c r="M3" s="369"/>
+      <c r="N3" s="369"/>
+      <c r="O3" s="370"/>
       <c r="P3" s="167"/>
       <c r="Q3" s="167"/>
       <c r="R3" s="167"/>
@@ -13316,89 +13262,89 @@
       <c r="Z3" s="167"/>
       <c r="AA3" s="167"/>
     </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="320" t="s">
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="324" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="320" t="s">
+      <c r="B4" s="324" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="320" t="s">
+      <c r="C4" s="324" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="320" t="s">
+      <c r="D4" s="324" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="328" t="s">
+      <c r="E4" s="321" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="328" t="s">
+      <c r="F4" s="321" t="s">
         <v>327</v>
       </c>
-      <c r="G4" s="328" t="s">
+      <c r="G4" s="321" t="s">
         <v>260</v>
       </c>
-      <c r="H4" s="328" t="s">
+      <c r="H4" s="321" t="s">
         <v>332</v>
       </c>
-      <c r="I4" s="328" t="s">
+      <c r="I4" s="321" t="s">
         <v>339</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="360" t="s">
         <v>328</v>
       </c>
       <c r="K4" s="83"/>
-      <c r="L4" s="359" t="s">
+      <c r="L4" s="365" t="s">
         <v>336</v>
       </c>
-      <c r="M4" s="328" t="s">
+      <c r="M4" s="321" t="s">
         <v>337</v>
       </c>
-      <c r="N4" s="328" t="s">
+      <c r="N4" s="321" t="s">
         <v>329</v>
       </c>
-      <c r="O4" s="328" t="s">
+      <c r="O4" s="321" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="31"/>
     </row>
-    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="321"/>
-      <c r="B5" s="321"/>
-      <c r="C5" s="321"/>
-      <c r="D5" s="321"/>
-      <c r="E5" s="329"/>
-      <c r="F5" s="329"/>
-      <c r="G5" s="329"/>
-      <c r="H5" s="329"/>
-      <c r="I5" s="329"/>
-      <c r="J5" s="370"/>
+    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="325"/>
+      <c r="B5" s="325"/>
+      <c r="C5" s="325"/>
+      <c r="D5" s="325"/>
+      <c r="E5" s="322"/>
+      <c r="F5" s="322"/>
+      <c r="G5" s="322"/>
+      <c r="H5" s="322"/>
+      <c r="I5" s="322"/>
+      <c r="J5" s="361"/>
       <c r="K5" s="83"/>
-      <c r="L5" s="360"/>
-      <c r="M5" s="329"/>
-      <c r="N5" s="329"/>
-      <c r="O5" s="329"/>
+      <c r="L5" s="366"/>
+      <c r="M5" s="322"/>
+      <c r="N5" s="322"/>
+      <c r="O5" s="322"/>
       <c r="R5" s="31"/>
     </row>
-    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="372"/>
-      <c r="B6" s="372"/>
-      <c r="C6" s="372"/>
-      <c r="D6" s="372"/>
-      <c r="E6" s="358"/>
-      <c r="F6" s="358"/>
-      <c r="G6" s="358"/>
-      <c r="H6" s="358"/>
-      <c r="I6" s="358"/>
-      <c r="J6" s="371"/>
+    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="364"/>
+      <c r="B6" s="364"/>
+      <c r="C6" s="364"/>
+      <c r="D6" s="364"/>
+      <c r="E6" s="363"/>
+      <c r="F6" s="363"/>
+      <c r="G6" s="363"/>
+      <c r="H6" s="363"/>
+      <c r="I6" s="363"/>
+      <c r="J6" s="362"/>
       <c r="K6" s="136"/>
-      <c r="L6" s="361"/>
-      <c r="M6" s="358"/>
-      <c r="N6" s="358"/>
-      <c r="O6" s="358"/>
+      <c r="L6" s="367"/>
+      <c r="M6" s="363"/>
+      <c r="N6" s="363"/>
+      <c r="O6" s="363"/>
       <c r="R6" s="31"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="137" t="s">
         <v>109</v>
       </c>
@@ -13450,10 +13396,10 @@
       <c r="P7" s="70">
         <v>0.7</v>
       </c>
-      <c r="R7" s="319"/>
-      <c r="S7" s="319"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="R7" s="330"/>
+      <c r="S7" s="330"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="137" t="s">
         <v>308</v>
       </c>
@@ -13507,10 +13453,10 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="319"/>
-      <c r="S8" s="319"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="R8" s="330"/>
+      <c r="S8" s="330"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="137" t="s">
         <v>110</v>
       </c>
@@ -13566,7 +13512,7 @@
       </c>
       <c r="S9" s="31"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="137" t="s">
         <v>111</v>
       </c>
@@ -13621,7 +13567,7 @@
       </c>
       <c r="S10" s="31"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="141" t="s">
         <v>112</v>
       </c>
@@ -13676,7 +13622,7 @@
       </c>
       <c r="S11" s="31"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="144" t="s">
         <v>40</v>
       </c>
@@ -13732,7 +13678,7 @@
       </c>
       <c r="S12" s="31"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="137" t="s">
         <v>41</v>
       </c>
@@ -13787,7 +13733,7 @@
       </c>
       <c r="S13" s="31"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="137" t="s">
         <v>42</v>
       </c>
@@ -13843,7 +13789,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="137" t="s">
         <v>43</v>
       </c>
@@ -13899,7 +13845,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="137" t="s">
         <v>44</v>
       </c>
@@ -13953,7 +13899,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A17" s="137" t="s">
         <v>45</v>
       </c>
@@ -14009,7 +13955,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A18" s="137" t="s">
         <v>46</v>
       </c>
@@ -14065,7 +14011,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A19" s="137" t="s">
         <v>47</v>
       </c>
@@ -14119,7 +14065,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A20" s="137" t="s">
         <v>48</v>
       </c>
@@ -14173,7 +14119,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A21" s="137" t="s">
         <v>49</v>
       </c>
@@ -14227,7 +14173,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A22" s="137" t="s">
         <v>50</v>
       </c>
@@ -14281,7 +14227,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A23" s="137" t="s">
         <v>51</v>
       </c>
@@ -14335,7 +14281,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A24" s="137" t="s">
         <v>52</v>
       </c>
@@ -14389,7 +14335,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A25" s="137" t="s">
         <v>53</v>
       </c>
@@ -14443,7 +14389,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A26" s="137" t="s">
         <v>54</v>
       </c>
@@ -14499,7 +14445,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A27" s="137" t="s">
         <v>55</v>
       </c>
@@ -14557,7 +14503,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="28" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A28" s="137" t="s">
         <v>56</v>
       </c>
@@ -14611,7 +14557,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="29" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A29" s="137" t="s">
         <v>57</v>
       </c>
@@ -14663,7 +14609,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A30" s="137" t="s">
         <v>58</v>
       </c>
@@ -14720,7 +14666,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="31" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A31" s="137" t="s">
         <v>59</v>
       </c>
@@ -14776,7 +14722,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="137" t="s">
         <v>60</v>
       </c>
@@ -14931,7 +14877,7 @@
       <c r="DI32" s="46"/>
       <c r="DJ32" s="46"/>
     </row>
-    <row r="33" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="137" t="s">
         <v>61</v>
       </c>
@@ -15085,7 +15031,7 @@
       <c r="DI33" s="46"/>
       <c r="DJ33" s="46"/>
     </row>
-    <row r="34" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="137" t="s">
         <v>62</v>
       </c>
@@ -15241,7 +15187,7 @@
       <c r="DI34" s="46"/>
       <c r="DJ34" s="46"/>
     </row>
-    <row r="35" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" s="92" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="137" t="s">
         <v>63</v>
       </c>
@@ -15391,7 +15337,7 @@
       <c r="DI35" s="46"/>
       <c r="DJ35" s="46"/>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="137" t="s">
         <v>64</v>
       </c>
@@ -15447,7 +15393,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="137" t="s">
         <v>65</v>
       </c>
@@ -15501,7 +15447,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="137" t="s">
         <v>66</v>
       </c>
@@ -15563,7 +15509,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A39" s="137" t="s">
         <v>67</v>
       </c>
@@ -15619,7 +15565,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="40" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A40" s="137" t="s">
         <v>68</v>
       </c>
@@ -15673,7 +15619,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="41" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A41" s="137" t="s">
         <v>69</v>
       </c>
@@ -15727,7 +15673,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A42" s="137" t="s">
         <v>70</v>
       </c>
@@ -15783,7 +15729,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A43" s="137" t="s">
         <v>71</v>
       </c>
@@ -15840,7 +15786,7 @@
       </c>
       <c r="Q43" s="31"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="137" t="s">
         <v>72</v>
       </c>
@@ -15897,7 +15843,7 @@
       </c>
       <c r="Q44" s="31"/>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="137" t="s">
         <v>73</v>
       </c>
@@ -15954,7 +15900,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="137" t="s">
         <v>74</v>
       </c>
@@ -16008,7 +15954,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="137" t="s">
         <v>75</v>
       </c>
@@ -16062,7 +16008,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="137" t="s">
         <v>76</v>
       </c>
@@ -16119,7 +16065,7 @@
       </c>
       <c r="R48" s="39"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="137" t="s">
         <v>77</v>
       </c>
@@ -16173,7 +16119,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="137" t="s">
         <v>78</v>
       </c>
@@ -16230,7 +16176,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="137" t="s">
         <v>79</v>
       </c>
@@ -16284,7 +16230,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="137" t="s">
         <v>80</v>
       </c>
@@ -16341,7 +16287,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="137" t="s">
         <v>81</v>
       </c>
@@ -16400,7 +16346,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="137" t="s">
         <v>82</v>
       </c>
@@ -16456,7 +16402,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="137" t="s">
         <v>83</v>
       </c>
@@ -16510,7 +16456,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="137" t="s">
         <v>84</v>
       </c>
@@ -16566,7 +16512,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="137" t="s">
         <v>85</v>
       </c>
@@ -16622,7 +16568,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="137" t="s">
         <v>86</v>
       </c>
@@ -16678,7 +16624,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="137" t="s">
         <v>87</v>
       </c>
@@ -16735,7 +16681,7 @@
       </c>
       <c r="S59" s="125"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="137" t="s">
         <v>88</v>
       </c>
@@ -16792,7 +16738,7 @@
       </c>
       <c r="S60" s="31"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="137" t="s">
         <v>89</v>
       </c>
@@ -16847,7 +16793,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="137" t="s">
         <v>90</v>
       </c>
@@ -16903,7 +16849,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="137" t="s">
         <v>91</v>
       </c>
@@ -16957,7 +16903,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="137" t="s">
         <v>92</v>
       </c>
@@ -17014,7 +16960,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="137" t="s">
         <v>93</v>
       </c>
@@ -17071,7 +17017,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="137" t="s">
         <v>94</v>
       </c>
@@ -17128,7 +17074,7 @@
       </c>
       <c r="Q66" s="46"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="137" t="s">
         <v>95</v>
       </c>
@@ -17184,7 +17130,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="137" t="s">
         <v>96</v>
       </c>
@@ -17230,7 +17176,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="137" t="s">
         <v>97</v>
       </c>
@@ -17285,7 +17231,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="137" t="s">
         <v>98</v>
       </c>
@@ -17341,7 +17287,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="137" t="s">
         <v>99</v>
       </c>
@@ -17397,7 +17343,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="137" t="s">
         <v>100</v>
       </c>
@@ -17453,7 +17399,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="137" t="s">
         <v>101</v>
       </c>
@@ -17508,7 +17454,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="137" t="s">
         <v>102</v>
       </c>
@@ -17564,7 +17510,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="137" t="s">
         <v>103</v>
       </c>
@@ -17618,7 +17564,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="137" t="s">
         <v>104</v>
       </c>
@@ -17674,7 +17620,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="137" t="s">
         <v>105</v>
       </c>
@@ -17731,7 +17677,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="137" t="s">
         <v>106</v>
       </c>
@@ -17787,7 +17733,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="137" t="s">
         <v>107</v>
       </c>
@@ -17843,7 +17789,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="137" t="s">
         <v>108</v>
       </c>
@@ -17899,7 +17845,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="23"/>
       <c r="B81" s="23"/>
       <c r="C81" s="64"/>
@@ -17916,7 +17862,7 @@
       <c r="N81" s="96"/>
       <c r="O81" s="97"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="18"/>
       <c r="B82" s="18"/>
       <c r="C82" s="18"/>
@@ -17957,6 +17903,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A1:O2"/>
     <mergeCell ref="R7:S8"/>
     <mergeCell ref="J4:J6"/>
     <mergeCell ref="N4:N6"/>
@@ -17972,8 +17920,6 @@
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="L4:L6"/>
     <mergeCell ref="M4:M6"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A1:O2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="85" orientation="landscape" r:id="rId1"/>
@@ -17981,214 +17927,320 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
+  <dimension ref="C1:M8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+    </row>
+    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C2" s="242" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2" s="243">
+        <v>1</v>
+      </c>
+      <c r="E2" s="243"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+    </row>
+    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C3" s="244" t="s">
+        <v>344</v>
+      </c>
+      <c r="D3" s="245"/>
+      <c r="E3" s="246">
+        <v>0</v>
+      </c>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="H3" s="172"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="174"/>
+      <c r="K3" s="247"/>
+      <c r="L3" s="247"/>
+      <c r="M3" s="247"/>
+    </row>
+    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C4" s="244" t="s">
+        <v>346</v>
+      </c>
+      <c r="D4" s="245" t="s">
+        <v>347</v>
+      </c>
+      <c r="E4" s="245" t="s">
+        <v>348</v>
+      </c>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>417</v>
+      </c>
+      <c r="I4" s="173"/>
+      <c r="J4" s="174"/>
+      <c r="K4" s="247"/>
+      <c r="L4" s="247"/>
+      <c r="M4" s="247"/>
+    </row>
+    <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="168" t="s">
+        <v>350</v>
+      </c>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="247"/>
+      <c r="L5" s="247"/>
+      <c r="M5" s="247"/>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C6" s="384" t="s">
+        <v>418</v>
+      </c>
+      <c r="D6" s="385"/>
+      <c r="E6" s="385"/>
+      <c r="F6" s="385"/>
+      <c r="G6" s="385"/>
+      <c r="H6" s="385"/>
+      <c r="I6" s="385"/>
+      <c r="J6" s="386"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+    </row>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C7" s="387"/>
+      <c r="D7" s="388"/>
+      <c r="E7" s="388"/>
+      <c r="F7" s="388"/>
+      <c r="G7" s="388"/>
+      <c r="H7" s="388"/>
+      <c r="I7" s="388"/>
+      <c r="J7" s="389"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+    </row>
+    <row r="8" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="390"/>
+      <c r="D8" s="391"/>
+      <c r="E8" s="391"/>
+      <c r="F8" s="391"/>
+      <c r="G8" s="391"/>
+      <c r="H8" s="391"/>
+      <c r="I8" s="391"/>
+      <c r="J8" s="392"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C6:J8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F334087C-F49A-40D2-A732-EFA1FDB50C59}">
   <dimension ref="C2:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="382" t="s">
-        <v>414</v>
-      </c>
-      <c r="D3" s="383"/>
-      <c r="E3" s="383"/>
-      <c r="F3" s="383"/>
-      <c r="G3" s="383"/>
-      <c r="H3" s="384"/>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C4" s="385" t="s">
-        <v>415</v>
-      </c>
-      <c r="D4" s="386" t="s">
-        <v>416</v>
-      </c>
-      <c r="E4" s="386"/>
-      <c r="F4" s="386"/>
-      <c r="G4" s="386" t="s">
-        <v>417</v>
-      </c>
-      <c r="H4" s="387"/>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C5" s="388" t="str">
+    <row r="2" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="381" t="s">
+        <v>409</v>
+      </c>
+      <c r="D3" s="382"/>
+      <c r="E3" s="382"/>
+      <c r="F3" s="382"/>
+      <c r="G3" s="382"/>
+      <c r="H3" s="383"/>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C4" s="267" t="s">
+        <v>410</v>
+      </c>
+      <c r="D4" s="268" t="s">
+        <v>411</v>
+      </c>
+      <c r="E4" s="268"/>
+      <c r="F4" s="268"/>
+      <c r="G4" s="268" t="s">
+        <v>412</v>
+      </c>
+      <c r="H4" s="269"/>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C5" s="270" t="str">
         <f>PRORRATEO!C31</f>
         <v>3ºF</v>
       </c>
-      <c r="D5" s="389" t="str">
+      <c r="D5" t="str">
         <f>PRORRATEO!D31</f>
         <v>Ayala, Roberto Adrian</v>
       </c>
-      <c r="E5" s="389"/>
-      <c r="F5" s="389"/>
-      <c r="G5" s="390">
+      <c r="G5" s="375">
         <f>PRORRATEO!N31</f>
         <v>2143819.12</v>
       </c>
-      <c r="H5" s="391"/>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C6" s="388"/>
-      <c r="D6" s="389"/>
-      <c r="E6" s="389"/>
-      <c r="F6" s="389"/>
-      <c r="G6" s="389"/>
-      <c r="H6" s="392"/>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C7" s="388"/>
-      <c r="D7" s="389"/>
-      <c r="E7" s="389"/>
-      <c r="F7" s="389"/>
-      <c r="G7" s="389" t="s">
-        <v>418</v>
-      </c>
-      <c r="H7" s="392"/>
-    </row>
-    <row r="8" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="393"/>
-      <c r="D8" s="394"/>
-      <c r="E8" s="394"/>
-      <c r="F8" s="394"/>
-      <c r="G8" s="395">
-        <v>0</v>
-      </c>
-      <c r="H8" s="396"/>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C9" s="385" t="s">
-        <v>415</v>
-      </c>
-      <c r="D9" s="386" t="s">
-        <v>416</v>
-      </c>
-      <c r="E9" s="386"/>
-      <c r="F9" s="386"/>
-      <c r="G9" s="386" t="s">
-        <v>417</v>
-      </c>
-      <c r="H9" s="387"/>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C10" s="388" t="str">
+      <c r="H5" s="376"/>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C6" s="270"/>
+      <c r="H6" s="271"/>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="270"/>
+      <c r="G7" t="s">
+        <v>413</v>
+      </c>
+      <c r="H7" s="271"/>
+    </row>
+    <row r="8" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="272"/>
+      <c r="D8" s="273"/>
+      <c r="E8" s="273"/>
+      <c r="F8" s="273"/>
+      <c r="G8" s="377">
+        <v>0</v>
+      </c>
+      <c r="H8" s="378"/>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="267" t="s">
+        <v>410</v>
+      </c>
+      <c r="D9" s="268" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" s="268"/>
+      <c r="F9" s="268"/>
+      <c r="G9" s="268" t="s">
+        <v>412</v>
+      </c>
+      <c r="H9" s="269"/>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="270" t="str">
         <f>PRORRATEO!C37</f>
         <v>4ºF</v>
       </c>
-      <c r="D10" s="389" t="str">
+      <c r="D10" t="str">
         <f>PRORRATEO!D37</f>
         <v>Ayala, Roberto Adrian</v>
       </c>
-      <c r="E10" s="389"/>
-      <c r="F10" s="389"/>
-      <c r="G10" s="390">
+      <c r="G10" s="375">
         <f>PRORRATEO!N37</f>
         <v>1626068.18</v>
       </c>
-      <c r="H10" s="391"/>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C11" s="388"/>
-      <c r="D11" s="389"/>
-      <c r="E11" s="389"/>
-      <c r="F11" s="389"/>
-      <c r="G11" s="389"/>
-      <c r="H11" s="392"/>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C12" s="388"/>
-      <c r="D12" s="389"/>
-      <c r="E12" s="389"/>
-      <c r="F12" s="389"/>
-      <c r="G12" s="389" t="s">
-        <v>419</v>
-      </c>
-      <c r="H12" s="392"/>
-    </row>
-    <row r="13" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="393"/>
-      <c r="D13" s="394"/>
-      <c r="E13" s="394"/>
-      <c r="F13" s="394"/>
-      <c r="G13" s="395">
-        <v>0</v>
-      </c>
-      <c r="H13" s="396"/>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C14" s="385" t="s">
-        <v>415</v>
-      </c>
-      <c r="D14" s="386" t="s">
-        <v>416</v>
-      </c>
-      <c r="E14" s="386"/>
-      <c r="F14" s="386"/>
-      <c r="G14" s="386" t="s">
-        <v>417</v>
-      </c>
-      <c r="H14" s="387"/>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C15" s="388" t="str">
+      <c r="H10" s="376"/>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="270"/>
+      <c r="H11" s="271"/>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="270"/>
+      <c r="G12" t="s">
+        <v>414</v>
+      </c>
+      <c r="H12" s="271"/>
+    </row>
+    <row r="13" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="272"/>
+      <c r="D13" s="273"/>
+      <c r="E13" s="273"/>
+      <c r="F13" s="273"/>
+      <c r="G13" s="377">
+        <v>0</v>
+      </c>
+      <c r="H13" s="378"/>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="267" t="s">
+        <v>410</v>
+      </c>
+      <c r="D14" s="268" t="s">
+        <v>411</v>
+      </c>
+      <c r="E14" s="268"/>
+      <c r="F14" s="268"/>
+      <c r="G14" s="268" t="s">
+        <v>412</v>
+      </c>
+      <c r="H14" s="269"/>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C15" s="270" t="str">
         <f>PRORRATEO!C43</f>
         <v>5ºF</v>
       </c>
-      <c r="D15" s="389" t="str">
+      <c r="D15" t="str">
         <f>PRORRATEO!D43</f>
         <v>Ayala, Agustin</v>
       </c>
-      <c r="E15" s="389"/>
-      <c r="F15" s="389"/>
-      <c r="G15" s="390">
+      <c r="G15" s="375">
         <f>PRORRATEO!N43</f>
         <v>1371288.24</v>
       </c>
-      <c r="H15" s="391"/>
-    </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C16" s="388"/>
-      <c r="D16" s="389"/>
-      <c r="E16" s="389"/>
-      <c r="F16" s="389"/>
-      <c r="G16" s="389"/>
-      <c r="H16" s="392"/>
-    </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C17" s="388"/>
-      <c r="D17" s="389"/>
-      <c r="E17" s="389"/>
-      <c r="F17" s="389"/>
-      <c r="G17" s="389" t="s">
-        <v>420</v>
-      </c>
-      <c r="H17" s="392"/>
-    </row>
-    <row r="18" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="393"/>
-      <c r="D18" s="394"/>
-      <c r="E18" s="394"/>
-      <c r="F18" s="394"/>
-      <c r="G18" s="395">
-        <v>0</v>
-      </c>
-      <c r="H18" s="396"/>
-    </row>
-    <row r="19" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="397" t="s">
-        <v>421</v>
-      </c>
-      <c r="D20" s="398"/>
-      <c r="E20" s="398"/>
-      <c r="F20" s="398"/>
-      <c r="G20" s="399">
+      <c r="H15" s="376"/>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C16" s="270"/>
+      <c r="H16" s="271"/>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C17" s="270"/>
+      <c r="G17" t="s">
+        <v>415</v>
+      </c>
+      <c r="H17" s="271"/>
+    </row>
+    <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="272"/>
+      <c r="D18" s="273"/>
+      <c r="E18" s="273"/>
+      <c r="F18" s="273"/>
+      <c r="G18" s="377">
+        <v>0</v>
+      </c>
+      <c r="H18" s="378"/>
+    </row>
+    <row r="19" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C20" s="274" t="s">
+        <v>416</v>
+      </c>
+      <c r="D20" s="275"/>
+      <c r="E20" s="275"/>
+      <c r="F20" s="275"/>
+      <c r="G20" s="379">
         <f>G15+G10+G5</f>
         <v>5141175.54</v>
       </c>
-      <c r="H20" s="400"/>
+      <c r="H20" s="380"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -18204,259 +18256,4 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="115" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
-  <dimension ref="C1:M17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-    </row>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C2" s="242" t="s">
-        <v>343</v>
-      </c>
-      <c r="D2" s="243">
-        <v>1</v>
-      </c>
-      <c r="E2" s="243"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-    </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C3" s="244" t="s">
-        <v>344</v>
-      </c>
-      <c r="D3" s="245"/>
-      <c r="E3" s="246">
-        <v>0</v>
-      </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46" t="s">
-        <v>345</v>
-      </c>
-      <c r="H3" s="172"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="174"/>
-      <c r="K3" s="262"/>
-      <c r="L3" s="262"/>
-      <c r="M3" s="247"/>
-    </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="244" t="s">
-        <v>346</v>
-      </c>
-      <c r="D4" s="245" t="s">
-        <v>347</v>
-      </c>
-      <c r="E4" s="245" t="s">
-        <v>348</v>
-      </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="H4" s="46" t="s">
-        <v>376</v>
-      </c>
-      <c r="I4" s="173"/>
-      <c r="J4" s="174"/>
-      <c r="K4" s="262"/>
-      <c r="L4" s="262"/>
-      <c r="M4" s="247"/>
-    </row>
-    <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="168" t="s">
-        <v>350</v>
-      </c>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
-      <c r="M5" s="247"/>
-    </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C6" s="373" t="s">
-        <v>377</v>
-      </c>
-      <c r="D6" s="374"/>
-      <c r="E6" s="374"/>
-      <c r="F6" s="374"/>
-      <c r="G6" s="374"/>
-      <c r="H6" s="374"/>
-      <c r="I6" s="374"/>
-      <c r="J6" s="375"/>
-      <c r="K6" s="261"/>
-      <c r="L6" s="261"/>
-      <c r="M6" s="46"/>
-    </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="376"/>
-      <c r="D7" s="377"/>
-      <c r="E7" s="377"/>
-      <c r="F7" s="377"/>
-      <c r="G7" s="377"/>
-      <c r="H7" s="377"/>
-      <c r="I7" s="377"/>
-      <c r="J7" s="378"/>
-      <c r="K7" s="261"/>
-      <c r="L7" s="261"/>
-      <c r="M7" s="46"/>
-    </row>
-    <row r="8" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="379"/>
-      <c r="D8" s="380"/>
-      <c r="E8" s="380"/>
-      <c r="F8" s="380"/>
-      <c r="G8" s="380"/>
-      <c r="H8" s="380"/>
-      <c r="I8" s="380"/>
-      <c r="J8" s="381"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-    </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-    </row>
-    <row r="10" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
-    </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C11" s="248" t="s">
-        <v>343</v>
-      </c>
-      <c r="D11" s="249">
-        <v>1</v>
-      </c>
-      <c r="E11" s="249"/>
-      <c r="F11" s="170"/>
-      <c r="G11" s="170"/>
-      <c r="H11" s="170"/>
-      <c r="I11" s="170"/>
-      <c r="J11" s="171"/>
-    </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="250" t="s">
-        <v>344</v>
-      </c>
-      <c r="D12" s="251"/>
-      <c r="E12" s="252">
-        <v>0</v>
-      </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46" t="s">
-        <v>345</v>
-      </c>
-      <c r="H12" s="172" t="s">
-        <v>379</v>
-      </c>
-      <c r="I12" s="173"/>
-      <c r="J12" s="174"/>
-      <c r="K12" s="261"/>
-      <c r="L12" s="261"/>
-      <c r="M12" s="261"/>
-    </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="250" t="s">
-        <v>346</v>
-      </c>
-      <c r="D13" s="251" t="s">
-        <v>347</v>
-      </c>
-      <c r="E13" s="251" t="s">
-        <v>348</v>
-      </c>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="H13" s="46" t="s">
-        <v>378</v>
-      </c>
-      <c r="I13" s="173"/>
-      <c r="J13" s="174"/>
-      <c r="K13" s="261"/>
-      <c r="L13" s="261"/>
-      <c r="M13" s="261"/>
-    </row>
-    <row r="14" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="168" t="s">
-        <v>350</v>
-      </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="175"/>
-      <c r="K14" s="261"/>
-      <c r="L14" s="261"/>
-      <c r="M14" s="261"/>
-    </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="373" t="s">
-        <v>380</v>
-      </c>
-      <c r="D15" s="374"/>
-      <c r="E15" s="374"/>
-      <c r="F15" s="374"/>
-      <c r="G15" s="374"/>
-      <c r="H15" s="374"/>
-      <c r="I15" s="374"/>
-      <c r="J15" s="375"/>
-      <c r="K15" s="261"/>
-      <c r="L15" s="261"/>
-      <c r="M15" s="261"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="376"/>
-      <c r="D16" s="377"/>
-      <c r="E16" s="377"/>
-      <c r="F16" s="377"/>
-      <c r="G16" s="377"/>
-      <c r="H16" s="377"/>
-      <c r="I16" s="377"/>
-      <c r="J16" s="378"/>
-      <c r="K16" s="261"/>
-      <c r="L16" s="261"/>
-      <c r="M16" s="261"/>
-    </row>
-    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="379"/>
-      <c r="D17" s="380"/>
-      <c r="E17" s="380"/>
-      <c r="F17" s="380"/>
-      <c r="G17" s="380"/>
-      <c r="H17" s="380"/>
-      <c r="I17" s="380"/>
-      <c r="J17" s="381"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C6:J8"/>
-    <mergeCell ref="C15:J17"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/2026/EL MIRADOR/Agosto/Agosto - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Agosto/Agosto - EL MIRADOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81945496-AA6C-4D8F-921B-690FACB71AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E808143A-8720-42B5-8F52-43DB7E60845F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="423">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1295,6 +1295,18 @@
   </si>
   <si>
     <t>Pago $34.752 y $770.504 de expensas y arba</t>
+  </si>
+  <si>
+    <t>El 5C pago con cualquier centavo, abono $529.029,96 el 07/09</t>
+  </si>
+  <si>
+    <t>5C</t>
+  </si>
+  <si>
+    <t>Jose ferraro</t>
+  </si>
+  <si>
+    <t>Jose Ferraro deposito $526.500 el 14/09</t>
   </si>
 </sst>
 </file>
@@ -1520,7 +1532,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1620,6 +1632,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1973,7 +1991,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="395">
+  <cellXfs count="409">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2338,11 +2356,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2455,53 +2507,14 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2520,6 +2533,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2590,19 +2612,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2612,6 +2631,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="23" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2634,6 +2656,45 @@
     </xf>
     <xf numFmtId="1" fontId="19" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2662,35 +2723,6 @@
     <xf numFmtId="0" fontId="18" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
@@ -3181,108 +3213,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="315" t="s">
+      <c r="A14" s="294" t="s">
         <v>243</v>
       </c>
-      <c r="B14" s="315"/>
-      <c r="C14" s="315"/>
-      <c r="D14" s="315"/>
-      <c r="E14" s="315"/>
-      <c r="F14" s="315"/>
-      <c r="G14" s="315"/>
-      <c r="H14" s="315"/>
-      <c r="I14" s="315"/>
-      <c r="J14" s="315"/>
+      <c r="B14" s="294"/>
+      <c r="C14" s="294"/>
+      <c r="D14" s="294"/>
+      <c r="E14" s="294"/>
+      <c r="F14" s="294"/>
+      <c r="G14" s="294"/>
+      <c r="H14" s="294"/>
+      <c r="I14" s="294"/>
+      <c r="J14" s="294"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="315"/>
-      <c r="B15" s="315"/>
-      <c r="C15" s="315"/>
-      <c r="D15" s="315"/>
-      <c r="E15" s="315"/>
-      <c r="F15" s="315"/>
-      <c r="G15" s="315"/>
-      <c r="H15" s="315"/>
-      <c r="I15" s="315"/>
-      <c r="J15" s="315"/>
+      <c r="A15" s="294"/>
+      <c r="B15" s="294"/>
+      <c r="C15" s="294"/>
+      <c r="D15" s="294"/>
+      <c r="E15" s="294"/>
+      <c r="F15" s="294"/>
+      <c r="G15" s="294"/>
+      <c r="H15" s="294"/>
+      <c r="I15" s="294"/>
+      <c r="J15" s="294"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="315"/>
-      <c r="B16" s="315"/>
-      <c r="C16" s="315"/>
-      <c r="D16" s="315"/>
-      <c r="E16" s="315"/>
-      <c r="F16" s="315"/>
-      <c r="G16" s="315"/>
-      <c r="H16" s="315"/>
-      <c r="I16" s="315"/>
-      <c r="J16" s="315"/>
+      <c r="A16" s="294"/>
+      <c r="B16" s="294"/>
+      <c r="C16" s="294"/>
+      <c r="D16" s="294"/>
+      <c r="E16" s="294"/>
+      <c r="F16" s="294"/>
+      <c r="G16" s="294"/>
+      <c r="H16" s="294"/>
+      <c r="I16" s="294"/>
+      <c r="J16" s="294"/>
     </row>
     <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="315"/>
-      <c r="B17" s="315"/>
-      <c r="C17" s="315"/>
-      <c r="D17" s="315"/>
-      <c r="E17" s="315"/>
-      <c r="F17" s="315"/>
-      <c r="G17" s="315"/>
-      <c r="H17" s="315"/>
-      <c r="I17" s="315"/>
-      <c r="J17" s="315"/>
+      <c r="A17" s="294"/>
+      <c r="B17" s="294"/>
+      <c r="C17" s="294"/>
+      <c r="D17" s="294"/>
+      <c r="E17" s="294"/>
+      <c r="F17" s="294"/>
+      <c r="G17" s="294"/>
+      <c r="H17" s="294"/>
+      <c r="I17" s="294"/>
+      <c r="J17" s="294"/>
     </row>
     <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="315"/>
-      <c r="B18" s="315"/>
-      <c r="C18" s="315"/>
-      <c r="D18" s="315"/>
-      <c r="E18" s="315"/>
-      <c r="F18" s="315"/>
-      <c r="G18" s="315"/>
-      <c r="H18" s="315"/>
-      <c r="I18" s="315"/>
-      <c r="J18" s="315"/>
+      <c r="A18" s="294"/>
+      <c r="B18" s="294"/>
+      <c r="C18" s="294"/>
+      <c r="D18" s="294"/>
+      <c r="E18" s="294"/>
+      <c r="F18" s="294"/>
+      <c r="G18" s="294"/>
+      <c r="H18" s="294"/>
+      <c r="I18" s="294"/>
+      <c r="J18" s="294"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="H19" s="60"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="316" t="s">
+      <c r="A20" s="295" t="s">
         <v>376</v>
       </c>
-      <c r="B20" s="316"/>
-      <c r="C20" s="316"/>
-      <c r="D20" s="316"/>
-      <c r="E20" s="316"/>
-      <c r="F20" s="316"/>
-      <c r="G20" s="316"/>
-      <c r="H20" s="316"/>
-      <c r="I20" s="316"/>
-      <c r="J20" s="316"/>
+      <c r="B20" s="295"/>
+      <c r="C20" s="295"/>
+      <c r="D20" s="295"/>
+      <c r="E20" s="295"/>
+      <c r="F20" s="295"/>
+      <c r="G20" s="295"/>
+      <c r="H20" s="295"/>
+      <c r="I20" s="295"/>
+      <c r="J20" s="295"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="316"/>
-      <c r="B21" s="316"/>
-      <c r="C21" s="316"/>
-      <c r="D21" s="316"/>
-      <c r="E21" s="316"/>
-      <c r="F21" s="316"/>
-      <c r="G21" s="316"/>
-      <c r="H21" s="316"/>
-      <c r="I21" s="316"/>
-      <c r="J21" s="316"/>
+      <c r="A21" s="295"/>
+      <c r="B21" s="295"/>
+      <c r="C21" s="295"/>
+      <c r="D21" s="295"/>
+      <c r="E21" s="295"/>
+      <c r="F21" s="295"/>
+      <c r="G21" s="295"/>
+      <c r="H21" s="295"/>
+      <c r="I21" s="295"/>
+      <c r="J21" s="295"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="316"/>
-      <c r="B22" s="316"/>
-      <c r="C22" s="316"/>
-      <c r="D22" s="316"/>
-      <c r="E22" s="316"/>
-      <c r="F22" s="316"/>
-      <c r="G22" s="316"/>
-      <c r="H22" s="316"/>
-      <c r="I22" s="316"/>
-      <c r="J22" s="316"/>
+      <c r="A22" s="295"/>
+      <c r="B22" s="295"/>
+      <c r="C22" s="295"/>
+      <c r="D22" s="295"/>
+      <c r="E22" s="295"/>
+      <c r="F22" s="295"/>
+      <c r="G22" s="295"/>
+      <c r="H22" s="295"/>
+      <c r="I22" s="295"/>
+      <c r="J22" s="295"/>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="56"/>
@@ -3724,8 +3756,8 @@
       <c r="L42" s="43"/>
     </row>
     <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="317"/>
-      <c r="B43" s="318"/>
+      <c r="A43" s="296"/>
+      <c r="B43" s="297"/>
       <c r="C43" s="157"/>
       <c r="D43" s="32"/>
       <c r="E43" s="186"/>
@@ -3956,10 +3988,10 @@
       <c r="N49" s="55"/>
     </row>
     <row r="50" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="276" t="s">
+      <c r="A50" s="292" t="s">
         <v>381</v>
       </c>
-      <c r="B50" s="277"/>
+      <c r="B50" s="293"/>
       <c r="C50" s="240" t="s">
         <v>393</v>
       </c>
@@ -4226,10 +4258,10 @@
       </c>
     </row>
     <row r="59" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="319" t="s">
+      <c r="A59" s="298" t="s">
         <v>391</v>
       </c>
-      <c r="B59" s="320"/>
+      <c r="B59" s="299"/>
       <c r="C59" s="119" t="s">
         <v>390</v>
       </c>
@@ -4270,10 +4302,10 @@
       </c>
     </row>
     <row r="60" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="319" t="s">
+      <c r="A60" s="298" t="s">
         <v>389</v>
       </c>
-      <c r="B60" s="320"/>
+      <c r="B60" s="299"/>
       <c r="C60" s="119" t="s">
         <v>390</v>
       </c>
@@ -4314,10 +4346,10 @@
       </c>
     </row>
     <row r="61" spans="1:14" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="276" t="s">
+      <c r="A61" s="292" t="s">
         <v>398</v>
       </c>
-      <c r="B61" s="277"/>
+      <c r="B61" s="293"/>
       <c r="C61" s="119" t="s">
         <v>392</v>
       </c>
@@ -4402,10 +4434,10 @@
       </c>
     </row>
     <row r="63" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="276" t="s">
+      <c r="A63" s="292" t="s">
         <v>400</v>
       </c>
-      <c r="B63" s="277"/>
+      <c r="B63" s="293"/>
       <c r="C63" s="240" t="s">
         <v>385</v>
       </c>
@@ -4431,10 +4463,10 @@
       </c>
     </row>
     <row r="64" spans="1:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="276" t="s">
+      <c r="A64" s="292" t="s">
         <v>386</v>
       </c>
-      <c r="B64" s="277"/>
+      <c r="B64" s="293"/>
       <c r="C64" s="240" t="s">
         <v>385</v>
       </c>
@@ -4475,10 +4507,10 @@
       </c>
     </row>
     <row r="65" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="276" t="s">
+      <c r="A65" s="292" t="s">
         <v>395</v>
       </c>
-      <c r="B65" s="277"/>
+      <c r="B65" s="293"/>
       <c r="C65" s="240" t="s">
         <v>394</v>
       </c>
@@ -4665,11 +4697,11 @@
       </c>
     </row>
     <row r="70" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="278" t="s">
+      <c r="A70" s="300" t="s">
         <v>401</v>
       </c>
-      <c r="B70" s="279"/>
-      <c r="C70" s="280"/>
+      <c r="B70" s="301"/>
+      <c r="C70" s="302"/>
       <c r="D70" s="32">
         <v>0</v>
       </c>
@@ -4885,11 +4917,11 @@
       <c r="L76" s="43"/>
     </row>
     <row r="77" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="312" t="s">
+      <c r="A77" s="334" t="s">
         <v>407</v>
       </c>
-      <c r="B77" s="313"/>
-      <c r="C77" s="314"/>
+      <c r="B77" s="335"/>
+      <c r="C77" s="336"/>
       <c r="D77" s="62">
         <f>24275955.4-15214817.97+1950000</f>
         <v>11011137.429999998</v>
@@ -5086,12 +5118,12 @@
       <c r="I86" s="40"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A87" s="299" t="s">
+      <c r="A87" s="321" t="s">
         <v>32</v>
       </c>
-      <c r="B87" s="300"/>
-      <c r="C87" s="300"/>
-      <c r="D87" s="300"/>
+      <c r="B87" s="322"/>
+      <c r="C87" s="322"/>
+      <c r="D87" s="322"/>
       <c r="E87" s="51" t="s">
         <v>10</v>
       </c>
@@ -5112,8 +5144,8 @@
       </c>
     </row>
     <row r="88" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="276"/>
-      <c r="B88" s="281"/>
+      <c r="A88" s="292"/>
+      <c r="B88" s="303"/>
       <c r="C88" s="220"/>
       <c r="D88" s="32"/>
       <c r="E88" s="198">
@@ -5127,8 +5159,8 @@
       <c r="J88" s="38"/>
     </row>
     <row r="89" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="301"/>
-      <c r="B89" s="302"/>
+      <c r="A89" s="323"/>
+      <c r="B89" s="324"/>
       <c r="C89" s="53"/>
       <c r="D89" s="32"/>
       <c r="E89" s="42"/>
@@ -5139,11 +5171,11 @@
       <c r="J89" s="38"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A90" s="296" t="s">
+      <c r="A90" s="318" t="s">
         <v>16</v>
       </c>
-      <c r="B90" s="297"/>
-      <c r="C90" s="298"/>
+      <c r="B90" s="319"/>
+      <c r="C90" s="320"/>
       <c r="D90" s="50">
         <f>SUM(D88:D89)</f>
         <v>0</v>
@@ -5193,30 +5225,30 @@
         <f>D79-D77</f>
         <v>15214817.970000001</v>
       </c>
-      <c r="D94" s="282" t="s">
+      <c r="D94" s="304" t="s">
         <v>373</v>
       </c>
-      <c r="E94" s="282"/>
-      <c r="F94" s="282"/>
-      <c r="G94" s="282"/>
-      <c r="H94" s="282"/>
-      <c r="I94" s="282"/>
+      <c r="E94" s="304"/>
+      <c r="F94" s="304"/>
+      <c r="G94" s="304"/>
+      <c r="H94" s="304"/>
+      <c r="I94" s="304"/>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D95" s="282"/>
-      <c r="E95" s="282"/>
-      <c r="F95" s="282"/>
-      <c r="G95" s="282"/>
-      <c r="H95" s="282"/>
-      <c r="I95" s="282"/>
+      <c r="D95" s="304"/>
+      <c r="E95" s="304"/>
+      <c r="F95" s="304"/>
+      <c r="G95" s="304"/>
+      <c r="H95" s="304"/>
+      <c r="I95" s="304"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D96" s="282"/>
-      <c r="E96" s="282"/>
-      <c r="F96" s="282"/>
-      <c r="G96" s="282"/>
-      <c r="H96" s="282"/>
-      <c r="I96" s="282"/>
+      <c r="D96" s="304"/>
+      <c r="E96" s="304"/>
+      <c r="F96" s="304"/>
+      <c r="G96" s="304"/>
+      <c r="H96" s="304"/>
+      <c r="I96" s="304"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
@@ -5224,12 +5256,12 @@
       </c>
       <c r="B97" s="8"/>
       <c r="C97" s="9"/>
-      <c r="D97" s="282"/>
-      <c r="E97" s="282"/>
-      <c r="F97" s="282"/>
-      <c r="G97" s="282"/>
-      <c r="H97" s="282"/>
-      <c r="I97" s="282"/>
+      <c r="D97" s="304"/>
+      <c r="E97" s="304"/>
+      <c r="F97" s="304"/>
+      <c r="G97" s="304"/>
+      <c r="H97" s="304"/>
+      <c r="I97" s="304"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
@@ -5239,12 +5271,12 @@
         <v>1682660.59</v>
       </c>
       <c r="C98" s="11"/>
-      <c r="D98" s="282"/>
-      <c r="E98" s="282"/>
-      <c r="F98" s="282"/>
-      <c r="G98" s="282"/>
-      <c r="H98" s="282"/>
-      <c r="I98" s="282"/>
+      <c r="D98" s="304"/>
+      <c r="E98" s="304"/>
+      <c r="F98" s="304"/>
+      <c r="G98" s="304"/>
+      <c r="H98" s="304"/>
+      <c r="I98" s="304"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
@@ -5257,12 +5289,12 @@
       <c r="C99" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D99" s="282"/>
-      <c r="E99" s="282"/>
-      <c r="F99" s="282"/>
-      <c r="G99" s="282"/>
-      <c r="H99" s="282"/>
-      <c r="I99" s="282"/>
+      <c r="D99" s="304"/>
+      <c r="E99" s="304"/>
+      <c r="F99" s="304"/>
+      <c r="G99" s="304"/>
+      <c r="H99" s="304"/>
+      <c r="I99" s="304"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
@@ -5273,12 +5305,12 @@
         <v>0</v>
       </c>
       <c r="C100" s="11"/>
-      <c r="D100" s="282"/>
-      <c r="E100" s="282"/>
-      <c r="F100" s="282"/>
-      <c r="G100" s="282"/>
-      <c r="H100" s="282"/>
-      <c r="I100" s="282"/>
+      <c r="D100" s="304"/>
+      <c r="E100" s="304"/>
+      <c r="F100" s="304"/>
+      <c r="G100" s="304"/>
+      <c r="H100" s="304"/>
+      <c r="I100" s="304"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
@@ -5289,12 +5321,12 @@
         <v>-15214817.970000001</v>
       </c>
       <c r="C101" s="9"/>
-      <c r="D101" s="282"/>
-      <c r="E101" s="282"/>
-      <c r="F101" s="282"/>
-      <c r="G101" s="282"/>
-      <c r="H101" s="282"/>
-      <c r="I101" s="282"/>
+      <c r="D101" s="304"/>
+      <c r="E101" s="304"/>
+      <c r="F101" s="304"/>
+      <c r="G101" s="304"/>
+      <c r="H101" s="304"/>
+      <c r="I101" s="304"/>
       <c r="K101" s="32"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
@@ -5306,12 +5338,12 @@
         <v>0</v>
       </c>
       <c r="C102" s="9"/>
-      <c r="D102" s="282"/>
-      <c r="E102" s="282"/>
-      <c r="F102" s="282"/>
-      <c r="G102" s="282"/>
-      <c r="H102" s="282"/>
-      <c r="I102" s="282"/>
+      <c r="D102" s="304"/>
+      <c r="E102" s="304"/>
+      <c r="F102" s="304"/>
+      <c r="G102" s="304"/>
+      <c r="H102" s="304"/>
+      <c r="I102" s="304"/>
       <c r="K102" s="33"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
@@ -5323,12 +5355,12 @@
         <v>0</v>
       </c>
       <c r="C103" s="9"/>
-      <c r="D103" s="282"/>
-      <c r="E103" s="282"/>
-      <c r="F103" s="282"/>
-      <c r="G103" s="282"/>
-      <c r="H103" s="282"/>
-      <c r="I103" s="282"/>
+      <c r="D103" s="304"/>
+      <c r="E103" s="304"/>
+      <c r="F103" s="304"/>
+      <c r="G103" s="304"/>
+      <c r="H103" s="304"/>
+      <c r="I103" s="304"/>
       <c r="K103" s="33"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
@@ -5339,12 +5371,12 @@
         <v>-141000</v>
       </c>
       <c r="C104" s="9"/>
-      <c r="D104" s="282"/>
-      <c r="E104" s="282"/>
-      <c r="F104" s="282"/>
-      <c r="G104" s="282"/>
-      <c r="H104" s="282"/>
-      <c r="I104" s="282"/>
+      <c r="D104" s="304"/>
+      <c r="E104" s="304"/>
+      <c r="F104" s="304"/>
+      <c r="G104" s="304"/>
+      <c r="H104" s="304"/>
+      <c r="I104" s="304"/>
       <c r="K104" s="33"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
@@ -5356,12 +5388,12 @@
         <v>-20000</v>
       </c>
       <c r="C105" s="13"/>
-      <c r="D105" s="282"/>
-      <c r="E105" s="282"/>
-      <c r="F105" s="282"/>
-      <c r="G105" s="282"/>
-      <c r="H105" s="282"/>
-      <c r="I105" s="282"/>
+      <c r="D105" s="304"/>
+      <c r="E105" s="304"/>
+      <c r="F105" s="304"/>
+      <c r="G105" s="304"/>
+      <c r="H105" s="304"/>
+      <c r="I105" s="304"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="12" t="s">
@@ -5372,12 +5404,12 @@
         <v>-406464</v>
       </c>
       <c r="C106" s="13"/>
-      <c r="D106" s="282"/>
-      <c r="E106" s="282"/>
-      <c r="F106" s="282"/>
-      <c r="G106" s="282"/>
-      <c r="H106" s="282"/>
-      <c r="I106" s="282"/>
+      <c r="D106" s="304"/>
+      <c r="E106" s="304"/>
+      <c r="F106" s="304"/>
+      <c r="G106" s="304"/>
+      <c r="H106" s="304"/>
+      <c r="I106" s="304"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
@@ -5388,22 +5420,22 @@
         <v>2575051.7590119969</v>
       </c>
       <c r="C107" s="44"/>
-      <c r="D107" s="282"/>
-      <c r="E107" s="282"/>
-      <c r="F107" s="282"/>
-      <c r="G107" s="282"/>
-      <c r="H107" s="282"/>
-      <c r="I107" s="282"/>
+      <c r="D107" s="304"/>
+      <c r="E107" s="304"/>
+      <c r="F107" s="304"/>
+      <c r="G107" s="304"/>
+      <c r="H107" s="304"/>
+      <c r="I107" s="304"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="13"/>
       <c r="C108" s="9"/>
-      <c r="D108" s="282"/>
-      <c r="E108" s="282"/>
-      <c r="F108" s="282"/>
-      <c r="G108" s="282"/>
-      <c r="H108" s="282"/>
-      <c r="I108" s="282"/>
+      <c r="D108" s="304"/>
+      <c r="E108" s="304"/>
+      <c r="F108" s="304"/>
+      <c r="G108" s="304"/>
+      <c r="H108" s="304"/>
+      <c r="I108" s="304"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
@@ -5411,12 +5443,12 @@
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="9"/>
-      <c r="D109" s="282"/>
-      <c r="E109" s="282"/>
-      <c r="F109" s="282"/>
-      <c r="G109" s="282"/>
-      <c r="H109" s="282"/>
-      <c r="I109" s="282"/>
+      <c r="D109" s="304"/>
+      <c r="E109" s="304"/>
+      <c r="F109" s="304"/>
+      <c r="G109" s="304"/>
+      <c r="H109" s="304"/>
+      <c r="I109" s="304"/>
     </row>
     <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="177"/>
@@ -5456,14 +5488,14 @@
         <v>-25817.72</v>
       </c>
       <c r="C114" s="9"/>
-      <c r="D114" s="303" t="s">
+      <c r="D114" s="325" t="s">
         <v>406</v>
       </c>
-      <c r="E114" s="304"/>
-      <c r="F114" s="304"/>
-      <c r="G114" s="304"/>
-      <c r="H114" s="304"/>
-      <c r="I114" s="305"/>
+      <c r="E114" s="326"/>
+      <c r="F114" s="326"/>
+      <c r="G114" s="326"/>
+      <c r="H114" s="326"/>
+      <c r="I114" s="327"/>
     </row>
     <row r="115" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="179" t="s">
@@ -5473,12 +5505,12 @@
         <v>-24000</v>
       </c>
       <c r="C115" s="9"/>
-      <c r="D115" s="306"/>
-      <c r="E115" s="307"/>
-      <c r="F115" s="307"/>
-      <c r="G115" s="307"/>
-      <c r="H115" s="307"/>
-      <c r="I115" s="308"/>
+      <c r="D115" s="328"/>
+      <c r="E115" s="329"/>
+      <c r="F115" s="329"/>
+      <c r="G115" s="329"/>
+      <c r="H115" s="329"/>
+      <c r="I115" s="330"/>
     </row>
     <row r="116" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="179" t="s">
@@ -5488,12 +5520,12 @@
         <v>-24000</v>
       </c>
       <c r="C116" s="9"/>
-      <c r="D116" s="306"/>
-      <c r="E116" s="307"/>
-      <c r="F116" s="307"/>
-      <c r="G116" s="307"/>
-      <c r="H116" s="307"/>
-      <c r="I116" s="308"/>
+      <c r="D116" s="328"/>
+      <c r="E116" s="329"/>
+      <c r="F116" s="329"/>
+      <c r="G116" s="329"/>
+      <c r="H116" s="329"/>
+      <c r="I116" s="330"/>
     </row>
     <row r="117" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="24" t="s">
@@ -5504,12 +5536,12 @@
         <v>-73817.72</v>
       </c>
       <c r="C117" s="9"/>
-      <c r="D117" s="309"/>
-      <c r="E117" s="310"/>
-      <c r="F117" s="310"/>
-      <c r="G117" s="310"/>
-      <c r="H117" s="310"/>
-      <c r="I117" s="311"/>
+      <c r="D117" s="331"/>
+      <c r="E117" s="332"/>
+      <c r="F117" s="332"/>
+      <c r="G117" s="332"/>
+      <c r="H117" s="332"/>
+      <c r="I117" s="333"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="13"/>
@@ -5536,15 +5568,15 @@
         <v>578840</v>
       </c>
       <c r="C122" s="15"/>
-      <c r="D122" s="283" t="s">
+      <c r="D122" s="305" t="s">
         <v>383</v>
       </c>
-      <c r="E122" s="284"/>
-      <c r="F122" s="284"/>
-      <c r="G122" s="284"/>
-      <c r="H122" s="284"/>
-      <c r="I122" s="284"/>
-      <c r="J122" s="285"/>
+      <c r="E122" s="306"/>
+      <c r="F122" s="306"/>
+      <c r="G122" s="306"/>
+      <c r="H122" s="306"/>
+      <c r="I122" s="306"/>
+      <c r="J122" s="307"/>
     </row>
     <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="10" t="s">
@@ -5554,13 +5586,13 @@
         <v>20000</v>
       </c>
       <c r="C123" s="15"/>
-      <c r="D123" s="286"/>
-      <c r="E123" s="287"/>
-      <c r="F123" s="287"/>
-      <c r="G123" s="287"/>
-      <c r="H123" s="287"/>
-      <c r="I123" s="287"/>
-      <c r="J123" s="288"/>
+      <c r="D123" s="308"/>
+      <c r="E123" s="309"/>
+      <c r="F123" s="309"/>
+      <c r="G123" s="309"/>
+      <c r="H123" s="309"/>
+      <c r="I123" s="309"/>
+      <c r="J123" s="310"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="24" t="s">
@@ -5571,51 +5603,51 @@
         <v>598840</v>
       </c>
       <c r="C124" s="15"/>
-      <c r="D124" s="286"/>
-      <c r="E124" s="287"/>
-      <c r="F124" s="287"/>
-      <c r="G124" s="287"/>
-      <c r="H124" s="287"/>
-      <c r="I124" s="287"/>
-      <c r="J124" s="288"/>
+      <c r="D124" s="308"/>
+      <c r="E124" s="309"/>
+      <c r="F124" s="309"/>
+      <c r="G124" s="309"/>
+      <c r="H124" s="309"/>
+      <c r="I124" s="309"/>
+      <c r="J124" s="310"/>
     </row>
     <row r="125" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C125" s="16"/>
-      <c r="D125" s="286"/>
-      <c r="E125" s="287"/>
-      <c r="F125" s="287"/>
-      <c r="G125" s="287"/>
-      <c r="H125" s="287"/>
-      <c r="I125" s="287"/>
-      <c r="J125" s="288"/>
+      <c r="D125" s="308"/>
+      <c r="E125" s="309"/>
+      <c r="F125" s="309"/>
+      <c r="G125" s="309"/>
+      <c r="H125" s="309"/>
+      <c r="I125" s="309"/>
+      <c r="J125" s="310"/>
     </row>
     <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="292" t="s">
+      <c r="A126" s="314" t="s">
         <v>356</v>
       </c>
-      <c r="B126" s="294">
+      <c r="B126" s="316">
         <f>B124+B107+B117</f>
         <v>3100074.0390119967</v>
       </c>
       <c r="C126" s="9"/>
-      <c r="D126" s="286"/>
-      <c r="E126" s="287"/>
-      <c r="F126" s="287"/>
-      <c r="G126" s="287"/>
-      <c r="H126" s="287"/>
-      <c r="I126" s="287"/>
-      <c r="J126" s="288"/>
+      <c r="D126" s="308"/>
+      <c r="E126" s="309"/>
+      <c r="F126" s="309"/>
+      <c r="G126" s="309"/>
+      <c r="H126" s="309"/>
+      <c r="I126" s="309"/>
+      <c r="J126" s="310"/>
     </row>
     <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="293"/>
-      <c r="B127" s="295"/>
-      <c r="D127" s="289"/>
-      <c r="E127" s="290"/>
-      <c r="F127" s="290"/>
-      <c r="G127" s="290"/>
-      <c r="H127" s="290"/>
-      <c r="I127" s="290"/>
-      <c r="J127" s="291"/>
+      <c r="A127" s="315"/>
+      <c r="B127" s="317"/>
+      <c r="D127" s="311"/>
+      <c r="E127" s="312"/>
+      <c r="F127" s="312"/>
+      <c r="G127" s="312"/>
+      <c r="H127" s="312"/>
+      <c r="I127" s="312"/>
+      <c r="J127" s="313"/>
     </row>
     <row r="132" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C132" s="46"/>
@@ -5707,15 +5739,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A14:J18"/>
-    <mergeCell ref="A20:J22"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A65:B65"/>
     <mergeCell ref="A70:C70"/>
     <mergeCell ref="A88:B88"/>
@@ -5728,6 +5751,15 @@
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="D114:I117"/>
     <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A14:J18"/>
+    <mergeCell ref="A20:J22"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5762,13 +5794,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="354" t="s">
+      <c r="A1" s="366" t="s">
         <v>298</v>
       </c>
-      <c r="B1" s="355"/>
-      <c r="C1" s="355"/>
-      <c r="D1" s="355"/>
-      <c r="E1" s="355"/>
+      <c r="B1" s="367"/>
+      <c r="C1" s="367"/>
+      <c r="D1" s="367"/>
+      <c r="E1" s="367"/>
       <c r="F1" s="103" t="s">
         <v>274</v>
       </c>
@@ -5780,20 +5812,20 @@
       <c r="L1" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="333">
+      <c r="M1" s="342">
         <f>RESUMEN!D79-N4</f>
         <v>26225955.399999999</v>
       </c>
-      <c r="N1" s="334"/>
+      <c r="N1" s="343"/>
       <c r="O1" s="104"/>
       <c r="P1" s="39"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="356"/>
-      <c r="B2" s="357"/>
-      <c r="C2" s="357"/>
-      <c r="D2" s="357"/>
-      <c r="E2" s="357"/>
+      <c r="A2" s="368"/>
+      <c r="B2" s="369"/>
+      <c r="C2" s="369"/>
+      <c r="D2" s="369"/>
+      <c r="E2" s="369"/>
       <c r="F2" s="4" t="s">
         <v>273</v>
       </c>
@@ -5814,11 +5846,11 @@
       <c r="P2" s="39"/>
     </row>
     <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="356"/>
-      <c r="B3" s="357"/>
-      <c r="C3" s="357"/>
-      <c r="D3" s="357"/>
-      <c r="E3" s="357"/>
+      <c r="A3" s="368"/>
+      <c r="B3" s="369"/>
+      <c r="C3" s="369"/>
+      <c r="D3" s="369"/>
+      <c r="E3" s="369"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -5837,11 +5869,11 @@
       <c r="P3" s="39"/>
     </row>
     <row r="4" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="356"/>
-      <c r="B4" s="357"/>
-      <c r="C4" s="357"/>
-      <c r="D4" s="357"/>
-      <c r="E4" s="357"/>
+      <c r="A4" s="368"/>
+      <c r="B4" s="369"/>
+      <c r="C4" s="369"/>
+      <c r="D4" s="369"/>
+      <c r="E4" s="369"/>
       <c r="F4" s="4" t="s">
         <v>275</v>
       </c>
@@ -5861,11 +5893,11 @@
       <c r="P4" s="6"/>
     </row>
     <row r="5" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="358"/>
-      <c r="B5" s="359"/>
-      <c r="C5" s="359"/>
-      <c r="D5" s="359"/>
-      <c r="E5" s="359"/>
+      <c r="A5" s="370"/>
+      <c r="B5" s="371"/>
+      <c r="C5" s="371"/>
+      <c r="D5" s="371"/>
+      <c r="E5" s="371"/>
       <c r="F5" s="108"/>
       <c r="G5" s="108"/>
       <c r="H5" s="108"/>
@@ -5881,95 +5913,95 @@
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="339" t="s">
+      <c r="C6" s="351" t="s">
         <v>368</v>
       </c>
-      <c r="D6" s="340"/>
-      <c r="E6" s="340"/>
-      <c r="F6" s="340"/>
-      <c r="G6" s="340"/>
-      <c r="H6" s="340"/>
-      <c r="I6" s="340"/>
-      <c r="J6" s="340"/>
-      <c r="K6" s="340"/>
-      <c r="L6" s="340"/>
-      <c r="M6" s="340"/>
-      <c r="N6" s="340"/>
-      <c r="O6" s="341"/>
+      <c r="D6" s="352"/>
+      <c r="E6" s="352"/>
+      <c r="F6" s="352"/>
+      <c r="G6" s="352"/>
+      <c r="H6" s="352"/>
+      <c r="I6" s="352"/>
+      <c r="J6" s="352"/>
+      <c r="K6" s="352"/>
+      <c r="L6" s="352"/>
+      <c r="M6" s="352"/>
+      <c r="N6" s="352"/>
+      <c r="O6" s="353"/>
       <c r="P6" s="6"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="342"/>
-      <c r="D7" s="343"/>
-      <c r="E7" s="343"/>
-      <c r="F7" s="343"/>
-      <c r="G7" s="343"/>
-      <c r="H7" s="343"/>
-      <c r="I7" s="343"/>
-      <c r="J7" s="343"/>
-      <c r="K7" s="343"/>
-      <c r="L7" s="343"/>
-      <c r="M7" s="343"/>
-      <c r="N7" s="343"/>
-      <c r="O7" s="344"/>
+      <c r="C7" s="354"/>
+      <c r="D7" s="355"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
+      <c r="G7" s="355"/>
+      <c r="H7" s="355"/>
+      <c r="I7" s="355"/>
+      <c r="J7" s="355"/>
+      <c r="K7" s="355"/>
+      <c r="L7" s="355"/>
+      <c r="M7" s="355"/>
+      <c r="N7" s="355"/>
+      <c r="O7" s="356"/>
       <c r="P7" s="6"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="342"/>
-      <c r="D8" s="343"/>
-      <c r="E8" s="343"/>
-      <c r="F8" s="343"/>
-      <c r="G8" s="343"/>
-      <c r="H8" s="343"/>
-      <c r="I8" s="343"/>
-      <c r="J8" s="343"/>
-      <c r="K8" s="343"/>
-      <c r="L8" s="343"/>
-      <c r="M8" s="343"/>
-      <c r="N8" s="343"/>
-      <c r="O8" s="344"/>
+      <c r="C8" s="354"/>
+      <c r="D8" s="355"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
+      <c r="G8" s="355"/>
+      <c r="H8" s="355"/>
+      <c r="I8" s="355"/>
+      <c r="J8" s="355"/>
+      <c r="K8" s="355"/>
+      <c r="L8" s="355"/>
+      <c r="M8" s="355"/>
+      <c r="N8" s="355"/>
+      <c r="O8" s="356"/>
       <c r="P8" s="6"/>
     </row>
     <row r="9" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="345"/>
-      <c r="D9" s="346"/>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
-      <c r="G9" s="346"/>
-      <c r="H9" s="346"/>
-      <c r="I9" s="346"/>
-      <c r="J9" s="346"/>
-      <c r="K9" s="346"/>
-      <c r="L9" s="346"/>
-      <c r="M9" s="346"/>
-      <c r="N9" s="346"/>
-      <c r="O9" s="347"/>
+      <c r="C9" s="357"/>
+      <c r="D9" s="358"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
+      <c r="G9" s="358"/>
+      <c r="H9" s="358"/>
+      <c r="I9" s="358"/>
+      <c r="J9" s="358"/>
+      <c r="K9" s="358"/>
+      <c r="L9" s="358"/>
+      <c r="M9" s="358"/>
+      <c r="N9" s="358"/>
+      <c r="O9" s="359"/>
       <c r="Q9" s="55"/>
     </row>
     <row r="10" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="348" t="s">
+      <c r="C10" s="360" t="s">
         <v>286</v>
       </c>
-      <c r="D10" s="349"/>
-      <c r="E10" s="349"/>
-      <c r="F10" s="349"/>
-      <c r="G10" s="349"/>
-      <c r="H10" s="349"/>
-      <c r="I10" s="349"/>
-      <c r="J10" s="349"/>
-      <c r="K10" s="349"/>
-      <c r="L10" s="349"/>
-      <c r="M10" s="349"/>
-      <c r="N10" s="349"/>
-      <c r="O10" s="350"/>
+      <c r="D10" s="361"/>
+      <c r="E10" s="361"/>
+      <c r="F10" s="361"/>
+      <c r="G10" s="361"/>
+      <c r="H10" s="361"/>
+      <c r="I10" s="361"/>
+      <c r="J10" s="361"/>
+      <c r="K10" s="361"/>
+      <c r="L10" s="361"/>
+      <c r="M10" s="361"/>
+      <c r="N10" s="361"/>
+      <c r="O10" s="362"/>
       <c r="Q10" t="s">
         <v>233</v>
       </c>
@@ -5981,19 +6013,19 @@
     <row r="11" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="351"/>
-      <c r="D11" s="352"/>
-      <c r="E11" s="352"/>
-      <c r="F11" s="352"/>
-      <c r="G11" s="352"/>
-      <c r="H11" s="352"/>
-      <c r="I11" s="352"/>
-      <c r="J11" s="352"/>
-      <c r="K11" s="352"/>
-      <c r="L11" s="352"/>
-      <c r="M11" s="352"/>
-      <c r="N11" s="352"/>
-      <c r="O11" s="353"/>
+      <c r="C11" s="363"/>
+      <c r="D11" s="364"/>
+      <c r="E11" s="364"/>
+      <c r="F11" s="364"/>
+      <c r="G11" s="364"/>
+      <c r="H11" s="364"/>
+      <c r="I11" s="364"/>
+      <c r="J11" s="364"/>
+      <c r="K11" s="364"/>
+      <c r="L11" s="364"/>
+      <c r="M11" s="364"/>
+      <c r="N11" s="364"/>
+      <c r="O11" s="365"/>
       <c r="Q11" t="s">
         <v>234</v>
       </c>
@@ -6003,49 +6035,49 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="324" t="s">
+      <c r="A12" s="338" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="326" t="s">
+      <c r="B12" s="372" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="324" t="s">
+      <c r="C12" s="338" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="328" t="s">
+      <c r="D12" s="374" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="328" t="s">
+      <c r="E12" s="374" t="s">
         <v>250</v>
       </c>
-      <c r="F12" s="324" t="s">
+      <c r="F12" s="338" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="324" t="s">
+      <c r="G12" s="338" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="324" t="s">
+      <c r="H12" s="338" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="335" t="s">
+      <c r="I12" s="344" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="321" t="s">
+      <c r="J12" s="346" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="321" t="s">
+      <c r="K12" s="346" t="s">
         <v>366</v>
       </c>
-      <c r="L12" s="321" t="s">
+      <c r="L12" s="346" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="337" t="s">
+      <c r="M12" s="349" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="321" t="s">
+      <c r="N12" s="346" t="s">
         <v>260</v>
       </c>
-      <c r="O12" s="321" t="s">
+      <c r="O12" s="346" t="s">
         <v>259</v>
       </c>
       <c r="Q12" t="s">
@@ -6057,21 +6089,21 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="325"/>
-      <c r="B13" s="327"/>
-      <c r="C13" s="325"/>
-      <c r="D13" s="329"/>
-      <c r="E13" s="329"/>
-      <c r="F13" s="325"/>
-      <c r="G13" s="325"/>
-      <c r="H13" s="325"/>
-      <c r="I13" s="336"/>
-      <c r="J13" s="322"/>
-      <c r="K13" s="322"/>
-      <c r="L13" s="322"/>
-      <c r="M13" s="338"/>
-      <c r="N13" s="322"/>
-      <c r="O13" s="322"/>
+      <c r="A13" s="339"/>
+      <c r="B13" s="373"/>
+      <c r="C13" s="339"/>
+      <c r="D13" s="375"/>
+      <c r="E13" s="375"/>
+      <c r="F13" s="339"/>
+      <c r="G13" s="339"/>
+      <c r="H13" s="339"/>
+      <c r="I13" s="345"/>
+      <c r="J13" s="347"/>
+      <c r="K13" s="347"/>
+      <c r="L13" s="347"/>
+      <c r="M13" s="350"/>
+      <c r="N13" s="347"/>
+      <c r="O13" s="347"/>
       <c r="Q13" t="s">
         <v>236</v>
       </c>
@@ -6081,19 +6113,19 @@
       </c>
     </row>
     <row r="14" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="325"/>
-      <c r="B14" s="327"/>
-      <c r="C14" s="325"/>
-      <c r="D14" s="329"/>
-      <c r="E14" s="329"/>
-      <c r="F14" s="325"/>
-      <c r="G14" s="325"/>
-      <c r="H14" s="325"/>
-      <c r="I14" s="336"/>
-      <c r="J14" s="322"/>
-      <c r="K14" s="323"/>
-      <c r="L14" s="323"/>
-      <c r="M14" s="338"/>
+      <c r="A14" s="339"/>
+      <c r="B14" s="373"/>
+      <c r="C14" s="339"/>
+      <c r="D14" s="375"/>
+      <c r="E14" s="375"/>
+      <c r="F14" s="339"/>
+      <c r="G14" s="339"/>
+      <c r="H14" s="339"/>
+      <c r="I14" s="345"/>
+      <c r="J14" s="347"/>
+      <c r="K14" s="348"/>
+      <c r="L14" s="348"/>
+      <c r="M14" s="350"/>
       <c r="N14" s="84" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/09</v>
@@ -6160,16 +6192,16 @@
       <c r="P15" s="70" t="s">
         <v>342</v>
       </c>
-      <c r="R15" s="330"/>
-      <c r="S15" s="330"/>
+      <c r="R15" s="337"/>
+      <c r="S15" s="337"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
-      <c r="C16" s="393" t="s">
+      <c r="C16" s="276" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="394" t="s">
+      <c r="D16" s="277" t="s">
         <v>296</v>
       </c>
       <c r="E16" s="131"/>
@@ -6209,8 +6241,8 @@
       <c r="P16" s="70" t="s">
         <v>341</v>
       </c>
-      <c r="R16" s="330"/>
-      <c r="S16" s="330"/>
+      <c r="R16" s="337"/>
+      <c r="S16" s="337"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
@@ -7437,10 +7469,10 @@
         <v>116</v>
       </c>
       <c r="B40" s="23"/>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="283" t="s">
         <v>60</v>
       </c>
-      <c r="D40" s="64" t="s">
+      <c r="D40" s="284" t="s">
         <v>182</v>
       </c>
       <c r="E40" s="87"/>
@@ -12339,10 +12371,10 @@
     <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="80"/>
       <c r="B125" s="23"/>
-      <c r="C125" s="23" t="s">
+      <c r="C125" s="290" t="s">
         <v>156</v>
       </c>
-      <c r="D125" s="64" t="s">
+      <c r="D125" s="291" t="s">
         <v>177</v>
       </c>
       <c r="E125" s="64"/>
@@ -12829,34 +12861,34 @@
       </c>
     </row>
     <row r="136" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="332"/>
-      <c r="D136" s="332"/>
-      <c r="E136" s="332"/>
-      <c r="F136" s="332"/>
-      <c r="G136" s="332"/>
-      <c r="H136" s="332"/>
-      <c r="I136" s="332"/>
-      <c r="J136" s="332"/>
-      <c r="K136" s="332"/>
-      <c r="L136" s="332"/>
-      <c r="M136" s="332"/>
-      <c r="N136" s="332"/>
-      <c r="O136" s="332"/>
+      <c r="C136" s="341"/>
+      <c r="D136" s="341"/>
+      <c r="E136" s="341"/>
+      <c r="F136" s="341"/>
+      <c r="G136" s="341"/>
+      <c r="H136" s="341"/>
+      <c r="I136" s="341"/>
+      <c r="J136" s="341"/>
+      <c r="K136" s="341"/>
+      <c r="L136" s="341"/>
+      <c r="M136" s="341"/>
+      <c r="N136" s="341"/>
+      <c r="O136" s="341"/>
     </row>
     <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C137" s="332"/>
-      <c r="D137" s="332"/>
-      <c r="E137" s="332"/>
-      <c r="F137" s="332"/>
-      <c r="G137" s="332"/>
-      <c r="H137" s="332"/>
-      <c r="I137" s="332"/>
-      <c r="J137" s="332"/>
-      <c r="K137" s="332"/>
-      <c r="L137" s="332"/>
-      <c r="M137" s="332"/>
-      <c r="N137" s="332"/>
-      <c r="O137" s="332"/>
+      <c r="C137" s="341"/>
+      <c r="D137" s="341"/>
+      <c r="E137" s="341"/>
+      <c r="F137" s="341"/>
+      <c r="G137" s="341"/>
+      <c r="H137" s="341"/>
+      <c r="I137" s="341"/>
+      <c r="J137" s="341"/>
+      <c r="K137" s="341"/>
+      <c r="L137" s="341"/>
+      <c r="M137" s="341"/>
+      <c r="N137" s="341"/>
+      <c r="O137" s="341"/>
     </row>
     <row r="138" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C138" s="49"/>
@@ -12874,126 +12906,126 @@
       <c r="O138" s="49"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C139" s="282" t="s">
+      <c r="C139" s="304" t="s">
         <v>243</v>
       </c>
-      <c r="D139" s="282"/>
-      <c r="E139" s="282"/>
-      <c r="F139" s="282"/>
-      <c r="G139" s="282"/>
-      <c r="H139" s="282"/>
-      <c r="I139" s="282"/>
-      <c r="J139" s="282"/>
-      <c r="K139" s="282"/>
-      <c r="L139" s="282"/>
-      <c r="M139" s="282"/>
-      <c r="N139" s="282"/>
-      <c r="O139" s="282"/>
+      <c r="D139" s="304"/>
+      <c r="E139" s="304"/>
+      <c r="F139" s="304"/>
+      <c r="G139" s="304"/>
+      <c r="H139" s="304"/>
+      <c r="I139" s="304"/>
+      <c r="J139" s="304"/>
+      <c r="K139" s="304"/>
+      <c r="L139" s="304"/>
+      <c r="M139" s="304"/>
+      <c r="N139" s="304"/>
+      <c r="O139" s="304"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C140" s="282"/>
-      <c r="D140" s="282"/>
-      <c r="E140" s="282"/>
-      <c r="F140" s="282"/>
-      <c r="G140" s="282"/>
-      <c r="H140" s="282"/>
-      <c r="I140" s="282"/>
-      <c r="J140" s="282"/>
-      <c r="K140" s="282"/>
-      <c r="L140" s="282"/>
-      <c r="M140" s="282"/>
-      <c r="N140" s="282"/>
-      <c r="O140" s="282"/>
+      <c r="C140" s="304"/>
+      <c r="D140" s="304"/>
+      <c r="E140" s="304"/>
+      <c r="F140" s="304"/>
+      <c r="G140" s="304"/>
+      <c r="H140" s="304"/>
+      <c r="I140" s="304"/>
+      <c r="J140" s="304"/>
+      <c r="K140" s="304"/>
+      <c r="L140" s="304"/>
+      <c r="M140" s="304"/>
+      <c r="N140" s="304"/>
+      <c r="O140" s="304"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C141" s="282"/>
-      <c r="D141" s="282"/>
-      <c r="E141" s="282"/>
-      <c r="F141" s="282"/>
-      <c r="G141" s="282"/>
-      <c r="H141" s="282"/>
-      <c r="I141" s="282"/>
-      <c r="J141" s="282"/>
-      <c r="K141" s="282"/>
-      <c r="L141" s="282"/>
-      <c r="M141" s="282"/>
-      <c r="N141" s="282"/>
-      <c r="O141" s="282"/>
+      <c r="C141" s="304"/>
+      <c r="D141" s="304"/>
+      <c r="E141" s="304"/>
+      <c r="F141" s="304"/>
+      <c r="G141" s="304"/>
+      <c r="H141" s="304"/>
+      <c r="I141" s="304"/>
+      <c r="J141" s="304"/>
+      <c r="K141" s="304"/>
+      <c r="L141" s="304"/>
+      <c r="M141" s="304"/>
+      <c r="N141" s="304"/>
+      <c r="O141" s="304"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C142" s="282"/>
-      <c r="D142" s="282"/>
-      <c r="E142" s="282"/>
-      <c r="F142" s="282"/>
-      <c r="G142" s="282"/>
-      <c r="H142" s="282"/>
-      <c r="I142" s="282"/>
-      <c r="J142" s="282"/>
-      <c r="K142" s="282"/>
-      <c r="L142" s="282"/>
-      <c r="M142" s="282"/>
-      <c r="N142" s="282"/>
-      <c r="O142" s="282"/>
+      <c r="C142" s="304"/>
+      <c r="D142" s="304"/>
+      <c r="E142" s="304"/>
+      <c r="F142" s="304"/>
+      <c r="G142" s="304"/>
+      <c r="H142" s="304"/>
+      <c r="I142" s="304"/>
+      <c r="J142" s="304"/>
+      <c r="K142" s="304"/>
+      <c r="L142" s="304"/>
+      <c r="M142" s="304"/>
+      <c r="N142" s="304"/>
+      <c r="O142" s="304"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C143" s="282"/>
-      <c r="D143" s="282"/>
-      <c r="E143" s="282"/>
-      <c r="F143" s="282"/>
-      <c r="G143" s="282"/>
-      <c r="H143" s="282"/>
-      <c r="I143" s="282"/>
-      <c r="J143" s="282"/>
-      <c r="K143" s="282"/>
-      <c r="L143" s="282"/>
-      <c r="M143" s="282"/>
-      <c r="N143" s="282"/>
-      <c r="O143" s="282"/>
+      <c r="C143" s="304"/>
+      <c r="D143" s="304"/>
+      <c r="E143" s="304"/>
+      <c r="F143" s="304"/>
+      <c r="G143" s="304"/>
+      <c r="H143" s="304"/>
+      <c r="I143" s="304"/>
+      <c r="J143" s="304"/>
+      <c r="K143" s="304"/>
+      <c r="L143" s="304"/>
+      <c r="M143" s="304"/>
+      <c r="N143" s="304"/>
+      <c r="O143" s="304"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C144" s="282"/>
-      <c r="D144" s="282"/>
-      <c r="E144" s="282"/>
-      <c r="F144" s="282"/>
-      <c r="G144" s="282"/>
-      <c r="H144" s="282"/>
-      <c r="I144" s="282"/>
-      <c r="J144" s="282"/>
-      <c r="K144" s="282"/>
-      <c r="L144" s="282"/>
-      <c r="M144" s="282"/>
-      <c r="N144" s="282"/>
-      <c r="O144" s="282"/>
+      <c r="C144" s="304"/>
+      <c r="D144" s="304"/>
+      <c r="E144" s="304"/>
+      <c r="F144" s="304"/>
+      <c r="G144" s="304"/>
+      <c r="H144" s="304"/>
+      <c r="I144" s="304"/>
+      <c r="J144" s="304"/>
+      <c r="K144" s="304"/>
+      <c r="L144" s="304"/>
+      <c r="M144" s="304"/>
+      <c r="N144" s="304"/>
+      <c r="O144" s="304"/>
     </row>
     <row r="145" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C145" s="282"/>
-      <c r="D145" s="282"/>
-      <c r="E145" s="282"/>
-      <c r="F145" s="282"/>
-      <c r="G145" s="282"/>
-      <c r="H145" s="282"/>
-      <c r="I145" s="282"/>
-      <c r="J145" s="282"/>
-      <c r="K145" s="282"/>
-      <c r="L145" s="282"/>
-      <c r="M145" s="282"/>
-      <c r="N145" s="282"/>
-      <c r="O145" s="282"/>
+      <c r="C145" s="304"/>
+      <c r="D145" s="304"/>
+      <c r="E145" s="304"/>
+      <c r="F145" s="304"/>
+      <c r="G145" s="304"/>
+      <c r="H145" s="304"/>
+      <c r="I145" s="304"/>
+      <c r="J145" s="304"/>
+      <c r="K145" s="304"/>
+      <c r="L145" s="304"/>
+      <c r="M145" s="304"/>
+      <c r="N145" s="304"/>
+      <c r="O145" s="304"/>
     </row>
     <row r="146" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C146" s="282"/>
-      <c r="D146" s="282"/>
-      <c r="E146" s="282"/>
-      <c r="F146" s="282"/>
-      <c r="G146" s="282"/>
-      <c r="H146" s="282"/>
-      <c r="I146" s="282"/>
-      <c r="J146" s="282"/>
-      <c r="K146" s="282"/>
-      <c r="L146" s="282"/>
-      <c r="M146" s="282"/>
-      <c r="N146" s="282"/>
-      <c r="O146" s="282"/>
+      <c r="C146" s="304"/>
+      <c r="D146" s="304"/>
+      <c r="E146" s="304"/>
+      <c r="F146" s="304"/>
+      <c r="G146" s="304"/>
+      <c r="H146" s="304"/>
+      <c r="I146" s="304"/>
+      <c r="J146" s="304"/>
+      <c r="K146" s="304"/>
+      <c r="L146" s="304"/>
+      <c r="M146" s="304"/>
+      <c r="N146" s="304"/>
+      <c r="O146" s="304"/>
     </row>
     <row r="147" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="49"/>
@@ -13026,118 +13058,125 @@
       <c r="O148" s="49"/>
     </row>
     <row r="149" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C149" s="331" t="s">
+      <c r="C149" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="D149" s="331"/>
-      <c r="E149" s="331"/>
-      <c r="F149" s="331"/>
-      <c r="G149" s="331"/>
-      <c r="H149" s="331"/>
-      <c r="I149" s="331"/>
-      <c r="J149" s="331"/>
-      <c r="K149" s="331"/>
-      <c r="L149" s="331"/>
-      <c r="M149" s="331"/>
-      <c r="N149" s="331"/>
-      <c r="O149" s="331"/>
+      <c r="D149" s="340"/>
+      <c r="E149" s="340"/>
+      <c r="F149" s="340"/>
+      <c r="G149" s="340"/>
+      <c r="H149" s="340"/>
+      <c r="I149" s="340"/>
+      <c r="J149" s="340"/>
+      <c r="K149" s="340"/>
+      <c r="L149" s="340"/>
+      <c r="M149" s="340"/>
+      <c r="N149" s="340"/>
+      <c r="O149" s="340"/>
     </row>
     <row r="150" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C150" s="331"/>
-      <c r="D150" s="331"/>
-      <c r="E150" s="331"/>
-      <c r="F150" s="331"/>
-      <c r="G150" s="331"/>
-      <c r="H150" s="331"/>
-      <c r="I150" s="331"/>
-      <c r="J150" s="331"/>
-      <c r="K150" s="331"/>
-      <c r="L150" s="331"/>
-      <c r="M150" s="331"/>
-      <c r="N150" s="331"/>
-      <c r="O150" s="331"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
+      <c r="G150" s="340"/>
+      <c r="H150" s="340"/>
+      <c r="I150" s="340"/>
+      <c r="J150" s="340"/>
+      <c r="K150" s="340"/>
+      <c r="L150" s="340"/>
+      <c r="M150" s="340"/>
+      <c r="N150" s="340"/>
+      <c r="O150" s="340"/>
     </row>
     <row r="151" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="C151" s="331"/>
-      <c r="D151" s="331"/>
-      <c r="E151" s="331"/>
-      <c r="F151" s="331"/>
-      <c r="G151" s="331"/>
-      <c r="H151" s="331"/>
-      <c r="I151" s="331"/>
-      <c r="J151" s="331"/>
-      <c r="K151" s="331"/>
-      <c r="L151" s="331"/>
-      <c r="M151" s="331"/>
-      <c r="N151" s="331"/>
-      <c r="O151" s="331"/>
+      <c r="C151" s="340"/>
+      <c r="D151" s="340"/>
+      <c r="E151" s="340"/>
+      <c r="F151" s="340"/>
+      <c r="G151" s="340"/>
+      <c r="H151" s="340"/>
+      <c r="I151" s="340"/>
+      <c r="J151" s="340"/>
+      <c r="K151" s="340"/>
+      <c r="L151" s="340"/>
+      <c r="M151" s="340"/>
+      <c r="N151" s="340"/>
+      <c r="O151" s="340"/>
       <c r="Q151" s="55">
         <f>M1-L134</f>
         <v>150436.23675993457</v>
       </c>
     </row>
     <row r="152" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="331"/>
-      <c r="D152" s="331"/>
-      <c r="E152" s="331"/>
-      <c r="F152" s="331"/>
-      <c r="G152" s="331"/>
-      <c r="H152" s="331"/>
-      <c r="I152" s="331"/>
-      <c r="J152" s="331"/>
-      <c r="K152" s="331"/>
-      <c r="L152" s="331"/>
-      <c r="M152" s="331"/>
-      <c r="N152" s="331"/>
-      <c r="O152" s="331"/>
+      <c r="C152" s="340"/>
+      <c r="D152" s="340"/>
+      <c r="E152" s="340"/>
+      <c r="F152" s="340"/>
+      <c r="G152" s="340"/>
+      <c r="H152" s="340"/>
+      <c r="I152" s="340"/>
+      <c r="J152" s="340"/>
+      <c r="K152" s="340"/>
+      <c r="L152" s="340"/>
+      <c r="M152" s="340"/>
+      <c r="N152" s="340"/>
+      <c r="O152" s="340"/>
     </row>
     <row r="153" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="331"/>
-      <c r="D153" s="331"/>
-      <c r="E153" s="331"/>
-      <c r="F153" s="331"/>
-      <c r="G153" s="331"/>
-      <c r="H153" s="331"/>
-      <c r="I153" s="331"/>
-      <c r="J153" s="331"/>
-      <c r="K153" s="331"/>
-      <c r="L153" s="331"/>
-      <c r="M153" s="331"/>
-      <c r="N153" s="331"/>
-      <c r="O153" s="331"/>
+      <c r="C153" s="340"/>
+      <c r="D153" s="340"/>
+      <c r="E153" s="340"/>
+      <c r="F153" s="340"/>
+      <c r="G153" s="340"/>
+      <c r="H153" s="340"/>
+      <c r="I153" s="340"/>
+      <c r="J153" s="340"/>
+      <c r="K153" s="340"/>
+      <c r="L153" s="340"/>
+      <c r="M153" s="340"/>
+      <c r="N153" s="340"/>
+      <c r="O153" s="340"/>
     </row>
     <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="331"/>
-      <c r="D154" s="331"/>
-      <c r="E154" s="331"/>
-      <c r="F154" s="331"/>
-      <c r="G154" s="331"/>
-      <c r="H154" s="331"/>
-      <c r="I154" s="331"/>
-      <c r="J154" s="331"/>
-      <c r="K154" s="331"/>
-      <c r="L154" s="331"/>
-      <c r="M154" s="331"/>
-      <c r="N154" s="331"/>
-      <c r="O154" s="331"/>
+      <c r="C154" s="340"/>
+      <c r="D154" s="340"/>
+      <c r="E154" s="340"/>
+      <c r="F154" s="340"/>
+      <c r="G154" s="340"/>
+      <c r="H154" s="340"/>
+      <c r="I154" s="340"/>
+      <c r="J154" s="340"/>
+      <c r="K154" s="340"/>
+      <c r="L154" s="340"/>
+      <c r="M154" s="340"/>
+      <c r="N154" s="340"/>
+      <c r="O154" s="340"/>
     </row>
     <row r="155" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C155" s="331"/>
-      <c r="D155" s="331"/>
-      <c r="E155" s="331"/>
-      <c r="F155" s="331"/>
-      <c r="G155" s="331"/>
-      <c r="H155" s="331"/>
-      <c r="I155" s="331"/>
-      <c r="J155" s="331"/>
-      <c r="K155" s="331"/>
-      <c r="L155" s="331"/>
-      <c r="M155" s="331"/>
-      <c r="N155" s="331"/>
-      <c r="O155" s="331"/>
+      <c r="C155" s="340"/>
+      <c r="D155" s="340"/>
+      <c r="E155" s="340"/>
+      <c r="F155" s="340"/>
+      <c r="G155" s="340"/>
+      <c r="H155" s="340"/>
+      <c r="I155" s="340"/>
+      <c r="J155" s="340"/>
+      <c r="K155" s="340"/>
+      <c r="L155" s="340"/>
+      <c r="M155" s="340"/>
+      <c r="N155" s="340"/>
+      <c r="O155" s="340"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="R15:S16"/>
     <mergeCell ref="G12:G14"/>
     <mergeCell ref="C149:O155"/>
@@ -13154,13 +13193,6 @@
     <mergeCell ref="C6:O9"/>
     <mergeCell ref="C10:O11"/>
     <mergeCell ref="A1:E5"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="E12:E14"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13194,61 +13226,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="371" t="s">
+      <c r="A1" s="383" t="s">
         <v>300</v>
       </c>
-      <c r="B1" s="371"/>
-      <c r="C1" s="371"/>
-      <c r="D1" s="371"/>
-      <c r="E1" s="371"/>
-      <c r="F1" s="371"/>
-      <c r="G1" s="371"/>
-      <c r="H1" s="371"/>
-      <c r="I1" s="371"/>
-      <c r="J1" s="371"/>
-      <c r="K1" s="371"/>
-      <c r="L1" s="371"/>
-      <c r="M1" s="371"/>
-      <c r="N1" s="371"/>
-      <c r="O1" s="372"/>
+      <c r="B1" s="383"/>
+      <c r="C1" s="383"/>
+      <c r="D1" s="383"/>
+      <c r="E1" s="383"/>
+      <c r="F1" s="383"/>
+      <c r="G1" s="383"/>
+      <c r="H1" s="383"/>
+      <c r="I1" s="383"/>
+      <c r="J1" s="383"/>
+      <c r="K1" s="383"/>
+      <c r="L1" s="383"/>
+      <c r="M1" s="383"/>
+      <c r="N1" s="383"/>
+      <c r="O1" s="384"/>
       <c r="R1" s="31"/>
     </row>
     <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="373"/>
-      <c r="B2" s="373"/>
-      <c r="C2" s="373"/>
-      <c r="D2" s="373"/>
-      <c r="E2" s="373"/>
-      <c r="F2" s="373"/>
-      <c r="G2" s="373"/>
-      <c r="H2" s="373"/>
-      <c r="I2" s="373"/>
-      <c r="J2" s="373"/>
-      <c r="K2" s="373"/>
-      <c r="L2" s="373"/>
-      <c r="M2" s="373"/>
-      <c r="N2" s="373"/>
-      <c r="O2" s="374"/>
+      <c r="A2" s="385"/>
+      <c r="B2" s="385"/>
+      <c r="C2" s="385"/>
+      <c r="D2" s="385"/>
+      <c r="E2" s="385"/>
+      <c r="F2" s="385"/>
+      <c r="G2" s="385"/>
+      <c r="H2" s="385"/>
+      <c r="I2" s="385"/>
+      <c r="J2" s="385"/>
+      <c r="K2" s="385"/>
+      <c r="L2" s="385"/>
+      <c r="M2" s="385"/>
+      <c r="N2" s="385"/>
+      <c r="O2" s="386"/>
       <c r="R2" s="31"/>
     </row>
     <row r="3" spans="1:27" s="166" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="368" t="s">
+      <c r="A3" s="380" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="369"/>
-      <c r="C3" s="369"/>
-      <c r="D3" s="369"/>
-      <c r="E3" s="369"/>
-      <c r="F3" s="369"/>
-      <c r="G3" s="369"/>
-      <c r="H3" s="369"/>
-      <c r="I3" s="369"/>
-      <c r="J3" s="369"/>
-      <c r="K3" s="369"/>
-      <c r="L3" s="369"/>
-      <c r="M3" s="369"/>
-      <c r="N3" s="369"/>
-      <c r="O3" s="370"/>
+      <c r="B3" s="381"/>
+      <c r="C3" s="381"/>
+      <c r="D3" s="381"/>
+      <c r="E3" s="381"/>
+      <c r="F3" s="381"/>
+      <c r="G3" s="381"/>
+      <c r="H3" s="381"/>
+      <c r="I3" s="381"/>
+      <c r="J3" s="381"/>
+      <c r="K3" s="381"/>
+      <c r="L3" s="381"/>
+      <c r="M3" s="381"/>
+      <c r="N3" s="381"/>
+      <c r="O3" s="382"/>
       <c r="P3" s="167"/>
       <c r="Q3" s="167"/>
       <c r="R3" s="167"/>
@@ -13263,85 +13295,85 @@
       <c r="AA3" s="167"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="324" t="s">
+      <c r="A4" s="338" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="324" t="s">
+      <c r="B4" s="338" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="324" t="s">
+      <c r="C4" s="338" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="324" t="s">
+      <c r="D4" s="338" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="321" t="s">
+      <c r="E4" s="346" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="321" t="s">
+      <c r="F4" s="346" t="s">
         <v>327</v>
       </c>
-      <c r="G4" s="321" t="s">
+      <c r="G4" s="346" t="s">
         <v>260</v>
       </c>
-      <c r="H4" s="321" t="s">
+      <c r="H4" s="346" t="s">
         <v>332</v>
       </c>
-      <c r="I4" s="321" t="s">
+      <c r="I4" s="346" t="s">
         <v>339</v>
       </c>
-      <c r="J4" s="360" t="s">
+      <c r="J4" s="387" t="s">
         <v>328</v>
       </c>
       <c r="K4" s="83"/>
-      <c r="L4" s="365" t="s">
+      <c r="L4" s="376" t="s">
         <v>336</v>
       </c>
-      <c r="M4" s="321" t="s">
+      <c r="M4" s="346" t="s">
         <v>337</v>
       </c>
-      <c r="N4" s="321" t="s">
+      <c r="N4" s="346" t="s">
         <v>329</v>
       </c>
-      <c r="O4" s="321" t="s">
+      <c r="O4" s="346" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="31"/>
     </row>
     <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="325"/>
-      <c r="B5" s="325"/>
-      <c r="C5" s="325"/>
-      <c r="D5" s="325"/>
-      <c r="E5" s="322"/>
-      <c r="F5" s="322"/>
-      <c r="G5" s="322"/>
-      <c r="H5" s="322"/>
-      <c r="I5" s="322"/>
-      <c r="J5" s="361"/>
+      <c r="A5" s="339"/>
+      <c r="B5" s="339"/>
+      <c r="C5" s="339"/>
+      <c r="D5" s="339"/>
+      <c r="E5" s="347"/>
+      <c r="F5" s="347"/>
+      <c r="G5" s="347"/>
+      <c r="H5" s="347"/>
+      <c r="I5" s="347"/>
+      <c r="J5" s="388"/>
       <c r="K5" s="83"/>
-      <c r="L5" s="366"/>
-      <c r="M5" s="322"/>
-      <c r="N5" s="322"/>
-      <c r="O5" s="322"/>
+      <c r="L5" s="377"/>
+      <c r="M5" s="347"/>
+      <c r="N5" s="347"/>
+      <c r="O5" s="347"/>
       <c r="R5" s="31"/>
     </row>
     <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="364"/>
-      <c r="B6" s="364"/>
-      <c r="C6" s="364"/>
-      <c r="D6" s="364"/>
-      <c r="E6" s="363"/>
-      <c r="F6" s="363"/>
-      <c r="G6" s="363"/>
-      <c r="H6" s="363"/>
-      <c r="I6" s="363"/>
-      <c r="J6" s="362"/>
+      <c r="A6" s="390"/>
+      <c r="B6" s="390"/>
+      <c r="C6" s="390"/>
+      <c r="D6" s="390"/>
+      <c r="E6" s="379"/>
+      <c r="F6" s="379"/>
+      <c r="G6" s="379"/>
+      <c r="H6" s="379"/>
+      <c r="I6" s="379"/>
+      <c r="J6" s="389"/>
       <c r="K6" s="136"/>
-      <c r="L6" s="367"/>
-      <c r="M6" s="363"/>
-      <c r="N6" s="363"/>
-      <c r="O6" s="363"/>
+      <c r="L6" s="378"/>
+      <c r="M6" s="379"/>
+      <c r="N6" s="379"/>
+      <c r="O6" s="379"/>
       <c r="R6" s="31"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
@@ -13396,8 +13428,8 @@
       <c r="P7" s="70">
         <v>0.7</v>
       </c>
-      <c r="R7" s="330"/>
-      <c r="S7" s="330"/>
+      <c r="R7" s="337"/>
+      <c r="S7" s="337"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="137" t="s">
@@ -13453,8 +13485,8 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="330"/>
-      <c r="S8" s="330"/>
+      <c r="R8" s="337"/>
+      <c r="S8" s="337"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="137" t="s">
@@ -17903,6 +17935,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="I4:I6"/>
+    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M4:M6"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A1:O2"/>
     <mergeCell ref="R7:S8"/>
@@ -17917,9 +17952,6 @@
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="H4:H6"/>
-    <mergeCell ref="I4:I6"/>
-    <mergeCell ref="L4:L6"/>
-    <mergeCell ref="M4:M6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="85" orientation="landscape" r:id="rId1"/>
@@ -17928,7 +17960,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
-  <dimension ref="C1:M8"/>
+  <dimension ref="C1:M26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -18011,49 +18043,241 @@
       <c r="M5" s="247"/>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C6" s="384" t="s">
+      <c r="C6" s="391" t="s">
         <v>418</v>
       </c>
-      <c r="D6" s="385"/>
-      <c r="E6" s="385"/>
-      <c r="F6" s="385"/>
-      <c r="G6" s="385"/>
-      <c r="H6" s="385"/>
-      <c r="I6" s="385"/>
-      <c r="J6" s="386"/>
+      <c r="D6" s="392"/>
+      <c r="E6" s="392"/>
+      <c r="F6" s="392"/>
+      <c r="G6" s="392"/>
+      <c r="H6" s="392"/>
+      <c r="I6" s="392"/>
+      <c r="J6" s="393"/>
       <c r="K6" s="46"/>
       <c r="L6" s="46"/>
       <c r="M6" s="46"/>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C7" s="387"/>
-      <c r="D7" s="388"/>
-      <c r="E7" s="388"/>
-      <c r="F7" s="388"/>
-      <c r="G7" s="388"/>
-      <c r="H7" s="388"/>
-      <c r="I7" s="388"/>
-      <c r="J7" s="389"/>
+      <c r="C7" s="394"/>
+      <c r="D7" s="395"/>
+      <c r="E7" s="395"/>
+      <c r="F7" s="395"/>
+      <c r="G7" s="395"/>
+      <c r="H7" s="395"/>
+      <c r="I7" s="395"/>
+      <c r="J7" s="396"/>
       <c r="K7" s="46"/>
       <c r="L7" s="46"/>
       <c r="M7" s="46"/>
     </row>
     <row r="8" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="390"/>
-      <c r="D8" s="391"/>
-      <c r="E8" s="391"/>
-      <c r="F8" s="391"/>
-      <c r="G8" s="391"/>
-      <c r="H8" s="391"/>
-      <c r="I8" s="391"/>
-      <c r="J8" s="392"/>
+      <c r="C8" s="397"/>
+      <c r="D8" s="398"/>
+      <c r="E8" s="398"/>
+      <c r="F8" s="398"/>
+      <c r="G8" s="398"/>
+      <c r="H8" s="398"/>
+      <c r="I8" s="398"/>
+      <c r="J8" s="399"/>
       <c r="K8" s="46"/>
       <c r="L8" s="46"/>
       <c r="M8" s="46"/>
     </row>
+    <row r="10" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C11" s="278" t="s">
+        <v>343</v>
+      </c>
+      <c r="D11" s="279">
+        <v>1</v>
+      </c>
+      <c r="E11" s="279"/>
+      <c r="F11" s="170"/>
+      <c r="G11" s="170"/>
+      <c r="H11" s="170"/>
+      <c r="I11" s="170"/>
+      <c r="J11" s="171"/>
+    </row>
+    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C12" s="280" t="s">
+        <v>344</v>
+      </c>
+      <c r="D12" s="281"/>
+      <c r="E12" s="282">
+        <v>0</v>
+      </c>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="H12" s="172"/>
+      <c r="I12" s="173"/>
+      <c r="J12" s="174"/>
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C13" s="280" t="s">
+        <v>346</v>
+      </c>
+      <c r="D13" s="281" t="s">
+        <v>347</v>
+      </c>
+      <c r="E13" s="281" t="s">
+        <v>348</v>
+      </c>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="H13" s="46" t="s">
+        <v>420</v>
+      </c>
+      <c r="I13" s="173"/>
+      <c r="J13" s="174"/>
+    </row>
+    <row r="14" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="168" t="s">
+        <v>350</v>
+      </c>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="175"/>
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C15" s="391" t="s">
+        <v>419</v>
+      </c>
+      <c r="D15" s="392"/>
+      <c r="E15" s="392"/>
+      <c r="F15" s="392"/>
+      <c r="G15" s="392"/>
+      <c r="H15" s="392"/>
+      <c r="I15" s="392"/>
+      <c r="J15" s="393"/>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C16" s="394"/>
+      <c r="D16" s="395"/>
+      <c r="E16" s="395"/>
+      <c r="F16" s="395"/>
+      <c r="G16" s="395"/>
+      <c r="H16" s="395"/>
+      <c r="I16" s="395"/>
+      <c r="J16" s="396"/>
+    </row>
+    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="397"/>
+      <c r="D17" s="398"/>
+      <c r="E17" s="398"/>
+      <c r="F17" s="398"/>
+      <c r="G17" s="398"/>
+      <c r="H17" s="398"/>
+      <c r="I17" s="398"/>
+      <c r="J17" s="399"/>
+    </row>
+    <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="285" t="s">
+        <v>343</v>
+      </c>
+      <c r="D20" s="286">
+        <v>1</v>
+      </c>
+      <c r="E20" s="286"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
+      <c r="I20" s="170"/>
+      <c r="J20" s="171"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="287" t="s">
+        <v>344</v>
+      </c>
+      <c r="D21" s="288"/>
+      <c r="E21" s="289">
+        <v>0</v>
+      </c>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="H21" s="172" t="s">
+        <v>421</v>
+      </c>
+      <c r="I21" s="173"/>
+      <c r="J21" s="174"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="287" t="s">
+        <v>346</v>
+      </c>
+      <c r="D22" s="288" t="s">
+        <v>347</v>
+      </c>
+      <c r="E22" s="288" t="s">
+        <v>348</v>
+      </c>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="H22" s="46"/>
+      <c r="I22" s="173"/>
+      <c r="J22" s="174"/>
+    </row>
+    <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="168" t="s">
+        <v>350</v>
+      </c>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="175"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="391" t="s">
+        <v>422</v>
+      </c>
+      <c r="D24" s="392"/>
+      <c r="E24" s="392"/>
+      <c r="F24" s="392"/>
+      <c r="G24" s="392"/>
+      <c r="H24" s="392"/>
+      <c r="I24" s="392"/>
+      <c r="J24" s="393"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="394"/>
+      <c r="D25" s="395"/>
+      <c r="E25" s="395"/>
+      <c r="F25" s="395"/>
+      <c r="G25" s="395"/>
+      <c r="H25" s="395"/>
+      <c r="I25" s="395"/>
+      <c r="J25" s="396"/>
+    </row>
+    <row r="26" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C26" s="397"/>
+      <c r="D26" s="398"/>
+      <c r="E26" s="398"/>
+      <c r="F26" s="398"/>
+      <c r="G26" s="398"/>
+      <c r="H26" s="398"/>
+      <c r="I26" s="398"/>
+      <c r="J26" s="399"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="C6:J8"/>
+    <mergeCell ref="C15:J17"/>
+    <mergeCell ref="C24:J26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18069,14 +18293,14 @@
   <sheetData>
     <row r="2" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="381" t="s">
+      <c r="C3" s="406" t="s">
         <v>409</v>
       </c>
-      <c r="D3" s="382"/>
-      <c r="E3" s="382"/>
-      <c r="F3" s="382"/>
-      <c r="G3" s="382"/>
-      <c r="H3" s="383"/>
+      <c r="D3" s="407"/>
+      <c r="E3" s="407"/>
+      <c r="F3" s="407"/>
+      <c r="G3" s="407"/>
+      <c r="H3" s="408"/>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" s="267" t="s">
@@ -18101,11 +18325,11 @@
         <f>PRORRATEO!D31</f>
         <v>Ayala, Roberto Adrian</v>
       </c>
-      <c r="G5" s="375">
+      <c r="G5" s="400">
         <f>PRORRATEO!N31</f>
         <v>2143819.12</v>
       </c>
-      <c r="H5" s="376"/>
+      <c r="H5" s="401"/>
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C6" s="270"/>
@@ -18123,10 +18347,10 @@
       <c r="D8" s="273"/>
       <c r="E8" s="273"/>
       <c r="F8" s="273"/>
-      <c r="G8" s="377">
-        <v>0</v>
-      </c>
-      <c r="H8" s="378"/>
+      <c r="G8" s="402">
+        <v>0</v>
+      </c>
+      <c r="H8" s="403"/>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C9" s="267" t="s">
@@ -18151,11 +18375,11 @@
         <f>PRORRATEO!D37</f>
         <v>Ayala, Roberto Adrian</v>
       </c>
-      <c r="G10" s="375">
+      <c r="G10" s="400">
         <f>PRORRATEO!N37</f>
         <v>1626068.18</v>
       </c>
-      <c r="H10" s="376"/>
+      <c r="H10" s="401"/>
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C11" s="270"/>
@@ -18173,10 +18397,10 @@
       <c r="D13" s="273"/>
       <c r="E13" s="273"/>
       <c r="F13" s="273"/>
-      <c r="G13" s="377">
-        <v>0</v>
-      </c>
-      <c r="H13" s="378"/>
+      <c r="G13" s="402">
+        <v>0</v>
+      </c>
+      <c r="H13" s="403"/>
     </row>
     <row r="14" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C14" s="267" t="s">
@@ -18201,11 +18425,11 @@
         <f>PRORRATEO!D43</f>
         <v>Ayala, Agustin</v>
       </c>
-      <c r="G15" s="375">
+      <c r="G15" s="400">
         <f>PRORRATEO!N43</f>
         <v>1371288.24</v>
       </c>
-      <c r="H15" s="376"/>
+      <c r="H15" s="401"/>
     </row>
     <row r="16" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C16" s="270"/>
@@ -18223,10 +18447,10 @@
       <c r="D18" s="273"/>
       <c r="E18" s="273"/>
       <c r="F18" s="273"/>
-      <c r="G18" s="377">
-        <v>0</v>
-      </c>
-      <c r="H18" s="378"/>
+      <c r="G18" s="402">
+        <v>0</v>
+      </c>
+      <c r="H18" s="403"/>
     </row>
     <row r="19" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -18236,11 +18460,11 @@
       <c r="D20" s="275"/>
       <c r="E20" s="275"/>
       <c r="F20" s="275"/>
-      <c r="G20" s="379">
+      <c r="G20" s="404">
         <f>G15+G10+G5</f>
         <v>5141175.54</v>
       </c>
-      <c r="H20" s="380"/>
+      <c r="H20" s="405"/>
     </row>
   </sheetData>
   <mergeCells count="8">
